--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -40,12 +40,42 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -290,39 +320,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -78,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -310,11 +314,145 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -353,6 +491,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -722,27 +873,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -752,52 +903,53 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="23" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="23" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="23" t="n"/>
       <c r="K1" s="2" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="23" t="n"/>
       <c r="N1" s="2" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="23" t="n"/>
       <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
+      <c r="R1" s="22" t="n"/>
+      <c r="S1" s="23" t="n"/>
       <c r="T1" s="2" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
+      <c r="U1" s="22" t="n"/>
+      <c r="V1" s="23" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="24" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>早出</t>
@@ -910,25 +1062,53 @@
           <t>7:00</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="C3" s="8" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="9" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="9" t="n"/>
-      <c r="K3" s="7" t="n"/>
+      <c r="K3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="7" t="n"/>
+      <c r="N3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="O3" s="8" t="n"/>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="7" t="n"/>
+      <c r="Q3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="R3" s="8" t="n"/>
       <c r="S3" s="9" t="n"/>
-      <c r="T3" s="7" t="n"/>
+      <c r="T3" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：排泄介助</t>
+        </is>
+      </c>
       <c r="U3" s="8" t="n"/>
       <c r="V3" s="9" t="n"/>
     </row>
@@ -938,25 +1118,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
+      <c r="B4" s="26" t="n"/>
       <c r="C4" s="12" t="n"/>
       <c r="D4" s="13" t="n"/>
-      <c r="E4" s="11" t="n"/>
+      <c r="E4" s="26" t="n"/>
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="13" t="n"/>
-      <c r="H4" s="11" t="n"/>
+      <c r="H4" s="26" t="n"/>
       <c r="I4" s="12" t="n"/>
       <c r="J4" s="13" t="n"/>
-      <c r="K4" s="11" t="n"/>
+      <c r="K4" s="26" t="n"/>
       <c r="L4" s="12" t="n"/>
       <c r="M4" s="13" t="n"/>
-      <c r="N4" s="11" t="n"/>
+      <c r="N4" s="26" t="n"/>
       <c r="O4" s="12" t="n"/>
       <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="11" t="n"/>
+      <c r="Q4" s="26" t="n"/>
       <c r="R4" s="12" t="n"/>
       <c r="S4" s="13" t="n"/>
-      <c r="T4" s="11" t="n"/>
+      <c r="T4" s="26" t="n"/>
       <c r="U4" s="12" t="n"/>
       <c r="V4" s="13" t="n"/>
     </row>
@@ -966,25 +1146,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
+      <c r="B5" s="27" t="n"/>
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="27" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="13" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="H5" s="27" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="13" t="n"/>
-      <c r="K5" s="11" t="n"/>
+      <c r="K5" s="27" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="13" t="n"/>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="27" t="n"/>
       <c r="O5" s="12" t="n"/>
       <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="11" t="n"/>
+      <c r="Q5" s="27" t="n"/>
       <c r="R5" s="12" t="n"/>
       <c r="S5" s="13" t="n"/>
-      <c r="T5" s="11" t="n"/>
+      <c r="T5" s="27" t="n"/>
       <c r="U5" s="12" t="n"/>
       <c r="V5" s="13" t="n"/>
     </row>
@@ -2254,25 +2434,53 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="7" t="n"/>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：買い物代行</t>
+        </is>
+      </c>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="7" t="n"/>
+      <c r="K51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="9" t="n"/>
-      <c r="N51" s="7" t="n"/>
+      <c r="N51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="7" t="n"/>
+      <c r="Q51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="R51" s="8" t="n"/>
       <c r="S51" s="9" t="n"/>
-      <c r="T51" s="7" t="n"/>
+      <c r="T51" s="25" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="U51" s="8" t="n"/>
       <c r="V51" s="9" t="n"/>
     </row>
@@ -2282,25 +2490,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n"/>
+      <c r="B52" s="26" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="13" t="n"/>
-      <c r="E52" s="11" t="n"/>
+      <c r="E52" s="26" t="n"/>
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="13" t="n"/>
-      <c r="H52" s="11" t="n"/>
+      <c r="H52" s="26" t="n"/>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="11" t="n"/>
+      <c r="K52" s="26" t="n"/>
       <c r="L52" s="12" t="n"/>
       <c r="M52" s="13" t="n"/>
-      <c r="N52" s="11" t="n"/>
+      <c r="N52" s="26" t="n"/>
       <c r="O52" s="12" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="11" t="n"/>
+      <c r="Q52" s="26" t="n"/>
       <c r="R52" s="12" t="n"/>
       <c r="S52" s="13" t="n"/>
-      <c r="T52" s="11" t="n"/>
+      <c r="T52" s="26" t="n"/>
       <c r="U52" s="12" t="n"/>
       <c r="V52" s="13" t="n"/>
     </row>
@@ -2310,25 +2518,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n"/>
+      <c r="B53" s="26" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="11" t="n"/>
+      <c r="E53" s="26" t="n"/>
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="13" t="n"/>
-      <c r="H53" s="11" t="n"/>
+      <c r="H53" s="27" t="n"/>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="13" t="n"/>
-      <c r="K53" s="11" t="n"/>
+      <c r="K53" s="26" t="n"/>
       <c r="L53" s="12" t="n"/>
       <c r="M53" s="13" t="n"/>
-      <c r="N53" s="11" t="n"/>
+      <c r="N53" s="27" t="n"/>
       <c r="O53" s="12" t="n"/>
       <c r="P53" s="13" t="n"/>
-      <c r="Q53" s="11" t="n"/>
+      <c r="Q53" s="27" t="n"/>
       <c r="R53" s="12" t="n"/>
       <c r="S53" s="13" t="n"/>
-      <c r="T53" s="11" t="n"/>
+      <c r="T53" s="27" t="n"/>
       <c r="U53" s="12" t="n"/>
       <c r="V53" s="13" t="n"/>
     </row>
@@ -2338,16 +2546,16 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="26" t="n"/>
       <c r="C54" s="12" t="n"/>
       <c r="D54" s="13" t="n"/>
-      <c r="E54" s="11" t="n"/>
+      <c r="E54" s="26" t="n"/>
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="13" t="n"/>
       <c r="H54" s="11" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="11" t="n"/>
+      <c r="K54" s="26" t="n"/>
       <c r="L54" s="12" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="11" t="n"/>
@@ -2366,16 +2574,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
+      <c r="B55" s="26" t="n"/>
       <c r="C55" s="12" t="n"/>
       <c r="D55" s="13" t="n"/>
-      <c r="E55" s="11" t="n"/>
+      <c r="E55" s="27" t="n"/>
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13" t="n"/>
-      <c r="K55" s="11" t="n"/>
+      <c r="K55" s="26" t="n"/>
       <c r="L55" s="12" t="n"/>
       <c r="M55" s="13" t="n"/>
       <c r="N55" s="11" t="n"/>
@@ -2394,7 +2602,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B56" s="11" t="n"/>
+      <c r="B56" s="26" t="n"/>
       <c r="C56" s="12" t="n"/>
       <c r="D56" s="13" t="n"/>
       <c r="E56" s="11" t="n"/>
@@ -2403,7 +2611,7 @@
       <c r="H56" s="11" t="n"/>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="11" t="n"/>
+      <c r="K56" s="26" t="n"/>
       <c r="L56" s="12" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="11" t="n"/>
@@ -2422,7 +2630,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n"/>
+      <c r="B57" s="26" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="13" t="n"/>
       <c r="E57" s="11" t="n"/>
@@ -2431,7 +2639,7 @@
       <c r="H57" s="11" t="n"/>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="13" t="n"/>
-      <c r="K57" s="11" t="n"/>
+      <c r="K57" s="26" t="n"/>
       <c r="L57" s="12" t="n"/>
       <c r="M57" s="13" t="n"/>
       <c r="N57" s="11" t="n"/>
@@ -2450,7 +2658,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
+      <c r="B58" s="26" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="13" t="n"/>
       <c r="E58" s="11" t="n"/>
@@ -2459,7 +2667,7 @@
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="11" t="n"/>
+      <c r="K58" s="26" t="n"/>
       <c r="L58" s="12" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="11" t="n"/>
@@ -2478,7 +2686,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n"/>
+      <c r="B59" s="26" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
       <c r="E59" s="11" t="n"/>
@@ -2487,7 +2695,7 @@
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="13" t="n"/>
-      <c r="K59" s="11" t="n"/>
+      <c r="K59" s="26" t="n"/>
       <c r="L59" s="12" t="n"/>
       <c r="M59" s="13" t="n"/>
       <c r="N59" s="11" t="n"/>
@@ -2506,7 +2714,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n"/>
+      <c r="B60" s="26" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
       <c r="E60" s="11" t="n"/>
@@ -2515,7 +2723,7 @@
       <c r="H60" s="11" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="11" t="n"/>
+      <c r="K60" s="26" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="11" t="n"/>
@@ -2534,7 +2742,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B61" s="11" t="n"/>
+      <c r="B61" s="27" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
       <c r="E61" s="11" t="n"/>
@@ -2543,7 +2751,7 @@
       <c r="H61" s="11" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
-      <c r="K61" s="11" t="n"/>
+      <c r="K61" s="27" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
       <c r="N61" s="11" t="n"/>
@@ -3935,25 +4143,53 @@
         </is>
       </c>
       <c r="B111" s="7" t="n"/>
-      <c r="C111" s="8" t="n"/>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="D111" s="9" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
+      <c r="F111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="G111" s="9" t="n"/>
       <c r="H111" s="7" t="n"/>
-      <c r="I111" s="8" t="n"/>
+      <c r="I111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="J111" s="9" t="n"/>
       <c r="K111" s="7" t="n"/>
-      <c r="L111" s="8" t="n"/>
+      <c r="L111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="7" t="n"/>
-      <c r="O111" s="8" t="n"/>
+      <c r="O111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="P111" s="9" t="n"/>
       <c r="Q111" s="7" t="n"/>
-      <c r="R111" s="8" t="n"/>
+      <c r="R111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="S111" s="9" t="n"/>
       <c r="T111" s="7" t="n"/>
-      <c r="U111" s="8" t="n"/>
+      <c r="U111" s="28" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="V111" s="9" t="n"/>
     </row>
     <row r="112">
@@ -3963,25 +4199,25 @@
         </is>
       </c>
       <c r="B112" s="11" t="n"/>
-      <c r="C112" s="12" t="n"/>
+      <c r="C112" s="29" t="n"/>
       <c r="D112" s="13" t="n"/>
       <c r="E112" s="11" t="n"/>
-      <c r="F112" s="12" t="n"/>
+      <c r="F112" s="29" t="n"/>
       <c r="G112" s="13" t="n"/>
       <c r="H112" s="11" t="n"/>
-      <c r="I112" s="12" t="n"/>
+      <c r="I112" s="29" t="n"/>
       <c r="J112" s="13" t="n"/>
       <c r="K112" s="11" t="n"/>
-      <c r="L112" s="12" t="n"/>
+      <c r="L112" s="29" t="n"/>
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="11" t="n"/>
-      <c r="O112" s="12" t="n"/>
+      <c r="O112" s="29" t="n"/>
       <c r="P112" s="13" t="n"/>
       <c r="Q112" s="11" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="R112" s="29" t="n"/>
       <c r="S112" s="13" t="n"/>
       <c r="T112" s="11" t="n"/>
-      <c r="U112" s="12" t="n"/>
+      <c r="U112" s="29" t="n"/>
       <c r="V112" s="13" t="n"/>
     </row>
     <row r="113">
@@ -3991,25 +4227,25 @@
         </is>
       </c>
       <c r="B113" s="11" t="n"/>
-      <c r="C113" s="12" t="n"/>
+      <c r="C113" s="29" t="n"/>
       <c r="D113" s="13" t="n"/>
       <c r="E113" s="11" t="n"/>
-      <c r="F113" s="12" t="n"/>
+      <c r="F113" s="29" t="n"/>
       <c r="G113" s="13" t="n"/>
       <c r="H113" s="11" t="n"/>
-      <c r="I113" s="12" t="n"/>
+      <c r="I113" s="29" t="n"/>
       <c r="J113" s="13" t="n"/>
       <c r="K113" s="11" t="n"/>
-      <c r="L113" s="12" t="n"/>
+      <c r="L113" s="29" t="n"/>
       <c r="M113" s="13" t="n"/>
       <c r="N113" s="11" t="n"/>
-      <c r="O113" s="12" t="n"/>
+      <c r="O113" s="29" t="n"/>
       <c r="P113" s="13" t="n"/>
       <c r="Q113" s="11" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="R113" s="29" t="n"/>
       <c r="S113" s="13" t="n"/>
       <c r="T113" s="11" t="n"/>
-      <c r="U113" s="12" t="n"/>
+      <c r="U113" s="29" t="n"/>
       <c r="V113" s="13" t="n"/>
     </row>
     <row r="114">
@@ -4019,25 +4255,25 @@
         </is>
       </c>
       <c r="B114" s="11" t="n"/>
-      <c r="C114" s="12" t="n"/>
+      <c r="C114" s="29" t="n"/>
       <c r="D114" s="13" t="n"/>
       <c r="E114" s="11" t="n"/>
-      <c r="F114" s="12" t="n"/>
+      <c r="F114" s="29" t="n"/>
       <c r="G114" s="13" t="n"/>
       <c r="H114" s="11" t="n"/>
-      <c r="I114" s="12" t="n"/>
+      <c r="I114" s="29" t="n"/>
       <c r="J114" s="13" t="n"/>
       <c r="K114" s="11" t="n"/>
-      <c r="L114" s="12" t="n"/>
+      <c r="L114" s="29" t="n"/>
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="11" t="n"/>
-      <c r="O114" s="12" t="n"/>
+      <c r="O114" s="29" t="n"/>
       <c r="P114" s="13" t="n"/>
       <c r="Q114" s="11" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="R114" s="29" t="n"/>
       <c r="S114" s="13" t="n"/>
       <c r="T114" s="11" t="n"/>
-      <c r="U114" s="12" t="n"/>
+      <c r="U114" s="29" t="n"/>
       <c r="V114" s="13" t="n"/>
     </row>
     <row r="115">
@@ -4047,25 +4283,25 @@
         </is>
       </c>
       <c r="B115" s="11" t="n"/>
-      <c r="C115" s="12" t="n"/>
+      <c r="C115" s="30" t="n"/>
       <c r="D115" s="13" t="n"/>
       <c r="E115" s="11" t="n"/>
-      <c r="F115" s="12" t="n"/>
+      <c r="F115" s="30" t="n"/>
       <c r="G115" s="13" t="n"/>
       <c r="H115" s="11" t="n"/>
-      <c r="I115" s="12" t="n"/>
+      <c r="I115" s="30" t="n"/>
       <c r="J115" s="13" t="n"/>
       <c r="K115" s="11" t="n"/>
-      <c r="L115" s="12" t="n"/>
+      <c r="L115" s="30" t="n"/>
       <c r="M115" s="13" t="n"/>
       <c r="N115" s="11" t="n"/>
-      <c r="O115" s="12" t="n"/>
+      <c r="O115" s="30" t="n"/>
       <c r="P115" s="13" t="n"/>
       <c r="Q115" s="11" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="R115" s="30" t="n"/>
       <c r="S115" s="13" t="n"/>
       <c r="T115" s="11" t="n"/>
-      <c r="U115" s="12" t="n"/>
+      <c r="U115" s="30" t="n"/>
       <c r="V115" s="13" t="n"/>
     </row>
     <row r="116">
@@ -5637,15 +5873,36 @@
       <c r="V171" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="T1:V1"/>
+  <mergeCells count="29">
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="K51:K61"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="T3:T5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="L111:L115"/>
+    <mergeCell ref="R111:R115"/>
+    <mergeCell ref="C111:C115"/>
+    <mergeCell ref="O111:O115"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="U111:U115"/>
+    <mergeCell ref="B51:B61"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="T51:T53"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -448,11 +448,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,6 +528,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1174,25 +1209,53 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="11" t="n"/>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="13" t="n"/>
-      <c r="H6" s="11" t="n"/>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="11" t="n"/>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="13" t="n"/>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="n"/>
       <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="11" t="n"/>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="R6" s="12" t="n"/>
       <c r="S6" s="13" t="n"/>
-      <c r="T6" s="11" t="n"/>
+      <c r="T6" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：起床介助</t>
+        </is>
+      </c>
       <c r="U6" s="12" t="n"/>
       <c r="V6" s="13" t="n"/>
     </row>
@@ -1202,25 +1265,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="26" t="n"/>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="26" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="13" t="n"/>
-      <c r="H7" s="11" t="n"/>
+      <c r="H7" s="26" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="13" t="n"/>
-      <c r="K7" s="11" t="n"/>
+      <c r="K7" s="26" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="13" t="n"/>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="26" t="n"/>
       <c r="O7" s="12" t="n"/>
       <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="11" t="n"/>
+      <c r="Q7" s="26" t="n"/>
       <c r="R7" s="12" t="n"/>
       <c r="S7" s="13" t="n"/>
-      <c r="T7" s="11" t="n"/>
+      <c r="T7" s="26" t="n"/>
       <c r="U7" s="12" t="n"/>
       <c r="V7" s="13" t="n"/>
     </row>
@@ -1230,25 +1293,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
+      <c r="B8" s="27" t="n"/>
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="11" t="n"/>
+      <c r="E8" s="27" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="11" t="n"/>
+      <c r="H8" s="27" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="11" t="n"/>
+      <c r="K8" s="27" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="13" t="n"/>
-      <c r="N8" s="11" t="n"/>
+      <c r="N8" s="27" t="n"/>
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="11" t="n"/>
+      <c r="Q8" s="27" t="n"/>
       <c r="R8" s="12" t="n"/>
       <c r="S8" s="13" t="n"/>
-      <c r="T8" s="11" t="n"/>
+      <c r="T8" s="27" t="n"/>
       <c r="U8" s="12" t="n"/>
       <c r="V8" s="13" t="n"/>
     </row>
@@ -2548,20 +2611,36 @@
       </c>
       <c r="B54" s="26" t="n"/>
       <c r="C54" s="12" t="n"/>
-      <c r="D54" s="13" t="n"/>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="E54" s="26" t="n"/>
       <c r="F54" s="12" t="n"/>
-      <c r="G54" s="13" t="n"/>
+      <c r="G54" s="32" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="H54" s="11" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="26" t="n"/>
       <c r="L54" s="12" t="n"/>
-      <c r="M54" s="13" t="n"/>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="N54" s="11" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="11" t="n"/>
+      <c r="Q54" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="R54" s="12" t="n"/>
       <c r="S54" s="13" t="n"/>
       <c r="T54" s="11" t="n"/>
@@ -2576,20 +2655,20 @@
       </c>
       <c r="B55" s="26" t="n"/>
       <c r="C55" s="12" t="n"/>
-      <c r="D55" s="13" t="n"/>
+      <c r="D55" s="33" t="n"/>
       <c r="E55" s="27" t="n"/>
       <c r="F55" s="12" t="n"/>
-      <c r="G55" s="13" t="n"/>
+      <c r="G55" s="33" t="n"/>
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13" t="n"/>
       <c r="K55" s="26" t="n"/>
       <c r="L55" s="12" t="n"/>
-      <c r="M55" s="13" t="n"/>
+      <c r="M55" s="33" t="n"/>
       <c r="N55" s="11" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="13" t="n"/>
-      <c r="Q55" s="11" t="n"/>
+      <c r="Q55" s="26" t="n"/>
       <c r="R55" s="12" t="n"/>
       <c r="S55" s="13" t="n"/>
       <c r="T55" s="11" t="n"/>
@@ -2604,20 +2683,20 @@
       </c>
       <c r="B56" s="26" t="n"/>
       <c r="C56" s="12" t="n"/>
-      <c r="D56" s="13" t="n"/>
+      <c r="D56" s="34" t="n"/>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="12" t="n"/>
-      <c r="G56" s="13" t="n"/>
+      <c r="G56" s="34" t="n"/>
       <c r="H56" s="11" t="n"/>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="26" t="n"/>
       <c r="L56" s="12" t="n"/>
-      <c r="M56" s="13" t="n"/>
+      <c r="M56" s="34" t="n"/>
       <c r="N56" s="11" t="n"/>
       <c r="O56" s="12" t="n"/>
       <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="11" t="n"/>
+      <c r="Q56" s="27" t="n"/>
       <c r="R56" s="12" t="n"/>
       <c r="S56" s="13" t="n"/>
       <c r="T56" s="11" t="n"/>
@@ -3152,7 +3231,11 @@
       <c r="Q75" s="7" t="n"/>
       <c r="R75" s="8" t="n"/>
       <c r="S75" s="9" t="n"/>
-      <c r="T75" s="7" t="n"/>
+      <c r="T75" s="25" t="inlineStr">
+        <is>
+          <t>長谷部融子：外出</t>
+        </is>
+      </c>
       <c r="U75" s="8" t="n"/>
       <c r="V75" s="9" t="n"/>
     </row>
@@ -3180,7 +3263,7 @@
       <c r="Q76" s="11" t="n"/>
       <c r="R76" s="12" t="n"/>
       <c r="S76" s="13" t="n"/>
-      <c r="T76" s="11" t="n"/>
+      <c r="T76" s="26" t="n"/>
       <c r="U76" s="12" t="n"/>
       <c r="V76" s="13" t="n"/>
     </row>
@@ -3208,7 +3291,7 @@
       <c r="Q77" s="11" t="n"/>
       <c r="R77" s="12" t="n"/>
       <c r="S77" s="13" t="n"/>
-      <c r="T77" s="11" t="n"/>
+      <c r="T77" s="26" t="n"/>
       <c r="U77" s="12" t="n"/>
       <c r="V77" s="13" t="n"/>
     </row>
@@ -3236,7 +3319,7 @@
       <c r="Q78" s="11" t="n"/>
       <c r="R78" s="12" t="n"/>
       <c r="S78" s="13" t="n"/>
-      <c r="T78" s="11" t="n"/>
+      <c r="T78" s="26" t="n"/>
       <c r="U78" s="12" t="n"/>
       <c r="V78" s="13" t="n"/>
     </row>
@@ -3264,7 +3347,7 @@
       <c r="Q79" s="11" t="n"/>
       <c r="R79" s="12" t="n"/>
       <c r="S79" s="13" t="n"/>
-      <c r="T79" s="11" t="n"/>
+      <c r="T79" s="26" t="n"/>
       <c r="U79" s="12" t="n"/>
       <c r="V79" s="13" t="n"/>
     </row>
@@ -3292,7 +3375,7 @@
       <c r="Q80" s="11" t="n"/>
       <c r="R80" s="12" t="n"/>
       <c r="S80" s="13" t="n"/>
-      <c r="T80" s="11" t="n"/>
+      <c r="T80" s="26" t="n"/>
       <c r="U80" s="12" t="n"/>
       <c r="V80" s="13" t="n"/>
     </row>
@@ -3311,7 +3394,11 @@
       <c r="H81" s="11" t="n"/>
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="13" t="n"/>
-      <c r="K81" s="11" t="n"/>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>長谷部融子：掃除</t>
+        </is>
+      </c>
       <c r="L81" s="12" t="n"/>
       <c r="M81" s="13" t="n"/>
       <c r="N81" s="11" t="n"/>
@@ -3320,7 +3407,7 @@
       <c r="Q81" s="11" t="n"/>
       <c r="R81" s="12" t="n"/>
       <c r="S81" s="13" t="n"/>
-      <c r="T81" s="11" t="n"/>
+      <c r="T81" s="26" t="n"/>
       <c r="U81" s="12" t="n"/>
       <c r="V81" s="13" t="n"/>
     </row>
@@ -3339,7 +3426,7 @@
       <c r="H82" s="11" t="n"/>
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="11" t="n"/>
+      <c r="K82" s="26" t="n"/>
       <c r="L82" s="12" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="11" t="n"/>
@@ -3348,7 +3435,7 @@
       <c r="Q82" s="11" t="n"/>
       <c r="R82" s="12" t="n"/>
       <c r="S82" s="13" t="n"/>
-      <c r="T82" s="11" t="n"/>
+      <c r="T82" s="26" t="n"/>
       <c r="U82" s="12" t="n"/>
       <c r="V82" s="13" t="n"/>
     </row>
@@ -3367,7 +3454,7 @@
       <c r="H83" s="11" t="n"/>
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="13" t="n"/>
-      <c r="K83" s="11" t="n"/>
+      <c r="K83" s="26" t="n"/>
       <c r="L83" s="12" t="n"/>
       <c r="M83" s="13" t="n"/>
       <c r="N83" s="11" t="n"/>
@@ -3376,7 +3463,7 @@
       <c r="Q83" s="11" t="n"/>
       <c r="R83" s="12" t="n"/>
       <c r="S83" s="13" t="n"/>
-      <c r="T83" s="11" t="n"/>
+      <c r="T83" s="26" t="n"/>
       <c r="U83" s="12" t="n"/>
       <c r="V83" s="13" t="n"/>
     </row>
@@ -3395,7 +3482,7 @@
       <c r="H84" s="11" t="n"/>
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="11" t="n"/>
+      <c r="K84" s="26" t="n"/>
       <c r="L84" s="12" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="11" t="n"/>
@@ -3404,7 +3491,7 @@
       <c r="Q84" s="11" t="n"/>
       <c r="R84" s="12" t="n"/>
       <c r="S84" s="13" t="n"/>
-      <c r="T84" s="11" t="n"/>
+      <c r="T84" s="26" t="n"/>
       <c r="U84" s="12" t="n"/>
       <c r="V84" s="13" t="n"/>
     </row>
@@ -3423,7 +3510,7 @@
       <c r="H85" s="11" t="n"/>
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="13" t="n"/>
-      <c r="K85" s="11" t="n"/>
+      <c r="K85" s="26" t="n"/>
       <c r="L85" s="12" t="n"/>
       <c r="M85" s="13" t="n"/>
       <c r="N85" s="11" t="n"/>
@@ -3432,7 +3519,7 @@
       <c r="Q85" s="11" t="n"/>
       <c r="R85" s="12" t="n"/>
       <c r="S85" s="13" t="n"/>
-      <c r="T85" s="11" t="n"/>
+      <c r="T85" s="27" t="n"/>
       <c r="U85" s="12" t="n"/>
       <c r="V85" s="13" t="n"/>
     </row>
@@ -3451,7 +3538,7 @@
       <c r="H86" s="15" t="n"/>
       <c r="I86" s="16" t="n"/>
       <c r="J86" s="17" t="n"/>
-      <c r="K86" s="15" t="n"/>
+      <c r="K86" s="26" t="n"/>
       <c r="L86" s="16" t="n"/>
       <c r="M86" s="17" t="n"/>
       <c r="N86" s="15" t="n"/>
@@ -3479,7 +3566,7 @@
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="8" t="n"/>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="7" t="n"/>
+      <c r="K87" s="26" t="n"/>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="7" t="n"/>
@@ -3507,7 +3594,7 @@
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="11" t="n"/>
+      <c r="K88" s="26" t="n"/>
       <c r="L88" s="12" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="11" t="n"/>
@@ -3535,7 +3622,7 @@
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="13" t="n"/>
-      <c r="K89" s="11" t="n"/>
+      <c r="K89" s="26" t="n"/>
       <c r="L89" s="12" t="n"/>
       <c r="M89" s="13" t="n"/>
       <c r="N89" s="11" t="n"/>
@@ -3563,7 +3650,7 @@
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="11" t="n"/>
+      <c r="K90" s="26" t="n"/>
       <c r="L90" s="12" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="11" t="n"/>
@@ -3591,7 +3678,7 @@
       <c r="H91" s="11" t="n"/>
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="13" t="n"/>
-      <c r="K91" s="11" t="n"/>
+      <c r="K91" s="27" t="n"/>
       <c r="L91" s="12" t="n"/>
       <c r="M91" s="13" t="n"/>
       <c r="N91" s="11" t="n"/>
@@ -4339,25 +4426,53 @@
         </is>
       </c>
       <c r="B117" s="11" t="n"/>
-      <c r="C117" s="12" t="n"/>
+      <c r="C117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="D117" s="13" t="n"/>
       <c r="E117" s="11" t="n"/>
-      <c r="F117" s="12" t="n"/>
+      <c r="F117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="G117" s="13" t="n"/>
       <c r="H117" s="11" t="n"/>
-      <c r="I117" s="12" t="n"/>
+      <c r="I117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="J117" s="13" t="n"/>
       <c r="K117" s="11" t="n"/>
-      <c r="L117" s="12" t="n"/>
+      <c r="L117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="M117" s="13" t="n"/>
       <c r="N117" s="11" t="n"/>
-      <c r="O117" s="12" t="n"/>
+      <c r="O117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="P117" s="13" t="n"/>
       <c r="Q117" s="11" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="R117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="S117" s="13" t="n"/>
       <c r="T117" s="11" t="n"/>
-      <c r="U117" s="12" t="n"/>
+      <c r="U117" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="V117" s="13" t="n"/>
     </row>
     <row r="118">
@@ -4367,25 +4482,25 @@
         </is>
       </c>
       <c r="B118" s="11" t="n"/>
-      <c r="C118" s="12" t="n"/>
+      <c r="C118" s="29" t="n"/>
       <c r="D118" s="13" t="n"/>
       <c r="E118" s="11" t="n"/>
-      <c r="F118" s="12" t="n"/>
+      <c r="F118" s="29" t="n"/>
       <c r="G118" s="13" t="n"/>
       <c r="H118" s="11" t="n"/>
-      <c r="I118" s="12" t="n"/>
+      <c r="I118" s="29" t="n"/>
       <c r="J118" s="13" t="n"/>
       <c r="K118" s="11" t="n"/>
-      <c r="L118" s="12" t="n"/>
+      <c r="L118" s="29" t="n"/>
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="11" t="n"/>
-      <c r="O118" s="12" t="n"/>
+      <c r="O118" s="29" t="n"/>
       <c r="P118" s="13" t="n"/>
       <c r="Q118" s="11" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="R118" s="29" t="n"/>
       <c r="S118" s="13" t="n"/>
       <c r="T118" s="11" t="n"/>
-      <c r="U118" s="12" t="n"/>
+      <c r="U118" s="29" t="n"/>
       <c r="V118" s="13" t="n"/>
     </row>
     <row r="119">
@@ -4395,25 +4510,25 @@
         </is>
       </c>
       <c r="B119" s="11" t="n"/>
-      <c r="C119" s="12" t="n"/>
+      <c r="C119" s="29" t="n"/>
       <c r="D119" s="13" t="n"/>
       <c r="E119" s="11" t="n"/>
-      <c r="F119" s="12" t="n"/>
+      <c r="F119" s="29" t="n"/>
       <c r="G119" s="13" t="n"/>
       <c r="H119" s="11" t="n"/>
-      <c r="I119" s="12" t="n"/>
+      <c r="I119" s="29" t="n"/>
       <c r="J119" s="13" t="n"/>
       <c r="K119" s="11" t="n"/>
-      <c r="L119" s="12" t="n"/>
+      <c r="L119" s="29" t="n"/>
       <c r="M119" s="13" t="n"/>
       <c r="N119" s="11" t="n"/>
-      <c r="O119" s="12" t="n"/>
+      <c r="O119" s="29" t="n"/>
       <c r="P119" s="13" t="n"/>
       <c r="Q119" s="11" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="R119" s="29" t="n"/>
       <c r="S119" s="13" t="n"/>
       <c r="T119" s="11" t="n"/>
-      <c r="U119" s="12" t="n"/>
+      <c r="U119" s="29" t="n"/>
       <c r="V119" s="13" t="n"/>
     </row>
     <row r="120">
@@ -4423,25 +4538,25 @@
         </is>
       </c>
       <c r="B120" s="11" t="n"/>
-      <c r="C120" s="12" t="n"/>
+      <c r="C120" s="29" t="n"/>
       <c r="D120" s="13" t="n"/>
       <c r="E120" s="11" t="n"/>
-      <c r="F120" s="12" t="n"/>
+      <c r="F120" s="29" t="n"/>
       <c r="G120" s="13" t="n"/>
       <c r="H120" s="11" t="n"/>
-      <c r="I120" s="12" t="n"/>
+      <c r="I120" s="29" t="n"/>
       <c r="J120" s="13" t="n"/>
       <c r="K120" s="11" t="n"/>
-      <c r="L120" s="12" t="n"/>
+      <c r="L120" s="29" t="n"/>
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="11" t="n"/>
-      <c r="O120" s="12" t="n"/>
+      <c r="O120" s="29" t="n"/>
       <c r="P120" s="13" t="n"/>
       <c r="Q120" s="11" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="R120" s="29" t="n"/>
       <c r="S120" s="13" t="n"/>
       <c r="T120" s="11" t="n"/>
-      <c r="U120" s="12" t="n"/>
+      <c r="U120" s="29" t="n"/>
       <c r="V120" s="13" t="n"/>
     </row>
     <row r="121">
@@ -4451,25 +4566,25 @@
         </is>
       </c>
       <c r="B121" s="11" t="n"/>
-      <c r="C121" s="12" t="n"/>
+      <c r="C121" s="30" t="n"/>
       <c r="D121" s="13" t="n"/>
       <c r="E121" s="11" t="n"/>
-      <c r="F121" s="12" t="n"/>
+      <c r="F121" s="30" t="n"/>
       <c r="G121" s="13" t="n"/>
       <c r="H121" s="11" t="n"/>
-      <c r="I121" s="12" t="n"/>
+      <c r="I121" s="30" t="n"/>
       <c r="J121" s="13" t="n"/>
       <c r="K121" s="11" t="n"/>
-      <c r="L121" s="12" t="n"/>
+      <c r="L121" s="30" t="n"/>
       <c r="M121" s="13" t="n"/>
       <c r="N121" s="11" t="n"/>
-      <c r="O121" s="12" t="n"/>
+      <c r="O121" s="30" t="n"/>
       <c r="P121" s="13" t="n"/>
       <c r="Q121" s="11" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="R121" s="30" t="n"/>
       <c r="S121" s="13" t="n"/>
       <c r="T121" s="11" t="n"/>
-      <c r="U121" s="12" t="n"/>
+      <c r="U121" s="30" t="n"/>
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
@@ -5683,25 +5798,53 @@
         </is>
       </c>
       <c r="B165" s="11" t="n"/>
-      <c r="C165" s="12" t="n"/>
+      <c r="C165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="D165" s="13" t="n"/>
       <c r="E165" s="11" t="n"/>
-      <c r="F165" s="12" t="n"/>
+      <c r="F165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="G165" s="13" t="n"/>
       <c r="H165" s="11" t="n"/>
-      <c r="I165" s="12" t="n"/>
+      <c r="I165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="J165" s="13" t="n"/>
       <c r="K165" s="11" t="n"/>
-      <c r="L165" s="12" t="n"/>
+      <c r="L165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="M165" s="13" t="n"/>
       <c r="N165" s="11" t="n"/>
-      <c r="O165" s="12" t="n"/>
+      <c r="O165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="P165" s="13" t="n"/>
       <c r="Q165" s="11" t="n"/>
-      <c r="R165" s="12" t="n"/>
+      <c r="R165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="S165" s="13" t="n"/>
       <c r="T165" s="11" t="n"/>
-      <c r="U165" s="12" t="n"/>
+      <c r="U165" s="35" t="inlineStr">
+        <is>
+          <t>長谷部融子：就寝介助</t>
+        </is>
+      </c>
       <c r="V165" s="13" t="n"/>
     </row>
     <row r="166">
@@ -5711,25 +5854,25 @@
         </is>
       </c>
       <c r="B166" s="11" t="n"/>
-      <c r="C166" s="12" t="n"/>
+      <c r="C166" s="29" t="n"/>
       <c r="D166" s="13" t="n"/>
       <c r="E166" s="11" t="n"/>
-      <c r="F166" s="12" t="n"/>
+      <c r="F166" s="29" t="n"/>
       <c r="G166" s="13" t="n"/>
       <c r="H166" s="11" t="n"/>
-      <c r="I166" s="12" t="n"/>
+      <c r="I166" s="29" t="n"/>
       <c r="J166" s="13" t="n"/>
       <c r="K166" s="11" t="n"/>
-      <c r="L166" s="12" t="n"/>
+      <c r="L166" s="29" t="n"/>
       <c r="M166" s="13" t="n"/>
       <c r="N166" s="11" t="n"/>
-      <c r="O166" s="12" t="n"/>
+      <c r="O166" s="29" t="n"/>
       <c r="P166" s="13" t="n"/>
       <c r="Q166" s="11" t="n"/>
-      <c r="R166" s="12" t="n"/>
+      <c r="R166" s="29" t="n"/>
       <c r="S166" s="13" t="n"/>
       <c r="T166" s="11" t="n"/>
-      <c r="U166" s="12" t="n"/>
+      <c r="U166" s="29" t="n"/>
       <c r="V166" s="13" t="n"/>
     </row>
     <row r="167">
@@ -5739,25 +5882,25 @@
         </is>
       </c>
       <c r="B167" s="11" t="n"/>
-      <c r="C167" s="12" t="n"/>
+      <c r="C167" s="29" t="n"/>
       <c r="D167" s="13" t="n"/>
       <c r="E167" s="11" t="n"/>
-      <c r="F167" s="12" t="n"/>
+      <c r="F167" s="29" t="n"/>
       <c r="G167" s="13" t="n"/>
       <c r="H167" s="11" t="n"/>
-      <c r="I167" s="12" t="n"/>
+      <c r="I167" s="29" t="n"/>
       <c r="J167" s="13" t="n"/>
       <c r="K167" s="11" t="n"/>
-      <c r="L167" s="12" t="n"/>
+      <c r="L167" s="29" t="n"/>
       <c r="M167" s="13" t="n"/>
       <c r="N167" s="11" t="n"/>
-      <c r="O167" s="12" t="n"/>
+      <c r="O167" s="29" t="n"/>
       <c r="P167" s="13" t="n"/>
       <c r="Q167" s="11" t="n"/>
-      <c r="R167" s="12" t="n"/>
+      <c r="R167" s="29" t="n"/>
       <c r="S167" s="13" t="n"/>
       <c r="T167" s="11" t="n"/>
-      <c r="U167" s="12" t="n"/>
+      <c r="U167" s="29" t="n"/>
       <c r="V167" s="13" t="n"/>
     </row>
     <row r="168">
@@ -5767,25 +5910,25 @@
         </is>
       </c>
       <c r="B168" s="11" t="n"/>
-      <c r="C168" s="12" t="n"/>
+      <c r="C168" s="29" t="n"/>
       <c r="D168" s="13" t="n"/>
       <c r="E168" s="11" t="n"/>
-      <c r="F168" s="12" t="n"/>
+      <c r="F168" s="29" t="n"/>
       <c r="G168" s="13" t="n"/>
       <c r="H168" s="11" t="n"/>
-      <c r="I168" s="12" t="n"/>
+      <c r="I168" s="29" t="n"/>
       <c r="J168" s="13" t="n"/>
       <c r="K168" s="11" t="n"/>
-      <c r="L168" s="12" t="n"/>
+      <c r="L168" s="29" t="n"/>
       <c r="M168" s="13" t="n"/>
       <c r="N168" s="11" t="n"/>
-      <c r="O168" s="12" t="n"/>
+      <c r="O168" s="29" t="n"/>
       <c r="P168" s="13" t="n"/>
       <c r="Q168" s="11" t="n"/>
-      <c r="R168" s="12" t="n"/>
+      <c r="R168" s="29" t="n"/>
       <c r="S168" s="13" t="n"/>
       <c r="T168" s="11" t="n"/>
-      <c r="U168" s="12" t="n"/>
+      <c r="U168" s="29" t="n"/>
       <c r="V168" s="13" t="n"/>
     </row>
     <row r="169">
@@ -5795,25 +5938,25 @@
         </is>
       </c>
       <c r="B169" s="11" t="n"/>
-      <c r="C169" s="12" t="n"/>
+      <c r="C169" s="30" t="n"/>
       <c r="D169" s="13" t="n"/>
       <c r="E169" s="11" t="n"/>
-      <c r="F169" s="12" t="n"/>
+      <c r="F169" s="30" t="n"/>
       <c r="G169" s="13" t="n"/>
       <c r="H169" s="11" t="n"/>
-      <c r="I169" s="12" t="n"/>
+      <c r="I169" s="30" t="n"/>
       <c r="J169" s="13" t="n"/>
       <c r="K169" s="11" t="n"/>
-      <c r="L169" s="12" t="n"/>
+      <c r="L169" s="30" t="n"/>
       <c r="M169" s="13" t="n"/>
       <c r="N169" s="11" t="n"/>
-      <c r="O169" s="12" t="n"/>
+      <c r="O169" s="30" t="n"/>
       <c r="P169" s="13" t="n"/>
       <c r="Q169" s="11" t="n"/>
-      <c r="R169" s="12" t="n"/>
+      <c r="R169" s="30" t="n"/>
       <c r="S169" s="13" t="n"/>
       <c r="T169" s="11" t="n"/>
-      <c r="U169" s="12" t="n"/>
+      <c r="U169" s="30" t="n"/>
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
@@ -5873,34 +6016,61 @@
       <c r="V171" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="56">
     <mergeCell ref="I111:I115"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="T6:T8"/>
     <mergeCell ref="K51:K61"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="U165:U169"/>
+    <mergeCell ref="F165:F169"/>
+    <mergeCell ref="I117:I121"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="U117:U121"/>
+    <mergeCell ref="R165:R169"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="K81:K91"/>
     <mergeCell ref="F111:F115"/>
+    <mergeCell ref="D54:D56"/>
     <mergeCell ref="H3:H5"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="T3:T5"/>
+    <mergeCell ref="F117:F121"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="N51:N53"/>
+    <mergeCell ref="C165:C169"/>
+    <mergeCell ref="O165:O169"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="R117:R121"/>
     <mergeCell ref="L111:L115"/>
     <mergeCell ref="R111:R115"/>
     <mergeCell ref="C111:C115"/>
     <mergeCell ref="O111:O115"/>
+    <mergeCell ref="T75:T85"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="N3:N5"/>
+    <mergeCell ref="L165:L169"/>
     <mergeCell ref="K1:M1"/>
+    <mergeCell ref="O117:O121"/>
+    <mergeCell ref="E6:E8"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="Q54:Q56"/>
     <mergeCell ref="U111:U115"/>
     <mergeCell ref="B51:B61"/>
     <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="H6:H8"/>
     <mergeCell ref="E51:E55"/>
     <mergeCell ref="H51:H53"/>
+    <mergeCell ref="I165:I169"/>
+    <mergeCell ref="M54:M56"/>
+    <mergeCell ref="L117:L121"/>
     <mergeCell ref="T51:T53"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="B6:B8"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -315,50 +315,6 @@
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="00000000"/>
       </left>
@@ -371,30 +327,6 @@
       <left style="medium">
         <color rgb="00000000"/>
       </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
@@ -448,35 +380,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,51 +402,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -938,53 +838,52 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="23" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="F1" s="22" t="n"/>
-      <c r="G1" s="23" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I1" s="22" t="n"/>
-      <c r="J1" s="23" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
       <c r="K1" s="2" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="L1" s="22" t="n"/>
-      <c r="M1" s="23" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
       <c r="N1" s="2" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="O1" s="22" t="n"/>
-      <c r="P1" s="23" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
       <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="R1" s="22" t="n"/>
-      <c r="S1" s="23" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="U1" s="22" t="n"/>
-      <c r="V1" s="23" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="24" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>早出</t>
@@ -1097,49 +996,49 @@
           <t>7:00</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="C3" s="8" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="9" t="n"/>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="9" t="n"/>
-      <c r="K3" s="25" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="25" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="O3" s="8" t="n"/>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="25" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
       </c>
       <c r="R3" s="8" t="n"/>
       <c r="S3" s="9" t="n"/>
-      <c r="T3" s="25" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>林郁子：排泄介助</t>
         </is>
@@ -1153,25 +1052,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
+      <c r="B4" s="11" t="n"/>
       <c r="C4" s="12" t="n"/>
       <c r="D4" s="13" t="n"/>
-      <c r="E4" s="26" t="n"/>
+      <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="13" t="n"/>
-      <c r="H4" s="26" t="n"/>
+      <c r="H4" s="11" t="n"/>
       <c r="I4" s="12" t="n"/>
       <c r="J4" s="13" t="n"/>
-      <c r="K4" s="26" t="n"/>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="12" t="n"/>
       <c r="M4" s="13" t="n"/>
-      <c r="N4" s="26" t="n"/>
+      <c r="N4" s="11" t="n"/>
       <c r="O4" s="12" t="n"/>
       <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="26" t="n"/>
+      <c r="Q4" s="11" t="n"/>
       <c r="R4" s="12" t="n"/>
       <c r="S4" s="13" t="n"/>
-      <c r="T4" s="26" t="n"/>
+      <c r="T4" s="11" t="n"/>
       <c r="U4" s="12" t="n"/>
       <c r="V4" s="13" t="n"/>
     </row>
@@ -1181,25 +1080,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
+      <c r="B5" s="14" t="n"/>
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="E5" s="14" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="13" t="n"/>
-      <c r="H5" s="27" t="n"/>
+      <c r="H5" s="14" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="13" t="n"/>
-      <c r="K5" s="27" t="n"/>
+      <c r="K5" s="14" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="13" t="n"/>
-      <c r="N5" s="27" t="n"/>
+      <c r="N5" s="14" t="n"/>
       <c r="O5" s="12" t="n"/>
       <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="27" t="n"/>
+      <c r="Q5" s="14" t="n"/>
       <c r="R5" s="12" t="n"/>
       <c r="S5" s="13" t="n"/>
-      <c r="T5" s="27" t="n"/>
+      <c r="T5" s="14" t="n"/>
       <c r="U5" s="12" t="n"/>
       <c r="V5" s="13" t="n"/>
     </row>
@@ -1209,49 +1108,49 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="13" t="n"/>
-      <c r="H6" s="31" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="31" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="13" t="n"/>
-      <c r="N6" s="31" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="O6" s="12" t="n"/>
       <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="31" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
       </c>
       <c r="R6" s="12" t="n"/>
       <c r="S6" s="13" t="n"/>
-      <c r="T6" s="31" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：起床介助</t>
         </is>
@@ -1265,25 +1164,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="26" t="n"/>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="13" t="n"/>
-      <c r="H7" s="26" t="n"/>
+      <c r="H7" s="11" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="13" t="n"/>
-      <c r="K7" s="26" t="n"/>
+      <c r="K7" s="11" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="13" t="n"/>
-      <c r="N7" s="26" t="n"/>
+      <c r="N7" s="11" t="n"/>
       <c r="O7" s="12" t="n"/>
       <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="26" t="n"/>
+      <c r="Q7" s="11" t="n"/>
       <c r="R7" s="12" t="n"/>
       <c r="S7" s="13" t="n"/>
-      <c r="T7" s="26" t="n"/>
+      <c r="T7" s="11" t="n"/>
       <c r="U7" s="12" t="n"/>
       <c r="V7" s="13" t="n"/>
     </row>
@@ -1293,25 +1192,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
+      <c r="B8" s="14" t="n"/>
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="E8" s="14" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="27" t="n"/>
+      <c r="H8" s="14" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="27" t="n"/>
+      <c r="K8" s="14" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="13" t="n"/>
-      <c r="N8" s="27" t="n"/>
+      <c r="N8" s="14" t="n"/>
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="27" t="n"/>
+      <c r="Q8" s="14" t="n"/>
       <c r="R8" s="12" t="n"/>
       <c r="S8" s="13" t="n"/>
-      <c r="T8" s="27" t="n"/>
+      <c r="T8" s="14" t="n"/>
       <c r="U8" s="12" t="n"/>
       <c r="V8" s="13" t="n"/>
     </row>
@@ -1321,25 +1220,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
+      <c r="B9" s="16" t="n"/>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="16" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="13" t="n"/>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="16" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="13" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="K9" s="16" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="13" t="n"/>
-      <c r="N9" s="11" t="n"/>
+      <c r="N9" s="16" t="n"/>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="11" t="n"/>
+      <c r="Q9" s="16" t="n"/>
       <c r="R9" s="12" t="n"/>
       <c r="S9" s="13" t="n"/>
-      <c r="T9" s="11" t="n"/>
+      <c r="T9" s="16" t="n"/>
       <c r="U9" s="12" t="n"/>
       <c r="V9" s="13" t="n"/>
     </row>
@@ -1349,25 +1248,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
+      <c r="B10" s="16" t="n"/>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="E10" s="16" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="H10" s="16" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="11" t="n"/>
+      <c r="K10" s="16" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="11" t="n"/>
+      <c r="N10" s="16" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="11" t="n"/>
+      <c r="Q10" s="16" t="n"/>
       <c r="R10" s="12" t="n"/>
       <c r="S10" s="13" t="n"/>
-      <c r="T10" s="11" t="n"/>
+      <c r="T10" s="16" t="n"/>
       <c r="U10" s="12" t="n"/>
       <c r="V10" s="13" t="n"/>
     </row>
@@ -1377,25 +1276,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
+      <c r="B11" s="16" t="n"/>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="E11" s="16" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="11" t="n"/>
+      <c r="H11" s="16" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="13" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="K11" s="16" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="13" t="n"/>
-      <c r="N11" s="11" t="n"/>
+      <c r="N11" s="16" t="n"/>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="11" t="n"/>
+      <c r="Q11" s="16" t="n"/>
       <c r="R11" s="12" t="n"/>
       <c r="S11" s="13" t="n"/>
-      <c r="T11" s="11" t="n"/>
+      <c r="T11" s="16" t="n"/>
       <c r="U11" s="12" t="n"/>
       <c r="V11" s="13" t="n"/>
     </row>
@@ -1405,25 +1304,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
+      <c r="B12" s="16" t="n"/>
       <c r="C12" s="12" t="n"/>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="16" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="16" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="11" t="n"/>
+      <c r="K12" s="16" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="13" t="n"/>
-      <c r="N12" s="11" t="n"/>
+      <c r="N12" s="16" t="n"/>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="11" t="n"/>
+      <c r="Q12" s="16" t="n"/>
       <c r="R12" s="12" t="n"/>
       <c r="S12" s="13" t="n"/>
-      <c r="T12" s="11" t="n"/>
+      <c r="T12" s="16" t="n"/>
       <c r="U12" s="12" t="n"/>
       <c r="V12" s="13" t="n"/>
     </row>
@@ -1433,55 +1332,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
+      <c r="B13" s="16" t="n"/>
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="E13" s="16" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="H13" s="16" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="13" t="n"/>
-      <c r="K13" s="11" t="n"/>
+      <c r="K13" s="16" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="13" t="n"/>
-      <c r="N13" s="11" t="n"/>
+      <c r="N13" s="16" t="n"/>
       <c r="O13" s="12" t="n"/>
       <c r="P13" s="13" t="n"/>
-      <c r="Q13" s="11" t="n"/>
+      <c r="Q13" s="16" t="n"/>
       <c r="R13" s="12" t="n"/>
       <c r="S13" s="13" t="n"/>
-      <c r="T13" s="11" t="n"/>
+      <c r="T13" s="16" t="n"/>
       <c r="U13" s="12" t="n"/>
       <c r="V13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="15" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="17" t="n"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n"/>
-      <c r="V14" s="17" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="20" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="20" t="n"/>
+      <c r="T14" s="18" t="n"/>
+      <c r="U14" s="19" t="n"/>
+      <c r="V14" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1489,25 +1388,25 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="21" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="H15" s="21" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="7" t="n"/>
+      <c r="K15" s="21" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="9" t="n"/>
-      <c r="N15" s="7" t="n"/>
+      <c r="N15" s="21" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="7" t="n"/>
+      <c r="Q15" s="21" t="n"/>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="9" t="n"/>
-      <c r="T15" s="7" t="n"/>
+      <c r="T15" s="21" t="n"/>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="9" t="n"/>
     </row>
@@ -1517,25 +1416,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
+      <c r="B16" s="16" t="n"/>
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="E16" s="16" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="H16" s="16" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="11" t="n"/>
+      <c r="K16" s="16" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="n"/>
-      <c r="N16" s="11" t="n"/>
+      <c r="N16" s="16" t="n"/>
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="11" t="n"/>
+      <c r="Q16" s="16" t="n"/>
       <c r="R16" s="12" t="n"/>
       <c r="S16" s="13" t="n"/>
-      <c r="T16" s="11" t="n"/>
+      <c r="T16" s="16" t="n"/>
       <c r="U16" s="12" t="n"/>
       <c r="V16" s="13" t="n"/>
     </row>
@@ -1545,25 +1444,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="E17" s="16" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="H17" s="16" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="13" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="K17" s="16" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="n"/>
-      <c r="N17" s="11" t="n"/>
+      <c r="N17" s="16" t="n"/>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="11" t="n"/>
+      <c r="Q17" s="16" t="n"/>
       <c r="R17" s="12" t="n"/>
       <c r="S17" s="13" t="n"/>
-      <c r="T17" s="11" t="n"/>
+      <c r="T17" s="16" t="n"/>
       <c r="U17" s="12" t="n"/>
       <c r="V17" s="13" t="n"/>
     </row>
@@ -1573,25 +1472,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="E18" s="16" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="16" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="11" t="n"/>
+      <c r="K18" s="16" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="n"/>
-      <c r="N18" s="11" t="n"/>
+      <c r="N18" s="16" t="n"/>
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="11" t="n"/>
+      <c r="Q18" s="16" t="n"/>
       <c r="R18" s="12" t="n"/>
       <c r="S18" s="13" t="n"/>
-      <c r="T18" s="11" t="n"/>
+      <c r="T18" s="16" t="n"/>
       <c r="U18" s="12" t="n"/>
       <c r="V18" s="13" t="n"/>
     </row>
@@ -1601,25 +1500,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="E19" s="16" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="13" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="H19" s="16" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="13" t="n"/>
-      <c r="K19" s="11" t="n"/>
+      <c r="K19" s="16" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="n"/>
-      <c r="N19" s="11" t="n"/>
+      <c r="N19" s="16" t="n"/>
       <c r="O19" s="12" t="n"/>
       <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="11" t="n"/>
+      <c r="Q19" s="16" t="n"/>
       <c r="R19" s="12" t="n"/>
       <c r="S19" s="13" t="n"/>
-      <c r="T19" s="11" t="n"/>
+      <c r="T19" s="16" t="n"/>
       <c r="U19" s="12" t="n"/>
       <c r="V19" s="13" t="n"/>
     </row>
@@ -1629,25 +1528,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
+      <c r="B20" s="16" t="n"/>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="E20" s="16" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="H20" s="16" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="11" t="n"/>
+      <c r="K20" s="16" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="n"/>
-      <c r="N20" s="11" t="n"/>
+      <c r="N20" s="16" t="n"/>
       <c r="O20" s="12" t="n"/>
       <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="11" t="n"/>
+      <c r="Q20" s="16" t="n"/>
       <c r="R20" s="12" t="n"/>
       <c r="S20" s="13" t="n"/>
-      <c r="T20" s="11" t="n"/>
+      <c r="T20" s="16" t="n"/>
       <c r="U20" s="12" t="n"/>
       <c r="V20" s="13" t="n"/>
     </row>
@@ -1657,25 +1556,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
+      <c r="B21" s="16" t="n"/>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="16" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="13" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="16" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="13" t="n"/>
-      <c r="K21" s="11" t="n"/>
+      <c r="K21" s="16" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="n"/>
-      <c r="N21" s="11" t="n"/>
+      <c r="N21" s="16" t="n"/>
       <c r="O21" s="12" t="n"/>
       <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="11" t="n"/>
+      <c r="Q21" s="16" t="n"/>
       <c r="R21" s="12" t="n"/>
       <c r="S21" s="13" t="n"/>
-      <c r="T21" s="11" t="n"/>
+      <c r="T21" s="16" t="n"/>
       <c r="U21" s="12" t="n"/>
       <c r="V21" s="13" t="n"/>
     </row>
@@ -1685,25 +1584,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
+      <c r="B22" s="16" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="E22" s="16" t="n"/>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="13" t="n"/>
-      <c r="H22" s="11" t="n"/>
+      <c r="H22" s="16" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="11" t="n"/>
+      <c r="K22" s="16" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="n"/>
-      <c r="N22" s="11" t="n"/>
+      <c r="N22" s="16" t="n"/>
       <c r="O22" s="12" t="n"/>
       <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="11" t="n"/>
+      <c r="Q22" s="16" t="n"/>
       <c r="R22" s="12" t="n"/>
       <c r="S22" s="13" t="n"/>
-      <c r="T22" s="11" t="n"/>
+      <c r="T22" s="16" t="n"/>
       <c r="U22" s="12" t="n"/>
       <c r="V22" s="13" t="n"/>
     </row>
@@ -1713,25 +1612,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
+      <c r="B23" s="16" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="E23" s="16" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="13" t="n"/>
-      <c r="H23" s="11" t="n"/>
+      <c r="H23" s="16" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="13" t="n"/>
-      <c r="K23" s="11" t="n"/>
+      <c r="K23" s="16" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="n"/>
-      <c r="N23" s="11" t="n"/>
+      <c r="N23" s="16" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="11" t="n"/>
+      <c r="Q23" s="16" t="n"/>
       <c r="R23" s="12" t="n"/>
       <c r="S23" s="13" t="n"/>
-      <c r="T23" s="11" t="n"/>
+      <c r="T23" s="16" t="n"/>
       <c r="U23" s="12" t="n"/>
       <c r="V23" s="13" t="n"/>
     </row>
@@ -1741,25 +1640,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n"/>
+      <c r="B24" s="16" t="n"/>
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="E24" s="16" t="n"/>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="13" t="n"/>
-      <c r="H24" s="11" t="n"/>
+      <c r="H24" s="16" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="11" t="n"/>
+      <c r="K24" s="16" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="n"/>
-      <c r="N24" s="11" t="n"/>
+      <c r="N24" s="16" t="n"/>
       <c r="O24" s="12" t="n"/>
       <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="11" t="n"/>
+      <c r="Q24" s="16" t="n"/>
       <c r="R24" s="12" t="n"/>
       <c r="S24" s="13" t="n"/>
-      <c r="T24" s="11" t="n"/>
+      <c r="T24" s="16" t="n"/>
       <c r="U24" s="12" t="n"/>
       <c r="V24" s="13" t="n"/>
     </row>
@@ -1769,55 +1668,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
+      <c r="B25" s="16" t="n"/>
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="E25" s="16" t="n"/>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="13" t="n"/>
-      <c r="H25" s="11" t="n"/>
+      <c r="H25" s="16" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="13" t="n"/>
-      <c r="K25" s="11" t="n"/>
+      <c r="K25" s="16" t="n"/>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="n"/>
-      <c r="N25" s="11" t="n"/>
+      <c r="N25" s="16" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="13" t="n"/>
-      <c r="Q25" s="11" t="n"/>
+      <c r="Q25" s="16" t="n"/>
       <c r="R25" s="12" t="n"/>
       <c r="S25" s="13" t="n"/>
-      <c r="T25" s="11" t="n"/>
+      <c r="T25" s="16" t="n"/>
       <c r="U25" s="12" t="n"/>
       <c r="V25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="16" t="n"/>
-      <c r="M26" s="17" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="16" t="n"/>
-      <c r="P26" s="17" t="n"/>
-      <c r="Q26" s="15" t="n"/>
-      <c r="R26" s="16" t="n"/>
-      <c r="S26" s="17" t="n"/>
-      <c r="T26" s="15" t="n"/>
-      <c r="U26" s="16" t="n"/>
-      <c r="V26" s="17" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="19" t="n"/>
+      <c r="J26" s="20" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="20" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="20" t="n"/>
+      <c r="Q26" s="18" t="n"/>
+      <c r="R26" s="19" t="n"/>
+      <c r="S26" s="20" t="n"/>
+      <c r="T26" s="18" t="n"/>
+      <c r="U26" s="19" t="n"/>
+      <c r="V26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1825,25 +1724,25 @@
           <t>9:00</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="21" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="H27" s="21" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="K27" s="21" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="9" t="n"/>
-      <c r="N27" s="7" t="n"/>
+      <c r="N27" s="21" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="7" t="n"/>
+      <c r="Q27" s="21" t="n"/>
       <c r="R27" s="8" t="n"/>
       <c r="S27" s="9" t="n"/>
-      <c r="T27" s="7" t="n"/>
+      <c r="T27" s="21" t="n"/>
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="9" t="n"/>
     </row>
@@ -1853,25 +1752,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
+      <c r="B28" s="16" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="11" t="n"/>
+      <c r="E28" s="16" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="13" t="n"/>
-      <c r="H28" s="11" t="n"/>
+      <c r="H28" s="16" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="11" t="n"/>
+      <c r="K28" s="16" t="n"/>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="13" t="n"/>
-      <c r="N28" s="11" t="n"/>
+      <c r="N28" s="16" t="n"/>
       <c r="O28" s="12" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="11" t="n"/>
+      <c r="Q28" s="16" t="n"/>
       <c r="R28" s="12" t="n"/>
       <c r="S28" s="13" t="n"/>
-      <c r="T28" s="11" t="n"/>
+      <c r="T28" s="16" t="n"/>
       <c r="U28" s="12" t="n"/>
       <c r="V28" s="13" t="n"/>
     </row>
@@ -1881,25 +1780,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
+      <c r="B29" s="16" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="11" t="n"/>
+      <c r="E29" s="16" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="13" t="n"/>
-      <c r="H29" s="11" t="n"/>
+      <c r="H29" s="16" t="n"/>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="13" t="n"/>
-      <c r="K29" s="11" t="n"/>
+      <c r="K29" s="16" t="n"/>
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="13" t="n"/>
-      <c r="N29" s="11" t="n"/>
+      <c r="N29" s="16" t="n"/>
       <c r="O29" s="12" t="n"/>
       <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="11" t="n"/>
+      <c r="Q29" s="16" t="n"/>
       <c r="R29" s="12" t="n"/>
       <c r="S29" s="13" t="n"/>
-      <c r="T29" s="11" t="n"/>
+      <c r="T29" s="16" t="n"/>
       <c r="U29" s="12" t="n"/>
       <c r="V29" s="13" t="n"/>
     </row>
@@ -1909,25 +1808,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
+      <c r="B30" s="16" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="11" t="n"/>
+      <c r="E30" s="16" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="13" t="n"/>
-      <c r="H30" s="11" t="n"/>
+      <c r="H30" s="16" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="11" t="n"/>
+      <c r="K30" s="16" t="n"/>
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="13" t="n"/>
-      <c r="N30" s="11" t="n"/>
+      <c r="N30" s="16" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="11" t="n"/>
+      <c r="Q30" s="16" t="n"/>
       <c r="R30" s="12" t="n"/>
       <c r="S30" s="13" t="n"/>
-      <c r="T30" s="11" t="n"/>
+      <c r="T30" s="16" t="n"/>
       <c r="U30" s="12" t="n"/>
       <c r="V30" s="13" t="n"/>
     </row>
@@ -1937,25 +1836,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
+      <c r="B31" s="16" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="E31" s="16" t="n"/>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="13" t="n"/>
-      <c r="H31" s="11" t="n"/>
+      <c r="H31" s="16" t="n"/>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="13" t="n"/>
-      <c r="K31" s="11" t="n"/>
+      <c r="K31" s="16" t="n"/>
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="13" t="n"/>
-      <c r="N31" s="11" t="n"/>
+      <c r="N31" s="16" t="n"/>
       <c r="O31" s="12" t="n"/>
       <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="11" t="n"/>
+      <c r="Q31" s="16" t="n"/>
       <c r="R31" s="12" t="n"/>
       <c r="S31" s="13" t="n"/>
-      <c r="T31" s="11" t="n"/>
+      <c r="T31" s="16" t="n"/>
       <c r="U31" s="12" t="n"/>
       <c r="V31" s="13" t="n"/>
     </row>
@@ -1965,25 +1864,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n"/>
+      <c r="B32" s="16" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="11" t="n"/>
+      <c r="E32" s="16" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="13" t="n"/>
-      <c r="H32" s="11" t="n"/>
+      <c r="H32" s="16" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="11" t="n"/>
+      <c r="K32" s="16" t="n"/>
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="13" t="n"/>
-      <c r="N32" s="11" t="n"/>
+      <c r="N32" s="16" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="11" t="n"/>
+      <c r="Q32" s="16" t="n"/>
       <c r="R32" s="12" t="n"/>
       <c r="S32" s="13" t="n"/>
-      <c r="T32" s="11" t="n"/>
+      <c r="T32" s="16" t="n"/>
       <c r="U32" s="12" t="n"/>
       <c r="V32" s="13" t="n"/>
     </row>
@@ -1993,25 +1892,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
+      <c r="B33" s="16" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="E33" s="16" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="13" t="n"/>
-      <c r="H33" s="11" t="n"/>
+      <c r="H33" s="16" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="13" t="n"/>
-      <c r="K33" s="11" t="n"/>
+      <c r="K33" s="16" t="n"/>
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="13" t="n"/>
-      <c r="N33" s="11" t="n"/>
+      <c r="N33" s="16" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="11" t="n"/>
+      <c r="Q33" s="16" t="n"/>
       <c r="R33" s="12" t="n"/>
       <c r="S33" s="13" t="n"/>
-      <c r="T33" s="11" t="n"/>
+      <c r="T33" s="16" t="n"/>
       <c r="U33" s="12" t="n"/>
       <c r="V33" s="13" t="n"/>
     </row>
@@ -2021,25 +1920,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n"/>
+      <c r="B34" s="16" t="n"/>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="11" t="n"/>
+      <c r="E34" s="16" t="n"/>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="13" t="n"/>
-      <c r="H34" s="11" t="n"/>
+      <c r="H34" s="16" t="n"/>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="11" t="n"/>
+      <c r="K34" s="16" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="13" t="n"/>
-      <c r="N34" s="11" t="n"/>
+      <c r="N34" s="16" t="n"/>
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="11" t="n"/>
+      <c r="Q34" s="16" t="n"/>
       <c r="R34" s="12" t="n"/>
       <c r="S34" s="13" t="n"/>
-      <c r="T34" s="11" t="n"/>
+      <c r="T34" s="16" t="n"/>
       <c r="U34" s="12" t="n"/>
       <c r="V34" s="13" t="n"/>
     </row>
@@ -2049,25 +1948,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n"/>
+      <c r="B35" s="16" t="n"/>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="11" t="n"/>
+      <c r="E35" s="16" t="n"/>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="13" t="n"/>
-      <c r="H35" s="11" t="n"/>
+      <c r="H35" s="16" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="13" t="n"/>
-      <c r="K35" s="11" t="n"/>
+      <c r="K35" s="16" t="n"/>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="13" t="n"/>
-      <c r="N35" s="11" t="n"/>
+      <c r="N35" s="16" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="13" t="n"/>
-      <c r="Q35" s="11" t="n"/>
+      <c r="Q35" s="16" t="n"/>
       <c r="R35" s="12" t="n"/>
       <c r="S35" s="13" t="n"/>
-      <c r="T35" s="11" t="n"/>
+      <c r="T35" s="16" t="n"/>
       <c r="U35" s="12" t="n"/>
       <c r="V35" s="13" t="n"/>
     </row>
@@ -2077,25 +1976,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n"/>
+      <c r="B36" s="16" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="11" t="n"/>
+      <c r="E36" s="16" t="n"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="13" t="n"/>
-      <c r="H36" s="11" t="n"/>
+      <c r="H36" s="16" t="n"/>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="11" t="n"/>
+      <c r="K36" s="16" t="n"/>
       <c r="L36" s="12" t="n"/>
       <c r="M36" s="13" t="n"/>
-      <c r="N36" s="11" t="n"/>
+      <c r="N36" s="16" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="11" t="n"/>
+      <c r="Q36" s="16" t="n"/>
       <c r="R36" s="12" t="n"/>
       <c r="S36" s="13" t="n"/>
-      <c r="T36" s="11" t="n"/>
+      <c r="T36" s="16" t="n"/>
       <c r="U36" s="12" t="n"/>
       <c r="V36" s="13" t="n"/>
     </row>
@@ -2105,55 +2004,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
+      <c r="B37" s="16" t="n"/>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="11" t="n"/>
+      <c r="E37" s="16" t="n"/>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="13" t="n"/>
-      <c r="H37" s="11" t="n"/>
+      <c r="H37" s="16" t="n"/>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="13" t="n"/>
-      <c r="K37" s="11" t="n"/>
+      <c r="K37" s="16" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="13" t="n"/>
-      <c r="N37" s="11" t="n"/>
+      <c r="N37" s="16" t="n"/>
       <c r="O37" s="12" t="n"/>
       <c r="P37" s="13" t="n"/>
-      <c r="Q37" s="11" t="n"/>
+      <c r="Q37" s="16" t="n"/>
       <c r="R37" s="12" t="n"/>
       <c r="S37" s="13" t="n"/>
-      <c r="T37" s="11" t="n"/>
+      <c r="T37" s="16" t="n"/>
       <c r="U37" s="12" t="n"/>
       <c r="V37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="16" t="n"/>
-      <c r="M38" s="17" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="16" t="n"/>
-      <c r="P38" s="17" t="n"/>
-      <c r="Q38" s="15" t="n"/>
-      <c r="R38" s="16" t="n"/>
-      <c r="S38" s="17" t="n"/>
-      <c r="T38" s="15" t="n"/>
-      <c r="U38" s="16" t="n"/>
-      <c r="V38" s="17" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="19" t="n"/>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="20" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="19" t="n"/>
+      <c r="P38" s="20" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="R38" s="19" t="n"/>
+      <c r="S38" s="20" t="n"/>
+      <c r="T38" s="18" t="n"/>
+      <c r="U38" s="19" t="n"/>
+      <c r="V38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2161,25 +2060,25 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n"/>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="21" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="H39" s="21" t="n"/>
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="7" t="n"/>
+      <c r="K39" s="21" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="9" t="n"/>
-      <c r="N39" s="7" t="n"/>
+      <c r="N39" s="21" t="n"/>
       <c r="O39" s="8" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="7" t="n"/>
+      <c r="Q39" s="21" t="n"/>
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="9" t="n"/>
-      <c r="T39" s="7" t="n"/>
+      <c r="T39" s="21" t="n"/>
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="9" t="n"/>
     </row>
@@ -2189,25 +2088,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
+      <c r="B40" s="16" t="n"/>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="11" t="n"/>
+      <c r="E40" s="16" t="n"/>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="13" t="n"/>
-      <c r="H40" s="11" t="n"/>
+      <c r="H40" s="16" t="n"/>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="11" t="n"/>
+      <c r="K40" s="16" t="n"/>
       <c r="L40" s="12" t="n"/>
       <c r="M40" s="13" t="n"/>
-      <c r="N40" s="11" t="n"/>
+      <c r="N40" s="16" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="11" t="n"/>
+      <c r="Q40" s="16" t="n"/>
       <c r="R40" s="12" t="n"/>
       <c r="S40" s="13" t="n"/>
-      <c r="T40" s="11" t="n"/>
+      <c r="T40" s="16" t="n"/>
       <c r="U40" s="12" t="n"/>
       <c r="V40" s="13" t="n"/>
     </row>
@@ -2217,25 +2116,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
+      <c r="B41" s="16" t="n"/>
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="11" t="n"/>
+      <c r="E41" s="16" t="n"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="13" t="n"/>
-      <c r="H41" s="11" t="n"/>
+      <c r="H41" s="16" t="n"/>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="13" t="n"/>
-      <c r="K41" s="11" t="n"/>
+      <c r="K41" s="16" t="n"/>
       <c r="L41" s="12" t="n"/>
       <c r="M41" s="13" t="n"/>
-      <c r="N41" s="11" t="n"/>
+      <c r="N41" s="16" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="13" t="n"/>
-      <c r="Q41" s="11" t="n"/>
+      <c r="Q41" s="16" t="n"/>
       <c r="R41" s="12" t="n"/>
       <c r="S41" s="13" t="n"/>
-      <c r="T41" s="11" t="n"/>
+      <c r="T41" s="16" t="n"/>
       <c r="U41" s="12" t="n"/>
       <c r="V41" s="13" t="n"/>
     </row>
@@ -2245,25 +2144,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n"/>
+      <c r="B42" s="16" t="n"/>
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="11" t="n"/>
+      <c r="E42" s="16" t="n"/>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="13" t="n"/>
-      <c r="H42" s="11" t="n"/>
+      <c r="H42" s="16" t="n"/>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="11" t="n"/>
+      <c r="K42" s="16" t="n"/>
       <c r="L42" s="12" t="n"/>
       <c r="M42" s="13" t="n"/>
-      <c r="N42" s="11" t="n"/>
+      <c r="N42" s="16" t="n"/>
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="11" t="n"/>
+      <c r="Q42" s="16" t="n"/>
       <c r="R42" s="12" t="n"/>
       <c r="S42" s="13" t="n"/>
-      <c r="T42" s="11" t="n"/>
+      <c r="T42" s="16" t="n"/>
       <c r="U42" s="12" t="n"/>
       <c r="V42" s="13" t="n"/>
     </row>
@@ -2273,25 +2172,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
+      <c r="B43" s="16" t="n"/>
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="11" t="n"/>
+      <c r="E43" s="16" t="n"/>
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="13" t="n"/>
-      <c r="H43" s="11" t="n"/>
+      <c r="H43" s="16" t="n"/>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="13" t="n"/>
-      <c r="K43" s="11" t="n"/>
+      <c r="K43" s="16" t="n"/>
       <c r="L43" s="12" t="n"/>
       <c r="M43" s="13" t="n"/>
-      <c r="N43" s="11" t="n"/>
+      <c r="N43" s="16" t="n"/>
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="13" t="n"/>
-      <c r="Q43" s="11" t="n"/>
+      <c r="Q43" s="16" t="n"/>
       <c r="R43" s="12" t="n"/>
       <c r="S43" s="13" t="n"/>
-      <c r="T43" s="11" t="n"/>
+      <c r="T43" s="16" t="n"/>
       <c r="U43" s="12" t="n"/>
       <c r="V43" s="13" t="n"/>
     </row>
@@ -2301,25 +2200,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
+      <c r="B44" s="16" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="11" t="n"/>
+      <c r="E44" s="16" t="n"/>
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="13" t="n"/>
-      <c r="H44" s="11" t="n"/>
+      <c r="H44" s="16" t="n"/>
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="11" t="n"/>
+      <c r="K44" s="16" t="n"/>
       <c r="L44" s="12" t="n"/>
       <c r="M44" s="13" t="n"/>
-      <c r="N44" s="11" t="n"/>
+      <c r="N44" s="16" t="n"/>
       <c r="O44" s="12" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="11" t="n"/>
+      <c r="Q44" s="16" t="n"/>
       <c r="R44" s="12" t="n"/>
       <c r="S44" s="13" t="n"/>
-      <c r="T44" s="11" t="n"/>
+      <c r="T44" s="16" t="n"/>
       <c r="U44" s="12" t="n"/>
       <c r="V44" s="13" t="n"/>
     </row>
@@ -2329,25 +2228,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n"/>
+      <c r="B45" s="16" t="n"/>
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="11" t="n"/>
+      <c r="E45" s="16" t="n"/>
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="13" t="n"/>
-      <c r="H45" s="11" t="n"/>
+      <c r="H45" s="16" t="n"/>
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="13" t="n"/>
-      <c r="K45" s="11" t="n"/>
+      <c r="K45" s="16" t="n"/>
       <c r="L45" s="12" t="n"/>
       <c r="M45" s="13" t="n"/>
-      <c r="N45" s="11" t="n"/>
+      <c r="N45" s="16" t="n"/>
       <c r="O45" s="12" t="n"/>
       <c r="P45" s="13" t="n"/>
-      <c r="Q45" s="11" t="n"/>
+      <c r="Q45" s="16" t="n"/>
       <c r="R45" s="12" t="n"/>
       <c r="S45" s="13" t="n"/>
-      <c r="T45" s="11" t="n"/>
+      <c r="T45" s="16" t="n"/>
       <c r="U45" s="12" t="n"/>
       <c r="V45" s="13" t="n"/>
     </row>
@@ -2357,25 +2256,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
+      <c r="B46" s="16" t="n"/>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="11" t="n"/>
+      <c r="E46" s="16" t="n"/>
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="13" t="n"/>
-      <c r="H46" s="11" t="n"/>
+      <c r="H46" s="16" t="n"/>
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="11" t="n"/>
+      <c r="K46" s="16" t="n"/>
       <c r="L46" s="12" t="n"/>
       <c r="M46" s="13" t="n"/>
-      <c r="N46" s="11" t="n"/>
+      <c r="N46" s="16" t="n"/>
       <c r="O46" s="12" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="11" t="n"/>
+      <c r="Q46" s="16" t="n"/>
       <c r="R46" s="12" t="n"/>
       <c r="S46" s="13" t="n"/>
-      <c r="T46" s="11" t="n"/>
+      <c r="T46" s="16" t="n"/>
       <c r="U46" s="12" t="n"/>
       <c r="V46" s="13" t="n"/>
     </row>
@@ -2385,25 +2284,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
+      <c r="B47" s="16" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="11" t="n"/>
+      <c r="E47" s="16" t="n"/>
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="13" t="n"/>
-      <c r="H47" s="11" t="n"/>
+      <c r="H47" s="16" t="n"/>
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="13" t="n"/>
-      <c r="K47" s="11" t="n"/>
+      <c r="K47" s="16" t="n"/>
       <c r="L47" s="12" t="n"/>
       <c r="M47" s="13" t="n"/>
-      <c r="N47" s="11" t="n"/>
+      <c r="N47" s="16" t="n"/>
       <c r="O47" s="12" t="n"/>
       <c r="P47" s="13" t="n"/>
-      <c r="Q47" s="11" t="n"/>
+      <c r="Q47" s="16" t="n"/>
       <c r="R47" s="12" t="n"/>
       <c r="S47" s="13" t="n"/>
-      <c r="T47" s="11" t="n"/>
+      <c r="T47" s="16" t="n"/>
       <c r="U47" s="12" t="n"/>
       <c r="V47" s="13" t="n"/>
     </row>
@@ -2413,25 +2312,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
+      <c r="B48" s="16" t="n"/>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="11" t="n"/>
+      <c r="E48" s="16" t="n"/>
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="13" t="n"/>
-      <c r="H48" s="11" t="n"/>
+      <c r="H48" s="16" t="n"/>
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="11" t="n"/>
+      <c r="K48" s="16" t="n"/>
       <c r="L48" s="12" t="n"/>
       <c r="M48" s="13" t="n"/>
-      <c r="N48" s="11" t="n"/>
+      <c r="N48" s="16" t="n"/>
       <c r="O48" s="12" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="11" t="n"/>
+      <c r="Q48" s="16" t="n"/>
       <c r="R48" s="12" t="n"/>
       <c r="S48" s="13" t="n"/>
-      <c r="T48" s="11" t="n"/>
+      <c r="T48" s="16" t="n"/>
       <c r="U48" s="12" t="n"/>
       <c r="V48" s="13" t="n"/>
     </row>
@@ -2441,55 +2340,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n"/>
+      <c r="B49" s="16" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="11" t="n"/>
+      <c r="E49" s="16" t="n"/>
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="13" t="n"/>
-      <c r="H49" s="11" t="n"/>
+      <c r="H49" s="16" t="n"/>
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="13" t="n"/>
-      <c r="K49" s="11" t="n"/>
+      <c r="K49" s="16" t="n"/>
       <c r="L49" s="12" t="n"/>
       <c r="M49" s="13" t="n"/>
-      <c r="N49" s="11" t="n"/>
+      <c r="N49" s="16" t="n"/>
       <c r="O49" s="12" t="n"/>
       <c r="P49" s="13" t="n"/>
-      <c r="Q49" s="11" t="n"/>
+      <c r="Q49" s="16" t="n"/>
       <c r="R49" s="12" t="n"/>
       <c r="S49" s="13" t="n"/>
-      <c r="T49" s="11" t="n"/>
+      <c r="T49" s="16" t="n"/>
       <c r="U49" s="12" t="n"/>
       <c r="V49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="15" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="17" t="n"/>
-      <c r="H50" s="15" t="n"/>
-      <c r="I50" s="16" t="n"/>
-      <c r="J50" s="17" t="n"/>
-      <c r="K50" s="15" t="n"/>
-      <c r="L50" s="16" t="n"/>
-      <c r="M50" s="17" t="n"/>
-      <c r="N50" s="15" t="n"/>
-      <c r="O50" s="16" t="n"/>
-      <c r="P50" s="17" t="n"/>
-      <c r="Q50" s="15" t="n"/>
-      <c r="R50" s="16" t="n"/>
-      <c r="S50" s="17" t="n"/>
-      <c r="T50" s="15" t="n"/>
-      <c r="U50" s="16" t="n"/>
-      <c r="V50" s="17" t="n"/>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="19" t="n"/>
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="19" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="18" t="n"/>
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="20" t="n"/>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="19" t="n"/>
+      <c r="P50" s="20" t="n"/>
+      <c r="Q50" s="18" t="n"/>
+      <c r="R50" s="19" t="n"/>
+      <c r="S50" s="20" t="n"/>
+      <c r="T50" s="18" t="n"/>
+      <c r="U50" s="19" t="n"/>
+      <c r="V50" s="20" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2497,49 +2396,37 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>林郁子：入浴掃除</t>
-        </is>
-      </c>
+      <c r="B51" s="21" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="25" t="inlineStr">
-        <is>
-          <t>林郁子：買い物代行</t>
-        </is>
-      </c>
+      <c r="E51" s="21" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="25" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="25" t="inlineStr">
-        <is>
-          <t>林郁子：入浴掃除</t>
-        </is>
-      </c>
+      <c r="K51" s="21" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="9" t="n"/>
-      <c r="N51" s="25" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="25" t="inlineStr">
+      <c r="Q51" s="7" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="R51" s="8" t="n"/>
       <c r="S51" s="9" t="n"/>
-      <c r="T51" s="25" t="inlineStr">
+      <c r="T51" s="7" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
@@ -2553,25 +2440,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B52" s="26" t="n"/>
+      <c r="B52" s="16" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="13" t="n"/>
-      <c r="E52" s="26" t="n"/>
+      <c r="E52" s="16" t="n"/>
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="13" t="n"/>
-      <c r="H52" s="26" t="n"/>
+      <c r="H52" s="11" t="n"/>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="26" t="n"/>
+      <c r="K52" s="16" t="n"/>
       <c r="L52" s="12" t="n"/>
       <c r="M52" s="13" t="n"/>
-      <c r="N52" s="26" t="n"/>
+      <c r="N52" s="11" t="n"/>
       <c r="O52" s="12" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="26" t="n"/>
+      <c r="Q52" s="11" t="n"/>
       <c r="R52" s="12" t="n"/>
       <c r="S52" s="13" t="n"/>
-      <c r="T52" s="26" t="n"/>
+      <c r="T52" s="11" t="n"/>
       <c r="U52" s="12" t="n"/>
       <c r="V52" s="13" t="n"/>
     </row>
@@ -2581,25 +2468,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="26" t="n"/>
+      <c r="B53" s="16" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="26" t="n"/>
+      <c r="E53" s="16" t="n"/>
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="13" t="n"/>
-      <c r="H53" s="27" t="n"/>
+      <c r="H53" s="14" t="n"/>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="13" t="n"/>
-      <c r="K53" s="26" t="n"/>
+      <c r="K53" s="16" t="n"/>
       <c r="L53" s="12" t="n"/>
       <c r="M53" s="13" t="n"/>
-      <c r="N53" s="27" t="n"/>
+      <c r="N53" s="14" t="n"/>
       <c r="O53" s="12" t="n"/>
       <c r="P53" s="13" t="n"/>
-      <c r="Q53" s="27" t="n"/>
+      <c r="Q53" s="14" t="n"/>
       <c r="R53" s="12" t="n"/>
       <c r="S53" s="13" t="n"/>
-      <c r="T53" s="27" t="n"/>
+      <c r="T53" s="14" t="n"/>
       <c r="U53" s="12" t="n"/>
       <c r="V53" s="13" t="n"/>
     </row>
@@ -2609,41 +2496,41 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B54" s="26" t="n"/>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="C54" s="12" t="n"/>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
-      <c r="E54" s="26" t="n"/>
       <c r="F54" s="12" t="n"/>
-      <c r="G54" s="32" t="inlineStr">
-        <is>
-          <t>長谷部融子：食事排泄</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="n"/>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="16" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="26" t="n"/>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>長谷部融子：食事排泄</t>
+        </is>
+      </c>
       <c r="L54" s="12" t="n"/>
-      <c r="M54" s="32" t="inlineStr">
-        <is>
-          <t>長谷部融子：食事排泄</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="16" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="31" t="inlineStr">
+      <c r="Q54" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="R54" s="12" t="n"/>
       <c r="S54" s="13" t="n"/>
-      <c r="T54" s="11" t="n"/>
+      <c r="T54" s="16" t="n"/>
       <c r="U54" s="12" t="n"/>
       <c r="V54" s="13" t="n"/>
     </row>
@@ -2653,25 +2540,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B55" s="26" t="n"/>
+      <c r="B55" s="11" t="n"/>
       <c r="C55" s="12" t="n"/>
-      <c r="D55" s="33" t="n"/>
-      <c r="E55" s="27" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="11" t="n"/>
       <c r="F55" s="12" t="n"/>
-      <c r="G55" s="33" t="n"/>
-      <c r="H55" s="11" t="n"/>
+      <c r="G55" s="13" t="n"/>
+      <c r="H55" s="16" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13" t="n"/>
-      <c r="K55" s="26" t="n"/>
+      <c r="K55" s="11" t="n"/>
       <c r="L55" s="12" t="n"/>
-      <c r="M55" s="33" t="n"/>
-      <c r="N55" s="11" t="n"/>
+      <c r="M55" s="13" t="n"/>
+      <c r="N55" s="16" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="13" t="n"/>
-      <c r="Q55" s="26" t="n"/>
+      <c r="Q55" s="11" t="n"/>
       <c r="R55" s="12" t="n"/>
       <c r="S55" s="13" t="n"/>
-      <c r="T55" s="11" t="n"/>
+      <c r="T55" s="16" t="n"/>
       <c r="U55" s="12" t="n"/>
       <c r="V55" s="13" t="n"/>
     </row>
@@ -2681,25 +2568,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B56" s="26" t="n"/>
+      <c r="B56" s="14" t="n"/>
       <c r="C56" s="12" t="n"/>
-      <c r="D56" s="34" t="n"/>
-      <c r="E56" s="11" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="14" t="n"/>
       <c r="F56" s="12" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="11" t="n"/>
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="16" t="n"/>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="26" t="n"/>
+      <c r="K56" s="14" t="n"/>
       <c r="L56" s="12" t="n"/>
-      <c r="M56" s="34" t="n"/>
-      <c r="N56" s="11" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="16" t="n"/>
       <c r="O56" s="12" t="n"/>
       <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="27" t="n"/>
+      <c r="Q56" s="14" t="n"/>
       <c r="R56" s="12" t="n"/>
       <c r="S56" s="13" t="n"/>
-      <c r="T56" s="11" t="n"/>
+      <c r="T56" s="16" t="n"/>
       <c r="U56" s="12" t="n"/>
       <c r="V56" s="13" t="n"/>
     </row>
@@ -2709,25 +2596,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B57" s="26" t="n"/>
+      <c r="B57" s="16" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="11" t="n"/>
+      <c r="E57" s="16" t="n"/>
       <c r="F57" s="12" t="n"/>
       <c r="G57" s="13" t="n"/>
-      <c r="H57" s="11" t="n"/>
+      <c r="H57" s="16" t="n"/>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="13" t="n"/>
-      <c r="K57" s="26" t="n"/>
+      <c r="K57" s="16" t="n"/>
       <c r="L57" s="12" t="n"/>
       <c r="M57" s="13" t="n"/>
-      <c r="N57" s="11" t="n"/>
+      <c r="N57" s="16" t="n"/>
       <c r="O57" s="12" t="n"/>
       <c r="P57" s="13" t="n"/>
-      <c r="Q57" s="11" t="n"/>
+      <c r="Q57" s="16" t="n"/>
       <c r="R57" s="12" t="n"/>
       <c r="S57" s="13" t="n"/>
-      <c r="T57" s="11" t="n"/>
+      <c r="T57" s="16" t="n"/>
       <c r="U57" s="12" t="n"/>
       <c r="V57" s="13" t="n"/>
     </row>
@@ -2737,25 +2624,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B58" s="26" t="n"/>
+      <c r="B58" s="16" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="11" t="n"/>
+      <c r="E58" s="16" t="n"/>
       <c r="F58" s="12" t="n"/>
       <c r="G58" s="13" t="n"/>
-      <c r="H58" s="11" t="n"/>
+      <c r="H58" s="16" t="n"/>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="26" t="n"/>
+      <c r="K58" s="16" t="n"/>
       <c r="L58" s="12" t="n"/>
       <c r="M58" s="13" t="n"/>
-      <c r="N58" s="11" t="n"/>
+      <c r="N58" s="16" t="n"/>
       <c r="O58" s="12" t="n"/>
       <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="11" t="n"/>
+      <c r="Q58" s="16" t="n"/>
       <c r="R58" s="12" t="n"/>
       <c r="S58" s="13" t="n"/>
-      <c r="T58" s="11" t="n"/>
+      <c r="T58" s="16" t="n"/>
       <c r="U58" s="12" t="n"/>
       <c r="V58" s="13" t="n"/>
     </row>
@@ -2765,25 +2652,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B59" s="26" t="n"/>
+      <c r="B59" s="16" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="11" t="n"/>
+      <c r="E59" s="16" t="n"/>
       <c r="F59" s="12" t="n"/>
       <c r="G59" s="13" t="n"/>
-      <c r="H59" s="11" t="n"/>
+      <c r="H59" s="16" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="13" t="n"/>
-      <c r="K59" s="26" t="n"/>
+      <c r="K59" s="16" t="n"/>
       <c r="L59" s="12" t="n"/>
       <c r="M59" s="13" t="n"/>
-      <c r="N59" s="11" t="n"/>
+      <c r="N59" s="16" t="n"/>
       <c r="O59" s="12" t="n"/>
       <c r="P59" s="13" t="n"/>
-      <c r="Q59" s="11" t="n"/>
+      <c r="Q59" s="16" t="n"/>
       <c r="R59" s="12" t="n"/>
       <c r="S59" s="13" t="n"/>
-      <c r="T59" s="11" t="n"/>
+      <c r="T59" s="16" t="n"/>
       <c r="U59" s="12" t="n"/>
       <c r="V59" s="13" t="n"/>
     </row>
@@ -2793,25 +2680,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B60" s="26" t="n"/>
+      <c r="B60" s="16" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="11" t="n"/>
+      <c r="E60" s="16" t="n"/>
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="11" t="n"/>
+      <c r="H60" s="16" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="26" t="n"/>
+      <c r="K60" s="16" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="N60" s="11" t="n"/>
+      <c r="N60" s="16" t="n"/>
       <c r="O60" s="12" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="11" t="n"/>
+      <c r="Q60" s="16" t="n"/>
       <c r="R60" s="12" t="n"/>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="11" t="n"/>
+      <c r="T60" s="16" t="n"/>
       <c r="U60" s="12" t="n"/>
       <c r="V60" s="13" t="n"/>
     </row>
@@ -2821,55 +2708,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B61" s="27" t="n"/>
+      <c r="B61" s="16" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
-      <c r="E61" s="11" t="n"/>
+      <c r="E61" s="16" t="n"/>
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="11" t="n"/>
+      <c r="H61" s="16" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
-      <c r="K61" s="27" t="n"/>
+      <c r="K61" s="16" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
-      <c r="N61" s="11" t="n"/>
+      <c r="N61" s="16" t="n"/>
       <c r="O61" s="12" t="n"/>
       <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="11" t="n"/>
+      <c r="Q61" s="16" t="n"/>
       <c r="R61" s="12" t="n"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="11" t="n"/>
+      <c r="T61" s="16" t="n"/>
       <c r="U61" s="12" t="n"/>
       <c r="V61" s="13" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="E62" s="15" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="17" t="n"/>
-      <c r="H62" s="15" t="n"/>
-      <c r="I62" s="16" t="n"/>
-      <c r="J62" s="17" t="n"/>
-      <c r="K62" s="15" t="n"/>
-      <c r="L62" s="16" t="n"/>
-      <c r="M62" s="17" t="n"/>
-      <c r="N62" s="15" t="n"/>
-      <c r="O62" s="16" t="n"/>
-      <c r="P62" s="17" t="n"/>
-      <c r="Q62" s="15" t="n"/>
-      <c r="R62" s="16" t="n"/>
-      <c r="S62" s="17" t="n"/>
-      <c r="T62" s="15" t="n"/>
-      <c r="U62" s="16" t="n"/>
-      <c r="V62" s="17" t="n"/>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="20" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="19" t="n"/>
+      <c r="J62" s="20" t="n"/>
+      <c r="K62" s="18" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="20" t="n"/>
+      <c r="N62" s="18" t="n"/>
+      <c r="O62" s="19" t="n"/>
+      <c r="P62" s="20" t="n"/>
+      <c r="Q62" s="18" t="n"/>
+      <c r="R62" s="19" t="n"/>
+      <c r="S62" s="20" t="n"/>
+      <c r="T62" s="18" t="n"/>
+      <c r="U62" s="19" t="n"/>
+      <c r="V62" s="20" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -2877,25 +2764,37 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="7" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：買い物代行</t>
+        </is>
+      </c>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="9" t="n"/>
-      <c r="H63" s="7" t="n"/>
+      <c r="H63" s="21" t="n"/>
       <c r="I63" s="8" t="n"/>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="7" t="n"/>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="9" t="n"/>
-      <c r="N63" s="7" t="n"/>
+      <c r="N63" s="21" t="n"/>
       <c r="O63" s="8" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="7" t="n"/>
+      <c r="Q63" s="21" t="n"/>
       <c r="R63" s="8" t="n"/>
       <c r="S63" s="9" t="n"/>
-      <c r="T63" s="7" t="n"/>
+      <c r="T63" s="21" t="n"/>
       <c r="U63" s="8" t="n"/>
       <c r="V63" s="9" t="n"/>
     </row>
@@ -2911,19 +2810,19 @@
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="13" t="n"/>
-      <c r="H64" s="11" t="n"/>
+      <c r="H64" s="16" t="n"/>
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="11" t="n"/>
       <c r="L64" s="12" t="n"/>
       <c r="M64" s="13" t="n"/>
-      <c r="N64" s="11" t="n"/>
+      <c r="N64" s="16" t="n"/>
       <c r="O64" s="12" t="n"/>
       <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="11" t="n"/>
+      <c r="Q64" s="16" t="n"/>
       <c r="R64" s="12" t="n"/>
       <c r="S64" s="13" t="n"/>
-      <c r="T64" s="11" t="n"/>
+      <c r="T64" s="16" t="n"/>
       <c r="U64" s="12" t="n"/>
       <c r="V64" s="13" t="n"/>
     </row>
@@ -2939,19 +2838,19 @@
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="13" t="n"/>
-      <c r="H65" s="11" t="n"/>
+      <c r="H65" s="16" t="n"/>
       <c r="I65" s="12" t="n"/>
       <c r="J65" s="13" t="n"/>
       <c r="K65" s="11" t="n"/>
       <c r="L65" s="12" t="n"/>
       <c r="M65" s="13" t="n"/>
-      <c r="N65" s="11" t="n"/>
+      <c r="N65" s="16" t="n"/>
       <c r="O65" s="12" t="n"/>
       <c r="P65" s="13" t="n"/>
-      <c r="Q65" s="11" t="n"/>
+      <c r="Q65" s="16" t="n"/>
       <c r="R65" s="12" t="n"/>
       <c r="S65" s="13" t="n"/>
-      <c r="T65" s="11" t="n"/>
+      <c r="T65" s="16" t="n"/>
       <c r="U65" s="12" t="n"/>
       <c r="V65" s="13" t="n"/>
     </row>
@@ -2967,19 +2866,19 @@
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="13" t="n"/>
-      <c r="H66" s="11" t="n"/>
+      <c r="H66" s="16" t="n"/>
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="11" t="n"/>
       <c r="L66" s="12" t="n"/>
       <c r="M66" s="13" t="n"/>
-      <c r="N66" s="11" t="n"/>
+      <c r="N66" s="16" t="n"/>
       <c r="O66" s="12" t="n"/>
       <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="11" t="n"/>
+      <c r="Q66" s="16" t="n"/>
       <c r="R66" s="12" t="n"/>
       <c r="S66" s="13" t="n"/>
-      <c r="T66" s="11" t="n"/>
+      <c r="T66" s="16" t="n"/>
       <c r="U66" s="12" t="n"/>
       <c r="V66" s="13" t="n"/>
     </row>
@@ -2992,22 +2891,22 @@
       <c r="B67" s="11" t="n"/>
       <c r="C67" s="12" t="n"/>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="11" t="n"/>
+      <c r="E67" s="14" t="n"/>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="13" t="n"/>
-      <c r="H67" s="11" t="n"/>
+      <c r="H67" s="16" t="n"/>
       <c r="I67" s="12" t="n"/>
       <c r="J67" s="13" t="n"/>
       <c r="K67" s="11" t="n"/>
       <c r="L67" s="12" t="n"/>
       <c r="M67" s="13" t="n"/>
-      <c r="N67" s="11" t="n"/>
+      <c r="N67" s="16" t="n"/>
       <c r="O67" s="12" t="n"/>
       <c r="P67" s="13" t="n"/>
-      <c r="Q67" s="11" t="n"/>
+      <c r="Q67" s="16" t="n"/>
       <c r="R67" s="12" t="n"/>
       <c r="S67" s="13" t="n"/>
-      <c r="T67" s="11" t="n"/>
+      <c r="T67" s="16" t="n"/>
       <c r="U67" s="12" t="n"/>
       <c r="V67" s="13" t="n"/>
     </row>
@@ -3020,22 +2919,22 @@
       <c r="B68" s="11" t="n"/>
       <c r="C68" s="12" t="n"/>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="11" t="n"/>
+      <c r="E68" s="16" t="n"/>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="13" t="n"/>
-      <c r="H68" s="11" t="n"/>
+      <c r="H68" s="16" t="n"/>
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="11" t="n"/>
       <c r="L68" s="12" t="n"/>
       <c r="M68" s="13" t="n"/>
-      <c r="N68" s="11" t="n"/>
+      <c r="N68" s="16" t="n"/>
       <c r="O68" s="12" t="n"/>
       <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="11" t="n"/>
+      <c r="Q68" s="16" t="n"/>
       <c r="R68" s="12" t="n"/>
       <c r="S68" s="13" t="n"/>
-      <c r="T68" s="11" t="n"/>
+      <c r="T68" s="16" t="n"/>
       <c r="U68" s="12" t="n"/>
       <c r="V68" s="13" t="n"/>
     </row>
@@ -3048,22 +2947,22 @@
       <c r="B69" s="11" t="n"/>
       <c r="C69" s="12" t="n"/>
       <c r="D69" s="13" t="n"/>
-      <c r="E69" s="11" t="n"/>
+      <c r="E69" s="16" t="n"/>
       <c r="F69" s="12" t="n"/>
       <c r="G69" s="13" t="n"/>
-      <c r="H69" s="11" t="n"/>
+      <c r="H69" s="16" t="n"/>
       <c r="I69" s="12" t="n"/>
       <c r="J69" s="13" t="n"/>
       <c r="K69" s="11" t="n"/>
       <c r="L69" s="12" t="n"/>
       <c r="M69" s="13" t="n"/>
-      <c r="N69" s="11" t="n"/>
+      <c r="N69" s="16" t="n"/>
       <c r="O69" s="12" t="n"/>
       <c r="P69" s="13" t="n"/>
-      <c r="Q69" s="11" t="n"/>
+      <c r="Q69" s="16" t="n"/>
       <c r="R69" s="12" t="n"/>
       <c r="S69" s="13" t="n"/>
-      <c r="T69" s="11" t="n"/>
+      <c r="T69" s="16" t="n"/>
       <c r="U69" s="12" t="n"/>
       <c r="V69" s="13" t="n"/>
     </row>
@@ -3076,22 +2975,22 @@
       <c r="B70" s="11" t="n"/>
       <c r="C70" s="12" t="n"/>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="11" t="n"/>
+      <c r="E70" s="16" t="n"/>
       <c r="F70" s="12" t="n"/>
       <c r="G70" s="13" t="n"/>
-      <c r="H70" s="11" t="n"/>
+      <c r="H70" s="16" t="n"/>
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="11" t="n"/>
       <c r="L70" s="12" t="n"/>
       <c r="M70" s="13" t="n"/>
-      <c r="N70" s="11" t="n"/>
+      <c r="N70" s="16" t="n"/>
       <c r="O70" s="12" t="n"/>
       <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="11" t="n"/>
+      <c r="Q70" s="16" t="n"/>
       <c r="R70" s="12" t="n"/>
       <c r="S70" s="13" t="n"/>
-      <c r="T70" s="11" t="n"/>
+      <c r="T70" s="16" t="n"/>
       <c r="U70" s="12" t="n"/>
       <c r="V70" s="13" t="n"/>
     </row>
@@ -3104,22 +3003,22 @@
       <c r="B71" s="11" t="n"/>
       <c r="C71" s="12" t="n"/>
       <c r="D71" s="13" t="n"/>
-      <c r="E71" s="11" t="n"/>
+      <c r="E71" s="16" t="n"/>
       <c r="F71" s="12" t="n"/>
       <c r="G71" s="13" t="n"/>
-      <c r="H71" s="11" t="n"/>
+      <c r="H71" s="16" t="n"/>
       <c r="I71" s="12" t="n"/>
       <c r="J71" s="13" t="n"/>
       <c r="K71" s="11" t="n"/>
       <c r="L71" s="12" t="n"/>
       <c r="M71" s="13" t="n"/>
-      <c r="N71" s="11" t="n"/>
+      <c r="N71" s="16" t="n"/>
       <c r="O71" s="12" t="n"/>
       <c r="P71" s="13" t="n"/>
-      <c r="Q71" s="11" t="n"/>
+      <c r="Q71" s="16" t="n"/>
       <c r="R71" s="12" t="n"/>
       <c r="S71" s="13" t="n"/>
-      <c r="T71" s="11" t="n"/>
+      <c r="T71" s="16" t="n"/>
       <c r="U71" s="12" t="n"/>
       <c r="V71" s="13" t="n"/>
     </row>
@@ -3132,22 +3031,22 @@
       <c r="B72" s="11" t="n"/>
       <c r="C72" s="12" t="n"/>
       <c r="D72" s="13" t="n"/>
-      <c r="E72" s="11" t="n"/>
+      <c r="E72" s="16" t="n"/>
       <c r="F72" s="12" t="n"/>
       <c r="G72" s="13" t="n"/>
-      <c r="H72" s="11" t="n"/>
+      <c r="H72" s="16" t="n"/>
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="11" t="n"/>
       <c r="L72" s="12" t="n"/>
       <c r="M72" s="13" t="n"/>
-      <c r="N72" s="11" t="n"/>
+      <c r="N72" s="16" t="n"/>
       <c r="O72" s="12" t="n"/>
       <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="11" t="n"/>
+      <c r="Q72" s="16" t="n"/>
       <c r="R72" s="12" t="n"/>
       <c r="S72" s="13" t="n"/>
-      <c r="T72" s="11" t="n"/>
+      <c r="T72" s="16" t="n"/>
       <c r="U72" s="12" t="n"/>
       <c r="V72" s="13" t="n"/>
     </row>
@@ -3157,55 +3056,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B73" s="11" t="n"/>
+      <c r="B73" s="14" t="n"/>
       <c r="C73" s="12" t="n"/>
       <c r="D73" s="13" t="n"/>
-      <c r="E73" s="11" t="n"/>
+      <c r="E73" s="16" t="n"/>
       <c r="F73" s="12" t="n"/>
       <c r="G73" s="13" t="n"/>
-      <c r="H73" s="11" t="n"/>
+      <c r="H73" s="16" t="n"/>
       <c r="I73" s="12" t="n"/>
       <c r="J73" s="13" t="n"/>
-      <c r="K73" s="11" t="n"/>
+      <c r="K73" s="14" t="n"/>
       <c r="L73" s="12" t="n"/>
       <c r="M73" s="13" t="n"/>
-      <c r="N73" s="11" t="n"/>
+      <c r="N73" s="16" t="n"/>
       <c r="O73" s="12" t="n"/>
       <c r="P73" s="13" t="n"/>
-      <c r="Q73" s="11" t="n"/>
+      <c r="Q73" s="16" t="n"/>
       <c r="R73" s="12" t="n"/>
       <c r="S73" s="13" t="n"/>
-      <c r="T73" s="11" t="n"/>
+      <c r="T73" s="16" t="n"/>
       <c r="U73" s="12" t="n"/>
       <c r="V73" s="13" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="14" t="inlineStr">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B74" s="15" t="n"/>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="15" t="n"/>
-      <c r="F74" s="16" t="n"/>
-      <c r="G74" s="17" t="n"/>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="16" t="n"/>
-      <c r="J74" s="17" t="n"/>
-      <c r="K74" s="15" t="n"/>
-      <c r="L74" s="16" t="n"/>
-      <c r="M74" s="17" t="n"/>
-      <c r="N74" s="15" t="n"/>
-      <c r="O74" s="16" t="n"/>
-      <c r="P74" s="17" t="n"/>
-      <c r="Q74" s="15" t="n"/>
-      <c r="R74" s="16" t="n"/>
-      <c r="S74" s="17" t="n"/>
-      <c r="T74" s="15" t="n"/>
-      <c r="U74" s="16" t="n"/>
-      <c r="V74" s="17" t="n"/>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="19" t="n"/>
+      <c r="J74" s="20" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="19" t="n"/>
+      <c r="M74" s="20" t="n"/>
+      <c r="N74" s="18" t="n"/>
+      <c r="O74" s="19" t="n"/>
+      <c r="P74" s="20" t="n"/>
+      <c r="Q74" s="18" t="n"/>
+      <c r="R74" s="19" t="n"/>
+      <c r="S74" s="20" t="n"/>
+      <c r="T74" s="18" t="n"/>
+      <c r="U74" s="19" t="n"/>
+      <c r="V74" s="20" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -3213,25 +3112,25 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="21" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="9" t="n"/>
-      <c r="E75" s="7" t="n"/>
+      <c r="E75" s="21" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="9" t="n"/>
-      <c r="H75" s="7" t="n"/>
+      <c r="H75" s="21" t="n"/>
       <c r="I75" s="8" t="n"/>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="7" t="n"/>
+      <c r="K75" s="21" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="9" t="n"/>
-      <c r="N75" s="7" t="n"/>
+      <c r="N75" s="21" t="n"/>
       <c r="O75" s="8" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="7" t="n"/>
+      <c r="Q75" s="21" t="n"/>
       <c r="R75" s="8" t="n"/>
       <c r="S75" s="9" t="n"/>
-      <c r="T75" s="25" t="inlineStr">
+      <c r="T75" s="7" t="inlineStr">
         <is>
           <t>長谷部融子：外出</t>
         </is>
@@ -3245,25 +3144,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B76" s="11" t="n"/>
+      <c r="B76" s="16" t="n"/>
       <c r="C76" s="12" t="n"/>
       <c r="D76" s="13" t="n"/>
-      <c r="E76" s="11" t="n"/>
+      <c r="E76" s="16" t="n"/>
       <c r="F76" s="12" t="n"/>
       <c r="G76" s="13" t="n"/>
-      <c r="H76" s="11" t="n"/>
+      <c r="H76" s="16" t="n"/>
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="11" t="n"/>
+      <c r="K76" s="16" t="n"/>
       <c r="L76" s="12" t="n"/>
       <c r="M76" s="13" t="n"/>
-      <c r="N76" s="11" t="n"/>
+      <c r="N76" s="16" t="n"/>
       <c r="O76" s="12" t="n"/>
       <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="11" t="n"/>
+      <c r="Q76" s="16" t="n"/>
       <c r="R76" s="12" t="n"/>
       <c r="S76" s="13" t="n"/>
-      <c r="T76" s="26" t="n"/>
+      <c r="T76" s="11" t="n"/>
       <c r="U76" s="12" t="n"/>
       <c r="V76" s="13" t="n"/>
     </row>
@@ -3273,25 +3172,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n"/>
+      <c r="B77" s="16" t="n"/>
       <c r="C77" s="12" t="n"/>
       <c r="D77" s="13" t="n"/>
-      <c r="E77" s="11" t="n"/>
+      <c r="E77" s="16" t="n"/>
       <c r="F77" s="12" t="n"/>
       <c r="G77" s="13" t="n"/>
-      <c r="H77" s="11" t="n"/>
+      <c r="H77" s="16" t="n"/>
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="13" t="n"/>
-      <c r="K77" s="11" t="n"/>
+      <c r="K77" s="16" t="n"/>
       <c r="L77" s="12" t="n"/>
       <c r="M77" s="13" t="n"/>
-      <c r="N77" s="11" t="n"/>
+      <c r="N77" s="16" t="n"/>
       <c r="O77" s="12" t="n"/>
       <c r="P77" s="13" t="n"/>
-      <c r="Q77" s="11" t="n"/>
+      <c r="Q77" s="16" t="n"/>
       <c r="R77" s="12" t="n"/>
       <c r="S77" s="13" t="n"/>
-      <c r="T77" s="26" t="n"/>
+      <c r="T77" s="11" t="n"/>
       <c r="U77" s="12" t="n"/>
       <c r="V77" s="13" t="n"/>
     </row>
@@ -3301,25 +3200,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
+      <c r="B78" s="16" t="n"/>
       <c r="C78" s="12" t="n"/>
       <c r="D78" s="13" t="n"/>
-      <c r="E78" s="11" t="n"/>
+      <c r="E78" s="16" t="n"/>
       <c r="F78" s="12" t="n"/>
       <c r="G78" s="13" t="n"/>
-      <c r="H78" s="11" t="n"/>
+      <c r="H78" s="16" t="n"/>
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="11" t="n"/>
+      <c r="K78" s="16" t="n"/>
       <c r="L78" s="12" t="n"/>
       <c r="M78" s="13" t="n"/>
-      <c r="N78" s="11" t="n"/>
+      <c r="N78" s="16" t="n"/>
       <c r="O78" s="12" t="n"/>
       <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="11" t="n"/>
+      <c r="Q78" s="16" t="n"/>
       <c r="R78" s="12" t="n"/>
       <c r="S78" s="13" t="n"/>
-      <c r="T78" s="26" t="n"/>
+      <c r="T78" s="11" t="n"/>
       <c r="U78" s="12" t="n"/>
       <c r="V78" s="13" t="n"/>
     </row>
@@ -3329,25 +3228,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n"/>
+      <c r="B79" s="16" t="n"/>
       <c r="C79" s="12" t="n"/>
       <c r="D79" s="13" t="n"/>
-      <c r="E79" s="11" t="n"/>
+      <c r="E79" s="16" t="n"/>
       <c r="F79" s="12" t="n"/>
       <c r="G79" s="13" t="n"/>
-      <c r="H79" s="11" t="n"/>
+      <c r="H79" s="16" t="n"/>
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="13" t="n"/>
-      <c r="K79" s="11" t="n"/>
+      <c r="K79" s="16" t="n"/>
       <c r="L79" s="12" t="n"/>
       <c r="M79" s="13" t="n"/>
-      <c r="N79" s="11" t="n"/>
+      <c r="N79" s="16" t="n"/>
       <c r="O79" s="12" t="n"/>
       <c r="P79" s="13" t="n"/>
-      <c r="Q79" s="11" t="n"/>
+      <c r="Q79" s="16" t="n"/>
       <c r="R79" s="12" t="n"/>
       <c r="S79" s="13" t="n"/>
-      <c r="T79" s="26" t="n"/>
+      <c r="T79" s="11" t="n"/>
       <c r="U79" s="12" t="n"/>
       <c r="V79" s="13" t="n"/>
     </row>
@@ -3357,25 +3256,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B80" s="11" t="n"/>
+      <c r="B80" s="16" t="n"/>
       <c r="C80" s="12" t="n"/>
       <c r="D80" s="13" t="n"/>
-      <c r="E80" s="11" t="n"/>
+      <c r="E80" s="16" t="n"/>
       <c r="F80" s="12" t="n"/>
       <c r="G80" s="13" t="n"/>
-      <c r="H80" s="11" t="n"/>
+      <c r="H80" s="16" t="n"/>
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="11" t="n"/>
+      <c r="K80" s="16" t="n"/>
       <c r="L80" s="12" t="n"/>
       <c r="M80" s="13" t="n"/>
-      <c r="N80" s="11" t="n"/>
+      <c r="N80" s="16" t="n"/>
       <c r="O80" s="12" t="n"/>
       <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="11" t="n"/>
+      <c r="Q80" s="16" t="n"/>
       <c r="R80" s="12" t="n"/>
       <c r="S80" s="13" t="n"/>
-      <c r="T80" s="26" t="n"/>
+      <c r="T80" s="11" t="n"/>
       <c r="U80" s="12" t="n"/>
       <c r="V80" s="13" t="n"/>
     </row>
@@ -3385,29 +3284,29 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B81" s="11" t="n"/>
+      <c r="B81" s="16" t="n"/>
       <c r="C81" s="12" t="n"/>
       <c r="D81" s="13" t="n"/>
-      <c r="E81" s="11" t="n"/>
+      <c r="E81" s="16" t="n"/>
       <c r="F81" s="12" t="n"/>
       <c r="G81" s="13" t="n"/>
-      <c r="H81" s="11" t="n"/>
+      <c r="H81" s="16" t="n"/>
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="13" t="n"/>
-      <c r="K81" s="31" t="inlineStr">
+      <c r="K81" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：掃除</t>
         </is>
       </c>
       <c r="L81" s="12" t="n"/>
       <c r="M81" s="13" t="n"/>
-      <c r="N81" s="11" t="n"/>
+      <c r="N81" s="16" t="n"/>
       <c r="O81" s="12" t="n"/>
       <c r="P81" s="13" t="n"/>
-      <c r="Q81" s="11" t="n"/>
+      <c r="Q81" s="16" t="n"/>
       <c r="R81" s="12" t="n"/>
       <c r="S81" s="13" t="n"/>
-      <c r="T81" s="26" t="n"/>
+      <c r="T81" s="11" t="n"/>
       <c r="U81" s="12" t="n"/>
       <c r="V81" s="13" t="n"/>
     </row>
@@ -3417,25 +3316,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B82" s="11" t="n"/>
+      <c r="B82" s="16" t="n"/>
       <c r="C82" s="12" t="n"/>
       <c r="D82" s="13" t="n"/>
-      <c r="E82" s="11" t="n"/>
+      <c r="E82" s="16" t="n"/>
       <c r="F82" s="12" t="n"/>
       <c r="G82" s="13" t="n"/>
-      <c r="H82" s="11" t="n"/>
+      <c r="H82" s="16" t="n"/>
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="26" t="n"/>
+      <c r="K82" s="11" t="n"/>
       <c r="L82" s="12" t="n"/>
       <c r="M82" s="13" t="n"/>
-      <c r="N82" s="11" t="n"/>
+      <c r="N82" s="16" t="n"/>
       <c r="O82" s="12" t="n"/>
       <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="11" t="n"/>
+      <c r="Q82" s="16" t="n"/>
       <c r="R82" s="12" t="n"/>
       <c r="S82" s="13" t="n"/>
-      <c r="T82" s="26" t="n"/>
+      <c r="T82" s="11" t="n"/>
       <c r="U82" s="12" t="n"/>
       <c r="V82" s="13" t="n"/>
     </row>
@@ -3445,25 +3344,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n"/>
+      <c r="B83" s="16" t="n"/>
       <c r="C83" s="12" t="n"/>
       <c r="D83" s="13" t="n"/>
-      <c r="E83" s="11" t="n"/>
+      <c r="E83" s="16" t="n"/>
       <c r="F83" s="12" t="n"/>
       <c r="G83" s="13" t="n"/>
-      <c r="H83" s="11" t="n"/>
+      <c r="H83" s="16" t="n"/>
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="13" t="n"/>
-      <c r="K83" s="26" t="n"/>
+      <c r="K83" s="11" t="n"/>
       <c r="L83" s="12" t="n"/>
       <c r="M83" s="13" t="n"/>
-      <c r="N83" s="11" t="n"/>
+      <c r="N83" s="16" t="n"/>
       <c r="O83" s="12" t="n"/>
       <c r="P83" s="13" t="n"/>
-      <c r="Q83" s="11" t="n"/>
+      <c r="Q83" s="16" t="n"/>
       <c r="R83" s="12" t="n"/>
       <c r="S83" s="13" t="n"/>
-      <c r="T83" s="26" t="n"/>
+      <c r="T83" s="11" t="n"/>
       <c r="U83" s="12" t="n"/>
       <c r="V83" s="13" t="n"/>
     </row>
@@ -3473,25 +3372,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B84" s="11" t="n"/>
+      <c r="B84" s="16" t="n"/>
       <c r="C84" s="12" t="n"/>
       <c r="D84" s="13" t="n"/>
-      <c r="E84" s="11" t="n"/>
+      <c r="E84" s="16" t="n"/>
       <c r="F84" s="12" t="n"/>
       <c r="G84" s="13" t="n"/>
-      <c r="H84" s="11" t="n"/>
+      <c r="H84" s="16" t="n"/>
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="26" t="n"/>
+      <c r="K84" s="11" t="n"/>
       <c r="L84" s="12" t="n"/>
       <c r="M84" s="13" t="n"/>
-      <c r="N84" s="11" t="n"/>
+      <c r="N84" s="16" t="n"/>
       <c r="O84" s="12" t="n"/>
       <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="11" t="n"/>
+      <c r="Q84" s="16" t="n"/>
       <c r="R84" s="12" t="n"/>
       <c r="S84" s="13" t="n"/>
-      <c r="T84" s="26" t="n"/>
+      <c r="T84" s="11" t="n"/>
       <c r="U84" s="12" t="n"/>
       <c r="V84" s="13" t="n"/>
     </row>
@@ -3501,55 +3400,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B85" s="11" t="n"/>
+      <c r="B85" s="16" t="n"/>
       <c r="C85" s="12" t="n"/>
       <c r="D85" s="13" t="n"/>
-      <c r="E85" s="11" t="n"/>
+      <c r="E85" s="16" t="n"/>
       <c r="F85" s="12" t="n"/>
       <c r="G85" s="13" t="n"/>
-      <c r="H85" s="11" t="n"/>
+      <c r="H85" s="16" t="n"/>
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="13" t="n"/>
-      <c r="K85" s="26" t="n"/>
+      <c r="K85" s="11" t="n"/>
       <c r="L85" s="12" t="n"/>
       <c r="M85" s="13" t="n"/>
-      <c r="N85" s="11" t="n"/>
+      <c r="N85" s="16" t="n"/>
       <c r="O85" s="12" t="n"/>
       <c r="P85" s="13" t="n"/>
-      <c r="Q85" s="11" t="n"/>
+      <c r="Q85" s="16" t="n"/>
       <c r="R85" s="12" t="n"/>
       <c r="S85" s="13" t="n"/>
-      <c r="T85" s="27" t="n"/>
+      <c r="T85" s="14" t="n"/>
       <c r="U85" s="12" t="n"/>
       <c r="V85" s="13" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="inlineStr">
+      <c r="A86" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B86" s="15" t="n"/>
-      <c r="C86" s="16" t="n"/>
-      <c r="D86" s="17" t="n"/>
-      <c r="E86" s="15" t="n"/>
-      <c r="F86" s="16" t="n"/>
-      <c r="G86" s="17" t="n"/>
-      <c r="H86" s="15" t="n"/>
-      <c r="I86" s="16" t="n"/>
-      <c r="J86" s="17" t="n"/>
-      <c r="K86" s="26" t="n"/>
-      <c r="L86" s="16" t="n"/>
-      <c r="M86" s="17" t="n"/>
-      <c r="N86" s="15" t="n"/>
-      <c r="O86" s="16" t="n"/>
-      <c r="P86" s="17" t="n"/>
-      <c r="Q86" s="15" t="n"/>
-      <c r="R86" s="16" t="n"/>
-      <c r="S86" s="17" t="n"/>
-      <c r="T86" s="15" t="n"/>
-      <c r="U86" s="16" t="n"/>
-      <c r="V86" s="17" t="n"/>
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="20" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="19" t="n"/>
+      <c r="J86" s="20" t="n"/>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="19" t="n"/>
+      <c r="M86" s="20" t="n"/>
+      <c r="N86" s="18" t="n"/>
+      <c r="O86" s="19" t="n"/>
+      <c r="P86" s="20" t="n"/>
+      <c r="Q86" s="18" t="n"/>
+      <c r="R86" s="19" t="n"/>
+      <c r="S86" s="20" t="n"/>
+      <c r="T86" s="18" t="n"/>
+      <c r="U86" s="19" t="n"/>
+      <c r="V86" s="20" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -3557,25 +3456,25 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B87" s="7" t="n"/>
+      <c r="B87" s="21" t="n"/>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="7" t="n"/>
+      <c r="E87" s="21" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="7" t="n"/>
+      <c r="H87" s="21" t="n"/>
       <c r="I87" s="8" t="n"/>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="26" t="n"/>
+      <c r="K87" s="11" t="n"/>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="9" t="n"/>
-      <c r="N87" s="7" t="n"/>
+      <c r="N87" s="21" t="n"/>
       <c r="O87" s="8" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="7" t="n"/>
+      <c r="Q87" s="21" t="n"/>
       <c r="R87" s="8" t="n"/>
       <c r="S87" s="9" t="n"/>
-      <c r="T87" s="7" t="n"/>
+      <c r="T87" s="21" t="n"/>
       <c r="U87" s="8" t="n"/>
       <c r="V87" s="9" t="n"/>
     </row>
@@ -3585,25 +3484,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B88" s="11" t="n"/>
+      <c r="B88" s="16" t="n"/>
       <c r="C88" s="12" t="n"/>
       <c r="D88" s="13" t="n"/>
-      <c r="E88" s="11" t="n"/>
+      <c r="E88" s="16" t="n"/>
       <c r="F88" s="12" t="n"/>
       <c r="G88" s="13" t="n"/>
-      <c r="H88" s="11" t="n"/>
+      <c r="H88" s="16" t="n"/>
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="26" t="n"/>
+      <c r="K88" s="11" t="n"/>
       <c r="L88" s="12" t="n"/>
       <c r="M88" s="13" t="n"/>
-      <c r="N88" s="11" t="n"/>
+      <c r="N88" s="16" t="n"/>
       <c r="O88" s="12" t="n"/>
       <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="11" t="n"/>
+      <c r="Q88" s="16" t="n"/>
       <c r="R88" s="12" t="n"/>
       <c r="S88" s="13" t="n"/>
-      <c r="T88" s="11" t="n"/>
+      <c r="T88" s="16" t="n"/>
       <c r="U88" s="12" t="n"/>
       <c r="V88" s="13" t="n"/>
     </row>
@@ -3613,25 +3512,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B89" s="11" t="n"/>
+      <c r="B89" s="16" t="n"/>
       <c r="C89" s="12" t="n"/>
       <c r="D89" s="13" t="n"/>
-      <c r="E89" s="11" t="n"/>
+      <c r="E89" s="16" t="n"/>
       <c r="F89" s="12" t="n"/>
       <c r="G89" s="13" t="n"/>
-      <c r="H89" s="11" t="n"/>
+      <c r="H89" s="16" t="n"/>
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="13" t="n"/>
-      <c r="K89" s="26" t="n"/>
+      <c r="K89" s="11" t="n"/>
       <c r="L89" s="12" t="n"/>
       <c r="M89" s="13" t="n"/>
-      <c r="N89" s="11" t="n"/>
+      <c r="N89" s="16" t="n"/>
       <c r="O89" s="12" t="n"/>
       <c r="P89" s="13" t="n"/>
-      <c r="Q89" s="11" t="n"/>
+      <c r="Q89" s="16" t="n"/>
       <c r="R89" s="12" t="n"/>
       <c r="S89" s="13" t="n"/>
-      <c r="T89" s="11" t="n"/>
+      <c r="T89" s="16" t="n"/>
       <c r="U89" s="12" t="n"/>
       <c r="V89" s="13" t="n"/>
     </row>
@@ -3641,25 +3540,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B90" s="11" t="n"/>
+      <c r="B90" s="16" t="n"/>
       <c r="C90" s="12" t="n"/>
       <c r="D90" s="13" t="n"/>
-      <c r="E90" s="11" t="n"/>
+      <c r="E90" s="16" t="n"/>
       <c r="F90" s="12" t="n"/>
       <c r="G90" s="13" t="n"/>
-      <c r="H90" s="11" t="n"/>
+      <c r="H90" s="16" t="n"/>
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="26" t="n"/>
+      <c r="K90" s="11" t="n"/>
       <c r="L90" s="12" t="n"/>
       <c r="M90" s="13" t="n"/>
-      <c r="N90" s="11" t="n"/>
+      <c r="N90" s="16" t="n"/>
       <c r="O90" s="12" t="n"/>
       <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="11" t="n"/>
+      <c r="Q90" s="16" t="n"/>
       <c r="R90" s="12" t="n"/>
       <c r="S90" s="13" t="n"/>
-      <c r="T90" s="11" t="n"/>
+      <c r="T90" s="16" t="n"/>
       <c r="U90" s="12" t="n"/>
       <c r="V90" s="13" t="n"/>
     </row>
@@ -3669,25 +3568,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B91" s="11" t="n"/>
+      <c r="B91" s="16" t="n"/>
       <c r="C91" s="12" t="n"/>
       <c r="D91" s="13" t="n"/>
-      <c r="E91" s="11" t="n"/>
+      <c r="E91" s="16" t="n"/>
       <c r="F91" s="12" t="n"/>
       <c r="G91" s="13" t="n"/>
-      <c r="H91" s="11" t="n"/>
+      <c r="H91" s="16" t="n"/>
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="13" t="n"/>
-      <c r="K91" s="27" t="n"/>
+      <c r="K91" s="14" t="n"/>
       <c r="L91" s="12" t="n"/>
       <c r="M91" s="13" t="n"/>
-      <c r="N91" s="11" t="n"/>
+      <c r="N91" s="16" t="n"/>
       <c r="O91" s="12" t="n"/>
       <c r="P91" s="13" t="n"/>
-      <c r="Q91" s="11" t="n"/>
+      <c r="Q91" s="16" t="n"/>
       <c r="R91" s="12" t="n"/>
       <c r="S91" s="13" t="n"/>
-      <c r="T91" s="11" t="n"/>
+      <c r="T91" s="16" t="n"/>
       <c r="U91" s="12" t="n"/>
       <c r="V91" s="13" t="n"/>
     </row>
@@ -3697,25 +3596,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B92" s="11" t="n"/>
+      <c r="B92" s="16" t="n"/>
       <c r="C92" s="12" t="n"/>
       <c r="D92" s="13" t="n"/>
-      <c r="E92" s="11" t="n"/>
+      <c r="E92" s="16" t="n"/>
       <c r="F92" s="12" t="n"/>
       <c r="G92" s="13" t="n"/>
-      <c r="H92" s="11" t="n"/>
+      <c r="H92" s="16" t="n"/>
       <c r="I92" s="12" t="n"/>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="11" t="n"/>
+      <c r="K92" s="16" t="n"/>
       <c r="L92" s="12" t="n"/>
       <c r="M92" s="13" t="n"/>
-      <c r="N92" s="11" t="n"/>
+      <c r="N92" s="16" t="n"/>
       <c r="O92" s="12" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="11" t="n"/>
+      <c r="Q92" s="16" t="n"/>
       <c r="R92" s="12" t="n"/>
       <c r="S92" s="13" t="n"/>
-      <c r="T92" s="11" t="n"/>
+      <c r="T92" s="16" t="n"/>
       <c r="U92" s="12" t="n"/>
       <c r="V92" s="13" t="n"/>
     </row>
@@ -3725,25 +3624,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B93" s="11" t="n"/>
+      <c r="B93" s="16" t="n"/>
       <c r="C93" s="12" t="n"/>
       <c r="D93" s="13" t="n"/>
-      <c r="E93" s="11" t="n"/>
+      <c r="E93" s="16" t="n"/>
       <c r="F93" s="12" t="n"/>
       <c r="G93" s="13" t="n"/>
-      <c r="H93" s="11" t="n"/>
+      <c r="H93" s="16" t="n"/>
       <c r="I93" s="12" t="n"/>
       <c r="J93" s="13" t="n"/>
-      <c r="K93" s="11" t="n"/>
+      <c r="K93" s="16" t="n"/>
       <c r="L93" s="12" t="n"/>
       <c r="M93" s="13" t="n"/>
-      <c r="N93" s="11" t="n"/>
+      <c r="N93" s="16" t="n"/>
       <c r="O93" s="12" t="n"/>
       <c r="P93" s="13" t="n"/>
-      <c r="Q93" s="11" t="n"/>
+      <c r="Q93" s="16" t="n"/>
       <c r="R93" s="12" t="n"/>
       <c r="S93" s="13" t="n"/>
-      <c r="T93" s="11" t="n"/>
+      <c r="T93" s="16" t="n"/>
       <c r="U93" s="12" t="n"/>
       <c r="V93" s="13" t="n"/>
     </row>
@@ -3753,25 +3652,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B94" s="11" t="n"/>
+      <c r="B94" s="16" t="n"/>
       <c r="C94" s="12" t="n"/>
       <c r="D94" s="13" t="n"/>
-      <c r="E94" s="11" t="n"/>
+      <c r="E94" s="16" t="n"/>
       <c r="F94" s="12" t="n"/>
       <c r="G94" s="13" t="n"/>
-      <c r="H94" s="11" t="n"/>
+      <c r="H94" s="16" t="n"/>
       <c r="I94" s="12" t="n"/>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="11" t="n"/>
+      <c r="K94" s="16" t="n"/>
       <c r="L94" s="12" t="n"/>
       <c r="M94" s="13" t="n"/>
-      <c r="N94" s="11" t="n"/>
+      <c r="N94" s="16" t="n"/>
       <c r="O94" s="12" t="n"/>
       <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="11" t="n"/>
+      <c r="Q94" s="16" t="n"/>
       <c r="R94" s="12" t="n"/>
       <c r="S94" s="13" t="n"/>
-      <c r="T94" s="11" t="n"/>
+      <c r="T94" s="16" t="n"/>
       <c r="U94" s="12" t="n"/>
       <c r="V94" s="13" t="n"/>
     </row>
@@ -3781,25 +3680,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B95" s="11" t="n"/>
+      <c r="B95" s="16" t="n"/>
       <c r="C95" s="12" t="n"/>
       <c r="D95" s="13" t="n"/>
-      <c r="E95" s="11" t="n"/>
+      <c r="E95" s="16" t="n"/>
       <c r="F95" s="12" t="n"/>
       <c r="G95" s="13" t="n"/>
-      <c r="H95" s="11" t="n"/>
+      <c r="H95" s="16" t="n"/>
       <c r="I95" s="12" t="n"/>
       <c r="J95" s="13" t="n"/>
-      <c r="K95" s="11" t="n"/>
+      <c r="K95" s="16" t="n"/>
       <c r="L95" s="12" t="n"/>
       <c r="M95" s="13" t="n"/>
-      <c r="N95" s="11" t="n"/>
+      <c r="N95" s="16" t="n"/>
       <c r="O95" s="12" t="n"/>
       <c r="P95" s="13" t="n"/>
-      <c r="Q95" s="11" t="n"/>
+      <c r="Q95" s="16" t="n"/>
       <c r="R95" s="12" t="n"/>
       <c r="S95" s="13" t="n"/>
-      <c r="T95" s="11" t="n"/>
+      <c r="T95" s="16" t="n"/>
       <c r="U95" s="12" t="n"/>
       <c r="V95" s="13" t="n"/>
     </row>
@@ -3809,25 +3708,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B96" s="11" t="n"/>
+      <c r="B96" s="16" t="n"/>
       <c r="C96" s="12" t="n"/>
       <c r="D96" s="13" t="n"/>
-      <c r="E96" s="11" t="n"/>
+      <c r="E96" s="16" t="n"/>
       <c r="F96" s="12" t="n"/>
       <c r="G96" s="13" t="n"/>
-      <c r="H96" s="11" t="n"/>
+      <c r="H96" s="16" t="n"/>
       <c r="I96" s="12" t="n"/>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="11" t="n"/>
+      <c r="K96" s="16" t="n"/>
       <c r="L96" s="12" t="n"/>
       <c r="M96" s="13" t="n"/>
-      <c r="N96" s="11" t="n"/>
+      <c r="N96" s="16" t="n"/>
       <c r="O96" s="12" t="n"/>
       <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="11" t="n"/>
+      <c r="Q96" s="16" t="n"/>
       <c r="R96" s="12" t="n"/>
       <c r="S96" s="13" t="n"/>
-      <c r="T96" s="11" t="n"/>
+      <c r="T96" s="16" t="n"/>
       <c r="U96" s="12" t="n"/>
       <c r="V96" s="13" t="n"/>
     </row>
@@ -3837,55 +3736,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B97" s="11" t="n"/>
+      <c r="B97" s="16" t="n"/>
       <c r="C97" s="12" t="n"/>
       <c r="D97" s="13" t="n"/>
-      <c r="E97" s="11" t="n"/>
+      <c r="E97" s="16" t="n"/>
       <c r="F97" s="12" t="n"/>
       <c r="G97" s="13" t="n"/>
-      <c r="H97" s="11" t="n"/>
+      <c r="H97" s="16" t="n"/>
       <c r="I97" s="12" t="n"/>
       <c r="J97" s="13" t="n"/>
-      <c r="K97" s="11" t="n"/>
+      <c r="K97" s="16" t="n"/>
       <c r="L97" s="12" t="n"/>
       <c r="M97" s="13" t="n"/>
-      <c r="N97" s="11" t="n"/>
+      <c r="N97" s="16" t="n"/>
       <c r="O97" s="12" t="n"/>
       <c r="P97" s="13" t="n"/>
-      <c r="Q97" s="11" t="n"/>
+      <c r="Q97" s="16" t="n"/>
       <c r="R97" s="12" t="n"/>
       <c r="S97" s="13" t="n"/>
-      <c r="T97" s="11" t="n"/>
+      <c r="T97" s="16" t="n"/>
       <c r="U97" s="12" t="n"/>
       <c r="V97" s="13" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="14" t="inlineStr">
+      <c r="A98" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B98" s="15" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="15" t="n"/>
-      <c r="F98" s="16" t="n"/>
-      <c r="G98" s="17" t="n"/>
-      <c r="H98" s="15" t="n"/>
-      <c r="I98" s="16" t="n"/>
-      <c r="J98" s="17" t="n"/>
-      <c r="K98" s="15" t="n"/>
-      <c r="L98" s="16" t="n"/>
-      <c r="M98" s="17" t="n"/>
-      <c r="N98" s="15" t="n"/>
-      <c r="O98" s="16" t="n"/>
-      <c r="P98" s="17" t="n"/>
-      <c r="Q98" s="15" t="n"/>
-      <c r="R98" s="16" t="n"/>
-      <c r="S98" s="17" t="n"/>
-      <c r="T98" s="15" t="n"/>
-      <c r="U98" s="16" t="n"/>
-      <c r="V98" s="17" t="n"/>
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="19" t="n"/>
+      <c r="D98" s="20" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="19" t="n"/>
+      <c r="G98" s="20" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="19" t="n"/>
+      <c r="J98" s="20" t="n"/>
+      <c r="K98" s="18" t="n"/>
+      <c r="L98" s="19" t="n"/>
+      <c r="M98" s="20" t="n"/>
+      <c r="N98" s="18" t="n"/>
+      <c r="O98" s="19" t="n"/>
+      <c r="P98" s="20" t="n"/>
+      <c r="Q98" s="18" t="n"/>
+      <c r="R98" s="19" t="n"/>
+      <c r="S98" s="20" t="n"/>
+      <c r="T98" s="18" t="n"/>
+      <c r="U98" s="19" t="n"/>
+      <c r="V98" s="20" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -3893,25 +3792,25 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B99" s="7" t="n"/>
+      <c r="B99" s="21" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="9" t="n"/>
-      <c r="E99" s="7" t="n"/>
+      <c r="E99" s="21" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="9" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="21" t="n"/>
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="7" t="n"/>
+      <c r="K99" s="21" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="9" t="n"/>
-      <c r="N99" s="7" t="n"/>
+      <c r="N99" s="21" t="n"/>
       <c r="O99" s="8" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="7" t="n"/>
+      <c r="Q99" s="21" t="n"/>
       <c r="R99" s="8" t="n"/>
       <c r="S99" s="9" t="n"/>
-      <c r="T99" s="7" t="n"/>
+      <c r="T99" s="21" t="n"/>
       <c r="U99" s="8" t="n"/>
       <c r="V99" s="9" t="n"/>
     </row>
@@ -3921,25 +3820,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n"/>
+      <c r="B100" s="16" t="n"/>
       <c r="C100" s="12" t="n"/>
       <c r="D100" s="13" t="n"/>
-      <c r="E100" s="11" t="n"/>
+      <c r="E100" s="16" t="n"/>
       <c r="F100" s="12" t="n"/>
       <c r="G100" s="13" t="n"/>
-      <c r="H100" s="11" t="n"/>
+      <c r="H100" s="16" t="n"/>
       <c r="I100" s="12" t="n"/>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="11" t="n"/>
+      <c r="K100" s="16" t="n"/>
       <c r="L100" s="12" t="n"/>
       <c r="M100" s="13" t="n"/>
-      <c r="N100" s="11" t="n"/>
+      <c r="N100" s="16" t="n"/>
       <c r="O100" s="12" t="n"/>
       <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="11" t="n"/>
+      <c r="Q100" s="16" t="n"/>
       <c r="R100" s="12" t="n"/>
       <c r="S100" s="13" t="n"/>
-      <c r="T100" s="11" t="n"/>
+      <c r="T100" s="16" t="n"/>
       <c r="U100" s="12" t="n"/>
       <c r="V100" s="13" t="n"/>
     </row>
@@ -3949,25 +3848,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B101" s="11" t="n"/>
+      <c r="B101" s="16" t="n"/>
       <c r="C101" s="12" t="n"/>
       <c r="D101" s="13" t="n"/>
-      <c r="E101" s="11" t="n"/>
+      <c r="E101" s="16" t="n"/>
       <c r="F101" s="12" t="n"/>
       <c r="G101" s="13" t="n"/>
-      <c r="H101" s="11" t="n"/>
+      <c r="H101" s="16" t="n"/>
       <c r="I101" s="12" t="n"/>
       <c r="J101" s="13" t="n"/>
-      <c r="K101" s="11" t="n"/>
+      <c r="K101" s="16" t="n"/>
       <c r="L101" s="12" t="n"/>
       <c r="M101" s="13" t="n"/>
-      <c r="N101" s="11" t="n"/>
+      <c r="N101" s="16" t="n"/>
       <c r="O101" s="12" t="n"/>
       <c r="P101" s="13" t="n"/>
-      <c r="Q101" s="11" t="n"/>
+      <c r="Q101" s="16" t="n"/>
       <c r="R101" s="12" t="n"/>
       <c r="S101" s="13" t="n"/>
-      <c r="T101" s="11" t="n"/>
+      <c r="T101" s="16" t="n"/>
       <c r="U101" s="12" t="n"/>
       <c r="V101" s="13" t="n"/>
     </row>
@@ -3977,25 +3876,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B102" s="11" t="n"/>
+      <c r="B102" s="16" t="n"/>
       <c r="C102" s="12" t="n"/>
       <c r="D102" s="13" t="n"/>
-      <c r="E102" s="11" t="n"/>
+      <c r="E102" s="16" t="n"/>
       <c r="F102" s="12" t="n"/>
       <c r="G102" s="13" t="n"/>
-      <c r="H102" s="11" t="n"/>
+      <c r="H102" s="16" t="n"/>
       <c r="I102" s="12" t="n"/>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="11" t="n"/>
+      <c r="K102" s="16" t="n"/>
       <c r="L102" s="12" t="n"/>
       <c r="M102" s="13" t="n"/>
-      <c r="N102" s="11" t="n"/>
+      <c r="N102" s="16" t="n"/>
       <c r="O102" s="12" t="n"/>
       <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="11" t="n"/>
+      <c r="Q102" s="16" t="n"/>
       <c r="R102" s="12" t="n"/>
       <c r="S102" s="13" t="n"/>
-      <c r="T102" s="11" t="n"/>
+      <c r="T102" s="16" t="n"/>
       <c r="U102" s="12" t="n"/>
       <c r="V102" s="13" t="n"/>
     </row>
@@ -4005,25 +3904,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B103" s="11" t="n"/>
+      <c r="B103" s="16" t="n"/>
       <c r="C103" s="12" t="n"/>
       <c r="D103" s="13" t="n"/>
-      <c r="E103" s="11" t="n"/>
+      <c r="E103" s="16" t="n"/>
       <c r="F103" s="12" t="n"/>
       <c r="G103" s="13" t="n"/>
-      <c r="H103" s="11" t="n"/>
+      <c r="H103" s="16" t="n"/>
       <c r="I103" s="12" t="n"/>
       <c r="J103" s="13" t="n"/>
-      <c r="K103" s="11" t="n"/>
+      <c r="K103" s="16" t="n"/>
       <c r="L103" s="12" t="n"/>
       <c r="M103" s="13" t="n"/>
-      <c r="N103" s="11" t="n"/>
+      <c r="N103" s="16" t="n"/>
       <c r="O103" s="12" t="n"/>
       <c r="P103" s="13" t="n"/>
-      <c r="Q103" s="11" t="n"/>
+      <c r="Q103" s="16" t="n"/>
       <c r="R103" s="12" t="n"/>
       <c r="S103" s="13" t="n"/>
-      <c r="T103" s="11" t="n"/>
+      <c r="T103" s="16" t="n"/>
       <c r="U103" s="12" t="n"/>
       <c r="V103" s="13" t="n"/>
     </row>
@@ -4033,25 +3932,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B104" s="11" t="n"/>
+      <c r="B104" s="16" t="n"/>
       <c r="C104" s="12" t="n"/>
       <c r="D104" s="13" t="n"/>
-      <c r="E104" s="11" t="n"/>
+      <c r="E104" s="16" t="n"/>
       <c r="F104" s="12" t="n"/>
       <c r="G104" s="13" t="n"/>
-      <c r="H104" s="11" t="n"/>
+      <c r="H104" s="16" t="n"/>
       <c r="I104" s="12" t="n"/>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="11" t="n"/>
+      <c r="K104" s="16" t="n"/>
       <c r="L104" s="12" t="n"/>
       <c r="M104" s="13" t="n"/>
-      <c r="N104" s="11" t="n"/>
+      <c r="N104" s="16" t="n"/>
       <c r="O104" s="12" t="n"/>
       <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="11" t="n"/>
+      <c r="Q104" s="16" t="n"/>
       <c r="R104" s="12" t="n"/>
       <c r="S104" s="13" t="n"/>
-      <c r="T104" s="11" t="n"/>
+      <c r="T104" s="16" t="n"/>
       <c r="U104" s="12" t="n"/>
       <c r="V104" s="13" t="n"/>
     </row>
@@ -4061,25 +3960,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B105" s="11" t="n"/>
+      <c r="B105" s="16" t="n"/>
       <c r="C105" s="12" t="n"/>
       <c r="D105" s="13" t="n"/>
-      <c r="E105" s="11" t="n"/>
+      <c r="E105" s="16" t="n"/>
       <c r="F105" s="12" t="n"/>
       <c r="G105" s="13" t="n"/>
-      <c r="H105" s="11" t="n"/>
+      <c r="H105" s="16" t="n"/>
       <c r="I105" s="12" t="n"/>
       <c r="J105" s="13" t="n"/>
-      <c r="K105" s="11" t="n"/>
+      <c r="K105" s="16" t="n"/>
       <c r="L105" s="12" t="n"/>
       <c r="M105" s="13" t="n"/>
-      <c r="N105" s="11" t="n"/>
+      <c r="N105" s="16" t="n"/>
       <c r="O105" s="12" t="n"/>
       <c r="P105" s="13" t="n"/>
-      <c r="Q105" s="11" t="n"/>
+      <c r="Q105" s="16" t="n"/>
       <c r="R105" s="12" t="n"/>
       <c r="S105" s="13" t="n"/>
-      <c r="T105" s="11" t="n"/>
+      <c r="T105" s="16" t="n"/>
       <c r="U105" s="12" t="n"/>
       <c r="V105" s="13" t="n"/>
     </row>
@@ -4089,25 +3988,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B106" s="11" t="n"/>
+      <c r="B106" s="16" t="n"/>
       <c r="C106" s="12" t="n"/>
       <c r="D106" s="13" t="n"/>
-      <c r="E106" s="11" t="n"/>
+      <c r="E106" s="16" t="n"/>
       <c r="F106" s="12" t="n"/>
       <c r="G106" s="13" t="n"/>
-      <c r="H106" s="11" t="n"/>
+      <c r="H106" s="16" t="n"/>
       <c r="I106" s="12" t="n"/>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="11" t="n"/>
+      <c r="K106" s="16" t="n"/>
       <c r="L106" s="12" t="n"/>
       <c r="M106" s="13" t="n"/>
-      <c r="N106" s="11" t="n"/>
+      <c r="N106" s="16" t="n"/>
       <c r="O106" s="12" t="n"/>
       <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="11" t="n"/>
+      <c r="Q106" s="16" t="n"/>
       <c r="R106" s="12" t="n"/>
       <c r="S106" s="13" t="n"/>
-      <c r="T106" s="11" t="n"/>
+      <c r="T106" s="16" t="n"/>
       <c r="U106" s="12" t="n"/>
       <c r="V106" s="13" t="n"/>
     </row>
@@ -4117,25 +4016,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B107" s="11" t="n"/>
+      <c r="B107" s="16" t="n"/>
       <c r="C107" s="12" t="n"/>
       <c r="D107" s="13" t="n"/>
-      <c r="E107" s="11" t="n"/>
+      <c r="E107" s="16" t="n"/>
       <c r="F107" s="12" t="n"/>
       <c r="G107" s="13" t="n"/>
-      <c r="H107" s="11" t="n"/>
+      <c r="H107" s="16" t="n"/>
       <c r="I107" s="12" t="n"/>
       <c r="J107" s="13" t="n"/>
-      <c r="K107" s="11" t="n"/>
+      <c r="K107" s="16" t="n"/>
       <c r="L107" s="12" t="n"/>
       <c r="M107" s="13" t="n"/>
-      <c r="N107" s="11" t="n"/>
+      <c r="N107" s="16" t="n"/>
       <c r="O107" s="12" t="n"/>
       <c r="P107" s="13" t="n"/>
-      <c r="Q107" s="11" t="n"/>
+      <c r="Q107" s="16" t="n"/>
       <c r="R107" s="12" t="n"/>
       <c r="S107" s="13" t="n"/>
-      <c r="T107" s="11" t="n"/>
+      <c r="T107" s="16" t="n"/>
       <c r="U107" s="12" t="n"/>
       <c r="V107" s="13" t="n"/>
     </row>
@@ -4145,25 +4044,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B108" s="11" t="n"/>
+      <c r="B108" s="16" t="n"/>
       <c r="C108" s="12" t="n"/>
       <c r="D108" s="13" t="n"/>
-      <c r="E108" s="11" t="n"/>
+      <c r="E108" s="16" t="n"/>
       <c r="F108" s="12" t="n"/>
       <c r="G108" s="13" t="n"/>
-      <c r="H108" s="11" t="n"/>
+      <c r="H108" s="16" t="n"/>
       <c r="I108" s="12" t="n"/>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="11" t="n"/>
+      <c r="K108" s="16" t="n"/>
       <c r="L108" s="12" t="n"/>
       <c r="M108" s="13" t="n"/>
-      <c r="N108" s="11" t="n"/>
+      <c r="N108" s="16" t="n"/>
       <c r="O108" s="12" t="n"/>
       <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="11" t="n"/>
+      <c r="Q108" s="16" t="n"/>
       <c r="R108" s="12" t="n"/>
       <c r="S108" s="13" t="n"/>
-      <c r="T108" s="11" t="n"/>
+      <c r="T108" s="16" t="n"/>
       <c r="U108" s="12" t="n"/>
       <c r="V108" s="13" t="n"/>
     </row>
@@ -4173,55 +4072,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B109" s="11" t="n"/>
+      <c r="B109" s="16" t="n"/>
       <c r="C109" s="12" t="n"/>
       <c r="D109" s="13" t="n"/>
-      <c r="E109" s="11" t="n"/>
+      <c r="E109" s="16" t="n"/>
       <c r="F109" s="12" t="n"/>
       <c r="G109" s="13" t="n"/>
-      <c r="H109" s="11" t="n"/>
+      <c r="H109" s="16" t="n"/>
       <c r="I109" s="12" t="n"/>
       <c r="J109" s="13" t="n"/>
-      <c r="K109" s="11" t="n"/>
+      <c r="K109" s="16" t="n"/>
       <c r="L109" s="12" t="n"/>
       <c r="M109" s="13" t="n"/>
-      <c r="N109" s="11" t="n"/>
+      <c r="N109" s="16" t="n"/>
       <c r="O109" s="12" t="n"/>
       <c r="P109" s="13" t="n"/>
-      <c r="Q109" s="11" t="n"/>
+      <c r="Q109" s="16" t="n"/>
       <c r="R109" s="12" t="n"/>
       <c r="S109" s="13" t="n"/>
-      <c r="T109" s="11" t="n"/>
+      <c r="T109" s="16" t="n"/>
       <c r="U109" s="12" t="n"/>
       <c r="V109" s="13" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="14" t="inlineStr">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B110" s="15" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="17" t="n"/>
-      <c r="E110" s="15" t="n"/>
-      <c r="F110" s="16" t="n"/>
-      <c r="G110" s="17" t="n"/>
-      <c r="H110" s="15" t="n"/>
-      <c r="I110" s="16" t="n"/>
-      <c r="J110" s="17" t="n"/>
-      <c r="K110" s="15" t="n"/>
-      <c r="L110" s="16" t="n"/>
-      <c r="M110" s="17" t="n"/>
-      <c r="N110" s="15" t="n"/>
-      <c r="O110" s="16" t="n"/>
-      <c r="P110" s="17" t="n"/>
-      <c r="Q110" s="15" t="n"/>
-      <c r="R110" s="16" t="n"/>
-      <c r="S110" s="17" t="n"/>
-      <c r="T110" s="15" t="n"/>
-      <c r="U110" s="16" t="n"/>
-      <c r="V110" s="17" t="n"/>
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="19" t="n"/>
+      <c r="D110" s="20" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="19" t="n"/>
+      <c r="G110" s="20" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="19" t="n"/>
+      <c r="J110" s="20" t="n"/>
+      <c r="K110" s="18" t="n"/>
+      <c r="L110" s="19" t="n"/>
+      <c r="M110" s="20" t="n"/>
+      <c r="N110" s="18" t="n"/>
+      <c r="O110" s="19" t="n"/>
+      <c r="P110" s="20" t="n"/>
+      <c r="Q110" s="18" t="n"/>
+      <c r="R110" s="19" t="n"/>
+      <c r="S110" s="20" t="n"/>
+      <c r="T110" s="18" t="n"/>
+      <c r="U110" s="19" t="n"/>
+      <c r="V110" s="20" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -4229,50 +4128,50 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B111" s="7" t="n"/>
-      <c r="C111" s="28" t="inlineStr">
+      <c r="B111" s="21" t="n"/>
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="28" t="inlineStr">
+      <c r="E111" s="21" t="n"/>
+      <c r="F111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="G111" s="9" t="n"/>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="28" t="inlineStr">
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="J111" s="9" t="n"/>
-      <c r="K111" s="7" t="n"/>
-      <c r="L111" s="28" t="inlineStr">
+      <c r="K111" s="21" t="n"/>
+      <c r="L111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="M111" s="9" t="n"/>
-      <c r="N111" s="7" t="n"/>
-      <c r="O111" s="28" t="inlineStr">
+      <c r="N111" s="21" t="n"/>
+      <c r="O111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="7" t="n"/>
-      <c r="R111" s="28" t="inlineStr">
+      <c r="Q111" s="21" t="n"/>
+      <c r="R111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="S111" s="9" t="n"/>
-      <c r="T111" s="7" t="n"/>
-      <c r="U111" s="28" t="inlineStr">
+      <c r="T111" s="21" t="n"/>
+      <c r="U111" s="22" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
@@ -4285,26 +4184,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B112" s="11" t="n"/>
-      <c r="C112" s="29" t="n"/>
+      <c r="B112" s="16" t="n"/>
+      <c r="C112" s="23" t="n"/>
       <c r="D112" s="13" t="n"/>
-      <c r="E112" s="11" t="n"/>
-      <c r="F112" s="29" t="n"/>
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="23" t="n"/>
       <c r="G112" s="13" t="n"/>
-      <c r="H112" s="11" t="n"/>
-      <c r="I112" s="29" t="n"/>
+      <c r="H112" s="16" t="n"/>
+      <c r="I112" s="23" t="n"/>
       <c r="J112" s="13" t="n"/>
-      <c r="K112" s="11" t="n"/>
-      <c r="L112" s="29" t="n"/>
+      <c r="K112" s="16" t="n"/>
+      <c r="L112" s="23" t="n"/>
       <c r="M112" s="13" t="n"/>
-      <c r="N112" s="11" t="n"/>
-      <c r="O112" s="29" t="n"/>
+      <c r="N112" s="16" t="n"/>
+      <c r="O112" s="23" t="n"/>
       <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="11" t="n"/>
-      <c r="R112" s="29" t="n"/>
+      <c r="Q112" s="16" t="n"/>
+      <c r="R112" s="23" t="n"/>
       <c r="S112" s="13" t="n"/>
-      <c r="T112" s="11" t="n"/>
-      <c r="U112" s="29" t="n"/>
+      <c r="T112" s="16" t="n"/>
+      <c r="U112" s="23" t="n"/>
       <c r="V112" s="13" t="n"/>
     </row>
     <row r="113">
@@ -4313,26 +4212,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B113" s="11" t="n"/>
-      <c r="C113" s="29" t="n"/>
+      <c r="B113" s="16" t="n"/>
+      <c r="C113" s="23" t="n"/>
       <c r="D113" s="13" t="n"/>
-      <c r="E113" s="11" t="n"/>
-      <c r="F113" s="29" t="n"/>
+      <c r="E113" s="16" t="n"/>
+      <c r="F113" s="23" t="n"/>
       <c r="G113" s="13" t="n"/>
-      <c r="H113" s="11" t="n"/>
-      <c r="I113" s="29" t="n"/>
+      <c r="H113" s="16" t="n"/>
+      <c r="I113" s="23" t="n"/>
       <c r="J113" s="13" t="n"/>
-      <c r="K113" s="11" t="n"/>
-      <c r="L113" s="29" t="n"/>
+      <c r="K113" s="16" t="n"/>
+      <c r="L113" s="23" t="n"/>
       <c r="M113" s="13" t="n"/>
-      <c r="N113" s="11" t="n"/>
-      <c r="O113" s="29" t="n"/>
+      <c r="N113" s="16" t="n"/>
+      <c r="O113" s="23" t="n"/>
       <c r="P113" s="13" t="n"/>
-      <c r="Q113" s="11" t="n"/>
-      <c r="R113" s="29" t="n"/>
+      <c r="Q113" s="16" t="n"/>
+      <c r="R113" s="23" t="n"/>
       <c r="S113" s="13" t="n"/>
-      <c r="T113" s="11" t="n"/>
-      <c r="U113" s="29" t="n"/>
+      <c r="T113" s="16" t="n"/>
+      <c r="U113" s="23" t="n"/>
       <c r="V113" s="13" t="n"/>
     </row>
     <row r="114">
@@ -4341,26 +4240,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B114" s="11" t="n"/>
-      <c r="C114" s="29" t="n"/>
+      <c r="B114" s="16" t="n"/>
+      <c r="C114" s="23" t="n"/>
       <c r="D114" s="13" t="n"/>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="29" t="n"/>
+      <c r="E114" s="16" t="n"/>
+      <c r="F114" s="23" t="n"/>
       <c r="G114" s="13" t="n"/>
-      <c r="H114" s="11" t="n"/>
-      <c r="I114" s="29" t="n"/>
+      <c r="H114" s="16" t="n"/>
+      <c r="I114" s="23" t="n"/>
       <c r="J114" s="13" t="n"/>
-      <c r="K114" s="11" t="n"/>
-      <c r="L114" s="29" t="n"/>
+      <c r="K114" s="16" t="n"/>
+      <c r="L114" s="23" t="n"/>
       <c r="M114" s="13" t="n"/>
-      <c r="N114" s="11" t="n"/>
-      <c r="O114" s="29" t="n"/>
+      <c r="N114" s="16" t="n"/>
+      <c r="O114" s="23" t="n"/>
       <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="11" t="n"/>
-      <c r="R114" s="29" t="n"/>
+      <c r="Q114" s="16" t="n"/>
+      <c r="R114" s="23" t="n"/>
       <c r="S114" s="13" t="n"/>
-      <c r="T114" s="11" t="n"/>
-      <c r="U114" s="29" t="n"/>
+      <c r="T114" s="16" t="n"/>
+      <c r="U114" s="23" t="n"/>
       <c r="V114" s="13" t="n"/>
     </row>
     <row r="115">
@@ -4369,26 +4268,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B115" s="11" t="n"/>
-      <c r="C115" s="30" t="n"/>
+      <c r="B115" s="16" t="n"/>
+      <c r="C115" s="24" t="n"/>
       <c r="D115" s="13" t="n"/>
-      <c r="E115" s="11" t="n"/>
-      <c r="F115" s="30" t="n"/>
+      <c r="E115" s="16" t="n"/>
+      <c r="F115" s="24" t="n"/>
       <c r="G115" s="13" t="n"/>
-      <c r="H115" s="11" t="n"/>
-      <c r="I115" s="30" t="n"/>
+      <c r="H115" s="16" t="n"/>
+      <c r="I115" s="24" t="n"/>
       <c r="J115" s="13" t="n"/>
-      <c r="K115" s="11" t="n"/>
-      <c r="L115" s="30" t="n"/>
+      <c r="K115" s="16" t="n"/>
+      <c r="L115" s="24" t="n"/>
       <c r="M115" s="13" t="n"/>
-      <c r="N115" s="11" t="n"/>
-      <c r="O115" s="30" t="n"/>
+      <c r="N115" s="16" t="n"/>
+      <c r="O115" s="24" t="n"/>
       <c r="P115" s="13" t="n"/>
-      <c r="Q115" s="11" t="n"/>
-      <c r="R115" s="30" t="n"/>
+      <c r="Q115" s="16" t="n"/>
+      <c r="R115" s="24" t="n"/>
       <c r="S115" s="13" t="n"/>
-      <c r="T115" s="11" t="n"/>
-      <c r="U115" s="30" t="n"/>
+      <c r="T115" s="16" t="n"/>
+      <c r="U115" s="24" t="n"/>
       <c r="V115" s="13" t="n"/>
     </row>
     <row r="116">
@@ -4397,25 +4296,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B116" s="11" t="n"/>
+      <c r="B116" s="16" t="n"/>
       <c r="C116" s="12" t="n"/>
       <c r="D116" s="13" t="n"/>
-      <c r="E116" s="11" t="n"/>
+      <c r="E116" s="16" t="n"/>
       <c r="F116" s="12" t="n"/>
       <c r="G116" s="13" t="n"/>
-      <c r="H116" s="11" t="n"/>
+      <c r="H116" s="16" t="n"/>
       <c r="I116" s="12" t="n"/>
       <c r="J116" s="13" t="n"/>
-      <c r="K116" s="11" t="n"/>
+      <c r="K116" s="16" t="n"/>
       <c r="L116" s="12" t="n"/>
       <c r="M116" s="13" t="n"/>
-      <c r="N116" s="11" t="n"/>
+      <c r="N116" s="16" t="n"/>
       <c r="O116" s="12" t="n"/>
       <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="11" t="n"/>
+      <c r="Q116" s="16" t="n"/>
       <c r="R116" s="12" t="n"/>
       <c r="S116" s="13" t="n"/>
-      <c r="T116" s="11" t="n"/>
+      <c r="T116" s="16" t="n"/>
       <c r="U116" s="12" t="n"/>
       <c r="V116" s="13" t="n"/>
     </row>
@@ -4425,50 +4324,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="35" t="inlineStr">
+      <c r="B117" s="16" t="n"/>
+      <c r="C117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="D117" s="13" t="n"/>
-      <c r="E117" s="11" t="n"/>
-      <c r="F117" s="35" t="inlineStr">
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="G117" s="13" t="n"/>
-      <c r="H117" s="11" t="n"/>
-      <c r="I117" s="35" t="inlineStr">
+      <c r="H117" s="16" t="n"/>
+      <c r="I117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="J117" s="13" t="n"/>
-      <c r="K117" s="11" t="n"/>
-      <c r="L117" s="35" t="inlineStr">
+      <c r="K117" s="16" t="n"/>
+      <c r="L117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="M117" s="13" t="n"/>
-      <c r="N117" s="11" t="n"/>
-      <c r="O117" s="35" t="inlineStr">
+      <c r="N117" s="16" t="n"/>
+      <c r="O117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="P117" s="13" t="n"/>
-      <c r="Q117" s="11" t="n"/>
-      <c r="R117" s="35" t="inlineStr">
+      <c r="Q117" s="16" t="n"/>
+      <c r="R117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="S117" s="13" t="n"/>
-      <c r="T117" s="11" t="n"/>
-      <c r="U117" s="35" t="inlineStr">
+      <c r="T117" s="16" t="n"/>
+      <c r="U117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
@@ -4481,26 +4380,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B118" s="11" t="n"/>
-      <c r="C118" s="29" t="n"/>
+      <c r="B118" s="16" t="n"/>
+      <c r="C118" s="23" t="n"/>
       <c r="D118" s="13" t="n"/>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="29" t="n"/>
+      <c r="E118" s="16" t="n"/>
+      <c r="F118" s="23" t="n"/>
       <c r="G118" s="13" t="n"/>
-      <c r="H118" s="11" t="n"/>
-      <c r="I118" s="29" t="n"/>
+      <c r="H118" s="16" t="n"/>
+      <c r="I118" s="23" t="n"/>
       <c r="J118" s="13" t="n"/>
-      <c r="K118" s="11" t="n"/>
-      <c r="L118" s="29" t="n"/>
+      <c r="K118" s="16" t="n"/>
+      <c r="L118" s="23" t="n"/>
       <c r="M118" s="13" t="n"/>
-      <c r="N118" s="11" t="n"/>
-      <c r="O118" s="29" t="n"/>
+      <c r="N118" s="16" t="n"/>
+      <c r="O118" s="23" t="n"/>
       <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="11" t="n"/>
-      <c r="R118" s="29" t="n"/>
+      <c r="Q118" s="16" t="n"/>
+      <c r="R118" s="23" t="n"/>
       <c r="S118" s="13" t="n"/>
-      <c r="T118" s="11" t="n"/>
-      <c r="U118" s="29" t="n"/>
+      <c r="T118" s="16" t="n"/>
+      <c r="U118" s="23" t="n"/>
       <c r="V118" s="13" t="n"/>
     </row>
     <row r="119">
@@ -4509,26 +4408,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B119" s="11" t="n"/>
-      <c r="C119" s="29" t="n"/>
+      <c r="B119" s="16" t="n"/>
+      <c r="C119" s="23" t="n"/>
       <c r="D119" s="13" t="n"/>
-      <c r="E119" s="11" t="n"/>
-      <c r="F119" s="29" t="n"/>
+      <c r="E119" s="16" t="n"/>
+      <c r="F119" s="23" t="n"/>
       <c r="G119" s="13" t="n"/>
-      <c r="H119" s="11" t="n"/>
-      <c r="I119" s="29" t="n"/>
+      <c r="H119" s="16" t="n"/>
+      <c r="I119" s="23" t="n"/>
       <c r="J119" s="13" t="n"/>
-      <c r="K119" s="11" t="n"/>
-      <c r="L119" s="29" t="n"/>
+      <c r="K119" s="16" t="n"/>
+      <c r="L119" s="23" t="n"/>
       <c r="M119" s="13" t="n"/>
-      <c r="N119" s="11" t="n"/>
-      <c r="O119" s="29" t="n"/>
+      <c r="N119" s="16" t="n"/>
+      <c r="O119" s="23" t="n"/>
       <c r="P119" s="13" t="n"/>
-      <c r="Q119" s="11" t="n"/>
-      <c r="R119" s="29" t="n"/>
+      <c r="Q119" s="16" t="n"/>
+      <c r="R119" s="23" t="n"/>
       <c r="S119" s="13" t="n"/>
-      <c r="T119" s="11" t="n"/>
-      <c r="U119" s="29" t="n"/>
+      <c r="T119" s="16" t="n"/>
+      <c r="U119" s="23" t="n"/>
       <c r="V119" s="13" t="n"/>
     </row>
     <row r="120">
@@ -4537,26 +4436,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B120" s="11" t="n"/>
-      <c r="C120" s="29" t="n"/>
+      <c r="B120" s="16" t="n"/>
+      <c r="C120" s="23" t="n"/>
       <c r="D120" s="13" t="n"/>
-      <c r="E120" s="11" t="n"/>
-      <c r="F120" s="29" t="n"/>
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="23" t="n"/>
       <c r="G120" s="13" t="n"/>
-      <c r="H120" s="11" t="n"/>
-      <c r="I120" s="29" t="n"/>
+      <c r="H120" s="16" t="n"/>
+      <c r="I120" s="23" t="n"/>
       <c r="J120" s="13" t="n"/>
-      <c r="K120" s="11" t="n"/>
-      <c r="L120" s="29" t="n"/>
+      <c r="K120" s="16" t="n"/>
+      <c r="L120" s="23" t="n"/>
       <c r="M120" s="13" t="n"/>
-      <c r="N120" s="11" t="n"/>
-      <c r="O120" s="29" t="n"/>
+      <c r="N120" s="16" t="n"/>
+      <c r="O120" s="23" t="n"/>
       <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="11" t="n"/>
-      <c r="R120" s="29" t="n"/>
+      <c r="Q120" s="16" t="n"/>
+      <c r="R120" s="23" t="n"/>
       <c r="S120" s="13" t="n"/>
-      <c r="T120" s="11" t="n"/>
-      <c r="U120" s="29" t="n"/>
+      <c r="T120" s="16" t="n"/>
+      <c r="U120" s="23" t="n"/>
       <c r="V120" s="13" t="n"/>
     </row>
     <row r="121">
@@ -4565,55 +4464,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B121" s="11" t="n"/>
-      <c r="C121" s="30" t="n"/>
+      <c r="B121" s="16" t="n"/>
+      <c r="C121" s="24" t="n"/>
       <c r="D121" s="13" t="n"/>
-      <c r="E121" s="11" t="n"/>
-      <c r="F121" s="30" t="n"/>
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="24" t="n"/>
       <c r="G121" s="13" t="n"/>
-      <c r="H121" s="11" t="n"/>
-      <c r="I121" s="30" t="n"/>
+      <c r="H121" s="16" t="n"/>
+      <c r="I121" s="24" t="n"/>
       <c r="J121" s="13" t="n"/>
-      <c r="K121" s="11" t="n"/>
-      <c r="L121" s="30" t="n"/>
+      <c r="K121" s="16" t="n"/>
+      <c r="L121" s="24" t="n"/>
       <c r="M121" s="13" t="n"/>
-      <c r="N121" s="11" t="n"/>
-      <c r="O121" s="30" t="n"/>
+      <c r="N121" s="16" t="n"/>
+      <c r="O121" s="24" t="n"/>
       <c r="P121" s="13" t="n"/>
-      <c r="Q121" s="11" t="n"/>
-      <c r="R121" s="30" t="n"/>
+      <c r="Q121" s="16" t="n"/>
+      <c r="R121" s="24" t="n"/>
       <c r="S121" s="13" t="n"/>
-      <c r="T121" s="11" t="n"/>
-      <c r="U121" s="30" t="n"/>
+      <c r="T121" s="16" t="n"/>
+      <c r="U121" s="24" t="n"/>
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="14" t="inlineStr">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B122" s="15" t="n"/>
-      <c r="C122" s="16" t="n"/>
-      <c r="D122" s="17" t="n"/>
-      <c r="E122" s="15" t="n"/>
-      <c r="F122" s="16" t="n"/>
-      <c r="G122" s="17" t="n"/>
-      <c r="H122" s="15" t="n"/>
-      <c r="I122" s="16" t="n"/>
-      <c r="J122" s="17" t="n"/>
-      <c r="K122" s="15" t="n"/>
-      <c r="L122" s="16" t="n"/>
-      <c r="M122" s="17" t="n"/>
-      <c r="N122" s="15" t="n"/>
-      <c r="O122" s="16" t="n"/>
-      <c r="P122" s="17" t="n"/>
-      <c r="Q122" s="15" t="n"/>
-      <c r="R122" s="16" t="n"/>
-      <c r="S122" s="17" t="n"/>
-      <c r="T122" s="15" t="n"/>
-      <c r="U122" s="16" t="n"/>
-      <c r="V122" s="17" t="n"/>
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="19" t="n"/>
+      <c r="D122" s="20" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="19" t="n"/>
+      <c r="G122" s="20" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="19" t="n"/>
+      <c r="J122" s="20" t="n"/>
+      <c r="K122" s="18" t="n"/>
+      <c r="L122" s="19" t="n"/>
+      <c r="M122" s="20" t="n"/>
+      <c r="N122" s="18" t="n"/>
+      <c r="O122" s="19" t="n"/>
+      <c r="P122" s="20" t="n"/>
+      <c r="Q122" s="18" t="n"/>
+      <c r="R122" s="19" t="n"/>
+      <c r="S122" s="20" t="n"/>
+      <c r="T122" s="18" t="n"/>
+      <c r="U122" s="19" t="n"/>
+      <c r="V122" s="20" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -4621,25 +4520,25 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B123" s="7" t="n"/>
+      <c r="B123" s="21" t="n"/>
       <c r="C123" s="8" t="n"/>
       <c r="D123" s="9" t="n"/>
-      <c r="E123" s="7" t="n"/>
+      <c r="E123" s="21" t="n"/>
       <c r="F123" s="8" t="n"/>
       <c r="G123" s="9" t="n"/>
-      <c r="H123" s="7" t="n"/>
+      <c r="H123" s="21" t="n"/>
       <c r="I123" s="8" t="n"/>
       <c r="J123" s="9" t="n"/>
-      <c r="K123" s="7" t="n"/>
+      <c r="K123" s="21" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="9" t="n"/>
-      <c r="N123" s="7" t="n"/>
+      <c r="N123" s="21" t="n"/>
       <c r="O123" s="8" t="n"/>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="7" t="n"/>
+      <c r="Q123" s="21" t="n"/>
       <c r="R123" s="8" t="n"/>
       <c r="S123" s="9" t="n"/>
-      <c r="T123" s="7" t="n"/>
+      <c r="T123" s="21" t="n"/>
       <c r="U123" s="8" t="n"/>
       <c r="V123" s="9" t="n"/>
     </row>
@@ -4649,25 +4548,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B124" s="11" t="n"/>
+      <c r="B124" s="16" t="n"/>
       <c r="C124" s="12" t="n"/>
       <c r="D124" s="13" t="n"/>
-      <c r="E124" s="11" t="n"/>
+      <c r="E124" s="16" t="n"/>
       <c r="F124" s="12" t="n"/>
       <c r="G124" s="13" t="n"/>
-      <c r="H124" s="11" t="n"/>
+      <c r="H124" s="16" t="n"/>
       <c r="I124" s="12" t="n"/>
       <c r="J124" s="13" t="n"/>
-      <c r="K124" s="11" t="n"/>
+      <c r="K124" s="16" t="n"/>
       <c r="L124" s="12" t="n"/>
       <c r="M124" s="13" t="n"/>
-      <c r="N124" s="11" t="n"/>
+      <c r="N124" s="16" t="n"/>
       <c r="O124" s="12" t="n"/>
       <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="11" t="n"/>
+      <c r="Q124" s="16" t="n"/>
       <c r="R124" s="12" t="n"/>
       <c r="S124" s="13" t="n"/>
-      <c r="T124" s="11" t="n"/>
+      <c r="T124" s="16" t="n"/>
       <c r="U124" s="12" t="n"/>
       <c r="V124" s="13" t="n"/>
     </row>
@@ -4677,25 +4576,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B125" s="11" t="n"/>
+      <c r="B125" s="16" t="n"/>
       <c r="C125" s="12" t="n"/>
       <c r="D125" s="13" t="n"/>
-      <c r="E125" s="11" t="n"/>
+      <c r="E125" s="16" t="n"/>
       <c r="F125" s="12" t="n"/>
       <c r="G125" s="13" t="n"/>
-      <c r="H125" s="11" t="n"/>
+      <c r="H125" s="16" t="n"/>
       <c r="I125" s="12" t="n"/>
       <c r="J125" s="13" t="n"/>
-      <c r="K125" s="11" t="n"/>
+      <c r="K125" s="16" t="n"/>
       <c r="L125" s="12" t="n"/>
       <c r="M125" s="13" t="n"/>
-      <c r="N125" s="11" t="n"/>
+      <c r="N125" s="16" t="n"/>
       <c r="O125" s="12" t="n"/>
       <c r="P125" s="13" t="n"/>
-      <c r="Q125" s="11" t="n"/>
+      <c r="Q125" s="16" t="n"/>
       <c r="R125" s="12" t="n"/>
       <c r="S125" s="13" t="n"/>
-      <c r="T125" s="11" t="n"/>
+      <c r="T125" s="16" t="n"/>
       <c r="U125" s="12" t="n"/>
       <c r="V125" s="13" t="n"/>
     </row>
@@ -4705,25 +4604,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B126" s="11" t="n"/>
+      <c r="B126" s="16" t="n"/>
       <c r="C126" s="12" t="n"/>
       <c r="D126" s="13" t="n"/>
-      <c r="E126" s="11" t="n"/>
+      <c r="E126" s="16" t="n"/>
       <c r="F126" s="12" t="n"/>
       <c r="G126" s="13" t="n"/>
-      <c r="H126" s="11" t="n"/>
+      <c r="H126" s="16" t="n"/>
       <c r="I126" s="12" t="n"/>
       <c r="J126" s="13" t="n"/>
-      <c r="K126" s="11" t="n"/>
+      <c r="K126" s="16" t="n"/>
       <c r="L126" s="12" t="n"/>
       <c r="M126" s="13" t="n"/>
-      <c r="N126" s="11" t="n"/>
+      <c r="N126" s="16" t="n"/>
       <c r="O126" s="12" t="n"/>
       <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="11" t="n"/>
+      <c r="Q126" s="16" t="n"/>
       <c r="R126" s="12" t="n"/>
       <c r="S126" s="13" t="n"/>
-      <c r="T126" s="11" t="n"/>
+      <c r="T126" s="16" t="n"/>
       <c r="U126" s="12" t="n"/>
       <c r="V126" s="13" t="n"/>
     </row>
@@ -4733,25 +4632,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B127" s="11" t="n"/>
+      <c r="B127" s="16" t="n"/>
       <c r="C127" s="12" t="n"/>
       <c r="D127" s="13" t="n"/>
-      <c r="E127" s="11" t="n"/>
+      <c r="E127" s="16" t="n"/>
       <c r="F127" s="12" t="n"/>
       <c r="G127" s="13" t="n"/>
-      <c r="H127" s="11" t="n"/>
+      <c r="H127" s="16" t="n"/>
       <c r="I127" s="12" t="n"/>
       <c r="J127" s="13" t="n"/>
-      <c r="K127" s="11" t="n"/>
+      <c r="K127" s="16" t="n"/>
       <c r="L127" s="12" t="n"/>
       <c r="M127" s="13" t="n"/>
-      <c r="N127" s="11" t="n"/>
+      <c r="N127" s="16" t="n"/>
       <c r="O127" s="12" t="n"/>
       <c r="P127" s="13" t="n"/>
-      <c r="Q127" s="11" t="n"/>
+      <c r="Q127" s="16" t="n"/>
       <c r="R127" s="12" t="n"/>
       <c r="S127" s="13" t="n"/>
-      <c r="T127" s="11" t="n"/>
+      <c r="T127" s="16" t="n"/>
       <c r="U127" s="12" t="n"/>
       <c r="V127" s="13" t="n"/>
     </row>
@@ -4761,25 +4660,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B128" s="11" t="n"/>
+      <c r="B128" s="16" t="n"/>
       <c r="C128" s="12" t="n"/>
       <c r="D128" s="13" t="n"/>
-      <c r="E128" s="11" t="n"/>
+      <c r="E128" s="16" t="n"/>
       <c r="F128" s="12" t="n"/>
       <c r="G128" s="13" t="n"/>
-      <c r="H128" s="11" t="n"/>
+      <c r="H128" s="16" t="n"/>
       <c r="I128" s="12" t="n"/>
       <c r="J128" s="13" t="n"/>
-      <c r="K128" s="11" t="n"/>
+      <c r="K128" s="16" t="n"/>
       <c r="L128" s="12" t="n"/>
       <c r="M128" s="13" t="n"/>
-      <c r="N128" s="11" t="n"/>
+      <c r="N128" s="16" t="n"/>
       <c r="O128" s="12" t="n"/>
       <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="11" t="n"/>
+      <c r="Q128" s="16" t="n"/>
       <c r="R128" s="12" t="n"/>
       <c r="S128" s="13" t="n"/>
-      <c r="T128" s="11" t="n"/>
+      <c r="T128" s="16" t="n"/>
       <c r="U128" s="12" t="n"/>
       <c r="V128" s="13" t="n"/>
     </row>
@@ -4789,25 +4688,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B129" s="11" t="n"/>
+      <c r="B129" s="16" t="n"/>
       <c r="C129" s="12" t="n"/>
       <c r="D129" s="13" t="n"/>
-      <c r="E129" s="11" t="n"/>
+      <c r="E129" s="16" t="n"/>
       <c r="F129" s="12" t="n"/>
       <c r="G129" s="13" t="n"/>
-      <c r="H129" s="11" t="n"/>
+      <c r="H129" s="16" t="n"/>
       <c r="I129" s="12" t="n"/>
       <c r="J129" s="13" t="n"/>
-      <c r="K129" s="11" t="n"/>
+      <c r="K129" s="16" t="n"/>
       <c r="L129" s="12" t="n"/>
       <c r="M129" s="13" t="n"/>
-      <c r="N129" s="11" t="n"/>
+      <c r="N129" s="16" t="n"/>
       <c r="O129" s="12" t="n"/>
       <c r="P129" s="13" t="n"/>
-      <c r="Q129" s="11" t="n"/>
+      <c r="Q129" s="16" t="n"/>
       <c r="R129" s="12" t="n"/>
       <c r="S129" s="13" t="n"/>
-      <c r="T129" s="11" t="n"/>
+      <c r="T129" s="16" t="n"/>
       <c r="U129" s="12" t="n"/>
       <c r="V129" s="13" t="n"/>
     </row>
@@ -4817,25 +4716,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B130" s="11" t="n"/>
+      <c r="B130" s="16" t="n"/>
       <c r="C130" s="12" t="n"/>
       <c r="D130" s="13" t="n"/>
-      <c r="E130" s="11" t="n"/>
+      <c r="E130" s="16" t="n"/>
       <c r="F130" s="12" t="n"/>
       <c r="G130" s="13" t="n"/>
-      <c r="H130" s="11" t="n"/>
+      <c r="H130" s="16" t="n"/>
       <c r="I130" s="12" t="n"/>
       <c r="J130" s="13" t="n"/>
-      <c r="K130" s="11" t="n"/>
+      <c r="K130" s="16" t="n"/>
       <c r="L130" s="12" t="n"/>
       <c r="M130" s="13" t="n"/>
-      <c r="N130" s="11" t="n"/>
+      <c r="N130" s="16" t="n"/>
       <c r="O130" s="12" t="n"/>
       <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="11" t="n"/>
+      <c r="Q130" s="16" t="n"/>
       <c r="R130" s="12" t="n"/>
       <c r="S130" s="13" t="n"/>
-      <c r="T130" s="11" t="n"/>
+      <c r="T130" s="16" t="n"/>
       <c r="U130" s="12" t="n"/>
       <c r="V130" s="13" t="n"/>
     </row>
@@ -4845,25 +4744,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B131" s="11" t="n"/>
+      <c r="B131" s="16" t="n"/>
       <c r="C131" s="12" t="n"/>
       <c r="D131" s="13" t="n"/>
-      <c r="E131" s="11" t="n"/>
+      <c r="E131" s="16" t="n"/>
       <c r="F131" s="12" t="n"/>
       <c r="G131" s="13" t="n"/>
-      <c r="H131" s="11" t="n"/>
+      <c r="H131" s="16" t="n"/>
       <c r="I131" s="12" t="n"/>
       <c r="J131" s="13" t="n"/>
-      <c r="K131" s="11" t="n"/>
+      <c r="K131" s="16" t="n"/>
       <c r="L131" s="12" t="n"/>
       <c r="M131" s="13" t="n"/>
-      <c r="N131" s="11" t="n"/>
+      <c r="N131" s="16" t="n"/>
       <c r="O131" s="12" t="n"/>
       <c r="P131" s="13" t="n"/>
-      <c r="Q131" s="11" t="n"/>
+      <c r="Q131" s="16" t="n"/>
       <c r="R131" s="12" t="n"/>
       <c r="S131" s="13" t="n"/>
-      <c r="T131" s="11" t="n"/>
+      <c r="T131" s="16" t="n"/>
       <c r="U131" s="12" t="n"/>
       <c r="V131" s="13" t="n"/>
     </row>
@@ -4873,25 +4772,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B132" s="11" t="n"/>
+      <c r="B132" s="16" t="n"/>
       <c r="C132" s="12" t="n"/>
       <c r="D132" s="13" t="n"/>
-      <c r="E132" s="11" t="n"/>
+      <c r="E132" s="16" t="n"/>
       <c r="F132" s="12" t="n"/>
       <c r="G132" s="13" t="n"/>
-      <c r="H132" s="11" t="n"/>
+      <c r="H132" s="16" t="n"/>
       <c r="I132" s="12" t="n"/>
       <c r="J132" s="13" t="n"/>
-      <c r="K132" s="11" t="n"/>
+      <c r="K132" s="16" t="n"/>
       <c r="L132" s="12" t="n"/>
       <c r="M132" s="13" t="n"/>
-      <c r="N132" s="11" t="n"/>
+      <c r="N132" s="16" t="n"/>
       <c r="O132" s="12" t="n"/>
       <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="11" t="n"/>
+      <c r="Q132" s="16" t="n"/>
       <c r="R132" s="12" t="n"/>
       <c r="S132" s="13" t="n"/>
-      <c r="T132" s="11" t="n"/>
+      <c r="T132" s="16" t="n"/>
       <c r="U132" s="12" t="n"/>
       <c r="V132" s="13" t="n"/>
     </row>
@@ -4901,55 +4800,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B133" s="11" t="n"/>
+      <c r="B133" s="16" t="n"/>
       <c r="C133" s="12" t="n"/>
       <c r="D133" s="13" t="n"/>
-      <c r="E133" s="11" t="n"/>
+      <c r="E133" s="16" t="n"/>
       <c r="F133" s="12" t="n"/>
       <c r="G133" s="13" t="n"/>
-      <c r="H133" s="11" t="n"/>
+      <c r="H133" s="16" t="n"/>
       <c r="I133" s="12" t="n"/>
       <c r="J133" s="13" t="n"/>
-      <c r="K133" s="11" t="n"/>
+      <c r="K133" s="16" t="n"/>
       <c r="L133" s="12" t="n"/>
       <c r="M133" s="13" t="n"/>
-      <c r="N133" s="11" t="n"/>
+      <c r="N133" s="16" t="n"/>
       <c r="O133" s="12" t="n"/>
       <c r="P133" s="13" t="n"/>
-      <c r="Q133" s="11" t="n"/>
+      <c r="Q133" s="16" t="n"/>
       <c r="R133" s="12" t="n"/>
       <c r="S133" s="13" t="n"/>
-      <c r="T133" s="11" t="n"/>
+      <c r="T133" s="16" t="n"/>
       <c r="U133" s="12" t="n"/>
       <c r="V133" s="13" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="14" t="inlineStr">
+      <c r="A134" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B134" s="15" t="n"/>
-      <c r="C134" s="16" t="n"/>
-      <c r="D134" s="17" t="n"/>
-      <c r="E134" s="15" t="n"/>
-      <c r="F134" s="16" t="n"/>
-      <c r="G134" s="17" t="n"/>
-      <c r="H134" s="15" t="n"/>
-      <c r="I134" s="16" t="n"/>
-      <c r="J134" s="17" t="n"/>
-      <c r="K134" s="15" t="n"/>
-      <c r="L134" s="16" t="n"/>
-      <c r="M134" s="17" t="n"/>
-      <c r="N134" s="15" t="n"/>
-      <c r="O134" s="16" t="n"/>
-      <c r="P134" s="17" t="n"/>
-      <c r="Q134" s="15" t="n"/>
-      <c r="R134" s="16" t="n"/>
-      <c r="S134" s="17" t="n"/>
-      <c r="T134" s="15" t="n"/>
-      <c r="U134" s="16" t="n"/>
-      <c r="V134" s="17" t="n"/>
+      <c r="B134" s="18" t="n"/>
+      <c r="C134" s="19" t="n"/>
+      <c r="D134" s="20" t="n"/>
+      <c r="E134" s="18" t="n"/>
+      <c r="F134" s="19" t="n"/>
+      <c r="G134" s="20" t="n"/>
+      <c r="H134" s="18" t="n"/>
+      <c r="I134" s="19" t="n"/>
+      <c r="J134" s="20" t="n"/>
+      <c r="K134" s="18" t="n"/>
+      <c r="L134" s="19" t="n"/>
+      <c r="M134" s="20" t="n"/>
+      <c r="N134" s="18" t="n"/>
+      <c r="O134" s="19" t="n"/>
+      <c r="P134" s="20" t="n"/>
+      <c r="Q134" s="18" t="n"/>
+      <c r="R134" s="19" t="n"/>
+      <c r="S134" s="20" t="n"/>
+      <c r="T134" s="18" t="n"/>
+      <c r="U134" s="19" t="n"/>
+      <c r="V134" s="20" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -4957,25 +4856,25 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B135" s="7" t="n"/>
+      <c r="B135" s="21" t="n"/>
       <c r="C135" s="8" t="n"/>
       <c r="D135" s="9" t="n"/>
-      <c r="E135" s="7" t="n"/>
+      <c r="E135" s="21" t="n"/>
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="9" t="n"/>
-      <c r="H135" s="7" t="n"/>
+      <c r="H135" s="21" t="n"/>
       <c r="I135" s="8" t="n"/>
       <c r="J135" s="9" t="n"/>
-      <c r="K135" s="7" t="n"/>
+      <c r="K135" s="21" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="9" t="n"/>
-      <c r="N135" s="7" t="n"/>
+      <c r="N135" s="21" t="n"/>
       <c r="O135" s="8" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="7" t="n"/>
+      <c r="Q135" s="21" t="n"/>
       <c r="R135" s="8" t="n"/>
       <c r="S135" s="9" t="n"/>
-      <c r="T135" s="7" t="n"/>
+      <c r="T135" s="21" t="n"/>
       <c r="U135" s="8" t="n"/>
       <c r="V135" s="9" t="n"/>
     </row>
@@ -4985,25 +4884,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B136" s="11" t="n"/>
+      <c r="B136" s="16" t="n"/>
       <c r="C136" s="12" t="n"/>
       <c r="D136" s="13" t="n"/>
-      <c r="E136" s="11" t="n"/>
+      <c r="E136" s="16" t="n"/>
       <c r="F136" s="12" t="n"/>
       <c r="G136" s="13" t="n"/>
-      <c r="H136" s="11" t="n"/>
+      <c r="H136" s="16" t="n"/>
       <c r="I136" s="12" t="n"/>
       <c r="J136" s="13" t="n"/>
-      <c r="K136" s="11" t="n"/>
+      <c r="K136" s="16" t="n"/>
       <c r="L136" s="12" t="n"/>
       <c r="M136" s="13" t="n"/>
-      <c r="N136" s="11" t="n"/>
+      <c r="N136" s="16" t="n"/>
       <c r="O136" s="12" t="n"/>
       <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="11" t="n"/>
+      <c r="Q136" s="16" t="n"/>
       <c r="R136" s="12" t="n"/>
       <c r="S136" s="13" t="n"/>
-      <c r="T136" s="11" t="n"/>
+      <c r="T136" s="16" t="n"/>
       <c r="U136" s="12" t="n"/>
       <c r="V136" s="13" t="n"/>
     </row>
@@ -5013,25 +4912,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B137" s="11" t="n"/>
+      <c r="B137" s="16" t="n"/>
       <c r="C137" s="12" t="n"/>
       <c r="D137" s="13" t="n"/>
-      <c r="E137" s="11" t="n"/>
+      <c r="E137" s="16" t="n"/>
       <c r="F137" s="12" t="n"/>
       <c r="G137" s="13" t="n"/>
-      <c r="H137" s="11" t="n"/>
+      <c r="H137" s="16" t="n"/>
       <c r="I137" s="12" t="n"/>
       <c r="J137" s="13" t="n"/>
-      <c r="K137" s="11" t="n"/>
+      <c r="K137" s="16" t="n"/>
       <c r="L137" s="12" t="n"/>
       <c r="M137" s="13" t="n"/>
-      <c r="N137" s="11" t="n"/>
+      <c r="N137" s="16" t="n"/>
       <c r="O137" s="12" t="n"/>
       <c r="P137" s="13" t="n"/>
-      <c r="Q137" s="11" t="n"/>
+      <c r="Q137" s="16" t="n"/>
       <c r="R137" s="12" t="n"/>
       <c r="S137" s="13" t="n"/>
-      <c r="T137" s="11" t="n"/>
+      <c r="T137" s="16" t="n"/>
       <c r="U137" s="12" t="n"/>
       <c r="V137" s="13" t="n"/>
     </row>
@@ -5041,25 +4940,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B138" s="11" t="n"/>
+      <c r="B138" s="16" t="n"/>
       <c r="C138" s="12" t="n"/>
       <c r="D138" s="13" t="n"/>
-      <c r="E138" s="11" t="n"/>
+      <c r="E138" s="16" t="n"/>
       <c r="F138" s="12" t="n"/>
       <c r="G138" s="13" t="n"/>
-      <c r="H138" s="11" t="n"/>
+      <c r="H138" s="16" t="n"/>
       <c r="I138" s="12" t="n"/>
       <c r="J138" s="13" t="n"/>
-      <c r="K138" s="11" t="n"/>
+      <c r="K138" s="16" t="n"/>
       <c r="L138" s="12" t="n"/>
       <c r="M138" s="13" t="n"/>
-      <c r="N138" s="11" t="n"/>
+      <c r="N138" s="16" t="n"/>
       <c r="O138" s="12" t="n"/>
       <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="11" t="n"/>
+      <c r="Q138" s="16" t="n"/>
       <c r="R138" s="12" t="n"/>
       <c r="S138" s="13" t="n"/>
-      <c r="T138" s="11" t="n"/>
+      <c r="T138" s="16" t="n"/>
       <c r="U138" s="12" t="n"/>
       <c r="V138" s="13" t="n"/>
     </row>
@@ -5069,25 +4968,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B139" s="11" t="n"/>
+      <c r="B139" s="16" t="n"/>
       <c r="C139" s="12" t="n"/>
       <c r="D139" s="13" t="n"/>
-      <c r="E139" s="11" t="n"/>
+      <c r="E139" s="16" t="n"/>
       <c r="F139" s="12" t="n"/>
       <c r="G139" s="13" t="n"/>
-      <c r="H139" s="11" t="n"/>
+      <c r="H139" s="16" t="n"/>
       <c r="I139" s="12" t="n"/>
       <c r="J139" s="13" t="n"/>
-      <c r="K139" s="11" t="n"/>
+      <c r="K139" s="16" t="n"/>
       <c r="L139" s="12" t="n"/>
       <c r="M139" s="13" t="n"/>
-      <c r="N139" s="11" t="n"/>
+      <c r="N139" s="16" t="n"/>
       <c r="O139" s="12" t="n"/>
       <c r="P139" s="13" t="n"/>
-      <c r="Q139" s="11" t="n"/>
+      <c r="Q139" s="16" t="n"/>
       <c r="R139" s="12" t="n"/>
       <c r="S139" s="13" t="n"/>
-      <c r="T139" s="11" t="n"/>
+      <c r="T139" s="16" t="n"/>
       <c r="U139" s="12" t="n"/>
       <c r="V139" s="13" t="n"/>
     </row>
@@ -5097,25 +4996,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B140" s="11" t="n"/>
+      <c r="B140" s="16" t="n"/>
       <c r="C140" s="12" t="n"/>
       <c r="D140" s="13" t="n"/>
-      <c r="E140" s="11" t="n"/>
+      <c r="E140" s="16" t="n"/>
       <c r="F140" s="12" t="n"/>
       <c r="G140" s="13" t="n"/>
-      <c r="H140" s="11" t="n"/>
+      <c r="H140" s="16" t="n"/>
       <c r="I140" s="12" t="n"/>
       <c r="J140" s="13" t="n"/>
-      <c r="K140" s="11" t="n"/>
+      <c r="K140" s="16" t="n"/>
       <c r="L140" s="12" t="n"/>
       <c r="M140" s="13" t="n"/>
-      <c r="N140" s="11" t="n"/>
+      <c r="N140" s="16" t="n"/>
       <c r="O140" s="12" t="n"/>
       <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="11" t="n"/>
+      <c r="Q140" s="16" t="n"/>
       <c r="R140" s="12" t="n"/>
       <c r="S140" s="13" t="n"/>
-      <c r="T140" s="11" t="n"/>
+      <c r="T140" s="16" t="n"/>
       <c r="U140" s="12" t="n"/>
       <c r="V140" s="13" t="n"/>
     </row>
@@ -5125,25 +5024,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B141" s="11" t="n"/>
+      <c r="B141" s="16" t="n"/>
       <c r="C141" s="12" t="n"/>
       <c r="D141" s="13" t="n"/>
-      <c r="E141" s="11" t="n"/>
+      <c r="E141" s="16" t="n"/>
       <c r="F141" s="12" t="n"/>
       <c r="G141" s="13" t="n"/>
-      <c r="H141" s="11" t="n"/>
+      <c r="H141" s="16" t="n"/>
       <c r="I141" s="12" t="n"/>
       <c r="J141" s="13" t="n"/>
-      <c r="K141" s="11" t="n"/>
+      <c r="K141" s="16" t="n"/>
       <c r="L141" s="12" t="n"/>
       <c r="M141" s="13" t="n"/>
-      <c r="N141" s="11" t="n"/>
+      <c r="N141" s="16" t="n"/>
       <c r="O141" s="12" t="n"/>
       <c r="P141" s="13" t="n"/>
-      <c r="Q141" s="11" t="n"/>
+      <c r="Q141" s="16" t="n"/>
       <c r="R141" s="12" t="n"/>
       <c r="S141" s="13" t="n"/>
-      <c r="T141" s="11" t="n"/>
+      <c r="T141" s="16" t="n"/>
       <c r="U141" s="12" t="n"/>
       <c r="V141" s="13" t="n"/>
     </row>
@@ -5153,25 +5052,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B142" s="11" t="n"/>
+      <c r="B142" s="16" t="n"/>
       <c r="C142" s="12" t="n"/>
       <c r="D142" s="13" t="n"/>
-      <c r="E142" s="11" t="n"/>
+      <c r="E142" s="16" t="n"/>
       <c r="F142" s="12" t="n"/>
       <c r="G142" s="13" t="n"/>
-      <c r="H142" s="11" t="n"/>
+      <c r="H142" s="16" t="n"/>
       <c r="I142" s="12" t="n"/>
       <c r="J142" s="13" t="n"/>
-      <c r="K142" s="11" t="n"/>
+      <c r="K142" s="16" t="n"/>
       <c r="L142" s="12" t="n"/>
       <c r="M142" s="13" t="n"/>
-      <c r="N142" s="11" t="n"/>
+      <c r="N142" s="16" t="n"/>
       <c r="O142" s="12" t="n"/>
       <c r="P142" s="13" t="n"/>
-      <c r="Q142" s="11" t="n"/>
+      <c r="Q142" s="16" t="n"/>
       <c r="R142" s="12" t="n"/>
       <c r="S142" s="13" t="n"/>
-      <c r="T142" s="11" t="n"/>
+      <c r="T142" s="16" t="n"/>
       <c r="U142" s="12" t="n"/>
       <c r="V142" s="13" t="n"/>
     </row>
@@ -5181,25 +5080,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B143" s="11" t="n"/>
+      <c r="B143" s="16" t="n"/>
       <c r="C143" s="12" t="n"/>
       <c r="D143" s="13" t="n"/>
-      <c r="E143" s="11" t="n"/>
+      <c r="E143" s="16" t="n"/>
       <c r="F143" s="12" t="n"/>
       <c r="G143" s="13" t="n"/>
-      <c r="H143" s="11" t="n"/>
+      <c r="H143" s="16" t="n"/>
       <c r="I143" s="12" t="n"/>
       <c r="J143" s="13" t="n"/>
-      <c r="K143" s="11" t="n"/>
+      <c r="K143" s="16" t="n"/>
       <c r="L143" s="12" t="n"/>
       <c r="M143" s="13" t="n"/>
-      <c r="N143" s="11" t="n"/>
+      <c r="N143" s="16" t="n"/>
       <c r="O143" s="12" t="n"/>
       <c r="P143" s="13" t="n"/>
-      <c r="Q143" s="11" t="n"/>
+      <c r="Q143" s="16" t="n"/>
       <c r="R143" s="12" t="n"/>
       <c r="S143" s="13" t="n"/>
-      <c r="T143" s="11" t="n"/>
+      <c r="T143" s="16" t="n"/>
       <c r="U143" s="12" t="n"/>
       <c r="V143" s="13" t="n"/>
     </row>
@@ -5209,25 +5108,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B144" s="11" t="n"/>
+      <c r="B144" s="16" t="n"/>
       <c r="C144" s="12" t="n"/>
       <c r="D144" s="13" t="n"/>
-      <c r="E144" s="11" t="n"/>
+      <c r="E144" s="16" t="n"/>
       <c r="F144" s="12" t="n"/>
       <c r="G144" s="13" t="n"/>
-      <c r="H144" s="11" t="n"/>
+      <c r="H144" s="16" t="n"/>
       <c r="I144" s="12" t="n"/>
       <c r="J144" s="13" t="n"/>
-      <c r="K144" s="11" t="n"/>
+      <c r="K144" s="16" t="n"/>
       <c r="L144" s="12" t="n"/>
       <c r="M144" s="13" t="n"/>
-      <c r="N144" s="11" t="n"/>
+      <c r="N144" s="16" t="n"/>
       <c r="O144" s="12" t="n"/>
       <c r="P144" s="13" t="n"/>
-      <c r="Q144" s="11" t="n"/>
+      <c r="Q144" s="16" t="n"/>
       <c r="R144" s="12" t="n"/>
       <c r="S144" s="13" t="n"/>
-      <c r="T144" s="11" t="n"/>
+      <c r="T144" s="16" t="n"/>
       <c r="U144" s="12" t="n"/>
       <c r="V144" s="13" t="n"/>
     </row>
@@ -5237,55 +5136,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B145" s="11" t="n"/>
+      <c r="B145" s="16" t="n"/>
       <c r="C145" s="12" t="n"/>
       <c r="D145" s="13" t="n"/>
-      <c r="E145" s="11" t="n"/>
+      <c r="E145" s="16" t="n"/>
       <c r="F145" s="12" t="n"/>
       <c r="G145" s="13" t="n"/>
-      <c r="H145" s="11" t="n"/>
+      <c r="H145" s="16" t="n"/>
       <c r="I145" s="12" t="n"/>
       <c r="J145" s="13" t="n"/>
-      <c r="K145" s="11" t="n"/>
+      <c r="K145" s="16" t="n"/>
       <c r="L145" s="12" t="n"/>
       <c r="M145" s="13" t="n"/>
-      <c r="N145" s="11" t="n"/>
+      <c r="N145" s="16" t="n"/>
       <c r="O145" s="12" t="n"/>
       <c r="P145" s="13" t="n"/>
-      <c r="Q145" s="11" t="n"/>
+      <c r="Q145" s="16" t="n"/>
       <c r="R145" s="12" t="n"/>
       <c r="S145" s="13" t="n"/>
-      <c r="T145" s="11" t="n"/>
+      <c r="T145" s="16" t="n"/>
       <c r="U145" s="12" t="n"/>
       <c r="V145" s="13" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="14" t="inlineStr">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B146" s="15" t="n"/>
-      <c r="C146" s="16" t="n"/>
-      <c r="D146" s="17" t="n"/>
-      <c r="E146" s="15" t="n"/>
-      <c r="F146" s="16" t="n"/>
-      <c r="G146" s="17" t="n"/>
-      <c r="H146" s="15" t="n"/>
-      <c r="I146" s="16" t="n"/>
-      <c r="J146" s="17" t="n"/>
-      <c r="K146" s="15" t="n"/>
-      <c r="L146" s="16" t="n"/>
-      <c r="M146" s="17" t="n"/>
-      <c r="N146" s="15" t="n"/>
-      <c r="O146" s="16" t="n"/>
-      <c r="P146" s="17" t="n"/>
-      <c r="Q146" s="15" t="n"/>
-      <c r="R146" s="16" t="n"/>
-      <c r="S146" s="17" t="n"/>
-      <c r="T146" s="15" t="n"/>
-      <c r="U146" s="16" t="n"/>
-      <c r="V146" s="17" t="n"/>
+      <c r="B146" s="18" t="n"/>
+      <c r="C146" s="19" t="n"/>
+      <c r="D146" s="20" t="n"/>
+      <c r="E146" s="18" t="n"/>
+      <c r="F146" s="19" t="n"/>
+      <c r="G146" s="20" t="n"/>
+      <c r="H146" s="18" t="n"/>
+      <c r="I146" s="19" t="n"/>
+      <c r="J146" s="20" t="n"/>
+      <c r="K146" s="18" t="n"/>
+      <c r="L146" s="19" t="n"/>
+      <c r="M146" s="20" t="n"/>
+      <c r="N146" s="18" t="n"/>
+      <c r="O146" s="19" t="n"/>
+      <c r="P146" s="20" t="n"/>
+      <c r="Q146" s="18" t="n"/>
+      <c r="R146" s="19" t="n"/>
+      <c r="S146" s="20" t="n"/>
+      <c r="T146" s="18" t="n"/>
+      <c r="U146" s="19" t="n"/>
+      <c r="V146" s="20" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -5293,25 +5192,25 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B147" s="7" t="n"/>
+      <c r="B147" s="21" t="n"/>
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="9" t="n"/>
-      <c r="E147" s="7" t="n"/>
+      <c r="E147" s="21" t="n"/>
       <c r="F147" s="8" t="n"/>
       <c r="G147" s="9" t="n"/>
-      <c r="H147" s="7" t="n"/>
+      <c r="H147" s="21" t="n"/>
       <c r="I147" s="8" t="n"/>
       <c r="J147" s="9" t="n"/>
-      <c r="K147" s="7" t="n"/>
+      <c r="K147" s="21" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="9" t="n"/>
-      <c r="N147" s="7" t="n"/>
+      <c r="N147" s="21" t="n"/>
       <c r="O147" s="8" t="n"/>
       <c r="P147" s="9" t="n"/>
-      <c r="Q147" s="7" t="n"/>
+      <c r="Q147" s="21" t="n"/>
       <c r="R147" s="8" t="n"/>
       <c r="S147" s="9" t="n"/>
-      <c r="T147" s="7" t="n"/>
+      <c r="T147" s="21" t="n"/>
       <c r="U147" s="8" t="n"/>
       <c r="V147" s="9" t="n"/>
     </row>
@@ -5321,25 +5220,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B148" s="11" t="n"/>
+      <c r="B148" s="16" t="n"/>
       <c r="C148" s="12" t="n"/>
       <c r="D148" s="13" t="n"/>
-      <c r="E148" s="11" t="n"/>
+      <c r="E148" s="16" t="n"/>
       <c r="F148" s="12" t="n"/>
       <c r="G148" s="13" t="n"/>
-      <c r="H148" s="11" t="n"/>
+      <c r="H148" s="16" t="n"/>
       <c r="I148" s="12" t="n"/>
       <c r="J148" s="13" t="n"/>
-      <c r="K148" s="11" t="n"/>
+      <c r="K148" s="16" t="n"/>
       <c r="L148" s="12" t="n"/>
       <c r="M148" s="13" t="n"/>
-      <c r="N148" s="11" t="n"/>
+      <c r="N148" s="16" t="n"/>
       <c r="O148" s="12" t="n"/>
       <c r="P148" s="13" t="n"/>
-      <c r="Q148" s="11" t="n"/>
+      <c r="Q148" s="16" t="n"/>
       <c r="R148" s="12" t="n"/>
       <c r="S148" s="13" t="n"/>
-      <c r="T148" s="11" t="n"/>
+      <c r="T148" s="16" t="n"/>
       <c r="U148" s="12" t="n"/>
       <c r="V148" s="13" t="n"/>
     </row>
@@ -5349,25 +5248,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B149" s="11" t="n"/>
+      <c r="B149" s="16" t="n"/>
       <c r="C149" s="12" t="n"/>
       <c r="D149" s="13" t="n"/>
-      <c r="E149" s="11" t="n"/>
+      <c r="E149" s="16" t="n"/>
       <c r="F149" s="12" t="n"/>
       <c r="G149" s="13" t="n"/>
-      <c r="H149" s="11" t="n"/>
+      <c r="H149" s="16" t="n"/>
       <c r="I149" s="12" t="n"/>
       <c r="J149" s="13" t="n"/>
-      <c r="K149" s="11" t="n"/>
+      <c r="K149" s="16" t="n"/>
       <c r="L149" s="12" t="n"/>
       <c r="M149" s="13" t="n"/>
-      <c r="N149" s="11" t="n"/>
+      <c r="N149" s="16" t="n"/>
       <c r="O149" s="12" t="n"/>
       <c r="P149" s="13" t="n"/>
-      <c r="Q149" s="11" t="n"/>
+      <c r="Q149" s="16" t="n"/>
       <c r="R149" s="12" t="n"/>
       <c r="S149" s="13" t="n"/>
-      <c r="T149" s="11" t="n"/>
+      <c r="T149" s="16" t="n"/>
       <c r="U149" s="12" t="n"/>
       <c r="V149" s="13" t="n"/>
     </row>
@@ -5377,25 +5276,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B150" s="11" t="n"/>
+      <c r="B150" s="16" t="n"/>
       <c r="C150" s="12" t="n"/>
       <c r="D150" s="13" t="n"/>
-      <c r="E150" s="11" t="n"/>
+      <c r="E150" s="16" t="n"/>
       <c r="F150" s="12" t="n"/>
       <c r="G150" s="13" t="n"/>
-      <c r="H150" s="11" t="n"/>
+      <c r="H150" s="16" t="n"/>
       <c r="I150" s="12" t="n"/>
       <c r="J150" s="13" t="n"/>
-      <c r="K150" s="11" t="n"/>
+      <c r="K150" s="16" t="n"/>
       <c r="L150" s="12" t="n"/>
       <c r="M150" s="13" t="n"/>
-      <c r="N150" s="11" t="n"/>
+      <c r="N150" s="16" t="n"/>
       <c r="O150" s="12" t="n"/>
       <c r="P150" s="13" t="n"/>
-      <c r="Q150" s="11" t="n"/>
+      <c r="Q150" s="16" t="n"/>
       <c r="R150" s="12" t="n"/>
       <c r="S150" s="13" t="n"/>
-      <c r="T150" s="11" t="n"/>
+      <c r="T150" s="16" t="n"/>
       <c r="U150" s="12" t="n"/>
       <c r="V150" s="13" t="n"/>
     </row>
@@ -5405,25 +5304,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B151" s="11" t="n"/>
+      <c r="B151" s="16" t="n"/>
       <c r="C151" s="12" t="n"/>
       <c r="D151" s="13" t="n"/>
-      <c r="E151" s="11" t="n"/>
+      <c r="E151" s="16" t="n"/>
       <c r="F151" s="12" t="n"/>
       <c r="G151" s="13" t="n"/>
-      <c r="H151" s="11" t="n"/>
+      <c r="H151" s="16" t="n"/>
       <c r="I151" s="12" t="n"/>
       <c r="J151" s="13" t="n"/>
-      <c r="K151" s="11" t="n"/>
+      <c r="K151" s="16" t="n"/>
       <c r="L151" s="12" t="n"/>
       <c r="M151" s="13" t="n"/>
-      <c r="N151" s="11" t="n"/>
+      <c r="N151" s="16" t="n"/>
       <c r="O151" s="12" t="n"/>
       <c r="P151" s="13" t="n"/>
-      <c r="Q151" s="11" t="n"/>
+      <c r="Q151" s="16" t="n"/>
       <c r="R151" s="12" t="n"/>
       <c r="S151" s="13" t="n"/>
-      <c r="T151" s="11" t="n"/>
+      <c r="T151" s="16" t="n"/>
       <c r="U151" s="12" t="n"/>
       <c r="V151" s="13" t="n"/>
     </row>
@@ -5433,25 +5332,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B152" s="11" t="n"/>
+      <c r="B152" s="16" t="n"/>
       <c r="C152" s="12" t="n"/>
       <c r="D152" s="13" t="n"/>
-      <c r="E152" s="11" t="n"/>
+      <c r="E152" s="16" t="n"/>
       <c r="F152" s="12" t="n"/>
       <c r="G152" s="13" t="n"/>
-      <c r="H152" s="11" t="n"/>
+      <c r="H152" s="16" t="n"/>
       <c r="I152" s="12" t="n"/>
       <c r="J152" s="13" t="n"/>
-      <c r="K152" s="11" t="n"/>
+      <c r="K152" s="16" t="n"/>
       <c r="L152" s="12" t="n"/>
       <c r="M152" s="13" t="n"/>
-      <c r="N152" s="11" t="n"/>
+      <c r="N152" s="16" t="n"/>
       <c r="O152" s="12" t="n"/>
       <c r="P152" s="13" t="n"/>
-      <c r="Q152" s="11" t="n"/>
+      <c r="Q152" s="16" t="n"/>
       <c r="R152" s="12" t="n"/>
       <c r="S152" s="13" t="n"/>
-      <c r="T152" s="11" t="n"/>
+      <c r="T152" s="16" t="n"/>
       <c r="U152" s="12" t="n"/>
       <c r="V152" s="13" t="n"/>
     </row>
@@ -5461,25 +5360,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B153" s="11" t="n"/>
+      <c r="B153" s="16" t="n"/>
       <c r="C153" s="12" t="n"/>
       <c r="D153" s="13" t="n"/>
-      <c r="E153" s="11" t="n"/>
+      <c r="E153" s="16" t="n"/>
       <c r="F153" s="12" t="n"/>
       <c r="G153" s="13" t="n"/>
-      <c r="H153" s="11" t="n"/>
+      <c r="H153" s="16" t="n"/>
       <c r="I153" s="12" t="n"/>
       <c r="J153" s="13" t="n"/>
-      <c r="K153" s="11" t="n"/>
+      <c r="K153" s="16" t="n"/>
       <c r="L153" s="12" t="n"/>
       <c r="M153" s="13" t="n"/>
-      <c r="N153" s="11" t="n"/>
+      <c r="N153" s="16" t="n"/>
       <c r="O153" s="12" t="n"/>
       <c r="P153" s="13" t="n"/>
-      <c r="Q153" s="11" t="n"/>
+      <c r="Q153" s="16" t="n"/>
       <c r="R153" s="12" t="n"/>
       <c r="S153" s="13" t="n"/>
-      <c r="T153" s="11" t="n"/>
+      <c r="T153" s="16" t="n"/>
       <c r="U153" s="12" t="n"/>
       <c r="V153" s="13" t="n"/>
     </row>
@@ -5489,25 +5388,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B154" s="11" t="n"/>
+      <c r="B154" s="16" t="n"/>
       <c r="C154" s="12" t="n"/>
       <c r="D154" s="13" t="n"/>
-      <c r="E154" s="11" t="n"/>
+      <c r="E154" s="16" t="n"/>
       <c r="F154" s="12" t="n"/>
       <c r="G154" s="13" t="n"/>
-      <c r="H154" s="11" t="n"/>
+      <c r="H154" s="16" t="n"/>
       <c r="I154" s="12" t="n"/>
       <c r="J154" s="13" t="n"/>
-      <c r="K154" s="11" t="n"/>
+      <c r="K154" s="16" t="n"/>
       <c r="L154" s="12" t="n"/>
       <c r="M154" s="13" t="n"/>
-      <c r="N154" s="11" t="n"/>
+      <c r="N154" s="16" t="n"/>
       <c r="O154" s="12" t="n"/>
       <c r="P154" s="13" t="n"/>
-      <c r="Q154" s="11" t="n"/>
+      <c r="Q154" s="16" t="n"/>
       <c r="R154" s="12" t="n"/>
       <c r="S154" s="13" t="n"/>
-      <c r="T154" s="11" t="n"/>
+      <c r="T154" s="16" t="n"/>
       <c r="U154" s="12" t="n"/>
       <c r="V154" s="13" t="n"/>
     </row>
@@ -5517,25 +5416,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B155" s="11" t="n"/>
+      <c r="B155" s="16" t="n"/>
       <c r="C155" s="12" t="n"/>
       <c r="D155" s="13" t="n"/>
-      <c r="E155" s="11" t="n"/>
+      <c r="E155" s="16" t="n"/>
       <c r="F155" s="12" t="n"/>
       <c r="G155" s="13" t="n"/>
-      <c r="H155" s="11" t="n"/>
+      <c r="H155" s="16" t="n"/>
       <c r="I155" s="12" t="n"/>
       <c r="J155" s="13" t="n"/>
-      <c r="K155" s="11" t="n"/>
+      <c r="K155" s="16" t="n"/>
       <c r="L155" s="12" t="n"/>
       <c r="M155" s="13" t="n"/>
-      <c r="N155" s="11" t="n"/>
+      <c r="N155" s="16" t="n"/>
       <c r="O155" s="12" t="n"/>
       <c r="P155" s="13" t="n"/>
-      <c r="Q155" s="11" t="n"/>
+      <c r="Q155" s="16" t="n"/>
       <c r="R155" s="12" t="n"/>
       <c r="S155" s="13" t="n"/>
-      <c r="T155" s="11" t="n"/>
+      <c r="T155" s="16" t="n"/>
       <c r="U155" s="12" t="n"/>
       <c r="V155" s="13" t="n"/>
     </row>
@@ -5545,25 +5444,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B156" s="11" t="n"/>
+      <c r="B156" s="16" t="n"/>
       <c r="C156" s="12" t="n"/>
       <c r="D156" s="13" t="n"/>
-      <c r="E156" s="11" t="n"/>
+      <c r="E156" s="16" t="n"/>
       <c r="F156" s="12" t="n"/>
       <c r="G156" s="13" t="n"/>
-      <c r="H156" s="11" t="n"/>
+      <c r="H156" s="16" t="n"/>
       <c r="I156" s="12" t="n"/>
       <c r="J156" s="13" t="n"/>
-      <c r="K156" s="11" t="n"/>
+      <c r="K156" s="16" t="n"/>
       <c r="L156" s="12" t="n"/>
       <c r="M156" s="13" t="n"/>
-      <c r="N156" s="11" t="n"/>
+      <c r="N156" s="16" t="n"/>
       <c r="O156" s="12" t="n"/>
       <c r="P156" s="13" t="n"/>
-      <c r="Q156" s="11" t="n"/>
+      <c r="Q156" s="16" t="n"/>
       <c r="R156" s="12" t="n"/>
       <c r="S156" s="13" t="n"/>
-      <c r="T156" s="11" t="n"/>
+      <c r="T156" s="16" t="n"/>
       <c r="U156" s="12" t="n"/>
       <c r="V156" s="13" t="n"/>
     </row>
@@ -5573,55 +5472,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B157" s="11" t="n"/>
+      <c r="B157" s="16" t="n"/>
       <c r="C157" s="12" t="n"/>
       <c r="D157" s="13" t="n"/>
-      <c r="E157" s="11" t="n"/>
+      <c r="E157" s="16" t="n"/>
       <c r="F157" s="12" t="n"/>
       <c r="G157" s="13" t="n"/>
-      <c r="H157" s="11" t="n"/>
+      <c r="H157" s="16" t="n"/>
       <c r="I157" s="12" t="n"/>
       <c r="J157" s="13" t="n"/>
-      <c r="K157" s="11" t="n"/>
+      <c r="K157" s="16" t="n"/>
       <c r="L157" s="12" t="n"/>
       <c r="M157" s="13" t="n"/>
-      <c r="N157" s="11" t="n"/>
+      <c r="N157" s="16" t="n"/>
       <c r="O157" s="12" t="n"/>
       <c r="P157" s="13" t="n"/>
-      <c r="Q157" s="11" t="n"/>
+      <c r="Q157" s="16" t="n"/>
       <c r="R157" s="12" t="n"/>
       <c r="S157" s="13" t="n"/>
-      <c r="T157" s="11" t="n"/>
+      <c r="T157" s="16" t="n"/>
       <c r="U157" s="12" t="n"/>
       <c r="V157" s="13" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="14" t="inlineStr">
+      <c r="A158" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B158" s="15" t="n"/>
-      <c r="C158" s="16" t="n"/>
-      <c r="D158" s="17" t="n"/>
-      <c r="E158" s="15" t="n"/>
-      <c r="F158" s="16" t="n"/>
-      <c r="G158" s="17" t="n"/>
-      <c r="H158" s="15" t="n"/>
-      <c r="I158" s="16" t="n"/>
-      <c r="J158" s="17" t="n"/>
-      <c r="K158" s="15" t="n"/>
-      <c r="L158" s="16" t="n"/>
-      <c r="M158" s="17" t="n"/>
-      <c r="N158" s="15" t="n"/>
-      <c r="O158" s="16" t="n"/>
-      <c r="P158" s="17" t="n"/>
-      <c r="Q158" s="15" t="n"/>
-      <c r="R158" s="16" t="n"/>
-      <c r="S158" s="17" t="n"/>
-      <c r="T158" s="15" t="n"/>
-      <c r="U158" s="16" t="n"/>
-      <c r="V158" s="17" t="n"/>
+      <c r="B158" s="18" t="n"/>
+      <c r="C158" s="19" t="n"/>
+      <c r="D158" s="20" t="n"/>
+      <c r="E158" s="18" t="n"/>
+      <c r="F158" s="19" t="n"/>
+      <c r="G158" s="20" t="n"/>
+      <c r="H158" s="18" t="n"/>
+      <c r="I158" s="19" t="n"/>
+      <c r="J158" s="20" t="n"/>
+      <c r="K158" s="18" t="n"/>
+      <c r="L158" s="19" t="n"/>
+      <c r="M158" s="20" t="n"/>
+      <c r="N158" s="18" t="n"/>
+      <c r="O158" s="19" t="n"/>
+      <c r="P158" s="20" t="n"/>
+      <c r="Q158" s="18" t="n"/>
+      <c r="R158" s="19" t="n"/>
+      <c r="S158" s="20" t="n"/>
+      <c r="T158" s="18" t="n"/>
+      <c r="U158" s="19" t="n"/>
+      <c r="V158" s="20" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -5629,25 +5528,25 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B159" s="7" t="n"/>
+      <c r="B159" s="21" t="n"/>
       <c r="C159" s="8" t="n"/>
       <c r="D159" s="9" t="n"/>
-      <c r="E159" s="7" t="n"/>
+      <c r="E159" s="21" t="n"/>
       <c r="F159" s="8" t="n"/>
       <c r="G159" s="9" t="n"/>
-      <c r="H159" s="7" t="n"/>
+      <c r="H159" s="21" t="n"/>
       <c r="I159" s="8" t="n"/>
       <c r="J159" s="9" t="n"/>
-      <c r="K159" s="7" t="n"/>
+      <c r="K159" s="21" t="n"/>
       <c r="L159" s="8" t="n"/>
       <c r="M159" s="9" t="n"/>
-      <c r="N159" s="7" t="n"/>
+      <c r="N159" s="21" t="n"/>
       <c r="O159" s="8" t="n"/>
       <c r="P159" s="9" t="n"/>
-      <c r="Q159" s="7" t="n"/>
+      <c r="Q159" s="21" t="n"/>
       <c r="R159" s="8" t="n"/>
       <c r="S159" s="9" t="n"/>
-      <c r="T159" s="7" t="n"/>
+      <c r="T159" s="21" t="n"/>
       <c r="U159" s="8" t="n"/>
       <c r="V159" s="9" t="n"/>
     </row>
@@ -5657,25 +5556,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B160" s="11" t="n"/>
+      <c r="B160" s="16" t="n"/>
       <c r="C160" s="12" t="n"/>
       <c r="D160" s="13" t="n"/>
-      <c r="E160" s="11" t="n"/>
+      <c r="E160" s="16" t="n"/>
       <c r="F160" s="12" t="n"/>
       <c r="G160" s="13" t="n"/>
-      <c r="H160" s="11" t="n"/>
+      <c r="H160" s="16" t="n"/>
       <c r="I160" s="12" t="n"/>
       <c r="J160" s="13" t="n"/>
-      <c r="K160" s="11" t="n"/>
+      <c r="K160" s="16" t="n"/>
       <c r="L160" s="12" t="n"/>
       <c r="M160" s="13" t="n"/>
-      <c r="N160" s="11" t="n"/>
+      <c r="N160" s="16" t="n"/>
       <c r="O160" s="12" t="n"/>
       <c r="P160" s="13" t="n"/>
-      <c r="Q160" s="11" t="n"/>
+      <c r="Q160" s="16" t="n"/>
       <c r="R160" s="12" t="n"/>
       <c r="S160" s="13" t="n"/>
-      <c r="T160" s="11" t="n"/>
+      <c r="T160" s="16" t="n"/>
       <c r="U160" s="12" t="n"/>
       <c r="V160" s="13" t="n"/>
     </row>
@@ -5685,25 +5584,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B161" s="11" t="n"/>
+      <c r="B161" s="16" t="n"/>
       <c r="C161" s="12" t="n"/>
       <c r="D161" s="13" t="n"/>
-      <c r="E161" s="11" t="n"/>
+      <c r="E161" s="16" t="n"/>
       <c r="F161" s="12" t="n"/>
       <c r="G161" s="13" t="n"/>
-      <c r="H161" s="11" t="n"/>
+      <c r="H161" s="16" t="n"/>
       <c r="I161" s="12" t="n"/>
       <c r="J161" s="13" t="n"/>
-      <c r="K161" s="11" t="n"/>
+      <c r="K161" s="16" t="n"/>
       <c r="L161" s="12" t="n"/>
       <c r="M161" s="13" t="n"/>
-      <c r="N161" s="11" t="n"/>
+      <c r="N161" s="16" t="n"/>
       <c r="O161" s="12" t="n"/>
       <c r="P161" s="13" t="n"/>
-      <c r="Q161" s="11" t="n"/>
+      <c r="Q161" s="16" t="n"/>
       <c r="R161" s="12" t="n"/>
       <c r="S161" s="13" t="n"/>
-      <c r="T161" s="11" t="n"/>
+      <c r="T161" s="16" t="n"/>
       <c r="U161" s="12" t="n"/>
       <c r="V161" s="13" t="n"/>
     </row>
@@ -5713,25 +5612,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B162" s="11" t="n"/>
+      <c r="B162" s="16" t="n"/>
       <c r="C162" s="12" t="n"/>
       <c r="D162" s="13" t="n"/>
-      <c r="E162" s="11" t="n"/>
+      <c r="E162" s="16" t="n"/>
       <c r="F162" s="12" t="n"/>
       <c r="G162" s="13" t="n"/>
-      <c r="H162" s="11" t="n"/>
+      <c r="H162" s="16" t="n"/>
       <c r="I162" s="12" t="n"/>
       <c r="J162" s="13" t="n"/>
-      <c r="K162" s="11" t="n"/>
+      <c r="K162" s="16" t="n"/>
       <c r="L162" s="12" t="n"/>
       <c r="M162" s="13" t="n"/>
-      <c r="N162" s="11" t="n"/>
+      <c r="N162" s="16" t="n"/>
       <c r="O162" s="12" t="n"/>
       <c r="P162" s="13" t="n"/>
-      <c r="Q162" s="11" t="n"/>
+      <c r="Q162" s="16" t="n"/>
       <c r="R162" s="12" t="n"/>
       <c r="S162" s="13" t="n"/>
-      <c r="T162" s="11" t="n"/>
+      <c r="T162" s="16" t="n"/>
       <c r="U162" s="12" t="n"/>
       <c r="V162" s="13" t="n"/>
     </row>
@@ -5741,25 +5640,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B163" s="11" t="n"/>
+      <c r="B163" s="16" t="n"/>
       <c r="C163" s="12" t="n"/>
       <c r="D163" s="13" t="n"/>
-      <c r="E163" s="11" t="n"/>
+      <c r="E163" s="16" t="n"/>
       <c r="F163" s="12" t="n"/>
       <c r="G163" s="13" t="n"/>
-      <c r="H163" s="11" t="n"/>
+      <c r="H163" s="16" t="n"/>
       <c r="I163" s="12" t="n"/>
       <c r="J163" s="13" t="n"/>
-      <c r="K163" s="11" t="n"/>
+      <c r="K163" s="16" t="n"/>
       <c r="L163" s="12" t="n"/>
       <c r="M163" s="13" t="n"/>
-      <c r="N163" s="11" t="n"/>
+      <c r="N163" s="16" t="n"/>
       <c r="O163" s="12" t="n"/>
       <c r="P163" s="13" t="n"/>
-      <c r="Q163" s="11" t="n"/>
+      <c r="Q163" s="16" t="n"/>
       <c r="R163" s="12" t="n"/>
       <c r="S163" s="13" t="n"/>
-      <c r="T163" s="11" t="n"/>
+      <c r="T163" s="16" t="n"/>
       <c r="U163" s="12" t="n"/>
       <c r="V163" s="13" t="n"/>
     </row>
@@ -5769,25 +5668,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B164" s="11" t="n"/>
+      <c r="B164" s="16" t="n"/>
       <c r="C164" s="12" t="n"/>
       <c r="D164" s="13" t="n"/>
-      <c r="E164" s="11" t="n"/>
+      <c r="E164" s="16" t="n"/>
       <c r="F164" s="12" t="n"/>
       <c r="G164" s="13" t="n"/>
-      <c r="H164" s="11" t="n"/>
+      <c r="H164" s="16" t="n"/>
       <c r="I164" s="12" t="n"/>
       <c r="J164" s="13" t="n"/>
-      <c r="K164" s="11" t="n"/>
+      <c r="K164" s="16" t="n"/>
       <c r="L164" s="12" t="n"/>
       <c r="M164" s="13" t="n"/>
-      <c r="N164" s="11" t="n"/>
+      <c r="N164" s="16" t="n"/>
       <c r="O164" s="12" t="n"/>
       <c r="P164" s="13" t="n"/>
-      <c r="Q164" s="11" t="n"/>
+      <c r="Q164" s="16" t="n"/>
       <c r="R164" s="12" t="n"/>
       <c r="S164" s="13" t="n"/>
-      <c r="T164" s="11" t="n"/>
+      <c r="T164" s="16" t="n"/>
       <c r="U164" s="12" t="n"/>
       <c r="V164" s="13" t="n"/>
     </row>
@@ -5797,50 +5696,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B165" s="11" t="n"/>
-      <c r="C165" s="35" t="inlineStr">
+      <c r="B165" s="16" t="n"/>
+      <c r="C165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="D165" s="13" t="n"/>
-      <c r="E165" s="11" t="n"/>
-      <c r="F165" s="35" t="inlineStr">
+      <c r="E165" s="16" t="n"/>
+      <c r="F165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="G165" s="13" t="n"/>
-      <c r="H165" s="11" t="n"/>
-      <c r="I165" s="35" t="inlineStr">
+      <c r="H165" s="16" t="n"/>
+      <c r="I165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="J165" s="13" t="n"/>
-      <c r="K165" s="11" t="n"/>
-      <c r="L165" s="35" t="inlineStr">
+      <c r="K165" s="16" t="n"/>
+      <c r="L165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="M165" s="13" t="n"/>
-      <c r="N165" s="11" t="n"/>
-      <c r="O165" s="35" t="inlineStr">
+      <c r="N165" s="16" t="n"/>
+      <c r="O165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="P165" s="13" t="n"/>
-      <c r="Q165" s="11" t="n"/>
-      <c r="R165" s="35" t="inlineStr">
+      <c r="Q165" s="16" t="n"/>
+      <c r="R165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="S165" s="13" t="n"/>
-      <c r="T165" s="11" t="n"/>
-      <c r="U165" s="35" t="inlineStr">
+      <c r="T165" s="16" t="n"/>
+      <c r="U165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
@@ -5853,26 +5752,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B166" s="11" t="n"/>
-      <c r="C166" s="29" t="n"/>
+      <c r="B166" s="16" t="n"/>
+      <c r="C166" s="23" t="n"/>
       <c r="D166" s="13" t="n"/>
-      <c r="E166" s="11" t="n"/>
-      <c r="F166" s="29" t="n"/>
+      <c r="E166" s="16" t="n"/>
+      <c r="F166" s="23" t="n"/>
       <c r="G166" s="13" t="n"/>
-      <c r="H166" s="11" t="n"/>
-      <c r="I166" s="29" t="n"/>
+      <c r="H166" s="16" t="n"/>
+      <c r="I166" s="23" t="n"/>
       <c r="J166" s="13" t="n"/>
-      <c r="K166" s="11" t="n"/>
-      <c r="L166" s="29" t="n"/>
+      <c r="K166" s="16" t="n"/>
+      <c r="L166" s="23" t="n"/>
       <c r="M166" s="13" t="n"/>
-      <c r="N166" s="11" t="n"/>
-      <c r="O166" s="29" t="n"/>
+      <c r="N166" s="16" t="n"/>
+      <c r="O166" s="23" t="n"/>
       <c r="P166" s="13" t="n"/>
-      <c r="Q166" s="11" t="n"/>
-      <c r="R166" s="29" t="n"/>
+      <c r="Q166" s="16" t="n"/>
+      <c r="R166" s="23" t="n"/>
       <c r="S166" s="13" t="n"/>
-      <c r="T166" s="11" t="n"/>
-      <c r="U166" s="29" t="n"/>
+      <c r="T166" s="16" t="n"/>
+      <c r="U166" s="23" t="n"/>
       <c r="V166" s="13" t="n"/>
     </row>
     <row r="167">
@@ -5881,26 +5780,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B167" s="11" t="n"/>
-      <c r="C167" s="29" t="n"/>
+      <c r="B167" s="16" t="n"/>
+      <c r="C167" s="23" t="n"/>
       <c r="D167" s="13" t="n"/>
-      <c r="E167" s="11" t="n"/>
-      <c r="F167" s="29" t="n"/>
+      <c r="E167" s="16" t="n"/>
+      <c r="F167" s="23" t="n"/>
       <c r="G167" s="13" t="n"/>
-      <c r="H167" s="11" t="n"/>
-      <c r="I167" s="29" t="n"/>
+      <c r="H167" s="16" t="n"/>
+      <c r="I167" s="23" t="n"/>
       <c r="J167" s="13" t="n"/>
-      <c r="K167" s="11" t="n"/>
-      <c r="L167" s="29" t="n"/>
+      <c r="K167" s="16" t="n"/>
+      <c r="L167" s="23" t="n"/>
       <c r="M167" s="13" t="n"/>
-      <c r="N167" s="11" t="n"/>
-      <c r="O167" s="29" t="n"/>
+      <c r="N167" s="16" t="n"/>
+      <c r="O167" s="23" t="n"/>
       <c r="P167" s="13" t="n"/>
-      <c r="Q167" s="11" t="n"/>
-      <c r="R167" s="29" t="n"/>
+      <c r="Q167" s="16" t="n"/>
+      <c r="R167" s="23" t="n"/>
       <c r="S167" s="13" t="n"/>
-      <c r="T167" s="11" t="n"/>
-      <c r="U167" s="29" t="n"/>
+      <c r="T167" s="16" t="n"/>
+      <c r="U167" s="23" t="n"/>
       <c r="V167" s="13" t="n"/>
     </row>
     <row r="168">
@@ -5909,26 +5808,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B168" s="11" t="n"/>
-      <c r="C168" s="29" t="n"/>
+      <c r="B168" s="16" t="n"/>
+      <c r="C168" s="23" t="n"/>
       <c r="D168" s="13" t="n"/>
-      <c r="E168" s="11" t="n"/>
-      <c r="F168" s="29" t="n"/>
+      <c r="E168" s="16" t="n"/>
+      <c r="F168" s="23" t="n"/>
       <c r="G168" s="13" t="n"/>
-      <c r="H168" s="11" t="n"/>
-      <c r="I168" s="29" t="n"/>
+      <c r="H168" s="16" t="n"/>
+      <c r="I168" s="23" t="n"/>
       <c r="J168" s="13" t="n"/>
-      <c r="K168" s="11" t="n"/>
-      <c r="L168" s="29" t="n"/>
+      <c r="K168" s="16" t="n"/>
+      <c r="L168" s="23" t="n"/>
       <c r="M168" s="13" t="n"/>
-      <c r="N168" s="11" t="n"/>
-      <c r="O168" s="29" t="n"/>
+      <c r="N168" s="16" t="n"/>
+      <c r="O168" s="23" t="n"/>
       <c r="P168" s="13" t="n"/>
-      <c r="Q168" s="11" t="n"/>
-      <c r="R168" s="29" t="n"/>
+      <c r="Q168" s="16" t="n"/>
+      <c r="R168" s="23" t="n"/>
       <c r="S168" s="13" t="n"/>
-      <c r="T168" s="11" t="n"/>
-      <c r="U168" s="29" t="n"/>
+      <c r="T168" s="16" t="n"/>
+      <c r="U168" s="23" t="n"/>
       <c r="V168" s="13" t="n"/>
     </row>
     <row r="169">
@@ -5937,94 +5836,94 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B169" s="11" t="n"/>
-      <c r="C169" s="30" t="n"/>
+      <c r="B169" s="16" t="n"/>
+      <c r="C169" s="24" t="n"/>
       <c r="D169" s="13" t="n"/>
-      <c r="E169" s="11" t="n"/>
-      <c r="F169" s="30" t="n"/>
+      <c r="E169" s="16" t="n"/>
+      <c r="F169" s="24" t="n"/>
       <c r="G169" s="13" t="n"/>
-      <c r="H169" s="11" t="n"/>
-      <c r="I169" s="30" t="n"/>
+      <c r="H169" s="16" t="n"/>
+      <c r="I169" s="24" t="n"/>
       <c r="J169" s="13" t="n"/>
-      <c r="K169" s="11" t="n"/>
-      <c r="L169" s="30" t="n"/>
+      <c r="K169" s="16" t="n"/>
+      <c r="L169" s="24" t="n"/>
       <c r="M169" s="13" t="n"/>
-      <c r="N169" s="11" t="n"/>
-      <c r="O169" s="30" t="n"/>
+      <c r="N169" s="16" t="n"/>
+      <c r="O169" s="24" t="n"/>
       <c r="P169" s="13" t="n"/>
-      <c r="Q169" s="11" t="n"/>
-      <c r="R169" s="30" t="n"/>
+      <c r="Q169" s="16" t="n"/>
+      <c r="R169" s="24" t="n"/>
       <c r="S169" s="13" t="n"/>
-      <c r="T169" s="11" t="n"/>
-      <c r="U169" s="30" t="n"/>
+      <c r="T169" s="16" t="n"/>
+      <c r="U169" s="24" t="n"/>
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="14" t="inlineStr">
+      <c r="A170" s="17" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B170" s="15" t="n"/>
-      <c r="C170" s="16" t="n"/>
-      <c r="D170" s="17" t="n"/>
-      <c r="E170" s="15" t="n"/>
-      <c r="F170" s="16" t="n"/>
-      <c r="G170" s="17" t="n"/>
-      <c r="H170" s="15" t="n"/>
-      <c r="I170" s="16" t="n"/>
-      <c r="J170" s="17" t="n"/>
-      <c r="K170" s="15" t="n"/>
-      <c r="L170" s="16" t="n"/>
-      <c r="M170" s="17" t="n"/>
-      <c r="N170" s="15" t="n"/>
-      <c r="O170" s="16" t="n"/>
-      <c r="P170" s="17" t="n"/>
-      <c r="Q170" s="15" t="n"/>
-      <c r="R170" s="16" t="n"/>
-      <c r="S170" s="17" t="n"/>
-      <c r="T170" s="15" t="n"/>
-      <c r="U170" s="16" t="n"/>
-      <c r="V170" s="17" t="n"/>
+      <c r="B170" s="18" t="n"/>
+      <c r="C170" s="19" t="n"/>
+      <c r="D170" s="20" t="n"/>
+      <c r="E170" s="18" t="n"/>
+      <c r="F170" s="19" t="n"/>
+      <c r="G170" s="20" t="n"/>
+      <c r="H170" s="18" t="n"/>
+      <c r="I170" s="19" t="n"/>
+      <c r="J170" s="20" t="n"/>
+      <c r="K170" s="18" t="n"/>
+      <c r="L170" s="19" t="n"/>
+      <c r="M170" s="20" t="n"/>
+      <c r="N170" s="18" t="n"/>
+      <c r="O170" s="19" t="n"/>
+      <c r="P170" s="20" t="n"/>
+      <c r="Q170" s="18" t="n"/>
+      <c r="R170" s="19" t="n"/>
+      <c r="S170" s="20" t="n"/>
+      <c r="T170" s="18" t="n"/>
+      <c r="U170" s="19" t="n"/>
+      <c r="V170" s="20" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="18" t="inlineStr">
+      <c r="A171" s="26" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="B171" s="19" t="n"/>
-      <c r="C171" s="20" t="n"/>
-      <c r="D171" s="21" t="n"/>
-      <c r="E171" s="19" t="n"/>
-      <c r="F171" s="20" t="n"/>
-      <c r="G171" s="21" t="n"/>
-      <c r="H171" s="19" t="n"/>
-      <c r="I171" s="20" t="n"/>
-      <c r="J171" s="21" t="n"/>
-      <c r="K171" s="19" t="n"/>
-      <c r="L171" s="20" t="n"/>
-      <c r="M171" s="21" t="n"/>
-      <c r="N171" s="19" t="n"/>
-      <c r="O171" s="20" t="n"/>
-      <c r="P171" s="21" t="n"/>
-      <c r="Q171" s="19" t="n"/>
-      <c r="R171" s="20" t="n"/>
-      <c r="S171" s="21" t="n"/>
-      <c r="T171" s="19" t="n"/>
-      <c r="U171" s="20" t="n"/>
-      <c r="V171" s="21" t="n"/>
+      <c r="B171" s="27" t="n"/>
+      <c r="C171" s="28" t="n"/>
+      <c r="D171" s="29" t="n"/>
+      <c r="E171" s="27" t="n"/>
+      <c r="F171" s="28" t="n"/>
+      <c r="G171" s="29" t="n"/>
+      <c r="H171" s="27" t="n"/>
+      <c r="I171" s="28" t="n"/>
+      <c r="J171" s="29" t="n"/>
+      <c r="K171" s="27" t="n"/>
+      <c r="L171" s="28" t="n"/>
+      <c r="M171" s="29" t="n"/>
+      <c r="N171" s="27" t="n"/>
+      <c r="O171" s="28" t="n"/>
+      <c r="P171" s="29" t="n"/>
+      <c r="Q171" s="27" t="n"/>
+      <c r="R171" s="28" t="n"/>
+      <c r="S171" s="29" t="n"/>
+      <c r="T171" s="27" t="n"/>
+      <c r="U171" s="28" t="n"/>
+      <c r="V171" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="K63:K73"/>
     <mergeCell ref="I111:I115"/>
-    <mergeCell ref="G54:G56"/>
     <mergeCell ref="T6:T8"/>
-    <mergeCell ref="K51:K61"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="U165:U169"/>
     <mergeCell ref="F165:F169"/>
+    <mergeCell ref="E54:E56"/>
     <mergeCell ref="I117:I121"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="U117:U121"/>
@@ -6033,8 +5932,8 @@
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="K81:K91"/>
+    <mergeCell ref="B54:B56"/>
     <mergeCell ref="F111:F115"/>
-    <mergeCell ref="D54:D56"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="K6:K8"/>
     <mergeCell ref="T1:V1"/>
@@ -6051,22 +5950,22 @@
     <mergeCell ref="C111:C115"/>
     <mergeCell ref="O111:O115"/>
     <mergeCell ref="T75:T85"/>
+    <mergeCell ref="K54:K56"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="L165:L169"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="O117:O121"/>
+    <mergeCell ref="B63:B73"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E63:E67"/>
+    <mergeCell ref="U111:U115"/>
     <mergeCell ref="Q54:Q56"/>
-    <mergeCell ref="U111:U115"/>
-    <mergeCell ref="B51:B61"/>
     <mergeCell ref="Q51:Q53"/>
     <mergeCell ref="H6:H8"/>
-    <mergeCell ref="E51:E55"/>
     <mergeCell ref="H51:H53"/>
     <mergeCell ref="I165:I169"/>
-    <mergeCell ref="M54:M56"/>
     <mergeCell ref="L117:L121"/>
     <mergeCell ref="T51:T53"/>
     <mergeCell ref="C117:C121"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -1220,25 +1220,53 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="16" t="n"/>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="13" t="n"/>
-      <c r="H9" s="16" t="n"/>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="13" t="n"/>
-      <c r="K9" s="16" t="n"/>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="13" t="n"/>
-      <c r="N9" s="16" t="n"/>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="16" t="n"/>
+      <c r="Q9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="R9" s="12" t="n"/>
       <c r="S9" s="13" t="n"/>
-      <c r="T9" s="16" t="n"/>
+      <c r="T9" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：起床介助</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="n"/>
       <c r="V9" s="13" t="n"/>
     </row>
@@ -1248,25 +1276,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="11" t="n"/>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="16" t="n"/>
+      <c r="H10" s="11" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="16" t="n"/>
+      <c r="K10" s="11" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="16" t="n"/>
+      <c r="N10" s="11" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="16" t="n"/>
+      <c r="Q10" s="11" t="n"/>
       <c r="R10" s="12" t="n"/>
       <c r="S10" s="13" t="n"/>
-      <c r="T10" s="16" t="n"/>
+      <c r="T10" s="11" t="n"/>
       <c r="U10" s="12" t="n"/>
       <c r="V10" s="13" t="n"/>
     </row>
@@ -1276,25 +1304,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="16" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="16" t="n"/>
+      <c r="H11" s="14" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="13" t="n"/>
-      <c r="K11" s="16" t="n"/>
+      <c r="K11" s="14" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="13" t="n"/>
-      <c r="N11" s="16" t="n"/>
+      <c r="N11" s="14" t="n"/>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="16" t="n"/>
+      <c r="Q11" s="14" t="n"/>
       <c r="R11" s="12" t="n"/>
       <c r="S11" s="13" t="n"/>
-      <c r="T11" s="16" t="n"/>
+      <c r="T11" s="14" t="n"/>
       <c r="U11" s="12" t="n"/>
       <c r="V11" s="13" t="n"/>
     </row>
@@ -2599,22 +2627,42 @@
       <c r="B57" s="16" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="16" t="n"/>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="F57" s="12" t="n"/>
       <c r="G57" s="13" t="n"/>
-      <c r="H57" s="16" t="n"/>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="13" t="n"/>
       <c r="K57" s="16" t="n"/>
       <c r="L57" s="12" t="n"/>
       <c r="M57" s="13" t="n"/>
-      <c r="N57" s="16" t="n"/>
+      <c r="N57" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="O57" s="12" t="n"/>
       <c r="P57" s="13" t="n"/>
-      <c r="Q57" s="16" t="n"/>
+      <c r="Q57" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="R57" s="12" t="n"/>
       <c r="S57" s="13" t="n"/>
-      <c r="T57" s="16" t="n"/>
+      <c r="T57" s="15" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="U57" s="12" t="n"/>
       <c r="V57" s="13" t="n"/>
     </row>
@@ -2627,22 +2675,22 @@
       <c r="B58" s="16" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="16" t="n"/>
+      <c r="E58" s="11" t="n"/>
       <c r="F58" s="12" t="n"/>
       <c r="G58" s="13" t="n"/>
-      <c r="H58" s="16" t="n"/>
+      <c r="H58" s="11" t="n"/>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="16" t="n"/>
       <c r="L58" s="12" t="n"/>
       <c r="M58" s="13" t="n"/>
-      <c r="N58" s="16" t="n"/>
+      <c r="N58" s="11" t="n"/>
       <c r="O58" s="12" t="n"/>
       <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="16" t="n"/>
+      <c r="Q58" s="11" t="n"/>
       <c r="R58" s="12" t="n"/>
       <c r="S58" s="13" t="n"/>
-      <c r="T58" s="16" t="n"/>
+      <c r="T58" s="11" t="n"/>
       <c r="U58" s="12" t="n"/>
       <c r="V58" s="13" t="n"/>
     </row>
@@ -2655,22 +2703,22 @@
       <c r="B59" s="16" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="16" t="n"/>
+      <c r="E59" s="11" t="n"/>
       <c r="F59" s="12" t="n"/>
       <c r="G59" s="13" t="n"/>
-      <c r="H59" s="16" t="n"/>
+      <c r="H59" s="11" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="13" t="n"/>
       <c r="K59" s="16" t="n"/>
       <c r="L59" s="12" t="n"/>
       <c r="M59" s="13" t="n"/>
-      <c r="N59" s="16" t="n"/>
+      <c r="N59" s="11" t="n"/>
       <c r="O59" s="12" t="n"/>
       <c r="P59" s="13" t="n"/>
-      <c r="Q59" s="16" t="n"/>
+      <c r="Q59" s="11" t="n"/>
       <c r="R59" s="12" t="n"/>
       <c r="S59" s="13" t="n"/>
-      <c r="T59" s="16" t="n"/>
+      <c r="T59" s="11" t="n"/>
       <c r="U59" s="12" t="n"/>
       <c r="V59" s="13" t="n"/>
     </row>
@@ -2683,22 +2731,22 @@
       <c r="B60" s="16" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="16" t="n"/>
+      <c r="E60" s="11" t="n"/>
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="16" t="n"/>
+      <c r="H60" s="11" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="16" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="N60" s="16" t="n"/>
+      <c r="N60" s="11" t="n"/>
       <c r="O60" s="12" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="16" t="n"/>
+      <c r="Q60" s="11" t="n"/>
       <c r="R60" s="12" t="n"/>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="16" t="n"/>
+      <c r="T60" s="11" t="n"/>
       <c r="U60" s="12" t="n"/>
       <c r="V60" s="13" t="n"/>
     </row>
@@ -2711,22 +2759,22 @@
       <c r="B61" s="16" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
-      <c r="E61" s="16" t="n"/>
+      <c r="E61" s="11" t="n"/>
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="16" t="n"/>
+      <c r="H61" s="11" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
       <c r="K61" s="16" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
-      <c r="N61" s="16" t="n"/>
+      <c r="N61" s="11" t="n"/>
       <c r="O61" s="12" t="n"/>
       <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="16" t="n"/>
+      <c r="Q61" s="11" t="n"/>
       <c r="R61" s="12" t="n"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="16" t="n"/>
+      <c r="T61" s="11" t="n"/>
       <c r="U61" s="12" t="n"/>
       <c r="V61" s="13" t="n"/>
     </row>
@@ -2739,22 +2787,22 @@
       <c r="B62" s="18" t="n"/>
       <c r="C62" s="19" t="n"/>
       <c r="D62" s="20" t="n"/>
-      <c r="E62" s="18" t="n"/>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="19" t="n"/>
       <c r="G62" s="20" t="n"/>
-      <c r="H62" s="18" t="n"/>
+      <c r="H62" s="14" t="n"/>
       <c r="I62" s="19" t="n"/>
       <c r="J62" s="20" t="n"/>
       <c r="K62" s="18" t="n"/>
       <c r="L62" s="19" t="n"/>
       <c r="M62" s="20" t="n"/>
-      <c r="N62" s="18" t="n"/>
+      <c r="N62" s="14" t="n"/>
       <c r="O62" s="19" t="n"/>
       <c r="P62" s="20" t="n"/>
-      <c r="Q62" s="18" t="n"/>
+      <c r="Q62" s="14" t="n"/>
       <c r="R62" s="19" t="n"/>
       <c r="S62" s="20" t="n"/>
-      <c r="T62" s="18" t="n"/>
+      <c r="T62" s="14" t="n"/>
       <c r="U62" s="19" t="n"/>
       <c r="V62" s="20" t="n"/>
     </row>
@@ -3462,7 +3510,11 @@
       <c r="E87" s="21" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="21" t="n"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>藤本敏博：掃除</t>
+        </is>
+      </c>
       <c r="I87" s="8" t="n"/>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="11" t="n"/>
@@ -3490,7 +3542,7 @@
       <c r="E88" s="16" t="n"/>
       <c r="F88" s="12" t="n"/>
       <c r="G88" s="13" t="n"/>
-      <c r="H88" s="16" t="n"/>
+      <c r="H88" s="11" t="n"/>
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="11" t="n"/>
@@ -3518,7 +3570,7 @@
       <c r="E89" s="16" t="n"/>
       <c r="F89" s="12" t="n"/>
       <c r="G89" s="13" t="n"/>
-      <c r="H89" s="16" t="n"/>
+      <c r="H89" s="11" t="n"/>
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="13" t="n"/>
       <c r="K89" s="11" t="n"/>
@@ -3546,7 +3598,7 @@
       <c r="E90" s="16" t="n"/>
       <c r="F90" s="12" t="n"/>
       <c r="G90" s="13" t="n"/>
-      <c r="H90" s="16" t="n"/>
+      <c r="H90" s="11" t="n"/>
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="11" t="n"/>
@@ -3574,7 +3626,7 @@
       <c r="E91" s="16" t="n"/>
       <c r="F91" s="12" t="n"/>
       <c r="G91" s="13" t="n"/>
-      <c r="H91" s="16" t="n"/>
+      <c r="H91" s="14" t="n"/>
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="13" t="n"/>
       <c r="K91" s="14" t="n"/>
@@ -4521,25 +4573,53 @@
         </is>
       </c>
       <c r="B123" s="21" t="n"/>
-      <c r="C123" s="8" t="n"/>
+      <c r="C123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="D123" s="9" t="n"/>
       <c r="E123" s="21" t="n"/>
-      <c r="F123" s="8" t="n"/>
+      <c r="F123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="G123" s="9" t="n"/>
       <c r="H123" s="21" t="n"/>
-      <c r="I123" s="8" t="n"/>
+      <c r="I123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="J123" s="9" t="n"/>
       <c r="K123" s="21" t="n"/>
-      <c r="L123" s="8" t="n"/>
+      <c r="L123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="21" t="n"/>
-      <c r="O123" s="8" t="n"/>
+      <c r="O123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="21" t="n"/>
-      <c r="R123" s="8" t="n"/>
+      <c r="R123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="S123" s="9" t="n"/>
       <c r="T123" s="21" t="n"/>
-      <c r="U123" s="8" t="n"/>
+      <c r="U123" s="22" t="inlineStr">
+        <is>
+          <t>藤本敏博：排泄介助</t>
+        </is>
+      </c>
       <c r="V123" s="9" t="n"/>
     </row>
     <row r="124">
@@ -4549,25 +4629,25 @@
         </is>
       </c>
       <c r="B124" s="16" t="n"/>
-      <c r="C124" s="12" t="n"/>
+      <c r="C124" s="23" t="n"/>
       <c r="D124" s="13" t="n"/>
       <c r="E124" s="16" t="n"/>
-      <c r="F124" s="12" t="n"/>
+      <c r="F124" s="23" t="n"/>
       <c r="G124" s="13" t="n"/>
       <c r="H124" s="16" t="n"/>
-      <c r="I124" s="12" t="n"/>
+      <c r="I124" s="23" t="n"/>
       <c r="J124" s="13" t="n"/>
       <c r="K124" s="16" t="n"/>
-      <c r="L124" s="12" t="n"/>
+      <c r="L124" s="23" t="n"/>
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="16" t="n"/>
-      <c r="O124" s="12" t="n"/>
+      <c r="O124" s="23" t="n"/>
       <c r="P124" s="13" t="n"/>
       <c r="Q124" s="16" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="R124" s="23" t="n"/>
       <c r="S124" s="13" t="n"/>
       <c r="T124" s="16" t="n"/>
-      <c r="U124" s="12" t="n"/>
+      <c r="U124" s="23" t="n"/>
       <c r="V124" s="13" t="n"/>
     </row>
     <row r="125">
@@ -4577,25 +4657,25 @@
         </is>
       </c>
       <c r="B125" s="16" t="n"/>
-      <c r="C125" s="12" t="n"/>
+      <c r="C125" s="23" t="n"/>
       <c r="D125" s="13" t="n"/>
       <c r="E125" s="16" t="n"/>
-      <c r="F125" s="12" t="n"/>
+      <c r="F125" s="23" t="n"/>
       <c r="G125" s="13" t="n"/>
       <c r="H125" s="16" t="n"/>
-      <c r="I125" s="12" t="n"/>
+      <c r="I125" s="23" t="n"/>
       <c r="J125" s="13" t="n"/>
       <c r="K125" s="16" t="n"/>
-      <c r="L125" s="12" t="n"/>
+      <c r="L125" s="23" t="n"/>
       <c r="M125" s="13" t="n"/>
       <c r="N125" s="16" t="n"/>
-      <c r="O125" s="12" t="n"/>
+      <c r="O125" s="23" t="n"/>
       <c r="P125" s="13" t="n"/>
       <c r="Q125" s="16" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="R125" s="23" t="n"/>
       <c r="S125" s="13" t="n"/>
       <c r="T125" s="16" t="n"/>
-      <c r="U125" s="12" t="n"/>
+      <c r="U125" s="23" t="n"/>
       <c r="V125" s="13" t="n"/>
     </row>
     <row r="126">
@@ -4605,25 +4685,25 @@
         </is>
       </c>
       <c r="B126" s="16" t="n"/>
-      <c r="C126" s="12" t="n"/>
+      <c r="C126" s="23" t="n"/>
       <c r="D126" s="13" t="n"/>
       <c r="E126" s="16" t="n"/>
-      <c r="F126" s="12" t="n"/>
+      <c r="F126" s="23" t="n"/>
       <c r="G126" s="13" t="n"/>
       <c r="H126" s="16" t="n"/>
-      <c r="I126" s="12" t="n"/>
+      <c r="I126" s="23" t="n"/>
       <c r="J126" s="13" t="n"/>
       <c r="K126" s="16" t="n"/>
-      <c r="L126" s="12" t="n"/>
+      <c r="L126" s="23" t="n"/>
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="16" t="n"/>
-      <c r="O126" s="12" t="n"/>
+      <c r="O126" s="23" t="n"/>
       <c r="P126" s="13" t="n"/>
       <c r="Q126" s="16" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="R126" s="23" t="n"/>
       <c r="S126" s="13" t="n"/>
       <c r="T126" s="16" t="n"/>
-      <c r="U126" s="12" t="n"/>
+      <c r="U126" s="23" t="n"/>
       <c r="V126" s="13" t="n"/>
     </row>
     <row r="127">
@@ -4633,25 +4713,25 @@
         </is>
       </c>
       <c r="B127" s="16" t="n"/>
-      <c r="C127" s="12" t="n"/>
+      <c r="C127" s="24" t="n"/>
       <c r="D127" s="13" t="n"/>
       <c r="E127" s="16" t="n"/>
-      <c r="F127" s="12" t="n"/>
+      <c r="F127" s="24" t="n"/>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="16" t="n"/>
-      <c r="I127" s="12" t="n"/>
+      <c r="I127" s="24" t="n"/>
       <c r="J127" s="13" t="n"/>
       <c r="K127" s="16" t="n"/>
-      <c r="L127" s="12" t="n"/>
+      <c r="L127" s="24" t="n"/>
       <c r="M127" s="13" t="n"/>
       <c r="N127" s="16" t="n"/>
-      <c r="O127" s="12" t="n"/>
+      <c r="O127" s="24" t="n"/>
       <c r="P127" s="13" t="n"/>
       <c r="Q127" s="16" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="R127" s="24" t="n"/>
       <c r="S127" s="13" t="n"/>
       <c r="T127" s="16" t="n"/>
-      <c r="U127" s="12" t="n"/>
+      <c r="U127" s="24" t="n"/>
       <c r="V127" s="13" t="n"/>
     </row>
     <row r="128">
@@ -5915,14 +5995,19 @@
       <c r="V171" s="29" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="76">
+    <mergeCell ref="Q57:Q62"/>
+    <mergeCell ref="Q9:Q11"/>
     <mergeCell ref="K63:K73"/>
     <mergeCell ref="I111:I115"/>
+    <mergeCell ref="C123:C127"/>
     <mergeCell ref="T6:T8"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="U165:U169"/>
     <mergeCell ref="F165:F169"/>
+    <mergeCell ref="I123:I127"/>
+    <mergeCell ref="O123:O127"/>
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I117:I121"/>
     <mergeCell ref="N1:P1"/>
@@ -5933,11 +6018,17 @@
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="K81:K91"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="N9:N11"/>
     <mergeCell ref="F111:F115"/>
+    <mergeCell ref="T57:T62"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="K6:K8"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="T3:T5"/>
+    <mergeCell ref="U123:U127"/>
+    <mergeCell ref="F123:F127"/>
+    <mergeCell ref="H87:H91"/>
+    <mergeCell ref="L123:L127"/>
     <mergeCell ref="F117:F121"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="N51:N53"/>
@@ -5947,25 +6038,34 @@
     <mergeCell ref="R117:R121"/>
     <mergeCell ref="L111:L115"/>
     <mergeCell ref="R111:R115"/>
+    <mergeCell ref="K9:K11"/>
     <mergeCell ref="C111:C115"/>
     <mergeCell ref="O111:O115"/>
     <mergeCell ref="T75:T85"/>
+    <mergeCell ref="R123:R127"/>
     <mergeCell ref="K54:K56"/>
+    <mergeCell ref="E57:E62"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="L165:L169"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="O117:O121"/>
+    <mergeCell ref="H57:H62"/>
+    <mergeCell ref="N57:N62"/>
     <mergeCell ref="B63:B73"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="E63:E67"/>
     <mergeCell ref="U111:U115"/>
     <mergeCell ref="Q54:Q56"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="T9:T11"/>
     <mergeCell ref="Q51:Q53"/>
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="H51:H53"/>
     <mergeCell ref="I165:I169"/>
+    <mergeCell ref="B9:B11"/>
     <mergeCell ref="L117:L121"/>
     <mergeCell ref="T51:T53"/>
     <mergeCell ref="C117:C121"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -44,7 +44,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="23">
     <border>
@@ -384,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -405,13 +410,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -422,21 +427,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -810,25 +821,25 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2817,33 +2828,33 @@
           <t>林郁子：入浴掃除</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n"/>
+      <c r="C63" s="22" t="n"/>
       <c r="D63" s="9" t="n"/>
       <c r="E63" s="7" t="inlineStr">
         <is>
           <t>林郁子：買い物代行</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="22" t="n"/>
       <c r="G63" s="9" t="n"/>
       <c r="H63" s="21" t="n"/>
-      <c r="I63" s="8" t="n"/>
+      <c r="I63" s="22" t="n"/>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="7" t="inlineStr">
         <is>
           <t>林郁子：入浴掃除</t>
         </is>
       </c>
-      <c r="L63" s="8" t="n"/>
+      <c r="L63" s="22" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="21" t="n"/>
-      <c r="O63" s="8" t="n"/>
+      <c r="O63" s="22" t="n"/>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="21" t="n"/>
-      <c r="R63" s="8" t="n"/>
+      <c r="R63" s="22" t="n"/>
       <c r="S63" s="9" t="n"/>
       <c r="T63" s="21" t="n"/>
-      <c r="U63" s="8" t="n"/>
+      <c r="U63" s="22" t="n"/>
       <c r="V63" s="9" t="n"/>
     </row>
     <row r="64">
@@ -2853,25 +2864,25 @@
         </is>
       </c>
       <c r="B64" s="11" t="n"/>
-      <c r="C64" s="12" t="n"/>
+      <c r="C64" s="23" t="n"/>
       <c r="D64" s="13" t="n"/>
       <c r="E64" s="11" t="n"/>
-      <c r="F64" s="12" t="n"/>
+      <c r="F64" s="23" t="n"/>
       <c r="G64" s="13" t="n"/>
       <c r="H64" s="16" t="n"/>
-      <c r="I64" s="12" t="n"/>
+      <c r="I64" s="23" t="n"/>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="11" t="n"/>
-      <c r="L64" s="12" t="n"/>
+      <c r="L64" s="23" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="16" t="n"/>
-      <c r="O64" s="12" t="n"/>
+      <c r="O64" s="23" t="n"/>
       <c r="P64" s="13" t="n"/>
       <c r="Q64" s="16" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="R64" s="23" t="n"/>
       <c r="S64" s="13" t="n"/>
       <c r="T64" s="16" t="n"/>
-      <c r="U64" s="12" t="n"/>
+      <c r="U64" s="23" t="n"/>
       <c r="V64" s="13" t="n"/>
     </row>
     <row r="65">
@@ -2881,25 +2892,25 @@
         </is>
       </c>
       <c r="B65" s="11" t="n"/>
-      <c r="C65" s="12" t="n"/>
+      <c r="C65" s="23" t="n"/>
       <c r="D65" s="13" t="n"/>
       <c r="E65" s="11" t="n"/>
-      <c r="F65" s="12" t="n"/>
+      <c r="F65" s="23" t="n"/>
       <c r="G65" s="13" t="n"/>
       <c r="H65" s="16" t="n"/>
-      <c r="I65" s="12" t="n"/>
+      <c r="I65" s="23" t="n"/>
       <c r="J65" s="13" t="n"/>
       <c r="K65" s="11" t="n"/>
-      <c r="L65" s="12" t="n"/>
+      <c r="L65" s="23" t="n"/>
       <c r="M65" s="13" t="n"/>
       <c r="N65" s="16" t="n"/>
-      <c r="O65" s="12" t="n"/>
+      <c r="O65" s="23" t="n"/>
       <c r="P65" s="13" t="n"/>
       <c r="Q65" s="16" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="R65" s="23" t="n"/>
       <c r="S65" s="13" t="n"/>
       <c r="T65" s="16" t="n"/>
-      <c r="U65" s="12" t="n"/>
+      <c r="U65" s="23" t="n"/>
       <c r="V65" s="13" t="n"/>
     </row>
     <row r="66">
@@ -2909,25 +2920,25 @@
         </is>
       </c>
       <c r="B66" s="11" t="n"/>
-      <c r="C66" s="12" t="n"/>
+      <c r="C66" s="23" t="n"/>
       <c r="D66" s="13" t="n"/>
       <c r="E66" s="11" t="n"/>
-      <c r="F66" s="12" t="n"/>
+      <c r="F66" s="23" t="n"/>
       <c r="G66" s="13" t="n"/>
       <c r="H66" s="16" t="n"/>
-      <c r="I66" s="12" t="n"/>
+      <c r="I66" s="23" t="n"/>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="11" t="n"/>
-      <c r="L66" s="12" t="n"/>
+      <c r="L66" s="23" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="16" t="n"/>
-      <c r="O66" s="12" t="n"/>
+      <c r="O66" s="23" t="n"/>
       <c r="P66" s="13" t="n"/>
       <c r="Q66" s="16" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="R66" s="23" t="n"/>
       <c r="S66" s="13" t="n"/>
       <c r="T66" s="16" t="n"/>
-      <c r="U66" s="12" t="n"/>
+      <c r="U66" s="23" t="n"/>
       <c r="V66" s="13" t="n"/>
     </row>
     <row r="67">
@@ -2937,25 +2948,25 @@
         </is>
       </c>
       <c r="B67" s="11" t="n"/>
-      <c r="C67" s="12" t="n"/>
+      <c r="C67" s="23" t="n"/>
       <c r="D67" s="13" t="n"/>
       <c r="E67" s="14" t="n"/>
-      <c r="F67" s="12" t="n"/>
+      <c r="F67" s="23" t="n"/>
       <c r="G67" s="13" t="n"/>
       <c r="H67" s="16" t="n"/>
-      <c r="I67" s="12" t="n"/>
+      <c r="I67" s="23" t="n"/>
       <c r="J67" s="13" t="n"/>
       <c r="K67" s="11" t="n"/>
-      <c r="L67" s="12" t="n"/>
+      <c r="L67" s="23" t="n"/>
       <c r="M67" s="13" t="n"/>
       <c r="N67" s="16" t="n"/>
-      <c r="O67" s="12" t="n"/>
+      <c r="O67" s="23" t="n"/>
       <c r="P67" s="13" t="n"/>
       <c r="Q67" s="16" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="R67" s="23" t="n"/>
       <c r="S67" s="13" t="n"/>
       <c r="T67" s="16" t="n"/>
-      <c r="U67" s="12" t="n"/>
+      <c r="U67" s="23" t="n"/>
       <c r="V67" s="13" t="n"/>
     </row>
     <row r="68">
@@ -2965,25 +2976,25 @@
         </is>
       </c>
       <c r="B68" s="11" t="n"/>
-      <c r="C68" s="12" t="n"/>
+      <c r="C68" s="23" t="n"/>
       <c r="D68" s="13" t="n"/>
       <c r="E68" s="16" t="n"/>
-      <c r="F68" s="12" t="n"/>
+      <c r="F68" s="23" t="n"/>
       <c r="G68" s="13" t="n"/>
       <c r="H68" s="16" t="n"/>
-      <c r="I68" s="12" t="n"/>
+      <c r="I68" s="23" t="n"/>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="11" t="n"/>
-      <c r="L68" s="12" t="n"/>
+      <c r="L68" s="23" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="16" t="n"/>
-      <c r="O68" s="12" t="n"/>
+      <c r="O68" s="23" t="n"/>
       <c r="P68" s="13" t="n"/>
       <c r="Q68" s="16" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="R68" s="23" t="n"/>
       <c r="S68" s="13" t="n"/>
       <c r="T68" s="16" t="n"/>
-      <c r="U68" s="12" t="n"/>
+      <c r="U68" s="23" t="n"/>
       <c r="V68" s="13" t="n"/>
     </row>
     <row r="69">
@@ -2993,25 +3004,25 @@
         </is>
       </c>
       <c r="B69" s="11" t="n"/>
-      <c r="C69" s="12" t="n"/>
+      <c r="C69" s="23" t="n"/>
       <c r="D69" s="13" t="n"/>
       <c r="E69" s="16" t="n"/>
-      <c r="F69" s="12" t="n"/>
+      <c r="F69" s="23" t="n"/>
       <c r="G69" s="13" t="n"/>
       <c r="H69" s="16" t="n"/>
-      <c r="I69" s="12" t="n"/>
+      <c r="I69" s="23" t="n"/>
       <c r="J69" s="13" t="n"/>
       <c r="K69" s="11" t="n"/>
-      <c r="L69" s="12" t="n"/>
+      <c r="L69" s="23" t="n"/>
       <c r="M69" s="13" t="n"/>
       <c r="N69" s="16" t="n"/>
-      <c r="O69" s="12" t="n"/>
+      <c r="O69" s="23" t="n"/>
       <c r="P69" s="13" t="n"/>
       <c r="Q69" s="16" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="R69" s="23" t="n"/>
       <c r="S69" s="13" t="n"/>
       <c r="T69" s="16" t="n"/>
-      <c r="U69" s="12" t="n"/>
+      <c r="U69" s="23" t="n"/>
       <c r="V69" s="13" t="n"/>
     </row>
     <row r="70">
@@ -3021,25 +3032,25 @@
         </is>
       </c>
       <c r="B70" s="11" t="n"/>
-      <c r="C70" s="12" t="n"/>
+      <c r="C70" s="23" t="n"/>
       <c r="D70" s="13" t="n"/>
       <c r="E70" s="16" t="n"/>
-      <c r="F70" s="12" t="n"/>
+      <c r="F70" s="23" t="n"/>
       <c r="G70" s="13" t="n"/>
       <c r="H70" s="16" t="n"/>
-      <c r="I70" s="12" t="n"/>
+      <c r="I70" s="23" t="n"/>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="11" t="n"/>
-      <c r="L70" s="12" t="n"/>
+      <c r="L70" s="23" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="16" t="n"/>
-      <c r="O70" s="12" t="n"/>
+      <c r="O70" s="23" t="n"/>
       <c r="P70" s="13" t="n"/>
       <c r="Q70" s="16" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="R70" s="23" t="n"/>
       <c r="S70" s="13" t="n"/>
       <c r="T70" s="16" t="n"/>
-      <c r="U70" s="12" t="n"/>
+      <c r="U70" s="23" t="n"/>
       <c r="V70" s="13" t="n"/>
     </row>
     <row r="71">
@@ -3049,25 +3060,25 @@
         </is>
       </c>
       <c r="B71" s="11" t="n"/>
-      <c r="C71" s="12" t="n"/>
+      <c r="C71" s="23" t="n"/>
       <c r="D71" s="13" t="n"/>
       <c r="E71" s="16" t="n"/>
-      <c r="F71" s="12" t="n"/>
+      <c r="F71" s="23" t="n"/>
       <c r="G71" s="13" t="n"/>
       <c r="H71" s="16" t="n"/>
-      <c r="I71" s="12" t="n"/>
+      <c r="I71" s="23" t="n"/>
       <c r="J71" s="13" t="n"/>
       <c r="K71" s="11" t="n"/>
-      <c r="L71" s="12" t="n"/>
+      <c r="L71" s="23" t="n"/>
       <c r="M71" s="13" t="n"/>
       <c r="N71" s="16" t="n"/>
-      <c r="O71" s="12" t="n"/>
+      <c r="O71" s="23" t="n"/>
       <c r="P71" s="13" t="n"/>
       <c r="Q71" s="16" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="R71" s="23" t="n"/>
       <c r="S71" s="13" t="n"/>
       <c r="T71" s="16" t="n"/>
-      <c r="U71" s="12" t="n"/>
+      <c r="U71" s="23" t="n"/>
       <c r="V71" s="13" t="n"/>
     </row>
     <row r="72">
@@ -3077,25 +3088,25 @@
         </is>
       </c>
       <c r="B72" s="11" t="n"/>
-      <c r="C72" s="12" t="n"/>
+      <c r="C72" s="23" t="n"/>
       <c r="D72" s="13" t="n"/>
       <c r="E72" s="16" t="n"/>
-      <c r="F72" s="12" t="n"/>
+      <c r="F72" s="23" t="n"/>
       <c r="G72" s="13" t="n"/>
       <c r="H72" s="16" t="n"/>
-      <c r="I72" s="12" t="n"/>
+      <c r="I72" s="23" t="n"/>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="11" t="n"/>
-      <c r="L72" s="12" t="n"/>
+      <c r="L72" s="23" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="16" t="n"/>
-      <c r="O72" s="12" t="n"/>
+      <c r="O72" s="23" t="n"/>
       <c r="P72" s="13" t="n"/>
       <c r="Q72" s="16" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="R72" s="23" t="n"/>
       <c r="S72" s="13" t="n"/>
       <c r="T72" s="16" t="n"/>
-      <c r="U72" s="12" t="n"/>
+      <c r="U72" s="23" t="n"/>
       <c r="V72" s="13" t="n"/>
     </row>
     <row r="73">
@@ -3105,25 +3116,25 @@
         </is>
       </c>
       <c r="B73" s="14" t="n"/>
-      <c r="C73" s="12" t="n"/>
+      <c r="C73" s="23" t="n"/>
       <c r="D73" s="13" t="n"/>
       <c r="E73" s="16" t="n"/>
-      <c r="F73" s="12" t="n"/>
+      <c r="F73" s="23" t="n"/>
       <c r="G73" s="13" t="n"/>
       <c r="H73" s="16" t="n"/>
-      <c r="I73" s="12" t="n"/>
+      <c r="I73" s="23" t="n"/>
       <c r="J73" s="13" t="n"/>
       <c r="K73" s="14" t="n"/>
-      <c r="L73" s="12" t="n"/>
+      <c r="L73" s="23" t="n"/>
       <c r="M73" s="13" t="n"/>
       <c r="N73" s="16" t="n"/>
-      <c r="O73" s="12" t="n"/>
+      <c r="O73" s="23" t="n"/>
       <c r="P73" s="13" t="n"/>
       <c r="Q73" s="16" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="R73" s="23" t="n"/>
       <c r="S73" s="13" t="n"/>
       <c r="T73" s="16" t="n"/>
-      <c r="U73" s="12" t="n"/>
+      <c r="U73" s="23" t="n"/>
       <c r="V73" s="13" t="n"/>
     </row>
     <row r="74">
@@ -3133,25 +3144,25 @@
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
-      <c r="C74" s="19" t="n"/>
+      <c r="C74" s="24" t="n"/>
       <c r="D74" s="20" t="n"/>
       <c r="E74" s="18" t="n"/>
-      <c r="F74" s="19" t="n"/>
+      <c r="F74" s="24" t="n"/>
       <c r="G74" s="20" t="n"/>
       <c r="H74" s="18" t="n"/>
-      <c r="I74" s="19" t="n"/>
+      <c r="I74" s="24" t="n"/>
       <c r="J74" s="20" t="n"/>
       <c r="K74" s="18" t="n"/>
-      <c r="L74" s="19" t="n"/>
+      <c r="L74" s="24" t="n"/>
       <c r="M74" s="20" t="n"/>
       <c r="N74" s="18" t="n"/>
-      <c r="O74" s="19" t="n"/>
+      <c r="O74" s="24" t="n"/>
       <c r="P74" s="20" t="n"/>
       <c r="Q74" s="18" t="n"/>
-      <c r="R74" s="19" t="n"/>
+      <c r="R74" s="24" t="n"/>
       <c r="S74" s="20" t="n"/>
       <c r="T74" s="18" t="n"/>
-      <c r="U74" s="19" t="n"/>
+      <c r="U74" s="24" t="n"/>
       <c r="V74" s="20" t="n"/>
     </row>
     <row r="75">
@@ -3161,29 +3172,29 @@
         </is>
       </c>
       <c r="B75" s="21" t="n"/>
-      <c r="C75" s="8" t="n"/>
+      <c r="C75" s="22" t="n"/>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="21" t="n"/>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="22" t="n"/>
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="21" t="n"/>
-      <c r="I75" s="8" t="n"/>
+      <c r="I75" s="22" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="21" t="n"/>
-      <c r="L75" s="8" t="n"/>
+      <c r="L75" s="22" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="21" t="n"/>
-      <c r="O75" s="8" t="n"/>
+      <c r="O75" s="22" t="n"/>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="21" t="n"/>
-      <c r="R75" s="8" t="n"/>
+      <c r="R75" s="22" t="n"/>
       <c r="S75" s="9" t="n"/>
       <c r="T75" s="7" t="inlineStr">
         <is>
           <t>長谷部融子：外出</t>
         </is>
       </c>
-      <c r="U75" s="8" t="n"/>
+      <c r="U75" s="22" t="n"/>
       <c r="V75" s="9" t="n"/>
     </row>
     <row r="76">
@@ -3193,25 +3204,25 @@
         </is>
       </c>
       <c r="B76" s="16" t="n"/>
-      <c r="C76" s="12" t="n"/>
+      <c r="C76" s="23" t="n"/>
       <c r="D76" s="13" t="n"/>
       <c r="E76" s="16" t="n"/>
-      <c r="F76" s="12" t="n"/>
+      <c r="F76" s="23" t="n"/>
       <c r="G76" s="13" t="n"/>
       <c r="H76" s="16" t="n"/>
-      <c r="I76" s="12" t="n"/>
+      <c r="I76" s="23" t="n"/>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="16" t="n"/>
-      <c r="L76" s="12" t="n"/>
+      <c r="L76" s="23" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="16" t="n"/>
-      <c r="O76" s="12" t="n"/>
+      <c r="O76" s="23" t="n"/>
       <c r="P76" s="13" t="n"/>
       <c r="Q76" s="16" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="R76" s="23" t="n"/>
       <c r="S76" s="13" t="n"/>
       <c r="T76" s="11" t="n"/>
-      <c r="U76" s="12" t="n"/>
+      <c r="U76" s="23" t="n"/>
       <c r="V76" s="13" t="n"/>
     </row>
     <row r="77">
@@ -3221,25 +3232,25 @@
         </is>
       </c>
       <c r="B77" s="16" t="n"/>
-      <c r="C77" s="12" t="n"/>
+      <c r="C77" s="23" t="n"/>
       <c r="D77" s="13" t="n"/>
       <c r="E77" s="16" t="n"/>
-      <c r="F77" s="12" t="n"/>
+      <c r="F77" s="23" t="n"/>
       <c r="G77" s="13" t="n"/>
       <c r="H77" s="16" t="n"/>
-      <c r="I77" s="12" t="n"/>
+      <c r="I77" s="23" t="n"/>
       <c r="J77" s="13" t="n"/>
       <c r="K77" s="16" t="n"/>
-      <c r="L77" s="12" t="n"/>
+      <c r="L77" s="23" t="n"/>
       <c r="M77" s="13" t="n"/>
       <c r="N77" s="16" t="n"/>
-      <c r="O77" s="12" t="n"/>
+      <c r="O77" s="23" t="n"/>
       <c r="P77" s="13" t="n"/>
       <c r="Q77" s="16" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="R77" s="23" t="n"/>
       <c r="S77" s="13" t="n"/>
       <c r="T77" s="11" t="n"/>
-      <c r="U77" s="12" t="n"/>
+      <c r="U77" s="23" t="n"/>
       <c r="V77" s="13" t="n"/>
     </row>
     <row r="78">
@@ -3249,25 +3260,25 @@
         </is>
       </c>
       <c r="B78" s="16" t="n"/>
-      <c r="C78" s="12" t="n"/>
+      <c r="C78" s="23" t="n"/>
       <c r="D78" s="13" t="n"/>
       <c r="E78" s="16" t="n"/>
-      <c r="F78" s="12" t="n"/>
+      <c r="F78" s="23" t="n"/>
       <c r="G78" s="13" t="n"/>
       <c r="H78" s="16" t="n"/>
-      <c r="I78" s="12" t="n"/>
+      <c r="I78" s="23" t="n"/>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="16" t="n"/>
-      <c r="L78" s="12" t="n"/>
+      <c r="L78" s="23" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="16" t="n"/>
-      <c r="O78" s="12" t="n"/>
+      <c r="O78" s="23" t="n"/>
       <c r="P78" s="13" t="n"/>
       <c r="Q78" s="16" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="R78" s="23" t="n"/>
       <c r="S78" s="13" t="n"/>
       <c r="T78" s="11" t="n"/>
-      <c r="U78" s="12" t="n"/>
+      <c r="U78" s="23" t="n"/>
       <c r="V78" s="13" t="n"/>
     </row>
     <row r="79">
@@ -3277,25 +3288,25 @@
         </is>
       </c>
       <c r="B79" s="16" t="n"/>
-      <c r="C79" s="12" t="n"/>
+      <c r="C79" s="23" t="n"/>
       <c r="D79" s="13" t="n"/>
       <c r="E79" s="16" t="n"/>
-      <c r="F79" s="12" t="n"/>
+      <c r="F79" s="23" t="n"/>
       <c r="G79" s="13" t="n"/>
       <c r="H79" s="16" t="n"/>
-      <c r="I79" s="12" t="n"/>
+      <c r="I79" s="23" t="n"/>
       <c r="J79" s="13" t="n"/>
       <c r="K79" s="16" t="n"/>
-      <c r="L79" s="12" t="n"/>
+      <c r="L79" s="23" t="n"/>
       <c r="M79" s="13" t="n"/>
       <c r="N79" s="16" t="n"/>
-      <c r="O79" s="12" t="n"/>
+      <c r="O79" s="23" t="n"/>
       <c r="P79" s="13" t="n"/>
       <c r="Q79" s="16" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="R79" s="23" t="n"/>
       <c r="S79" s="13" t="n"/>
       <c r="T79" s="11" t="n"/>
-      <c r="U79" s="12" t="n"/>
+      <c r="U79" s="23" t="n"/>
       <c r="V79" s="13" t="n"/>
     </row>
     <row r="80">
@@ -3305,25 +3316,25 @@
         </is>
       </c>
       <c r="B80" s="16" t="n"/>
-      <c r="C80" s="12" t="n"/>
+      <c r="C80" s="23" t="n"/>
       <c r="D80" s="13" t="n"/>
       <c r="E80" s="16" t="n"/>
-      <c r="F80" s="12" t="n"/>
+      <c r="F80" s="23" t="n"/>
       <c r="G80" s="13" t="n"/>
       <c r="H80" s="16" t="n"/>
-      <c r="I80" s="12" t="n"/>
+      <c r="I80" s="23" t="n"/>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="16" t="n"/>
-      <c r="L80" s="12" t="n"/>
+      <c r="L80" s="23" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="16" t="n"/>
-      <c r="O80" s="12" t="n"/>
+      <c r="O80" s="23" t="n"/>
       <c r="P80" s="13" t="n"/>
       <c r="Q80" s="16" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="R80" s="23" t="n"/>
       <c r="S80" s="13" t="n"/>
       <c r="T80" s="11" t="n"/>
-      <c r="U80" s="12" t="n"/>
+      <c r="U80" s="23" t="n"/>
       <c r="V80" s="13" t="n"/>
     </row>
     <row r="81">
@@ -3333,29 +3344,29 @@
         </is>
       </c>
       <c r="B81" s="16" t="n"/>
-      <c r="C81" s="12" t="n"/>
+      <c r="C81" s="23" t="n"/>
       <c r="D81" s="13" t="n"/>
       <c r="E81" s="16" t="n"/>
-      <c r="F81" s="12" t="n"/>
+      <c r="F81" s="23" t="n"/>
       <c r="G81" s="13" t="n"/>
       <c r="H81" s="16" t="n"/>
-      <c r="I81" s="12" t="n"/>
+      <c r="I81" s="23" t="n"/>
       <c r="J81" s="13" t="n"/>
       <c r="K81" s="15" t="inlineStr">
         <is>
           <t>長谷部融子：掃除</t>
         </is>
       </c>
-      <c r="L81" s="12" t="n"/>
+      <c r="L81" s="23" t="n"/>
       <c r="M81" s="13" t="n"/>
       <c r="N81" s="16" t="n"/>
-      <c r="O81" s="12" t="n"/>
+      <c r="O81" s="23" t="n"/>
       <c r="P81" s="13" t="n"/>
       <c r="Q81" s="16" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="R81" s="23" t="n"/>
       <c r="S81" s="13" t="n"/>
       <c r="T81" s="11" t="n"/>
-      <c r="U81" s="12" t="n"/>
+      <c r="U81" s="23" t="n"/>
       <c r="V81" s="13" t="n"/>
     </row>
     <row r="82">
@@ -3365,25 +3376,25 @@
         </is>
       </c>
       <c r="B82" s="16" t="n"/>
-      <c r="C82" s="12" t="n"/>
+      <c r="C82" s="23" t="n"/>
       <c r="D82" s="13" t="n"/>
       <c r="E82" s="16" t="n"/>
-      <c r="F82" s="12" t="n"/>
+      <c r="F82" s="23" t="n"/>
       <c r="G82" s="13" t="n"/>
       <c r="H82" s="16" t="n"/>
-      <c r="I82" s="12" t="n"/>
+      <c r="I82" s="23" t="n"/>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="11" t="n"/>
-      <c r="L82" s="12" t="n"/>
+      <c r="L82" s="23" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="16" t="n"/>
-      <c r="O82" s="12" t="n"/>
+      <c r="O82" s="23" t="n"/>
       <c r="P82" s="13" t="n"/>
       <c r="Q82" s="16" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="R82" s="23" t="n"/>
       <c r="S82" s="13" t="n"/>
       <c r="T82" s="11" t="n"/>
-      <c r="U82" s="12" t="n"/>
+      <c r="U82" s="23" t="n"/>
       <c r="V82" s="13" t="n"/>
     </row>
     <row r="83">
@@ -3393,25 +3404,25 @@
         </is>
       </c>
       <c r="B83" s="16" t="n"/>
-      <c r="C83" s="12" t="n"/>
+      <c r="C83" s="23" t="n"/>
       <c r="D83" s="13" t="n"/>
       <c r="E83" s="16" t="n"/>
-      <c r="F83" s="12" t="n"/>
+      <c r="F83" s="23" t="n"/>
       <c r="G83" s="13" t="n"/>
       <c r="H83" s="16" t="n"/>
-      <c r="I83" s="12" t="n"/>
+      <c r="I83" s="23" t="n"/>
       <c r="J83" s="13" t="n"/>
       <c r="K83" s="11" t="n"/>
-      <c r="L83" s="12" t="n"/>
+      <c r="L83" s="23" t="n"/>
       <c r="M83" s="13" t="n"/>
       <c r="N83" s="16" t="n"/>
-      <c r="O83" s="12" t="n"/>
+      <c r="O83" s="23" t="n"/>
       <c r="P83" s="13" t="n"/>
       <c r="Q83" s="16" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="R83" s="23" t="n"/>
       <c r="S83" s="13" t="n"/>
       <c r="T83" s="11" t="n"/>
-      <c r="U83" s="12" t="n"/>
+      <c r="U83" s="23" t="n"/>
       <c r="V83" s="13" t="n"/>
     </row>
     <row r="84">
@@ -3421,25 +3432,25 @@
         </is>
       </c>
       <c r="B84" s="16" t="n"/>
-      <c r="C84" s="12" t="n"/>
+      <c r="C84" s="23" t="n"/>
       <c r="D84" s="13" t="n"/>
       <c r="E84" s="16" t="n"/>
-      <c r="F84" s="12" t="n"/>
+      <c r="F84" s="23" t="n"/>
       <c r="G84" s="13" t="n"/>
       <c r="H84" s="16" t="n"/>
-      <c r="I84" s="12" t="n"/>
+      <c r="I84" s="23" t="n"/>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="11" t="n"/>
-      <c r="L84" s="12" t="n"/>
+      <c r="L84" s="23" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="16" t="n"/>
-      <c r="O84" s="12" t="n"/>
+      <c r="O84" s="23" t="n"/>
       <c r="P84" s="13" t="n"/>
       <c r="Q84" s="16" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="R84" s="23" t="n"/>
       <c r="S84" s="13" t="n"/>
       <c r="T84" s="11" t="n"/>
-      <c r="U84" s="12" t="n"/>
+      <c r="U84" s="23" t="n"/>
       <c r="V84" s="13" t="n"/>
     </row>
     <row r="85">
@@ -3449,25 +3460,25 @@
         </is>
       </c>
       <c r="B85" s="16" t="n"/>
-      <c r="C85" s="12" t="n"/>
+      <c r="C85" s="23" t="n"/>
       <c r="D85" s="13" t="n"/>
       <c r="E85" s="16" t="n"/>
-      <c r="F85" s="12" t="n"/>
+      <c r="F85" s="23" t="n"/>
       <c r="G85" s="13" t="n"/>
       <c r="H85" s="16" t="n"/>
-      <c r="I85" s="12" t="n"/>
+      <c r="I85" s="23" t="n"/>
       <c r="J85" s="13" t="n"/>
       <c r="K85" s="11" t="n"/>
-      <c r="L85" s="12" t="n"/>
+      <c r="L85" s="23" t="n"/>
       <c r="M85" s="13" t="n"/>
       <c r="N85" s="16" t="n"/>
-      <c r="O85" s="12" t="n"/>
+      <c r="O85" s="23" t="n"/>
       <c r="P85" s="13" t="n"/>
       <c r="Q85" s="16" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="R85" s="23" t="n"/>
       <c r="S85" s="13" t="n"/>
       <c r="T85" s="14" t="n"/>
-      <c r="U85" s="12" t="n"/>
+      <c r="U85" s="23" t="n"/>
       <c r="V85" s="13" t="n"/>
     </row>
     <row r="86">
@@ -3477,25 +3488,25 @@
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
-      <c r="C86" s="19" t="n"/>
+      <c r="C86" s="24" t="n"/>
       <c r="D86" s="20" t="n"/>
       <c r="E86" s="18" t="n"/>
-      <c r="F86" s="19" t="n"/>
+      <c r="F86" s="24" t="n"/>
       <c r="G86" s="20" t="n"/>
       <c r="H86" s="18" t="n"/>
-      <c r="I86" s="19" t="n"/>
+      <c r="I86" s="24" t="n"/>
       <c r="J86" s="20" t="n"/>
       <c r="K86" s="11" t="n"/>
-      <c r="L86" s="19" t="n"/>
+      <c r="L86" s="24" t="n"/>
       <c r="M86" s="20" t="n"/>
       <c r="N86" s="18" t="n"/>
-      <c r="O86" s="19" t="n"/>
+      <c r="O86" s="24" t="n"/>
       <c r="P86" s="20" t="n"/>
       <c r="Q86" s="18" t="n"/>
-      <c r="R86" s="19" t="n"/>
+      <c r="R86" s="24" t="n"/>
       <c r="S86" s="20" t="n"/>
       <c r="T86" s="18" t="n"/>
-      <c r="U86" s="19" t="n"/>
+      <c r="U86" s="24" t="n"/>
       <c r="V86" s="20" t="n"/>
     </row>
     <row r="87">
@@ -3505,29 +3516,29 @@
         </is>
       </c>
       <c r="B87" s="21" t="n"/>
-      <c r="C87" s="8" t="n"/>
+      <c r="C87" s="22" t="n"/>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="21" t="n"/>
-      <c r="F87" s="8" t="n"/>
+      <c r="F87" s="22" t="n"/>
       <c r="G87" s="9" t="n"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
           <t>藤本敏博：掃除</t>
         </is>
       </c>
-      <c r="I87" s="8" t="n"/>
+      <c r="I87" s="22" t="n"/>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="11" t="n"/>
-      <c r="L87" s="8" t="n"/>
+      <c r="L87" s="22" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="21" t="n"/>
-      <c r="O87" s="8" t="n"/>
+      <c r="O87" s="22" t="n"/>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="21" t="n"/>
-      <c r="R87" s="8" t="n"/>
+      <c r="R87" s="22" t="n"/>
       <c r="S87" s="9" t="n"/>
       <c r="T87" s="21" t="n"/>
-      <c r="U87" s="8" t="n"/>
+      <c r="U87" s="22" t="n"/>
       <c r="V87" s="9" t="n"/>
     </row>
     <row r="88">
@@ -3537,25 +3548,25 @@
         </is>
       </c>
       <c r="B88" s="16" t="n"/>
-      <c r="C88" s="12" t="n"/>
+      <c r="C88" s="23" t="n"/>
       <c r="D88" s="13" t="n"/>
       <c r="E88" s="16" t="n"/>
-      <c r="F88" s="12" t="n"/>
+      <c r="F88" s="23" t="n"/>
       <c r="G88" s="13" t="n"/>
       <c r="H88" s="11" t="n"/>
-      <c r="I88" s="12" t="n"/>
+      <c r="I88" s="23" t="n"/>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="11" t="n"/>
-      <c r="L88" s="12" t="n"/>
+      <c r="L88" s="23" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="16" t="n"/>
-      <c r="O88" s="12" t="n"/>
+      <c r="O88" s="23" t="n"/>
       <c r="P88" s="13" t="n"/>
       <c r="Q88" s="16" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="R88" s="23" t="n"/>
       <c r="S88" s="13" t="n"/>
       <c r="T88" s="16" t="n"/>
-      <c r="U88" s="12" t="n"/>
+      <c r="U88" s="23" t="n"/>
       <c r="V88" s="13" t="n"/>
     </row>
     <row r="89">
@@ -3565,25 +3576,25 @@
         </is>
       </c>
       <c r="B89" s="16" t="n"/>
-      <c r="C89" s="12" t="n"/>
+      <c r="C89" s="23" t="n"/>
       <c r="D89" s="13" t="n"/>
       <c r="E89" s="16" t="n"/>
-      <c r="F89" s="12" t="n"/>
+      <c r="F89" s="23" t="n"/>
       <c r="G89" s="13" t="n"/>
       <c r="H89" s="11" t="n"/>
-      <c r="I89" s="12" t="n"/>
+      <c r="I89" s="23" t="n"/>
       <c r="J89" s="13" t="n"/>
       <c r="K89" s="11" t="n"/>
-      <c r="L89" s="12" t="n"/>
+      <c r="L89" s="23" t="n"/>
       <c r="M89" s="13" t="n"/>
       <c r="N89" s="16" t="n"/>
-      <c r="O89" s="12" t="n"/>
+      <c r="O89" s="23" t="n"/>
       <c r="P89" s="13" t="n"/>
       <c r="Q89" s="16" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="R89" s="23" t="n"/>
       <c r="S89" s="13" t="n"/>
       <c r="T89" s="16" t="n"/>
-      <c r="U89" s="12" t="n"/>
+      <c r="U89" s="23" t="n"/>
       <c r="V89" s="13" t="n"/>
     </row>
     <row r="90">
@@ -3593,25 +3604,25 @@
         </is>
       </c>
       <c r="B90" s="16" t="n"/>
-      <c r="C90" s="12" t="n"/>
+      <c r="C90" s="23" t="n"/>
       <c r="D90" s="13" t="n"/>
       <c r="E90" s="16" t="n"/>
-      <c r="F90" s="12" t="n"/>
+      <c r="F90" s="23" t="n"/>
       <c r="G90" s="13" t="n"/>
       <c r="H90" s="11" t="n"/>
-      <c r="I90" s="12" t="n"/>
+      <c r="I90" s="23" t="n"/>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="11" t="n"/>
-      <c r="L90" s="12" t="n"/>
+      <c r="L90" s="23" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="16" t="n"/>
-      <c r="O90" s="12" t="n"/>
+      <c r="O90" s="23" t="n"/>
       <c r="P90" s="13" t="n"/>
       <c r="Q90" s="16" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="R90" s="23" t="n"/>
       <c r="S90" s="13" t="n"/>
       <c r="T90" s="16" t="n"/>
-      <c r="U90" s="12" t="n"/>
+      <c r="U90" s="23" t="n"/>
       <c r="V90" s="13" t="n"/>
     </row>
     <row r="91">
@@ -3621,25 +3632,25 @@
         </is>
       </c>
       <c r="B91" s="16" t="n"/>
-      <c r="C91" s="12" t="n"/>
+      <c r="C91" s="23" t="n"/>
       <c r="D91" s="13" t="n"/>
       <c r="E91" s="16" t="n"/>
-      <c r="F91" s="12" t="n"/>
+      <c r="F91" s="23" t="n"/>
       <c r="G91" s="13" t="n"/>
       <c r="H91" s="14" t="n"/>
-      <c r="I91" s="12" t="n"/>
+      <c r="I91" s="23" t="n"/>
       <c r="J91" s="13" t="n"/>
       <c r="K91" s="14" t="n"/>
-      <c r="L91" s="12" t="n"/>
+      <c r="L91" s="23" t="n"/>
       <c r="M91" s="13" t="n"/>
       <c r="N91" s="16" t="n"/>
-      <c r="O91" s="12" t="n"/>
+      <c r="O91" s="23" t="n"/>
       <c r="P91" s="13" t="n"/>
       <c r="Q91" s="16" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="R91" s="23" t="n"/>
       <c r="S91" s="13" t="n"/>
       <c r="T91" s="16" t="n"/>
-      <c r="U91" s="12" t="n"/>
+      <c r="U91" s="23" t="n"/>
       <c r="V91" s="13" t="n"/>
     </row>
     <row r="92">
@@ -3649,25 +3660,25 @@
         </is>
       </c>
       <c r="B92" s="16" t="n"/>
-      <c r="C92" s="12" t="n"/>
+      <c r="C92" s="23" t="n"/>
       <c r="D92" s="13" t="n"/>
       <c r="E92" s="16" t="n"/>
-      <c r="F92" s="12" t="n"/>
+      <c r="F92" s="23" t="n"/>
       <c r="G92" s="13" t="n"/>
       <c r="H92" s="16" t="n"/>
-      <c r="I92" s="12" t="n"/>
+      <c r="I92" s="23" t="n"/>
       <c r="J92" s="13" t="n"/>
       <c r="K92" s="16" t="n"/>
-      <c r="L92" s="12" t="n"/>
+      <c r="L92" s="23" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="16" t="n"/>
-      <c r="O92" s="12" t="n"/>
+      <c r="O92" s="23" t="n"/>
       <c r="P92" s="13" t="n"/>
       <c r="Q92" s="16" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="R92" s="23" t="n"/>
       <c r="S92" s="13" t="n"/>
       <c r="T92" s="16" t="n"/>
-      <c r="U92" s="12" t="n"/>
+      <c r="U92" s="23" t="n"/>
       <c r="V92" s="13" t="n"/>
     </row>
     <row r="93">
@@ -3677,25 +3688,25 @@
         </is>
       </c>
       <c r="B93" s="16" t="n"/>
-      <c r="C93" s="12" t="n"/>
+      <c r="C93" s="23" t="n"/>
       <c r="D93" s="13" t="n"/>
       <c r="E93" s="16" t="n"/>
-      <c r="F93" s="12" t="n"/>
+      <c r="F93" s="23" t="n"/>
       <c r="G93" s="13" t="n"/>
       <c r="H93" s="16" t="n"/>
-      <c r="I93" s="12" t="n"/>
+      <c r="I93" s="23" t="n"/>
       <c r="J93" s="13" t="n"/>
       <c r="K93" s="16" t="n"/>
-      <c r="L93" s="12" t="n"/>
+      <c r="L93" s="23" t="n"/>
       <c r="M93" s="13" t="n"/>
       <c r="N93" s="16" t="n"/>
-      <c r="O93" s="12" t="n"/>
+      <c r="O93" s="23" t="n"/>
       <c r="P93" s="13" t="n"/>
       <c r="Q93" s="16" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="R93" s="23" t="n"/>
       <c r="S93" s="13" t="n"/>
       <c r="T93" s="16" t="n"/>
-      <c r="U93" s="12" t="n"/>
+      <c r="U93" s="23" t="n"/>
       <c r="V93" s="13" t="n"/>
     </row>
     <row r="94">
@@ -3705,25 +3716,25 @@
         </is>
       </c>
       <c r="B94" s="16" t="n"/>
-      <c r="C94" s="12" t="n"/>
+      <c r="C94" s="23" t="n"/>
       <c r="D94" s="13" t="n"/>
       <c r="E94" s="16" t="n"/>
-      <c r="F94" s="12" t="n"/>
+      <c r="F94" s="23" t="n"/>
       <c r="G94" s="13" t="n"/>
       <c r="H94" s="16" t="n"/>
-      <c r="I94" s="12" t="n"/>
+      <c r="I94" s="23" t="n"/>
       <c r="J94" s="13" t="n"/>
       <c r="K94" s="16" t="n"/>
-      <c r="L94" s="12" t="n"/>
+      <c r="L94" s="23" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="16" t="n"/>
-      <c r="O94" s="12" t="n"/>
+      <c r="O94" s="23" t="n"/>
       <c r="P94" s="13" t="n"/>
       <c r="Q94" s="16" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="R94" s="23" t="n"/>
       <c r="S94" s="13" t="n"/>
       <c r="T94" s="16" t="n"/>
-      <c r="U94" s="12" t="n"/>
+      <c r="U94" s="23" t="n"/>
       <c r="V94" s="13" t="n"/>
     </row>
     <row r="95">
@@ -3733,25 +3744,25 @@
         </is>
       </c>
       <c r="B95" s="16" t="n"/>
-      <c r="C95" s="12" t="n"/>
+      <c r="C95" s="23" t="n"/>
       <c r="D95" s="13" t="n"/>
       <c r="E95" s="16" t="n"/>
-      <c r="F95" s="12" t="n"/>
+      <c r="F95" s="23" t="n"/>
       <c r="G95" s="13" t="n"/>
       <c r="H95" s="16" t="n"/>
-      <c r="I95" s="12" t="n"/>
+      <c r="I95" s="23" t="n"/>
       <c r="J95" s="13" t="n"/>
       <c r="K95" s="16" t="n"/>
-      <c r="L95" s="12" t="n"/>
+      <c r="L95" s="23" t="n"/>
       <c r="M95" s="13" t="n"/>
       <c r="N95" s="16" t="n"/>
-      <c r="O95" s="12" t="n"/>
+      <c r="O95" s="23" t="n"/>
       <c r="P95" s="13" t="n"/>
       <c r="Q95" s="16" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="R95" s="23" t="n"/>
       <c r="S95" s="13" t="n"/>
       <c r="T95" s="16" t="n"/>
-      <c r="U95" s="12" t="n"/>
+      <c r="U95" s="23" t="n"/>
       <c r="V95" s="13" t="n"/>
     </row>
     <row r="96">
@@ -3761,25 +3772,25 @@
         </is>
       </c>
       <c r="B96" s="16" t="n"/>
-      <c r="C96" s="12" t="n"/>
+      <c r="C96" s="23" t="n"/>
       <c r="D96" s="13" t="n"/>
       <c r="E96" s="16" t="n"/>
-      <c r="F96" s="12" t="n"/>
+      <c r="F96" s="23" t="n"/>
       <c r="G96" s="13" t="n"/>
       <c r="H96" s="16" t="n"/>
-      <c r="I96" s="12" t="n"/>
+      <c r="I96" s="23" t="n"/>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="16" t="n"/>
-      <c r="L96" s="12" t="n"/>
+      <c r="L96" s="23" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="16" t="n"/>
-      <c r="O96" s="12" t="n"/>
+      <c r="O96" s="23" t="n"/>
       <c r="P96" s="13" t="n"/>
       <c r="Q96" s="16" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="R96" s="23" t="n"/>
       <c r="S96" s="13" t="n"/>
       <c r="T96" s="16" t="n"/>
-      <c r="U96" s="12" t="n"/>
+      <c r="U96" s="23" t="n"/>
       <c r="V96" s="13" t="n"/>
     </row>
     <row r="97">
@@ -3789,25 +3800,25 @@
         </is>
       </c>
       <c r="B97" s="16" t="n"/>
-      <c r="C97" s="12" t="n"/>
+      <c r="C97" s="23" t="n"/>
       <c r="D97" s="13" t="n"/>
       <c r="E97" s="16" t="n"/>
-      <c r="F97" s="12" t="n"/>
+      <c r="F97" s="23" t="n"/>
       <c r="G97" s="13" t="n"/>
       <c r="H97" s="16" t="n"/>
-      <c r="I97" s="12" t="n"/>
+      <c r="I97" s="23" t="n"/>
       <c r="J97" s="13" t="n"/>
       <c r="K97" s="16" t="n"/>
-      <c r="L97" s="12" t="n"/>
+      <c r="L97" s="23" t="n"/>
       <c r="M97" s="13" t="n"/>
       <c r="N97" s="16" t="n"/>
-      <c r="O97" s="12" t="n"/>
+      <c r="O97" s="23" t="n"/>
       <c r="P97" s="13" t="n"/>
       <c r="Q97" s="16" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="R97" s="23" t="n"/>
       <c r="S97" s="13" t="n"/>
       <c r="T97" s="16" t="n"/>
-      <c r="U97" s="12" t="n"/>
+      <c r="U97" s="23" t="n"/>
       <c r="V97" s="13" t="n"/>
     </row>
     <row r="98">
@@ -3817,25 +3828,25 @@
         </is>
       </c>
       <c r="B98" s="18" t="n"/>
-      <c r="C98" s="19" t="n"/>
+      <c r="C98" s="24" t="n"/>
       <c r="D98" s="20" t="n"/>
       <c r="E98" s="18" t="n"/>
-      <c r="F98" s="19" t="n"/>
+      <c r="F98" s="24" t="n"/>
       <c r="G98" s="20" t="n"/>
       <c r="H98" s="18" t="n"/>
-      <c r="I98" s="19" t="n"/>
+      <c r="I98" s="24" t="n"/>
       <c r="J98" s="20" t="n"/>
       <c r="K98" s="18" t="n"/>
-      <c r="L98" s="19" t="n"/>
+      <c r="L98" s="24" t="n"/>
       <c r="M98" s="20" t="n"/>
       <c r="N98" s="18" t="n"/>
-      <c r="O98" s="19" t="n"/>
+      <c r="O98" s="24" t="n"/>
       <c r="P98" s="20" t="n"/>
       <c r="Q98" s="18" t="n"/>
-      <c r="R98" s="19" t="n"/>
+      <c r="R98" s="24" t="n"/>
       <c r="S98" s="20" t="n"/>
       <c r="T98" s="18" t="n"/>
-      <c r="U98" s="19" t="n"/>
+      <c r="U98" s="24" t="n"/>
       <c r="V98" s="20" t="n"/>
     </row>
     <row r="99">
@@ -3845,25 +3856,25 @@
         </is>
       </c>
       <c r="B99" s="21" t="n"/>
-      <c r="C99" s="8" t="n"/>
+      <c r="C99" s="22" t="n"/>
       <c r="D99" s="9" t="n"/>
       <c r="E99" s="21" t="n"/>
-      <c r="F99" s="8" t="n"/>
+      <c r="F99" s="22" t="n"/>
       <c r="G99" s="9" t="n"/>
       <c r="H99" s="21" t="n"/>
-      <c r="I99" s="8" t="n"/>
+      <c r="I99" s="22" t="n"/>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="21" t="n"/>
-      <c r="L99" s="8" t="n"/>
+      <c r="L99" s="22" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="21" t="n"/>
-      <c r="O99" s="8" t="n"/>
+      <c r="O99" s="22" t="n"/>
       <c r="P99" s="9" t="n"/>
       <c r="Q99" s="21" t="n"/>
-      <c r="R99" s="8" t="n"/>
+      <c r="R99" s="22" t="n"/>
       <c r="S99" s="9" t="n"/>
       <c r="T99" s="21" t="n"/>
-      <c r="U99" s="8" t="n"/>
+      <c r="U99" s="22" t="n"/>
       <c r="V99" s="9" t="n"/>
     </row>
     <row r="100">
@@ -3873,25 +3884,25 @@
         </is>
       </c>
       <c r="B100" s="16" t="n"/>
-      <c r="C100" s="12" t="n"/>
+      <c r="C100" s="23" t="n"/>
       <c r="D100" s="13" t="n"/>
       <c r="E100" s="16" t="n"/>
-      <c r="F100" s="12" t="n"/>
+      <c r="F100" s="23" t="n"/>
       <c r="G100" s="13" t="n"/>
       <c r="H100" s="16" t="n"/>
-      <c r="I100" s="12" t="n"/>
+      <c r="I100" s="23" t="n"/>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="16" t="n"/>
-      <c r="L100" s="12" t="n"/>
+      <c r="L100" s="23" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="16" t="n"/>
-      <c r="O100" s="12" t="n"/>
+      <c r="O100" s="23" t="n"/>
       <c r="P100" s="13" t="n"/>
       <c r="Q100" s="16" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="R100" s="23" t="n"/>
       <c r="S100" s="13" t="n"/>
       <c r="T100" s="16" t="n"/>
-      <c r="U100" s="12" t="n"/>
+      <c r="U100" s="23" t="n"/>
       <c r="V100" s="13" t="n"/>
     </row>
     <row r="101">
@@ -3901,25 +3912,25 @@
         </is>
       </c>
       <c r="B101" s="16" t="n"/>
-      <c r="C101" s="12" t="n"/>
+      <c r="C101" s="23" t="n"/>
       <c r="D101" s="13" t="n"/>
       <c r="E101" s="16" t="n"/>
-      <c r="F101" s="12" t="n"/>
+      <c r="F101" s="23" t="n"/>
       <c r="G101" s="13" t="n"/>
       <c r="H101" s="16" t="n"/>
-      <c r="I101" s="12" t="n"/>
+      <c r="I101" s="23" t="n"/>
       <c r="J101" s="13" t="n"/>
       <c r="K101" s="16" t="n"/>
-      <c r="L101" s="12" t="n"/>
+      <c r="L101" s="23" t="n"/>
       <c r="M101" s="13" t="n"/>
       <c r="N101" s="16" t="n"/>
-      <c r="O101" s="12" t="n"/>
+      <c r="O101" s="23" t="n"/>
       <c r="P101" s="13" t="n"/>
       <c r="Q101" s="16" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="R101" s="23" t="n"/>
       <c r="S101" s="13" t="n"/>
       <c r="T101" s="16" t="n"/>
-      <c r="U101" s="12" t="n"/>
+      <c r="U101" s="23" t="n"/>
       <c r="V101" s="13" t="n"/>
     </row>
     <row r="102">
@@ -3929,25 +3940,25 @@
         </is>
       </c>
       <c r="B102" s="16" t="n"/>
-      <c r="C102" s="12" t="n"/>
+      <c r="C102" s="23" t="n"/>
       <c r="D102" s="13" t="n"/>
       <c r="E102" s="16" t="n"/>
-      <c r="F102" s="12" t="n"/>
+      <c r="F102" s="23" t="n"/>
       <c r="G102" s="13" t="n"/>
       <c r="H102" s="16" t="n"/>
-      <c r="I102" s="12" t="n"/>
+      <c r="I102" s="23" t="n"/>
       <c r="J102" s="13" t="n"/>
       <c r="K102" s="16" t="n"/>
-      <c r="L102" s="12" t="n"/>
+      <c r="L102" s="23" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="16" t="n"/>
-      <c r="O102" s="12" t="n"/>
+      <c r="O102" s="23" t="n"/>
       <c r="P102" s="13" t="n"/>
       <c r="Q102" s="16" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="R102" s="23" t="n"/>
       <c r="S102" s="13" t="n"/>
       <c r="T102" s="16" t="n"/>
-      <c r="U102" s="12" t="n"/>
+      <c r="U102" s="23" t="n"/>
       <c r="V102" s="13" t="n"/>
     </row>
     <row r="103">
@@ -3957,25 +3968,25 @@
         </is>
       </c>
       <c r="B103" s="16" t="n"/>
-      <c r="C103" s="12" t="n"/>
+      <c r="C103" s="23" t="n"/>
       <c r="D103" s="13" t="n"/>
       <c r="E103" s="16" t="n"/>
-      <c r="F103" s="12" t="n"/>
+      <c r="F103" s="23" t="n"/>
       <c r="G103" s="13" t="n"/>
       <c r="H103" s="16" t="n"/>
-      <c r="I103" s="12" t="n"/>
+      <c r="I103" s="23" t="n"/>
       <c r="J103" s="13" t="n"/>
       <c r="K103" s="16" t="n"/>
-      <c r="L103" s="12" t="n"/>
+      <c r="L103" s="23" t="n"/>
       <c r="M103" s="13" t="n"/>
       <c r="N103" s="16" t="n"/>
-      <c r="O103" s="12" t="n"/>
+      <c r="O103" s="23" t="n"/>
       <c r="P103" s="13" t="n"/>
       <c r="Q103" s="16" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="R103" s="23" t="n"/>
       <c r="S103" s="13" t="n"/>
       <c r="T103" s="16" t="n"/>
-      <c r="U103" s="12" t="n"/>
+      <c r="U103" s="23" t="n"/>
       <c r="V103" s="13" t="n"/>
     </row>
     <row r="104">
@@ -3985,25 +3996,25 @@
         </is>
       </c>
       <c r="B104" s="16" t="n"/>
-      <c r="C104" s="12" t="n"/>
+      <c r="C104" s="23" t="n"/>
       <c r="D104" s="13" t="n"/>
       <c r="E104" s="16" t="n"/>
-      <c r="F104" s="12" t="n"/>
+      <c r="F104" s="23" t="n"/>
       <c r="G104" s="13" t="n"/>
       <c r="H104" s="16" t="n"/>
-      <c r="I104" s="12" t="n"/>
+      <c r="I104" s="23" t="n"/>
       <c r="J104" s="13" t="n"/>
       <c r="K104" s="16" t="n"/>
-      <c r="L104" s="12" t="n"/>
+      <c r="L104" s="23" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="16" t="n"/>
-      <c r="O104" s="12" t="n"/>
+      <c r="O104" s="23" t="n"/>
       <c r="P104" s="13" t="n"/>
       <c r="Q104" s="16" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="R104" s="23" t="n"/>
       <c r="S104" s="13" t="n"/>
       <c r="T104" s="16" t="n"/>
-      <c r="U104" s="12" t="n"/>
+      <c r="U104" s="23" t="n"/>
       <c r="V104" s="13" t="n"/>
     </row>
     <row r="105">
@@ -4013,25 +4024,25 @@
         </is>
       </c>
       <c r="B105" s="16" t="n"/>
-      <c r="C105" s="12" t="n"/>
+      <c r="C105" s="23" t="n"/>
       <c r="D105" s="13" t="n"/>
       <c r="E105" s="16" t="n"/>
-      <c r="F105" s="12" t="n"/>
+      <c r="F105" s="23" t="n"/>
       <c r="G105" s="13" t="n"/>
       <c r="H105" s="16" t="n"/>
-      <c r="I105" s="12" t="n"/>
+      <c r="I105" s="23" t="n"/>
       <c r="J105" s="13" t="n"/>
       <c r="K105" s="16" t="n"/>
-      <c r="L105" s="12" t="n"/>
+      <c r="L105" s="23" t="n"/>
       <c r="M105" s="13" t="n"/>
       <c r="N105" s="16" t="n"/>
-      <c r="O105" s="12" t="n"/>
+      <c r="O105" s="23" t="n"/>
       <c r="P105" s="13" t="n"/>
       <c r="Q105" s="16" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="R105" s="23" t="n"/>
       <c r="S105" s="13" t="n"/>
       <c r="T105" s="16" t="n"/>
-      <c r="U105" s="12" t="n"/>
+      <c r="U105" s="23" t="n"/>
       <c r="V105" s="13" t="n"/>
     </row>
     <row r="106">
@@ -4041,25 +4052,25 @@
         </is>
       </c>
       <c r="B106" s="16" t="n"/>
-      <c r="C106" s="12" t="n"/>
+      <c r="C106" s="23" t="n"/>
       <c r="D106" s="13" t="n"/>
       <c r="E106" s="16" t="n"/>
-      <c r="F106" s="12" t="n"/>
+      <c r="F106" s="23" t="n"/>
       <c r="G106" s="13" t="n"/>
       <c r="H106" s="16" t="n"/>
-      <c r="I106" s="12" t="n"/>
+      <c r="I106" s="23" t="n"/>
       <c r="J106" s="13" t="n"/>
       <c r="K106" s="16" t="n"/>
-      <c r="L106" s="12" t="n"/>
+      <c r="L106" s="23" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="16" t="n"/>
-      <c r="O106" s="12" t="n"/>
+      <c r="O106" s="23" t="n"/>
       <c r="P106" s="13" t="n"/>
       <c r="Q106" s="16" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="R106" s="23" t="n"/>
       <c r="S106" s="13" t="n"/>
       <c r="T106" s="16" t="n"/>
-      <c r="U106" s="12" t="n"/>
+      <c r="U106" s="23" t="n"/>
       <c r="V106" s="13" t="n"/>
     </row>
     <row r="107">
@@ -4069,25 +4080,25 @@
         </is>
       </c>
       <c r="B107" s="16" t="n"/>
-      <c r="C107" s="12" t="n"/>
+      <c r="C107" s="23" t="n"/>
       <c r="D107" s="13" t="n"/>
       <c r="E107" s="16" t="n"/>
-      <c r="F107" s="12" t="n"/>
+      <c r="F107" s="23" t="n"/>
       <c r="G107" s="13" t="n"/>
       <c r="H107" s="16" t="n"/>
-      <c r="I107" s="12" t="n"/>
+      <c r="I107" s="23" t="n"/>
       <c r="J107" s="13" t="n"/>
       <c r="K107" s="16" t="n"/>
-      <c r="L107" s="12" t="n"/>
+      <c r="L107" s="23" t="n"/>
       <c r="M107" s="13" t="n"/>
       <c r="N107" s="16" t="n"/>
-      <c r="O107" s="12" t="n"/>
+      <c r="O107" s="23" t="n"/>
       <c r="P107" s="13" t="n"/>
       <c r="Q107" s="16" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="R107" s="23" t="n"/>
       <c r="S107" s="13" t="n"/>
       <c r="T107" s="16" t="n"/>
-      <c r="U107" s="12" t="n"/>
+      <c r="U107" s="23" t="n"/>
       <c r="V107" s="13" t="n"/>
     </row>
     <row r="108">
@@ -4097,25 +4108,25 @@
         </is>
       </c>
       <c r="B108" s="16" t="n"/>
-      <c r="C108" s="12" t="n"/>
+      <c r="C108" s="23" t="n"/>
       <c r="D108" s="13" t="n"/>
       <c r="E108" s="16" t="n"/>
-      <c r="F108" s="12" t="n"/>
+      <c r="F108" s="23" t="n"/>
       <c r="G108" s="13" t="n"/>
       <c r="H108" s="16" t="n"/>
-      <c r="I108" s="12" t="n"/>
+      <c r="I108" s="23" t="n"/>
       <c r="J108" s="13" t="n"/>
       <c r="K108" s="16" t="n"/>
-      <c r="L108" s="12" t="n"/>
+      <c r="L108" s="23" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="16" t="n"/>
-      <c r="O108" s="12" t="n"/>
+      <c r="O108" s="23" t="n"/>
       <c r="P108" s="13" t="n"/>
       <c r="Q108" s="16" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="R108" s="23" t="n"/>
       <c r="S108" s="13" t="n"/>
       <c r="T108" s="16" t="n"/>
-      <c r="U108" s="12" t="n"/>
+      <c r="U108" s="23" t="n"/>
       <c r="V108" s="13" t="n"/>
     </row>
     <row r="109">
@@ -4125,25 +4136,25 @@
         </is>
       </c>
       <c r="B109" s="16" t="n"/>
-      <c r="C109" s="12" t="n"/>
+      <c r="C109" s="23" t="n"/>
       <c r="D109" s="13" t="n"/>
       <c r="E109" s="16" t="n"/>
-      <c r="F109" s="12" t="n"/>
+      <c r="F109" s="23" t="n"/>
       <c r="G109" s="13" t="n"/>
       <c r="H109" s="16" t="n"/>
-      <c r="I109" s="12" t="n"/>
+      <c r="I109" s="23" t="n"/>
       <c r="J109" s="13" t="n"/>
       <c r="K109" s="16" t="n"/>
-      <c r="L109" s="12" t="n"/>
+      <c r="L109" s="23" t="n"/>
       <c r="M109" s="13" t="n"/>
       <c r="N109" s="16" t="n"/>
-      <c r="O109" s="12" t="n"/>
+      <c r="O109" s="23" t="n"/>
       <c r="P109" s="13" t="n"/>
       <c r="Q109" s="16" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="R109" s="23" t="n"/>
       <c r="S109" s="13" t="n"/>
       <c r="T109" s="16" t="n"/>
-      <c r="U109" s="12" t="n"/>
+      <c r="U109" s="23" t="n"/>
       <c r="V109" s="13" t="n"/>
     </row>
     <row r="110">
@@ -4153,25 +4164,25 @@
         </is>
       </c>
       <c r="B110" s="18" t="n"/>
-      <c r="C110" s="19" t="n"/>
+      <c r="C110" s="24" t="n"/>
       <c r="D110" s="20" t="n"/>
       <c r="E110" s="18" t="n"/>
-      <c r="F110" s="19" t="n"/>
+      <c r="F110" s="24" t="n"/>
       <c r="G110" s="20" t="n"/>
       <c r="H110" s="18" t="n"/>
-      <c r="I110" s="19" t="n"/>
+      <c r="I110" s="24" t="n"/>
       <c r="J110" s="20" t="n"/>
       <c r="K110" s="18" t="n"/>
-      <c r="L110" s="19" t="n"/>
+      <c r="L110" s="24" t="n"/>
       <c r="M110" s="20" t="n"/>
       <c r="N110" s="18" t="n"/>
-      <c r="O110" s="19" t="n"/>
+      <c r="O110" s="24" t="n"/>
       <c r="P110" s="20" t="n"/>
       <c r="Q110" s="18" t="n"/>
-      <c r="R110" s="19" t="n"/>
+      <c r="R110" s="24" t="n"/>
       <c r="S110" s="20" t="n"/>
       <c r="T110" s="18" t="n"/>
-      <c r="U110" s="19" t="n"/>
+      <c r="U110" s="24" t="n"/>
       <c r="V110" s="20" t="n"/>
     </row>
     <row r="111">
@@ -4180,50 +4191,50 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B111" s="21" t="n"/>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
-      <c r="E111" s="21" t="n"/>
-      <c r="F111" s="22" t="inlineStr">
+      <c r="E111" s="25" t="n"/>
+      <c r="F111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="G111" s="9" t="n"/>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="22" t="inlineStr">
+      <c r="H111" s="25" t="n"/>
+      <c r="I111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="J111" s="9" t="n"/>
-      <c r="K111" s="21" t="n"/>
-      <c r="L111" s="22" t="inlineStr">
+      <c r="K111" s="25" t="n"/>
+      <c r="L111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="M111" s="9" t="n"/>
-      <c r="N111" s="21" t="n"/>
-      <c r="O111" s="22" t="inlineStr">
+      <c r="N111" s="25" t="n"/>
+      <c r="O111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="21" t="n"/>
-      <c r="R111" s="22" t="inlineStr">
+      <c r="Q111" s="25" t="n"/>
+      <c r="R111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="S111" s="9" t="n"/>
-      <c r="T111" s="21" t="n"/>
-      <c r="U111" s="22" t="inlineStr">
+      <c r="T111" s="25" t="n"/>
+      <c r="U111" s="26" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
@@ -4236,26 +4247,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B112" s="16" t="n"/>
-      <c r="C112" s="23" t="n"/>
+      <c r="B112" s="27" t="n"/>
+      <c r="C112" s="28" t="n"/>
       <c r="D112" s="13" t="n"/>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="23" t="n"/>
+      <c r="E112" s="27" t="n"/>
+      <c r="F112" s="28" t="n"/>
       <c r="G112" s="13" t="n"/>
-      <c r="H112" s="16" t="n"/>
-      <c r="I112" s="23" t="n"/>
+      <c r="H112" s="27" t="n"/>
+      <c r="I112" s="28" t="n"/>
       <c r="J112" s="13" t="n"/>
-      <c r="K112" s="16" t="n"/>
-      <c r="L112" s="23" t="n"/>
+      <c r="K112" s="27" t="n"/>
+      <c r="L112" s="28" t="n"/>
       <c r="M112" s="13" t="n"/>
-      <c r="N112" s="16" t="n"/>
-      <c r="O112" s="23" t="n"/>
+      <c r="N112" s="27" t="n"/>
+      <c r="O112" s="28" t="n"/>
       <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="16" t="n"/>
-      <c r="R112" s="23" t="n"/>
+      <c r="Q112" s="27" t="n"/>
+      <c r="R112" s="28" t="n"/>
       <c r="S112" s="13" t="n"/>
-      <c r="T112" s="16" t="n"/>
-      <c r="U112" s="23" t="n"/>
+      <c r="T112" s="27" t="n"/>
+      <c r="U112" s="28" t="n"/>
       <c r="V112" s="13" t="n"/>
     </row>
     <row r="113">
@@ -4264,26 +4275,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B113" s="16" t="n"/>
-      <c r="C113" s="23" t="n"/>
+      <c r="B113" s="27" t="n"/>
+      <c r="C113" s="28" t="n"/>
       <c r="D113" s="13" t="n"/>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="23" t="n"/>
+      <c r="E113" s="27" t="n"/>
+      <c r="F113" s="28" t="n"/>
       <c r="G113" s="13" t="n"/>
-      <c r="H113" s="16" t="n"/>
-      <c r="I113" s="23" t="n"/>
+      <c r="H113" s="27" t="n"/>
+      <c r="I113" s="28" t="n"/>
       <c r="J113" s="13" t="n"/>
-      <c r="K113" s="16" t="n"/>
-      <c r="L113" s="23" t="n"/>
+      <c r="K113" s="27" t="n"/>
+      <c r="L113" s="28" t="n"/>
       <c r="M113" s="13" t="n"/>
-      <c r="N113" s="16" t="n"/>
-      <c r="O113" s="23" t="n"/>
+      <c r="N113" s="27" t="n"/>
+      <c r="O113" s="28" t="n"/>
       <c r="P113" s="13" t="n"/>
-      <c r="Q113" s="16" t="n"/>
-      <c r="R113" s="23" t="n"/>
+      <c r="Q113" s="27" t="n"/>
+      <c r="R113" s="28" t="n"/>
       <c r="S113" s="13" t="n"/>
-      <c r="T113" s="16" t="n"/>
-      <c r="U113" s="23" t="n"/>
+      <c r="T113" s="27" t="n"/>
+      <c r="U113" s="28" t="n"/>
       <c r="V113" s="13" t="n"/>
     </row>
     <row r="114">
@@ -4292,26 +4303,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B114" s="16" t="n"/>
-      <c r="C114" s="23" t="n"/>
+      <c r="B114" s="27" t="n"/>
+      <c r="C114" s="28" t="n"/>
       <c r="D114" s="13" t="n"/>
-      <c r="E114" s="16" t="n"/>
-      <c r="F114" s="23" t="n"/>
+      <c r="E114" s="27" t="n"/>
+      <c r="F114" s="28" t="n"/>
       <c r="G114" s="13" t="n"/>
-      <c r="H114" s="16" t="n"/>
-      <c r="I114" s="23" t="n"/>
+      <c r="H114" s="27" t="n"/>
+      <c r="I114" s="28" t="n"/>
       <c r="J114" s="13" t="n"/>
-      <c r="K114" s="16" t="n"/>
-      <c r="L114" s="23" t="n"/>
+      <c r="K114" s="27" t="n"/>
+      <c r="L114" s="28" t="n"/>
       <c r="M114" s="13" t="n"/>
-      <c r="N114" s="16" t="n"/>
-      <c r="O114" s="23" t="n"/>
+      <c r="N114" s="27" t="n"/>
+      <c r="O114" s="28" t="n"/>
       <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="16" t="n"/>
-      <c r="R114" s="23" t="n"/>
+      <c r="Q114" s="27" t="n"/>
+      <c r="R114" s="28" t="n"/>
       <c r="S114" s="13" t="n"/>
-      <c r="T114" s="16" t="n"/>
-      <c r="U114" s="23" t="n"/>
+      <c r="T114" s="27" t="n"/>
+      <c r="U114" s="28" t="n"/>
       <c r="V114" s="13" t="n"/>
     </row>
     <row r="115">
@@ -4320,26 +4331,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B115" s="16" t="n"/>
-      <c r="C115" s="24" t="n"/>
+      <c r="B115" s="27" t="n"/>
+      <c r="C115" s="29" t="n"/>
       <c r="D115" s="13" t="n"/>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="24" t="n"/>
+      <c r="E115" s="27" t="n"/>
+      <c r="F115" s="29" t="n"/>
       <c r="G115" s="13" t="n"/>
-      <c r="H115" s="16" t="n"/>
-      <c r="I115" s="24" t="n"/>
+      <c r="H115" s="27" t="n"/>
+      <c r="I115" s="29" t="n"/>
       <c r="J115" s="13" t="n"/>
-      <c r="K115" s="16" t="n"/>
-      <c r="L115" s="24" t="n"/>
+      <c r="K115" s="27" t="n"/>
+      <c r="L115" s="29" t="n"/>
       <c r="M115" s="13" t="n"/>
-      <c r="N115" s="16" t="n"/>
-      <c r="O115" s="24" t="n"/>
+      <c r="N115" s="27" t="n"/>
+      <c r="O115" s="29" t="n"/>
       <c r="P115" s="13" t="n"/>
-      <c r="Q115" s="16" t="n"/>
-      <c r="R115" s="24" t="n"/>
+      <c r="Q115" s="27" t="n"/>
+      <c r="R115" s="29" t="n"/>
       <c r="S115" s="13" t="n"/>
-      <c r="T115" s="16" t="n"/>
-      <c r="U115" s="24" t="n"/>
+      <c r="T115" s="27" t="n"/>
+      <c r="U115" s="29" t="n"/>
       <c r="V115" s="13" t="n"/>
     </row>
     <row r="116">
@@ -4348,26 +4359,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B116" s="16" t="n"/>
-      <c r="C116" s="12" t="n"/>
+      <c r="B116" s="27" t="n"/>
+      <c r="C116" s="23" t="n"/>
       <c r="D116" s="13" t="n"/>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="12" t="n"/>
+      <c r="E116" s="27" t="n"/>
+      <c r="F116" s="23" t="n"/>
       <c r="G116" s="13" t="n"/>
-      <c r="H116" s="16" t="n"/>
-      <c r="I116" s="12" t="n"/>
+      <c r="H116" s="27" t="n"/>
+      <c r="I116" s="23" t="n"/>
       <c r="J116" s="13" t="n"/>
-      <c r="K116" s="16" t="n"/>
-      <c r="L116" s="12" t="n"/>
+      <c r="K116" s="27" t="n"/>
+      <c r="L116" s="23" t="n"/>
       <c r="M116" s="13" t="n"/>
-      <c r="N116" s="16" t="n"/>
-      <c r="O116" s="12" t="n"/>
+      <c r="N116" s="27" t="n"/>
+      <c r="O116" s="23" t="n"/>
       <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="16" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="Q116" s="27" t="n"/>
+      <c r="R116" s="23" t="n"/>
       <c r="S116" s="13" t="n"/>
-      <c r="T116" s="16" t="n"/>
-      <c r="U116" s="12" t="n"/>
+      <c r="T116" s="27" t="n"/>
+      <c r="U116" s="23" t="n"/>
       <c r="V116" s="13" t="n"/>
     </row>
     <row r="117">
@@ -4376,50 +4387,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B117" s="16" t="n"/>
-      <c r="C117" s="25" t="inlineStr">
+      <c r="B117" s="27" t="n"/>
+      <c r="C117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="D117" s="13" t="n"/>
-      <c r="E117" s="16" t="n"/>
-      <c r="F117" s="25" t="inlineStr">
+      <c r="E117" s="27" t="n"/>
+      <c r="F117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="G117" s="13" t="n"/>
-      <c r="H117" s="16" t="n"/>
-      <c r="I117" s="25" t="inlineStr">
+      <c r="H117" s="27" t="n"/>
+      <c r="I117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="J117" s="13" t="n"/>
-      <c r="K117" s="16" t="n"/>
-      <c r="L117" s="25" t="inlineStr">
+      <c r="K117" s="27" t="n"/>
+      <c r="L117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="M117" s="13" t="n"/>
-      <c r="N117" s="16" t="n"/>
-      <c r="O117" s="25" t="inlineStr">
+      <c r="N117" s="27" t="n"/>
+      <c r="O117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="P117" s="13" t="n"/>
-      <c r="Q117" s="16" t="n"/>
-      <c r="R117" s="25" t="inlineStr">
+      <c r="Q117" s="27" t="n"/>
+      <c r="R117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="S117" s="13" t="n"/>
-      <c r="T117" s="16" t="n"/>
-      <c r="U117" s="25" t="inlineStr">
+      <c r="T117" s="27" t="n"/>
+      <c r="U117" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
@@ -4432,26 +4443,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B118" s="16" t="n"/>
-      <c r="C118" s="23" t="n"/>
+      <c r="B118" s="27" t="n"/>
+      <c r="C118" s="28" t="n"/>
       <c r="D118" s="13" t="n"/>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="23" t="n"/>
+      <c r="E118" s="27" t="n"/>
+      <c r="F118" s="28" t="n"/>
       <c r="G118" s="13" t="n"/>
-      <c r="H118" s="16" t="n"/>
-      <c r="I118" s="23" t="n"/>
+      <c r="H118" s="27" t="n"/>
+      <c r="I118" s="28" t="n"/>
       <c r="J118" s="13" t="n"/>
-      <c r="K118" s="16" t="n"/>
-      <c r="L118" s="23" t="n"/>
+      <c r="K118" s="27" t="n"/>
+      <c r="L118" s="28" t="n"/>
       <c r="M118" s="13" t="n"/>
-      <c r="N118" s="16" t="n"/>
-      <c r="O118" s="23" t="n"/>
+      <c r="N118" s="27" t="n"/>
+      <c r="O118" s="28" t="n"/>
       <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="16" t="n"/>
-      <c r="R118" s="23" t="n"/>
+      <c r="Q118" s="27" t="n"/>
+      <c r="R118" s="28" t="n"/>
       <c r="S118" s="13" t="n"/>
-      <c r="T118" s="16" t="n"/>
-      <c r="U118" s="23" t="n"/>
+      <c r="T118" s="27" t="n"/>
+      <c r="U118" s="28" t="n"/>
       <c r="V118" s="13" t="n"/>
     </row>
     <row r="119">
@@ -4460,26 +4471,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B119" s="16" t="n"/>
-      <c r="C119" s="23" t="n"/>
+      <c r="B119" s="27" t="n"/>
+      <c r="C119" s="28" t="n"/>
       <c r="D119" s="13" t="n"/>
-      <c r="E119" s="16" t="n"/>
-      <c r="F119" s="23" t="n"/>
+      <c r="E119" s="27" t="n"/>
+      <c r="F119" s="28" t="n"/>
       <c r="G119" s="13" t="n"/>
-      <c r="H119" s="16" t="n"/>
-      <c r="I119" s="23" t="n"/>
+      <c r="H119" s="27" t="n"/>
+      <c r="I119" s="28" t="n"/>
       <c r="J119" s="13" t="n"/>
-      <c r="K119" s="16" t="n"/>
-      <c r="L119" s="23" t="n"/>
+      <c r="K119" s="27" t="n"/>
+      <c r="L119" s="28" t="n"/>
       <c r="M119" s="13" t="n"/>
-      <c r="N119" s="16" t="n"/>
-      <c r="O119" s="23" t="n"/>
+      <c r="N119" s="27" t="n"/>
+      <c r="O119" s="28" t="n"/>
       <c r="P119" s="13" t="n"/>
-      <c r="Q119" s="16" t="n"/>
-      <c r="R119" s="23" t="n"/>
+      <c r="Q119" s="27" t="n"/>
+      <c r="R119" s="28" t="n"/>
       <c r="S119" s="13" t="n"/>
-      <c r="T119" s="16" t="n"/>
-      <c r="U119" s="23" t="n"/>
+      <c r="T119" s="27" t="n"/>
+      <c r="U119" s="28" t="n"/>
       <c r="V119" s="13" t="n"/>
     </row>
     <row r="120">
@@ -4488,26 +4499,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B120" s="16" t="n"/>
-      <c r="C120" s="23" t="n"/>
+      <c r="B120" s="27" t="n"/>
+      <c r="C120" s="28" t="n"/>
       <c r="D120" s="13" t="n"/>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="23" t="n"/>
+      <c r="E120" s="27" t="n"/>
+      <c r="F120" s="28" t="n"/>
       <c r="G120" s="13" t="n"/>
-      <c r="H120" s="16" t="n"/>
-      <c r="I120" s="23" t="n"/>
+      <c r="H120" s="27" t="n"/>
+      <c r="I120" s="28" t="n"/>
       <c r="J120" s="13" t="n"/>
-      <c r="K120" s="16" t="n"/>
-      <c r="L120" s="23" t="n"/>
+      <c r="K120" s="27" t="n"/>
+      <c r="L120" s="28" t="n"/>
       <c r="M120" s="13" t="n"/>
-      <c r="N120" s="16" t="n"/>
-      <c r="O120" s="23" t="n"/>
+      <c r="N120" s="27" t="n"/>
+      <c r="O120" s="28" t="n"/>
       <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="16" t="n"/>
-      <c r="R120" s="23" t="n"/>
+      <c r="Q120" s="27" t="n"/>
+      <c r="R120" s="28" t="n"/>
       <c r="S120" s="13" t="n"/>
-      <c r="T120" s="16" t="n"/>
-      <c r="U120" s="23" t="n"/>
+      <c r="T120" s="27" t="n"/>
+      <c r="U120" s="28" t="n"/>
       <c r="V120" s="13" t="n"/>
     </row>
     <row r="121">
@@ -4516,26 +4527,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B121" s="16" t="n"/>
-      <c r="C121" s="24" t="n"/>
+      <c r="B121" s="27" t="n"/>
+      <c r="C121" s="29" t="n"/>
       <c r="D121" s="13" t="n"/>
-      <c r="E121" s="16" t="n"/>
-      <c r="F121" s="24" t="n"/>
+      <c r="E121" s="27" t="n"/>
+      <c r="F121" s="29" t="n"/>
       <c r="G121" s="13" t="n"/>
-      <c r="H121" s="16" t="n"/>
-      <c r="I121" s="24" t="n"/>
+      <c r="H121" s="27" t="n"/>
+      <c r="I121" s="29" t="n"/>
       <c r="J121" s="13" t="n"/>
-      <c r="K121" s="16" t="n"/>
-      <c r="L121" s="24" t="n"/>
+      <c r="K121" s="27" t="n"/>
+      <c r="L121" s="29" t="n"/>
       <c r="M121" s="13" t="n"/>
-      <c r="N121" s="16" t="n"/>
-      <c r="O121" s="24" t="n"/>
+      <c r="N121" s="27" t="n"/>
+      <c r="O121" s="29" t="n"/>
       <c r="P121" s="13" t="n"/>
-      <c r="Q121" s="16" t="n"/>
-      <c r="R121" s="24" t="n"/>
+      <c r="Q121" s="27" t="n"/>
+      <c r="R121" s="29" t="n"/>
       <c r="S121" s="13" t="n"/>
-      <c r="T121" s="16" t="n"/>
-      <c r="U121" s="24" t="n"/>
+      <c r="T121" s="27" t="n"/>
+      <c r="U121" s="29" t="n"/>
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
@@ -4544,26 +4555,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="19" t="n"/>
+      <c r="B122" s="31" t="n"/>
+      <c r="C122" s="24" t="n"/>
       <c r="D122" s="20" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="19" t="n"/>
+      <c r="E122" s="31" t="n"/>
+      <c r="F122" s="24" t="n"/>
       <c r="G122" s="20" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="19" t="n"/>
+      <c r="H122" s="31" t="n"/>
+      <c r="I122" s="24" t="n"/>
       <c r="J122" s="20" t="n"/>
-      <c r="K122" s="18" t="n"/>
-      <c r="L122" s="19" t="n"/>
+      <c r="K122" s="31" t="n"/>
+      <c r="L122" s="24" t="n"/>
       <c r="M122" s="20" t="n"/>
-      <c r="N122" s="18" t="n"/>
-      <c r="O122" s="19" t="n"/>
+      <c r="N122" s="31" t="n"/>
+      <c r="O122" s="24" t="n"/>
       <c r="P122" s="20" t="n"/>
-      <c r="Q122" s="18" t="n"/>
-      <c r="R122" s="19" t="n"/>
+      <c r="Q122" s="31" t="n"/>
+      <c r="R122" s="24" t="n"/>
       <c r="S122" s="20" t="n"/>
-      <c r="T122" s="18" t="n"/>
-      <c r="U122" s="19" t="n"/>
+      <c r="T122" s="31" t="n"/>
+      <c r="U122" s="24" t="n"/>
       <c r="V122" s="20" t="n"/>
     </row>
     <row r="123">
@@ -4572,50 +4583,50 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B123" s="21" t="n"/>
-      <c r="C123" s="22" t="inlineStr">
+      <c r="B123" s="25" t="n"/>
+      <c r="C123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="22" t="inlineStr">
+      <c r="E123" s="25" t="n"/>
+      <c r="F123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="G123" s="9" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="22" t="inlineStr">
+      <c r="H123" s="25" t="n"/>
+      <c r="I123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="J123" s="9" t="n"/>
-      <c r="K123" s="21" t="n"/>
-      <c r="L123" s="22" t="inlineStr">
+      <c r="K123" s="25" t="n"/>
+      <c r="L123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="M123" s="9" t="n"/>
-      <c r="N123" s="21" t="n"/>
-      <c r="O123" s="22" t="inlineStr">
+      <c r="N123" s="25" t="n"/>
+      <c r="O123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="21" t="n"/>
-      <c r="R123" s="22" t="inlineStr">
+      <c r="Q123" s="25" t="n"/>
+      <c r="R123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="S123" s="9" t="n"/>
-      <c r="T123" s="21" t="n"/>
-      <c r="U123" s="22" t="inlineStr">
+      <c r="T123" s="25" t="n"/>
+      <c r="U123" s="26" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
@@ -4628,26 +4639,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B124" s="16" t="n"/>
-      <c r="C124" s="23" t="n"/>
+      <c r="B124" s="27" t="n"/>
+      <c r="C124" s="28" t="n"/>
       <c r="D124" s="13" t="n"/>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="23" t="n"/>
+      <c r="E124" s="27" t="n"/>
+      <c r="F124" s="28" t="n"/>
       <c r="G124" s="13" t="n"/>
-      <c r="H124" s="16" t="n"/>
-      <c r="I124" s="23" t="n"/>
+      <c r="H124" s="27" t="n"/>
+      <c r="I124" s="28" t="n"/>
       <c r="J124" s="13" t="n"/>
-      <c r="K124" s="16" t="n"/>
-      <c r="L124" s="23" t="n"/>
+      <c r="K124" s="27" t="n"/>
+      <c r="L124" s="28" t="n"/>
       <c r="M124" s="13" t="n"/>
-      <c r="N124" s="16" t="n"/>
-      <c r="O124" s="23" t="n"/>
+      <c r="N124" s="27" t="n"/>
+      <c r="O124" s="28" t="n"/>
       <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="16" t="n"/>
-      <c r="R124" s="23" t="n"/>
+      <c r="Q124" s="27" t="n"/>
+      <c r="R124" s="28" t="n"/>
       <c r="S124" s="13" t="n"/>
-      <c r="T124" s="16" t="n"/>
-      <c r="U124" s="23" t="n"/>
+      <c r="T124" s="27" t="n"/>
+      <c r="U124" s="28" t="n"/>
       <c r="V124" s="13" t="n"/>
     </row>
     <row r="125">
@@ -4656,26 +4667,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B125" s="16" t="n"/>
-      <c r="C125" s="23" t="n"/>
+      <c r="B125" s="27" t="n"/>
+      <c r="C125" s="28" t="n"/>
       <c r="D125" s="13" t="n"/>
-      <c r="E125" s="16" t="n"/>
-      <c r="F125" s="23" t="n"/>
+      <c r="E125" s="27" t="n"/>
+      <c r="F125" s="28" t="n"/>
       <c r="G125" s="13" t="n"/>
-      <c r="H125" s="16" t="n"/>
-      <c r="I125" s="23" t="n"/>
+      <c r="H125" s="27" t="n"/>
+      <c r="I125" s="28" t="n"/>
       <c r="J125" s="13" t="n"/>
-      <c r="K125" s="16" t="n"/>
-      <c r="L125" s="23" t="n"/>
+      <c r="K125" s="27" t="n"/>
+      <c r="L125" s="28" t="n"/>
       <c r="M125" s="13" t="n"/>
-      <c r="N125" s="16" t="n"/>
-      <c r="O125" s="23" t="n"/>
+      <c r="N125" s="27" t="n"/>
+      <c r="O125" s="28" t="n"/>
       <c r="P125" s="13" t="n"/>
-      <c r="Q125" s="16" t="n"/>
-      <c r="R125" s="23" t="n"/>
+      <c r="Q125" s="27" t="n"/>
+      <c r="R125" s="28" t="n"/>
       <c r="S125" s="13" t="n"/>
-      <c r="T125" s="16" t="n"/>
-      <c r="U125" s="23" t="n"/>
+      <c r="T125" s="27" t="n"/>
+      <c r="U125" s="28" t="n"/>
       <c r="V125" s="13" t="n"/>
     </row>
     <row r="126">
@@ -4684,26 +4695,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B126" s="16" t="n"/>
-      <c r="C126" s="23" t="n"/>
+      <c r="B126" s="27" t="n"/>
+      <c r="C126" s="28" t="n"/>
       <c r="D126" s="13" t="n"/>
-      <c r="E126" s="16" t="n"/>
-      <c r="F126" s="23" t="n"/>
+      <c r="E126" s="27" t="n"/>
+      <c r="F126" s="28" t="n"/>
       <c r="G126" s="13" t="n"/>
-      <c r="H126" s="16" t="n"/>
-      <c r="I126" s="23" t="n"/>
+      <c r="H126" s="27" t="n"/>
+      <c r="I126" s="28" t="n"/>
       <c r="J126" s="13" t="n"/>
-      <c r="K126" s="16" t="n"/>
-      <c r="L126" s="23" t="n"/>
+      <c r="K126" s="27" t="n"/>
+      <c r="L126" s="28" t="n"/>
       <c r="M126" s="13" t="n"/>
-      <c r="N126" s="16" t="n"/>
-      <c r="O126" s="23" t="n"/>
+      <c r="N126" s="27" t="n"/>
+      <c r="O126" s="28" t="n"/>
       <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="16" t="n"/>
-      <c r="R126" s="23" t="n"/>
+      <c r="Q126" s="27" t="n"/>
+      <c r="R126" s="28" t="n"/>
       <c r="S126" s="13" t="n"/>
-      <c r="T126" s="16" t="n"/>
-      <c r="U126" s="23" t="n"/>
+      <c r="T126" s="27" t="n"/>
+      <c r="U126" s="28" t="n"/>
       <c r="V126" s="13" t="n"/>
     </row>
     <row r="127">
@@ -4712,26 +4723,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B127" s="16" t="n"/>
-      <c r="C127" s="24" t="n"/>
+      <c r="B127" s="27" t="n"/>
+      <c r="C127" s="29" t="n"/>
       <c r="D127" s="13" t="n"/>
-      <c r="E127" s="16" t="n"/>
-      <c r="F127" s="24" t="n"/>
+      <c r="E127" s="27" t="n"/>
+      <c r="F127" s="29" t="n"/>
       <c r="G127" s="13" t="n"/>
-      <c r="H127" s="16" t="n"/>
-      <c r="I127" s="24" t="n"/>
+      <c r="H127" s="27" t="n"/>
+      <c r="I127" s="29" t="n"/>
       <c r="J127" s="13" t="n"/>
-      <c r="K127" s="16" t="n"/>
-      <c r="L127" s="24" t="n"/>
+      <c r="K127" s="27" t="n"/>
+      <c r="L127" s="29" t="n"/>
       <c r="M127" s="13" t="n"/>
-      <c r="N127" s="16" t="n"/>
-      <c r="O127" s="24" t="n"/>
+      <c r="N127" s="27" t="n"/>
+      <c r="O127" s="29" t="n"/>
       <c r="P127" s="13" t="n"/>
-      <c r="Q127" s="16" t="n"/>
-      <c r="R127" s="24" t="n"/>
+      <c r="Q127" s="27" t="n"/>
+      <c r="R127" s="29" t="n"/>
       <c r="S127" s="13" t="n"/>
-      <c r="T127" s="16" t="n"/>
-      <c r="U127" s="24" t="n"/>
+      <c r="T127" s="27" t="n"/>
+      <c r="U127" s="29" t="n"/>
       <c r="V127" s="13" t="n"/>
     </row>
     <row r="128">
@@ -4740,26 +4751,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B128" s="16" t="n"/>
-      <c r="C128" s="12" t="n"/>
+      <c r="B128" s="27" t="n"/>
+      <c r="C128" s="23" t="n"/>
       <c r="D128" s="13" t="n"/>
-      <c r="E128" s="16" t="n"/>
-      <c r="F128" s="12" t="n"/>
+      <c r="E128" s="27" t="n"/>
+      <c r="F128" s="23" t="n"/>
       <c r="G128" s="13" t="n"/>
-      <c r="H128" s="16" t="n"/>
-      <c r="I128" s="12" t="n"/>
+      <c r="H128" s="27" t="n"/>
+      <c r="I128" s="23" t="n"/>
       <c r="J128" s="13" t="n"/>
-      <c r="K128" s="16" t="n"/>
-      <c r="L128" s="12" t="n"/>
+      <c r="K128" s="27" t="n"/>
+      <c r="L128" s="23" t="n"/>
       <c r="M128" s="13" t="n"/>
-      <c r="N128" s="16" t="n"/>
-      <c r="O128" s="12" t="n"/>
+      <c r="N128" s="27" t="n"/>
+      <c r="O128" s="23" t="n"/>
       <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="16" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="Q128" s="27" t="n"/>
+      <c r="R128" s="23" t="n"/>
       <c r="S128" s="13" t="n"/>
-      <c r="T128" s="16" t="n"/>
-      <c r="U128" s="12" t="n"/>
+      <c r="T128" s="27" t="n"/>
+      <c r="U128" s="23" t="n"/>
       <c r="V128" s="13" t="n"/>
     </row>
     <row r="129">
@@ -4768,26 +4779,26 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B129" s="16" t="n"/>
-      <c r="C129" s="12" t="n"/>
+      <c r="B129" s="27" t="n"/>
+      <c r="C129" s="23" t="n"/>
       <c r="D129" s="13" t="n"/>
-      <c r="E129" s="16" t="n"/>
-      <c r="F129" s="12" t="n"/>
+      <c r="E129" s="27" t="n"/>
+      <c r="F129" s="23" t="n"/>
       <c r="G129" s="13" t="n"/>
-      <c r="H129" s="16" t="n"/>
-      <c r="I129" s="12" t="n"/>
+      <c r="H129" s="27" t="n"/>
+      <c r="I129" s="23" t="n"/>
       <c r="J129" s="13" t="n"/>
-      <c r="K129" s="16" t="n"/>
-      <c r="L129" s="12" t="n"/>
+      <c r="K129" s="27" t="n"/>
+      <c r="L129" s="23" t="n"/>
       <c r="M129" s="13" t="n"/>
-      <c r="N129" s="16" t="n"/>
-      <c r="O129" s="12" t="n"/>
+      <c r="N129" s="27" t="n"/>
+      <c r="O129" s="23" t="n"/>
       <c r="P129" s="13" t="n"/>
-      <c r="Q129" s="16" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="Q129" s="27" t="n"/>
+      <c r="R129" s="23" t="n"/>
       <c r="S129" s="13" t="n"/>
-      <c r="T129" s="16" t="n"/>
-      <c r="U129" s="12" t="n"/>
+      <c r="T129" s="27" t="n"/>
+      <c r="U129" s="23" t="n"/>
       <c r="V129" s="13" t="n"/>
     </row>
     <row r="130">
@@ -4796,26 +4807,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B130" s="16" t="n"/>
-      <c r="C130" s="12" t="n"/>
+      <c r="B130" s="27" t="n"/>
+      <c r="C130" s="23" t="n"/>
       <c r="D130" s="13" t="n"/>
-      <c r="E130" s="16" t="n"/>
-      <c r="F130" s="12" t="n"/>
+      <c r="E130" s="27" t="n"/>
+      <c r="F130" s="23" t="n"/>
       <c r="G130" s="13" t="n"/>
-      <c r="H130" s="16" t="n"/>
-      <c r="I130" s="12" t="n"/>
+      <c r="H130" s="27" t="n"/>
+      <c r="I130" s="23" t="n"/>
       <c r="J130" s="13" t="n"/>
-      <c r="K130" s="16" t="n"/>
-      <c r="L130" s="12" t="n"/>
+      <c r="K130" s="27" t="n"/>
+      <c r="L130" s="23" t="n"/>
       <c r="M130" s="13" t="n"/>
-      <c r="N130" s="16" t="n"/>
-      <c r="O130" s="12" t="n"/>
+      <c r="N130" s="27" t="n"/>
+      <c r="O130" s="23" t="n"/>
       <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="16" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="Q130" s="27" t="n"/>
+      <c r="R130" s="23" t="n"/>
       <c r="S130" s="13" t="n"/>
-      <c r="T130" s="16" t="n"/>
-      <c r="U130" s="12" t="n"/>
+      <c r="T130" s="27" t="n"/>
+      <c r="U130" s="23" t="n"/>
       <c r="V130" s="13" t="n"/>
     </row>
     <row r="131">
@@ -4824,26 +4835,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B131" s="16" t="n"/>
-      <c r="C131" s="12" t="n"/>
+      <c r="B131" s="27" t="n"/>
+      <c r="C131" s="23" t="n"/>
       <c r="D131" s="13" t="n"/>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="12" t="n"/>
+      <c r="E131" s="27" t="n"/>
+      <c r="F131" s="23" t="n"/>
       <c r="G131" s="13" t="n"/>
-      <c r="H131" s="16" t="n"/>
-      <c r="I131" s="12" t="n"/>
+      <c r="H131" s="27" t="n"/>
+      <c r="I131" s="23" t="n"/>
       <c r="J131" s="13" t="n"/>
-      <c r="K131" s="16" t="n"/>
-      <c r="L131" s="12" t="n"/>
+      <c r="K131" s="27" t="n"/>
+      <c r="L131" s="23" t="n"/>
       <c r="M131" s="13" t="n"/>
-      <c r="N131" s="16" t="n"/>
-      <c r="O131" s="12" t="n"/>
+      <c r="N131" s="27" t="n"/>
+      <c r="O131" s="23" t="n"/>
       <c r="P131" s="13" t="n"/>
-      <c r="Q131" s="16" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="Q131" s="27" t="n"/>
+      <c r="R131" s="23" t="n"/>
       <c r="S131" s="13" t="n"/>
-      <c r="T131" s="16" t="n"/>
-      <c r="U131" s="12" t="n"/>
+      <c r="T131" s="27" t="n"/>
+      <c r="U131" s="23" t="n"/>
       <c r="V131" s="13" t="n"/>
     </row>
     <row r="132">
@@ -4852,26 +4863,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B132" s="16" t="n"/>
-      <c r="C132" s="12" t="n"/>
+      <c r="B132" s="27" t="n"/>
+      <c r="C132" s="23" t="n"/>
       <c r="D132" s="13" t="n"/>
-      <c r="E132" s="16" t="n"/>
-      <c r="F132" s="12" t="n"/>
+      <c r="E132" s="27" t="n"/>
+      <c r="F132" s="23" t="n"/>
       <c r="G132" s="13" t="n"/>
-      <c r="H132" s="16" t="n"/>
-      <c r="I132" s="12" t="n"/>
+      <c r="H132" s="27" t="n"/>
+      <c r="I132" s="23" t="n"/>
       <c r="J132" s="13" t="n"/>
-      <c r="K132" s="16" t="n"/>
-      <c r="L132" s="12" t="n"/>
+      <c r="K132" s="27" t="n"/>
+      <c r="L132" s="23" t="n"/>
       <c r="M132" s="13" t="n"/>
-      <c r="N132" s="16" t="n"/>
-      <c r="O132" s="12" t="n"/>
+      <c r="N132" s="27" t="n"/>
+      <c r="O132" s="23" t="n"/>
       <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="16" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="Q132" s="27" t="n"/>
+      <c r="R132" s="23" t="n"/>
       <c r="S132" s="13" t="n"/>
-      <c r="T132" s="16" t="n"/>
-      <c r="U132" s="12" t="n"/>
+      <c r="T132" s="27" t="n"/>
+      <c r="U132" s="23" t="n"/>
       <c r="V132" s="13" t="n"/>
     </row>
     <row r="133">
@@ -4880,26 +4891,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B133" s="16" t="n"/>
-      <c r="C133" s="12" t="n"/>
+      <c r="B133" s="27" t="n"/>
+      <c r="C133" s="23" t="n"/>
       <c r="D133" s="13" t="n"/>
-      <c r="E133" s="16" t="n"/>
-      <c r="F133" s="12" t="n"/>
+      <c r="E133" s="27" t="n"/>
+      <c r="F133" s="23" t="n"/>
       <c r="G133" s="13" t="n"/>
-      <c r="H133" s="16" t="n"/>
-      <c r="I133" s="12" t="n"/>
+      <c r="H133" s="27" t="n"/>
+      <c r="I133" s="23" t="n"/>
       <c r="J133" s="13" t="n"/>
-      <c r="K133" s="16" t="n"/>
-      <c r="L133" s="12" t="n"/>
+      <c r="K133" s="27" t="n"/>
+      <c r="L133" s="23" t="n"/>
       <c r="M133" s="13" t="n"/>
-      <c r="N133" s="16" t="n"/>
-      <c r="O133" s="12" t="n"/>
+      <c r="N133" s="27" t="n"/>
+      <c r="O133" s="23" t="n"/>
       <c r="P133" s="13" t="n"/>
-      <c r="Q133" s="16" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="Q133" s="27" t="n"/>
+      <c r="R133" s="23" t="n"/>
       <c r="S133" s="13" t="n"/>
-      <c r="T133" s="16" t="n"/>
-      <c r="U133" s="12" t="n"/>
+      <c r="T133" s="27" t="n"/>
+      <c r="U133" s="23" t="n"/>
       <c r="V133" s="13" t="n"/>
     </row>
     <row r="134">
@@ -4908,26 +4919,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B134" s="18" t="n"/>
-      <c r="C134" s="19" t="n"/>
+      <c r="B134" s="31" t="n"/>
+      <c r="C134" s="24" t="n"/>
       <c r="D134" s="20" t="n"/>
-      <c r="E134" s="18" t="n"/>
-      <c r="F134" s="19" t="n"/>
+      <c r="E134" s="31" t="n"/>
+      <c r="F134" s="24" t="n"/>
       <c r="G134" s="20" t="n"/>
-      <c r="H134" s="18" t="n"/>
-      <c r="I134" s="19" t="n"/>
+      <c r="H134" s="31" t="n"/>
+      <c r="I134" s="24" t="n"/>
       <c r="J134" s="20" t="n"/>
-      <c r="K134" s="18" t="n"/>
-      <c r="L134" s="19" t="n"/>
+      <c r="K134" s="31" t="n"/>
+      <c r="L134" s="24" t="n"/>
       <c r="M134" s="20" t="n"/>
-      <c r="N134" s="18" t="n"/>
-      <c r="O134" s="19" t="n"/>
+      <c r="N134" s="31" t="n"/>
+      <c r="O134" s="24" t="n"/>
       <c r="P134" s="20" t="n"/>
-      <c r="Q134" s="18" t="n"/>
-      <c r="R134" s="19" t="n"/>
+      <c r="Q134" s="31" t="n"/>
+      <c r="R134" s="24" t="n"/>
       <c r="S134" s="20" t="n"/>
-      <c r="T134" s="18" t="n"/>
-      <c r="U134" s="19" t="n"/>
+      <c r="T134" s="31" t="n"/>
+      <c r="U134" s="24" t="n"/>
       <c r="V134" s="20" t="n"/>
     </row>
     <row r="135">
@@ -4936,26 +4947,26 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B135" s="21" t="n"/>
-      <c r="C135" s="8" t="n"/>
+      <c r="B135" s="25" t="n"/>
+      <c r="C135" s="22" t="n"/>
       <c r="D135" s="9" t="n"/>
-      <c r="E135" s="21" t="n"/>
-      <c r="F135" s="8" t="n"/>
+      <c r="E135" s="25" t="n"/>
+      <c r="F135" s="22" t="n"/>
       <c r="G135" s="9" t="n"/>
-      <c r="H135" s="21" t="n"/>
-      <c r="I135" s="8" t="n"/>
+      <c r="H135" s="25" t="n"/>
+      <c r="I135" s="22" t="n"/>
       <c r="J135" s="9" t="n"/>
-      <c r="K135" s="21" t="n"/>
-      <c r="L135" s="8" t="n"/>
+      <c r="K135" s="25" t="n"/>
+      <c r="L135" s="22" t="n"/>
       <c r="M135" s="9" t="n"/>
-      <c r="N135" s="21" t="n"/>
-      <c r="O135" s="8" t="n"/>
+      <c r="N135" s="25" t="n"/>
+      <c r="O135" s="22" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="21" t="n"/>
-      <c r="R135" s="8" t="n"/>
+      <c r="Q135" s="25" t="n"/>
+      <c r="R135" s="22" t="n"/>
       <c r="S135" s="9" t="n"/>
-      <c r="T135" s="21" t="n"/>
-      <c r="U135" s="8" t="n"/>
+      <c r="T135" s="25" t="n"/>
+      <c r="U135" s="22" t="n"/>
       <c r="V135" s="9" t="n"/>
     </row>
     <row r="136">
@@ -4964,26 +4975,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B136" s="16" t="n"/>
-      <c r="C136" s="12" t="n"/>
+      <c r="B136" s="27" t="n"/>
+      <c r="C136" s="23" t="n"/>
       <c r="D136" s="13" t="n"/>
-      <c r="E136" s="16" t="n"/>
-      <c r="F136" s="12" t="n"/>
+      <c r="E136" s="27" t="n"/>
+      <c r="F136" s="23" t="n"/>
       <c r="G136" s="13" t="n"/>
-      <c r="H136" s="16" t="n"/>
-      <c r="I136" s="12" t="n"/>
+      <c r="H136" s="27" t="n"/>
+      <c r="I136" s="23" t="n"/>
       <c r="J136" s="13" t="n"/>
-      <c r="K136" s="16" t="n"/>
-      <c r="L136" s="12" t="n"/>
+      <c r="K136" s="27" t="n"/>
+      <c r="L136" s="23" t="n"/>
       <c r="M136" s="13" t="n"/>
-      <c r="N136" s="16" t="n"/>
-      <c r="O136" s="12" t="n"/>
+      <c r="N136" s="27" t="n"/>
+      <c r="O136" s="23" t="n"/>
       <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="16" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="Q136" s="27" t="n"/>
+      <c r="R136" s="23" t="n"/>
       <c r="S136" s="13" t="n"/>
-      <c r="T136" s="16" t="n"/>
-      <c r="U136" s="12" t="n"/>
+      <c r="T136" s="27" t="n"/>
+      <c r="U136" s="23" t="n"/>
       <c r="V136" s="13" t="n"/>
     </row>
     <row r="137">
@@ -4992,26 +5003,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B137" s="16" t="n"/>
-      <c r="C137" s="12" t="n"/>
+      <c r="B137" s="27" t="n"/>
+      <c r="C137" s="23" t="n"/>
       <c r="D137" s="13" t="n"/>
-      <c r="E137" s="16" t="n"/>
-      <c r="F137" s="12" t="n"/>
+      <c r="E137" s="27" t="n"/>
+      <c r="F137" s="23" t="n"/>
       <c r="G137" s="13" t="n"/>
-      <c r="H137" s="16" t="n"/>
-      <c r="I137" s="12" t="n"/>
+      <c r="H137" s="27" t="n"/>
+      <c r="I137" s="23" t="n"/>
       <c r="J137" s="13" t="n"/>
-      <c r="K137" s="16" t="n"/>
-      <c r="L137" s="12" t="n"/>
+      <c r="K137" s="27" t="n"/>
+      <c r="L137" s="23" t="n"/>
       <c r="M137" s="13" t="n"/>
-      <c r="N137" s="16" t="n"/>
-      <c r="O137" s="12" t="n"/>
+      <c r="N137" s="27" t="n"/>
+      <c r="O137" s="23" t="n"/>
       <c r="P137" s="13" t="n"/>
-      <c r="Q137" s="16" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="Q137" s="27" t="n"/>
+      <c r="R137" s="23" t="n"/>
       <c r="S137" s="13" t="n"/>
-      <c r="T137" s="16" t="n"/>
-      <c r="U137" s="12" t="n"/>
+      <c r="T137" s="27" t="n"/>
+      <c r="U137" s="23" t="n"/>
       <c r="V137" s="13" t="n"/>
     </row>
     <row r="138">
@@ -5020,26 +5031,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B138" s="16" t="n"/>
-      <c r="C138" s="12" t="n"/>
+      <c r="B138" s="27" t="n"/>
+      <c r="C138" s="23" t="n"/>
       <c r="D138" s="13" t="n"/>
-      <c r="E138" s="16" t="n"/>
-      <c r="F138" s="12" t="n"/>
+      <c r="E138" s="27" t="n"/>
+      <c r="F138" s="23" t="n"/>
       <c r="G138" s="13" t="n"/>
-      <c r="H138" s="16" t="n"/>
-      <c r="I138" s="12" t="n"/>
+      <c r="H138" s="27" t="n"/>
+      <c r="I138" s="23" t="n"/>
       <c r="J138" s="13" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="12" t="n"/>
+      <c r="K138" s="27" t="n"/>
+      <c r="L138" s="23" t="n"/>
       <c r="M138" s="13" t="n"/>
-      <c r="N138" s="16" t="n"/>
-      <c r="O138" s="12" t="n"/>
+      <c r="N138" s="27" t="n"/>
+      <c r="O138" s="23" t="n"/>
       <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="16" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="Q138" s="27" t="n"/>
+      <c r="R138" s="23" t="n"/>
       <c r="S138" s="13" t="n"/>
-      <c r="T138" s="16" t="n"/>
-      <c r="U138" s="12" t="n"/>
+      <c r="T138" s="27" t="n"/>
+      <c r="U138" s="23" t="n"/>
       <c r="V138" s="13" t="n"/>
     </row>
     <row r="139">
@@ -5048,26 +5059,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B139" s="16" t="n"/>
-      <c r="C139" s="12" t="n"/>
+      <c r="B139" s="27" t="n"/>
+      <c r="C139" s="23" t="n"/>
       <c r="D139" s="13" t="n"/>
-      <c r="E139" s="16" t="n"/>
-      <c r="F139" s="12" t="n"/>
+      <c r="E139" s="27" t="n"/>
+      <c r="F139" s="23" t="n"/>
       <c r="G139" s="13" t="n"/>
-      <c r="H139" s="16" t="n"/>
-      <c r="I139" s="12" t="n"/>
+      <c r="H139" s="27" t="n"/>
+      <c r="I139" s="23" t="n"/>
       <c r="J139" s="13" t="n"/>
-      <c r="K139" s="16" t="n"/>
-      <c r="L139" s="12" t="n"/>
+      <c r="K139" s="27" t="n"/>
+      <c r="L139" s="23" t="n"/>
       <c r="M139" s="13" t="n"/>
-      <c r="N139" s="16" t="n"/>
-      <c r="O139" s="12" t="n"/>
+      <c r="N139" s="27" t="n"/>
+      <c r="O139" s="23" t="n"/>
       <c r="P139" s="13" t="n"/>
-      <c r="Q139" s="16" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="Q139" s="27" t="n"/>
+      <c r="R139" s="23" t="n"/>
       <c r="S139" s="13" t="n"/>
-      <c r="T139" s="16" t="n"/>
-      <c r="U139" s="12" t="n"/>
+      <c r="T139" s="27" t="n"/>
+      <c r="U139" s="23" t="n"/>
       <c r="V139" s="13" t="n"/>
     </row>
     <row r="140">
@@ -5076,26 +5087,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B140" s="16" t="n"/>
-      <c r="C140" s="12" t="n"/>
+      <c r="B140" s="27" t="n"/>
+      <c r="C140" s="23" t="n"/>
       <c r="D140" s="13" t="n"/>
-      <c r="E140" s="16" t="n"/>
-      <c r="F140" s="12" t="n"/>
+      <c r="E140" s="27" t="n"/>
+      <c r="F140" s="23" t="n"/>
       <c r="G140" s="13" t="n"/>
-      <c r="H140" s="16" t="n"/>
-      <c r="I140" s="12" t="n"/>
+      <c r="H140" s="27" t="n"/>
+      <c r="I140" s="23" t="n"/>
       <c r="J140" s="13" t="n"/>
-      <c r="K140" s="16" t="n"/>
-      <c r="L140" s="12" t="n"/>
+      <c r="K140" s="27" t="n"/>
+      <c r="L140" s="23" t="n"/>
       <c r="M140" s="13" t="n"/>
-      <c r="N140" s="16" t="n"/>
-      <c r="O140" s="12" t="n"/>
+      <c r="N140" s="27" t="n"/>
+      <c r="O140" s="23" t="n"/>
       <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="16" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="Q140" s="27" t="n"/>
+      <c r="R140" s="23" t="n"/>
       <c r="S140" s="13" t="n"/>
-      <c r="T140" s="16" t="n"/>
-      <c r="U140" s="12" t="n"/>
+      <c r="T140" s="27" t="n"/>
+      <c r="U140" s="23" t="n"/>
       <c r="V140" s="13" t="n"/>
     </row>
     <row r="141">
@@ -5104,26 +5115,26 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B141" s="16" t="n"/>
-      <c r="C141" s="12" t="n"/>
+      <c r="B141" s="27" t="n"/>
+      <c r="C141" s="23" t="n"/>
       <c r="D141" s="13" t="n"/>
-      <c r="E141" s="16" t="n"/>
-      <c r="F141" s="12" t="n"/>
+      <c r="E141" s="27" t="n"/>
+      <c r="F141" s="23" t="n"/>
       <c r="G141" s="13" t="n"/>
-      <c r="H141" s="16" t="n"/>
-      <c r="I141" s="12" t="n"/>
+      <c r="H141" s="27" t="n"/>
+      <c r="I141" s="23" t="n"/>
       <c r="J141" s="13" t="n"/>
-      <c r="K141" s="16" t="n"/>
-      <c r="L141" s="12" t="n"/>
+      <c r="K141" s="27" t="n"/>
+      <c r="L141" s="23" t="n"/>
       <c r="M141" s="13" t="n"/>
-      <c r="N141" s="16" t="n"/>
-      <c r="O141" s="12" t="n"/>
+      <c r="N141" s="27" t="n"/>
+      <c r="O141" s="23" t="n"/>
       <c r="P141" s="13" t="n"/>
-      <c r="Q141" s="16" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="Q141" s="27" t="n"/>
+      <c r="R141" s="23" t="n"/>
       <c r="S141" s="13" t="n"/>
-      <c r="T141" s="16" t="n"/>
-      <c r="U141" s="12" t="n"/>
+      <c r="T141" s="27" t="n"/>
+      <c r="U141" s="23" t="n"/>
       <c r="V141" s="13" t="n"/>
     </row>
     <row r="142">
@@ -5132,26 +5143,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B142" s="16" t="n"/>
-      <c r="C142" s="12" t="n"/>
+      <c r="B142" s="27" t="n"/>
+      <c r="C142" s="23" t="n"/>
       <c r="D142" s="13" t="n"/>
-      <c r="E142" s="16" t="n"/>
-      <c r="F142" s="12" t="n"/>
+      <c r="E142" s="27" t="n"/>
+      <c r="F142" s="23" t="n"/>
       <c r="G142" s="13" t="n"/>
-      <c r="H142" s="16" t="n"/>
-      <c r="I142" s="12" t="n"/>
+      <c r="H142" s="27" t="n"/>
+      <c r="I142" s="23" t="n"/>
       <c r="J142" s="13" t="n"/>
-      <c r="K142" s="16" t="n"/>
-      <c r="L142" s="12" t="n"/>
+      <c r="K142" s="27" t="n"/>
+      <c r="L142" s="23" t="n"/>
       <c r="M142" s="13" t="n"/>
-      <c r="N142" s="16" t="n"/>
-      <c r="O142" s="12" t="n"/>
+      <c r="N142" s="27" t="n"/>
+      <c r="O142" s="23" t="n"/>
       <c r="P142" s="13" t="n"/>
-      <c r="Q142" s="16" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="Q142" s="27" t="n"/>
+      <c r="R142" s="23" t="n"/>
       <c r="S142" s="13" t="n"/>
-      <c r="T142" s="16" t="n"/>
-      <c r="U142" s="12" t="n"/>
+      <c r="T142" s="27" t="n"/>
+      <c r="U142" s="23" t="n"/>
       <c r="V142" s="13" t="n"/>
     </row>
     <row r="143">
@@ -5160,26 +5171,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B143" s="16" t="n"/>
-      <c r="C143" s="12" t="n"/>
+      <c r="B143" s="27" t="n"/>
+      <c r="C143" s="23" t="n"/>
       <c r="D143" s="13" t="n"/>
-      <c r="E143" s="16" t="n"/>
-      <c r="F143" s="12" t="n"/>
+      <c r="E143" s="27" t="n"/>
+      <c r="F143" s="23" t="n"/>
       <c r="G143" s="13" t="n"/>
-      <c r="H143" s="16" t="n"/>
-      <c r="I143" s="12" t="n"/>
+      <c r="H143" s="27" t="n"/>
+      <c r="I143" s="23" t="n"/>
       <c r="J143" s="13" t="n"/>
-      <c r="K143" s="16" t="n"/>
-      <c r="L143" s="12" t="n"/>
+      <c r="K143" s="27" t="n"/>
+      <c r="L143" s="23" t="n"/>
       <c r="M143" s="13" t="n"/>
-      <c r="N143" s="16" t="n"/>
-      <c r="O143" s="12" t="n"/>
+      <c r="N143" s="27" t="n"/>
+      <c r="O143" s="23" t="n"/>
       <c r="P143" s="13" t="n"/>
-      <c r="Q143" s="16" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="Q143" s="27" t="n"/>
+      <c r="R143" s="23" t="n"/>
       <c r="S143" s="13" t="n"/>
-      <c r="T143" s="16" t="n"/>
-      <c r="U143" s="12" t="n"/>
+      <c r="T143" s="27" t="n"/>
+      <c r="U143" s="23" t="n"/>
       <c r="V143" s="13" t="n"/>
     </row>
     <row r="144">
@@ -5188,26 +5199,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B144" s="16" t="n"/>
-      <c r="C144" s="12" t="n"/>
+      <c r="B144" s="27" t="n"/>
+      <c r="C144" s="23" t="n"/>
       <c r="D144" s="13" t="n"/>
-      <c r="E144" s="16" t="n"/>
-      <c r="F144" s="12" t="n"/>
+      <c r="E144" s="27" t="n"/>
+      <c r="F144" s="23" t="n"/>
       <c r="G144" s="13" t="n"/>
-      <c r="H144" s="16" t="n"/>
-      <c r="I144" s="12" t="n"/>
+      <c r="H144" s="27" t="n"/>
+      <c r="I144" s="23" t="n"/>
       <c r="J144" s="13" t="n"/>
-      <c r="K144" s="16" t="n"/>
-      <c r="L144" s="12" t="n"/>
+      <c r="K144" s="27" t="n"/>
+      <c r="L144" s="23" t="n"/>
       <c r="M144" s="13" t="n"/>
-      <c r="N144" s="16" t="n"/>
-      <c r="O144" s="12" t="n"/>
+      <c r="N144" s="27" t="n"/>
+      <c r="O144" s="23" t="n"/>
       <c r="P144" s="13" t="n"/>
-      <c r="Q144" s="16" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="Q144" s="27" t="n"/>
+      <c r="R144" s="23" t="n"/>
       <c r="S144" s="13" t="n"/>
-      <c r="T144" s="16" t="n"/>
-      <c r="U144" s="12" t="n"/>
+      <c r="T144" s="27" t="n"/>
+      <c r="U144" s="23" t="n"/>
       <c r="V144" s="13" t="n"/>
     </row>
     <row r="145">
@@ -5216,26 +5227,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B145" s="16" t="n"/>
-      <c r="C145" s="12" t="n"/>
+      <c r="B145" s="27" t="n"/>
+      <c r="C145" s="23" t="n"/>
       <c r="D145" s="13" t="n"/>
-      <c r="E145" s="16" t="n"/>
-      <c r="F145" s="12" t="n"/>
+      <c r="E145" s="27" t="n"/>
+      <c r="F145" s="23" t="n"/>
       <c r="G145" s="13" t="n"/>
-      <c r="H145" s="16" t="n"/>
-      <c r="I145" s="12" t="n"/>
+      <c r="H145" s="27" t="n"/>
+      <c r="I145" s="23" t="n"/>
       <c r="J145" s="13" t="n"/>
-      <c r="K145" s="16" t="n"/>
-      <c r="L145" s="12" t="n"/>
+      <c r="K145" s="27" t="n"/>
+      <c r="L145" s="23" t="n"/>
       <c r="M145" s="13" t="n"/>
-      <c r="N145" s="16" t="n"/>
-      <c r="O145" s="12" t="n"/>
+      <c r="N145" s="27" t="n"/>
+      <c r="O145" s="23" t="n"/>
       <c r="P145" s="13" t="n"/>
-      <c r="Q145" s="16" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="Q145" s="27" t="n"/>
+      <c r="R145" s="23" t="n"/>
       <c r="S145" s="13" t="n"/>
-      <c r="T145" s="16" t="n"/>
-      <c r="U145" s="12" t="n"/>
+      <c r="T145" s="27" t="n"/>
+      <c r="U145" s="23" t="n"/>
       <c r="V145" s="13" t="n"/>
     </row>
     <row r="146">
@@ -5244,26 +5255,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B146" s="18" t="n"/>
-      <c r="C146" s="19" t="n"/>
+      <c r="B146" s="31" t="n"/>
+      <c r="C146" s="24" t="n"/>
       <c r="D146" s="20" t="n"/>
-      <c r="E146" s="18" t="n"/>
-      <c r="F146" s="19" t="n"/>
+      <c r="E146" s="31" t="n"/>
+      <c r="F146" s="24" t="n"/>
       <c r="G146" s="20" t="n"/>
-      <c r="H146" s="18" t="n"/>
-      <c r="I146" s="19" t="n"/>
+      <c r="H146" s="31" t="n"/>
+      <c r="I146" s="24" t="n"/>
       <c r="J146" s="20" t="n"/>
-      <c r="K146" s="18" t="n"/>
-      <c r="L146" s="19" t="n"/>
+      <c r="K146" s="31" t="n"/>
+      <c r="L146" s="24" t="n"/>
       <c r="M146" s="20" t="n"/>
-      <c r="N146" s="18" t="n"/>
-      <c r="O146" s="19" t="n"/>
+      <c r="N146" s="31" t="n"/>
+      <c r="O146" s="24" t="n"/>
       <c r="P146" s="20" t="n"/>
-      <c r="Q146" s="18" t="n"/>
-      <c r="R146" s="19" t="n"/>
+      <c r="Q146" s="31" t="n"/>
+      <c r="R146" s="24" t="n"/>
       <c r="S146" s="20" t="n"/>
-      <c r="T146" s="18" t="n"/>
-      <c r="U146" s="19" t="n"/>
+      <c r="T146" s="31" t="n"/>
+      <c r="U146" s="24" t="n"/>
       <c r="V146" s="20" t="n"/>
     </row>
     <row r="147">
@@ -5272,26 +5283,26 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B147" s="21" t="n"/>
-      <c r="C147" s="8" t="n"/>
+      <c r="B147" s="25" t="n"/>
+      <c r="C147" s="22" t="n"/>
       <c r="D147" s="9" t="n"/>
-      <c r="E147" s="21" t="n"/>
-      <c r="F147" s="8" t="n"/>
+      <c r="E147" s="25" t="n"/>
+      <c r="F147" s="22" t="n"/>
       <c r="G147" s="9" t="n"/>
-      <c r="H147" s="21" t="n"/>
-      <c r="I147" s="8" t="n"/>
+      <c r="H147" s="25" t="n"/>
+      <c r="I147" s="22" t="n"/>
       <c r="J147" s="9" t="n"/>
-      <c r="K147" s="21" t="n"/>
-      <c r="L147" s="8" t="n"/>
+      <c r="K147" s="25" t="n"/>
+      <c r="L147" s="22" t="n"/>
       <c r="M147" s="9" t="n"/>
-      <c r="N147" s="21" t="n"/>
-      <c r="O147" s="8" t="n"/>
+      <c r="N147" s="25" t="n"/>
+      <c r="O147" s="22" t="n"/>
       <c r="P147" s="9" t="n"/>
-      <c r="Q147" s="21" t="n"/>
-      <c r="R147" s="8" t="n"/>
+      <c r="Q147" s="25" t="n"/>
+      <c r="R147" s="22" t="n"/>
       <c r="S147" s="9" t="n"/>
-      <c r="T147" s="21" t="n"/>
-      <c r="U147" s="8" t="n"/>
+      <c r="T147" s="25" t="n"/>
+      <c r="U147" s="22" t="n"/>
       <c r="V147" s="9" t="n"/>
     </row>
     <row r="148">
@@ -5300,26 +5311,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B148" s="16" t="n"/>
-      <c r="C148" s="12" t="n"/>
+      <c r="B148" s="27" t="n"/>
+      <c r="C148" s="23" t="n"/>
       <c r="D148" s="13" t="n"/>
-      <c r="E148" s="16" t="n"/>
-      <c r="F148" s="12" t="n"/>
+      <c r="E148" s="27" t="n"/>
+      <c r="F148" s="23" t="n"/>
       <c r="G148" s="13" t="n"/>
-      <c r="H148" s="16" t="n"/>
-      <c r="I148" s="12" t="n"/>
+      <c r="H148" s="27" t="n"/>
+      <c r="I148" s="23" t="n"/>
       <c r="J148" s="13" t="n"/>
-      <c r="K148" s="16" t="n"/>
-      <c r="L148" s="12" t="n"/>
+      <c r="K148" s="27" t="n"/>
+      <c r="L148" s="23" t="n"/>
       <c r="M148" s="13" t="n"/>
-      <c r="N148" s="16" t="n"/>
-      <c r="O148" s="12" t="n"/>
+      <c r="N148" s="27" t="n"/>
+      <c r="O148" s="23" t="n"/>
       <c r="P148" s="13" t="n"/>
-      <c r="Q148" s="16" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="Q148" s="27" t="n"/>
+      <c r="R148" s="23" t="n"/>
       <c r="S148" s="13" t="n"/>
-      <c r="T148" s="16" t="n"/>
-      <c r="U148" s="12" t="n"/>
+      <c r="T148" s="27" t="n"/>
+      <c r="U148" s="23" t="n"/>
       <c r="V148" s="13" t="n"/>
     </row>
     <row r="149">
@@ -5328,26 +5339,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B149" s="16" t="n"/>
-      <c r="C149" s="12" t="n"/>
+      <c r="B149" s="27" t="n"/>
+      <c r="C149" s="23" t="n"/>
       <c r="D149" s="13" t="n"/>
-      <c r="E149" s="16" t="n"/>
-      <c r="F149" s="12" t="n"/>
+      <c r="E149" s="27" t="n"/>
+      <c r="F149" s="23" t="n"/>
       <c r="G149" s="13" t="n"/>
-      <c r="H149" s="16" t="n"/>
-      <c r="I149" s="12" t="n"/>
+      <c r="H149" s="27" t="n"/>
+      <c r="I149" s="23" t="n"/>
       <c r="J149" s="13" t="n"/>
-      <c r="K149" s="16" t="n"/>
-      <c r="L149" s="12" t="n"/>
+      <c r="K149" s="27" t="n"/>
+      <c r="L149" s="23" t="n"/>
       <c r="M149" s="13" t="n"/>
-      <c r="N149" s="16" t="n"/>
-      <c r="O149" s="12" t="n"/>
+      <c r="N149" s="27" t="n"/>
+      <c r="O149" s="23" t="n"/>
       <c r="P149" s="13" t="n"/>
-      <c r="Q149" s="16" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="Q149" s="27" t="n"/>
+      <c r="R149" s="23" t="n"/>
       <c r="S149" s="13" t="n"/>
-      <c r="T149" s="16" t="n"/>
-      <c r="U149" s="12" t="n"/>
+      <c r="T149" s="27" t="n"/>
+      <c r="U149" s="23" t="n"/>
       <c r="V149" s="13" t="n"/>
     </row>
     <row r="150">
@@ -5356,26 +5367,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B150" s="16" t="n"/>
-      <c r="C150" s="12" t="n"/>
+      <c r="B150" s="27" t="n"/>
+      <c r="C150" s="23" t="n"/>
       <c r="D150" s="13" t="n"/>
-      <c r="E150" s="16" t="n"/>
-      <c r="F150" s="12" t="n"/>
+      <c r="E150" s="27" t="n"/>
+      <c r="F150" s="23" t="n"/>
       <c r="G150" s="13" t="n"/>
-      <c r="H150" s="16" t="n"/>
-      <c r="I150" s="12" t="n"/>
+      <c r="H150" s="27" t="n"/>
+      <c r="I150" s="23" t="n"/>
       <c r="J150" s="13" t="n"/>
-      <c r="K150" s="16" t="n"/>
-      <c r="L150" s="12" t="n"/>
+      <c r="K150" s="27" t="n"/>
+      <c r="L150" s="23" t="n"/>
       <c r="M150" s="13" t="n"/>
-      <c r="N150" s="16" t="n"/>
-      <c r="O150" s="12" t="n"/>
+      <c r="N150" s="27" t="n"/>
+      <c r="O150" s="23" t="n"/>
       <c r="P150" s="13" t="n"/>
-      <c r="Q150" s="16" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="Q150" s="27" t="n"/>
+      <c r="R150" s="23" t="n"/>
       <c r="S150" s="13" t="n"/>
-      <c r="T150" s="16" t="n"/>
-      <c r="U150" s="12" t="n"/>
+      <c r="T150" s="27" t="n"/>
+      <c r="U150" s="23" t="n"/>
       <c r="V150" s="13" t="n"/>
     </row>
     <row r="151">
@@ -5384,26 +5395,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B151" s="16" t="n"/>
-      <c r="C151" s="12" t="n"/>
+      <c r="B151" s="27" t="n"/>
+      <c r="C151" s="23" t="n"/>
       <c r="D151" s="13" t="n"/>
-      <c r="E151" s="16" t="n"/>
-      <c r="F151" s="12" t="n"/>
+      <c r="E151" s="27" t="n"/>
+      <c r="F151" s="23" t="n"/>
       <c r="G151" s="13" t="n"/>
-      <c r="H151" s="16" t="n"/>
-      <c r="I151" s="12" t="n"/>
+      <c r="H151" s="27" t="n"/>
+      <c r="I151" s="23" t="n"/>
       <c r="J151" s="13" t="n"/>
-      <c r="K151" s="16" t="n"/>
-      <c r="L151" s="12" t="n"/>
+      <c r="K151" s="27" t="n"/>
+      <c r="L151" s="23" t="n"/>
       <c r="M151" s="13" t="n"/>
-      <c r="N151" s="16" t="n"/>
-      <c r="O151" s="12" t="n"/>
+      <c r="N151" s="27" t="n"/>
+      <c r="O151" s="23" t="n"/>
       <c r="P151" s="13" t="n"/>
-      <c r="Q151" s="16" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="Q151" s="27" t="n"/>
+      <c r="R151" s="23" t="n"/>
       <c r="S151" s="13" t="n"/>
-      <c r="T151" s="16" t="n"/>
-      <c r="U151" s="12" t="n"/>
+      <c r="T151" s="27" t="n"/>
+      <c r="U151" s="23" t="n"/>
       <c r="V151" s="13" t="n"/>
     </row>
     <row r="152">
@@ -5412,26 +5423,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B152" s="16" t="n"/>
-      <c r="C152" s="12" t="n"/>
+      <c r="B152" s="27" t="n"/>
+      <c r="C152" s="23" t="n"/>
       <c r="D152" s="13" t="n"/>
-      <c r="E152" s="16" t="n"/>
-      <c r="F152" s="12" t="n"/>
+      <c r="E152" s="27" t="n"/>
+      <c r="F152" s="23" t="n"/>
       <c r="G152" s="13" t="n"/>
-      <c r="H152" s="16" t="n"/>
-      <c r="I152" s="12" t="n"/>
+      <c r="H152" s="27" t="n"/>
+      <c r="I152" s="23" t="n"/>
       <c r="J152" s="13" t="n"/>
-      <c r="K152" s="16" t="n"/>
-      <c r="L152" s="12" t="n"/>
+      <c r="K152" s="27" t="n"/>
+      <c r="L152" s="23" t="n"/>
       <c r="M152" s="13" t="n"/>
-      <c r="N152" s="16" t="n"/>
-      <c r="O152" s="12" t="n"/>
+      <c r="N152" s="27" t="n"/>
+      <c r="O152" s="23" t="n"/>
       <c r="P152" s="13" t="n"/>
-      <c r="Q152" s="16" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="Q152" s="27" t="n"/>
+      <c r="R152" s="23" t="n"/>
       <c r="S152" s="13" t="n"/>
-      <c r="T152" s="16" t="n"/>
-      <c r="U152" s="12" t="n"/>
+      <c r="T152" s="27" t="n"/>
+      <c r="U152" s="23" t="n"/>
       <c r="V152" s="13" t="n"/>
     </row>
     <row r="153">
@@ -5440,26 +5451,26 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B153" s="16" t="n"/>
-      <c r="C153" s="12" t="n"/>
+      <c r="B153" s="27" t="n"/>
+      <c r="C153" s="23" t="n"/>
       <c r="D153" s="13" t="n"/>
-      <c r="E153" s="16" t="n"/>
-      <c r="F153" s="12" t="n"/>
+      <c r="E153" s="27" t="n"/>
+      <c r="F153" s="23" t="n"/>
       <c r="G153" s="13" t="n"/>
-      <c r="H153" s="16" t="n"/>
-      <c r="I153" s="12" t="n"/>
+      <c r="H153" s="27" t="n"/>
+      <c r="I153" s="23" t="n"/>
       <c r="J153" s="13" t="n"/>
-      <c r="K153" s="16" t="n"/>
-      <c r="L153" s="12" t="n"/>
+      <c r="K153" s="27" t="n"/>
+      <c r="L153" s="23" t="n"/>
       <c r="M153" s="13" t="n"/>
-      <c r="N153" s="16" t="n"/>
-      <c r="O153" s="12" t="n"/>
+      <c r="N153" s="27" t="n"/>
+      <c r="O153" s="23" t="n"/>
       <c r="P153" s="13" t="n"/>
-      <c r="Q153" s="16" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="Q153" s="27" t="n"/>
+      <c r="R153" s="23" t="n"/>
       <c r="S153" s="13" t="n"/>
-      <c r="T153" s="16" t="n"/>
-      <c r="U153" s="12" t="n"/>
+      <c r="T153" s="27" t="n"/>
+      <c r="U153" s="23" t="n"/>
       <c r="V153" s="13" t="n"/>
     </row>
     <row r="154">
@@ -5468,26 +5479,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B154" s="16" t="n"/>
-      <c r="C154" s="12" t="n"/>
+      <c r="B154" s="27" t="n"/>
+      <c r="C154" s="23" t="n"/>
       <c r="D154" s="13" t="n"/>
-      <c r="E154" s="16" t="n"/>
-      <c r="F154" s="12" t="n"/>
+      <c r="E154" s="27" t="n"/>
+      <c r="F154" s="23" t="n"/>
       <c r="G154" s="13" t="n"/>
-      <c r="H154" s="16" t="n"/>
-      <c r="I154" s="12" t="n"/>
+      <c r="H154" s="27" t="n"/>
+      <c r="I154" s="23" t="n"/>
       <c r="J154" s="13" t="n"/>
-      <c r="K154" s="16" t="n"/>
-      <c r="L154" s="12" t="n"/>
+      <c r="K154" s="27" t="n"/>
+      <c r="L154" s="23" t="n"/>
       <c r="M154" s="13" t="n"/>
-      <c r="N154" s="16" t="n"/>
-      <c r="O154" s="12" t="n"/>
+      <c r="N154" s="27" t="n"/>
+      <c r="O154" s="23" t="n"/>
       <c r="P154" s="13" t="n"/>
-      <c r="Q154" s="16" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="Q154" s="27" t="n"/>
+      <c r="R154" s="23" t="n"/>
       <c r="S154" s="13" t="n"/>
-      <c r="T154" s="16" t="n"/>
-      <c r="U154" s="12" t="n"/>
+      <c r="T154" s="27" t="n"/>
+      <c r="U154" s="23" t="n"/>
       <c r="V154" s="13" t="n"/>
     </row>
     <row r="155">
@@ -5496,26 +5507,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B155" s="16" t="n"/>
-      <c r="C155" s="12" t="n"/>
+      <c r="B155" s="27" t="n"/>
+      <c r="C155" s="23" t="n"/>
       <c r="D155" s="13" t="n"/>
-      <c r="E155" s="16" t="n"/>
-      <c r="F155" s="12" t="n"/>
+      <c r="E155" s="27" t="n"/>
+      <c r="F155" s="23" t="n"/>
       <c r="G155" s="13" t="n"/>
-      <c r="H155" s="16" t="n"/>
-      <c r="I155" s="12" t="n"/>
+      <c r="H155" s="27" t="n"/>
+      <c r="I155" s="23" t="n"/>
       <c r="J155" s="13" t="n"/>
-      <c r="K155" s="16" t="n"/>
-      <c r="L155" s="12" t="n"/>
+      <c r="K155" s="27" t="n"/>
+      <c r="L155" s="23" t="n"/>
       <c r="M155" s="13" t="n"/>
-      <c r="N155" s="16" t="n"/>
-      <c r="O155" s="12" t="n"/>
+      <c r="N155" s="27" t="n"/>
+      <c r="O155" s="23" t="n"/>
       <c r="P155" s="13" t="n"/>
-      <c r="Q155" s="16" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="Q155" s="27" t="n"/>
+      <c r="R155" s="23" t="n"/>
       <c r="S155" s="13" t="n"/>
-      <c r="T155" s="16" t="n"/>
-      <c r="U155" s="12" t="n"/>
+      <c r="T155" s="27" t="n"/>
+      <c r="U155" s="23" t="n"/>
       <c r="V155" s="13" t="n"/>
     </row>
     <row r="156">
@@ -5524,26 +5535,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B156" s="16" t="n"/>
-      <c r="C156" s="12" t="n"/>
+      <c r="B156" s="27" t="n"/>
+      <c r="C156" s="23" t="n"/>
       <c r="D156" s="13" t="n"/>
-      <c r="E156" s="16" t="n"/>
-      <c r="F156" s="12" t="n"/>
+      <c r="E156" s="27" t="n"/>
+      <c r="F156" s="23" t="n"/>
       <c r="G156" s="13" t="n"/>
-      <c r="H156" s="16" t="n"/>
-      <c r="I156" s="12" t="n"/>
+      <c r="H156" s="27" t="n"/>
+      <c r="I156" s="23" t="n"/>
       <c r="J156" s="13" t="n"/>
-      <c r="K156" s="16" t="n"/>
-      <c r="L156" s="12" t="n"/>
+      <c r="K156" s="27" t="n"/>
+      <c r="L156" s="23" t="n"/>
       <c r="M156" s="13" t="n"/>
-      <c r="N156" s="16" t="n"/>
-      <c r="O156" s="12" t="n"/>
+      <c r="N156" s="27" t="n"/>
+      <c r="O156" s="23" t="n"/>
       <c r="P156" s="13" t="n"/>
-      <c r="Q156" s="16" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="Q156" s="27" t="n"/>
+      <c r="R156" s="23" t="n"/>
       <c r="S156" s="13" t="n"/>
-      <c r="T156" s="16" t="n"/>
-      <c r="U156" s="12" t="n"/>
+      <c r="T156" s="27" t="n"/>
+      <c r="U156" s="23" t="n"/>
       <c r="V156" s="13" t="n"/>
     </row>
     <row r="157">
@@ -5552,26 +5563,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B157" s="16" t="n"/>
-      <c r="C157" s="12" t="n"/>
+      <c r="B157" s="27" t="n"/>
+      <c r="C157" s="23" t="n"/>
       <c r="D157" s="13" t="n"/>
-      <c r="E157" s="16" t="n"/>
-      <c r="F157" s="12" t="n"/>
+      <c r="E157" s="27" t="n"/>
+      <c r="F157" s="23" t="n"/>
       <c r="G157" s="13" t="n"/>
-      <c r="H157" s="16" t="n"/>
-      <c r="I157" s="12" t="n"/>
+      <c r="H157" s="27" t="n"/>
+      <c r="I157" s="23" t="n"/>
       <c r="J157" s="13" t="n"/>
-      <c r="K157" s="16" t="n"/>
-      <c r="L157" s="12" t="n"/>
+      <c r="K157" s="27" t="n"/>
+      <c r="L157" s="23" t="n"/>
       <c r="M157" s="13" t="n"/>
-      <c r="N157" s="16" t="n"/>
-      <c r="O157" s="12" t="n"/>
+      <c r="N157" s="27" t="n"/>
+      <c r="O157" s="23" t="n"/>
       <c r="P157" s="13" t="n"/>
-      <c r="Q157" s="16" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="Q157" s="27" t="n"/>
+      <c r="R157" s="23" t="n"/>
       <c r="S157" s="13" t="n"/>
-      <c r="T157" s="16" t="n"/>
-      <c r="U157" s="12" t="n"/>
+      <c r="T157" s="27" t="n"/>
+      <c r="U157" s="23" t="n"/>
       <c r="V157" s="13" t="n"/>
     </row>
     <row r="158">
@@ -5580,26 +5591,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B158" s="18" t="n"/>
-      <c r="C158" s="19" t="n"/>
+      <c r="B158" s="31" t="n"/>
+      <c r="C158" s="24" t="n"/>
       <c r="D158" s="20" t="n"/>
-      <c r="E158" s="18" t="n"/>
-      <c r="F158" s="19" t="n"/>
+      <c r="E158" s="31" t="n"/>
+      <c r="F158" s="24" t="n"/>
       <c r="G158" s="20" t="n"/>
-      <c r="H158" s="18" t="n"/>
-      <c r="I158" s="19" t="n"/>
+      <c r="H158" s="31" t="n"/>
+      <c r="I158" s="24" t="n"/>
       <c r="J158" s="20" t="n"/>
-      <c r="K158" s="18" t="n"/>
-      <c r="L158" s="19" t="n"/>
+      <c r="K158" s="31" t="n"/>
+      <c r="L158" s="24" t="n"/>
       <c r="M158" s="20" t="n"/>
-      <c r="N158" s="18" t="n"/>
-      <c r="O158" s="19" t="n"/>
+      <c r="N158" s="31" t="n"/>
+      <c r="O158" s="24" t="n"/>
       <c r="P158" s="20" t="n"/>
-      <c r="Q158" s="18" t="n"/>
-      <c r="R158" s="19" t="n"/>
+      <c r="Q158" s="31" t="n"/>
+      <c r="R158" s="24" t="n"/>
       <c r="S158" s="20" t="n"/>
-      <c r="T158" s="18" t="n"/>
-      <c r="U158" s="19" t="n"/>
+      <c r="T158" s="31" t="n"/>
+      <c r="U158" s="24" t="n"/>
       <c r="V158" s="20" t="n"/>
     </row>
     <row r="159">
@@ -5608,26 +5619,26 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B159" s="21" t="n"/>
-      <c r="C159" s="8" t="n"/>
+      <c r="B159" s="25" t="n"/>
+      <c r="C159" s="22" t="n"/>
       <c r="D159" s="9" t="n"/>
-      <c r="E159" s="21" t="n"/>
-      <c r="F159" s="8" t="n"/>
+      <c r="E159" s="25" t="n"/>
+      <c r="F159" s="22" t="n"/>
       <c r="G159" s="9" t="n"/>
-      <c r="H159" s="21" t="n"/>
-      <c r="I159" s="8" t="n"/>
+      <c r="H159" s="25" t="n"/>
+      <c r="I159" s="22" t="n"/>
       <c r="J159" s="9" t="n"/>
-      <c r="K159" s="21" t="n"/>
-      <c r="L159" s="8" t="n"/>
+      <c r="K159" s="25" t="n"/>
+      <c r="L159" s="22" t="n"/>
       <c r="M159" s="9" t="n"/>
-      <c r="N159" s="21" t="n"/>
-      <c r="O159" s="8" t="n"/>
+      <c r="N159" s="25" t="n"/>
+      <c r="O159" s="22" t="n"/>
       <c r="P159" s="9" t="n"/>
-      <c r="Q159" s="21" t="n"/>
-      <c r="R159" s="8" t="n"/>
+      <c r="Q159" s="25" t="n"/>
+      <c r="R159" s="22" t="n"/>
       <c r="S159" s="9" t="n"/>
-      <c r="T159" s="21" t="n"/>
-      <c r="U159" s="8" t="n"/>
+      <c r="T159" s="25" t="n"/>
+      <c r="U159" s="22" t="n"/>
       <c r="V159" s="9" t="n"/>
     </row>
     <row r="160">
@@ -5636,26 +5647,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B160" s="16" t="n"/>
-      <c r="C160" s="12" t="n"/>
+      <c r="B160" s="27" t="n"/>
+      <c r="C160" s="23" t="n"/>
       <c r="D160" s="13" t="n"/>
-      <c r="E160" s="16" t="n"/>
-      <c r="F160" s="12" t="n"/>
+      <c r="E160" s="27" t="n"/>
+      <c r="F160" s="23" t="n"/>
       <c r="G160" s="13" t="n"/>
-      <c r="H160" s="16" t="n"/>
-      <c r="I160" s="12" t="n"/>
+      <c r="H160" s="27" t="n"/>
+      <c r="I160" s="23" t="n"/>
       <c r="J160" s="13" t="n"/>
-      <c r="K160" s="16" t="n"/>
-      <c r="L160" s="12" t="n"/>
+      <c r="K160" s="27" t="n"/>
+      <c r="L160" s="23" t="n"/>
       <c r="M160" s="13" t="n"/>
-      <c r="N160" s="16" t="n"/>
-      <c r="O160" s="12" t="n"/>
+      <c r="N160" s="27" t="n"/>
+      <c r="O160" s="23" t="n"/>
       <c r="P160" s="13" t="n"/>
-      <c r="Q160" s="16" t="n"/>
-      <c r="R160" s="12" t="n"/>
+      <c r="Q160" s="27" t="n"/>
+      <c r="R160" s="23" t="n"/>
       <c r="S160" s="13" t="n"/>
-      <c r="T160" s="16" t="n"/>
-      <c r="U160" s="12" t="n"/>
+      <c r="T160" s="27" t="n"/>
+      <c r="U160" s="23" t="n"/>
       <c r="V160" s="13" t="n"/>
     </row>
     <row r="161">
@@ -5664,26 +5675,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B161" s="16" t="n"/>
-      <c r="C161" s="12" t="n"/>
+      <c r="B161" s="27" t="n"/>
+      <c r="C161" s="23" t="n"/>
       <c r="D161" s="13" t="n"/>
-      <c r="E161" s="16" t="n"/>
-      <c r="F161" s="12" t="n"/>
+      <c r="E161" s="27" t="n"/>
+      <c r="F161" s="23" t="n"/>
       <c r="G161" s="13" t="n"/>
-      <c r="H161" s="16" t="n"/>
-      <c r="I161" s="12" t="n"/>
+      <c r="H161" s="27" t="n"/>
+      <c r="I161" s="23" t="n"/>
       <c r="J161" s="13" t="n"/>
-      <c r="K161" s="16" t="n"/>
-      <c r="L161" s="12" t="n"/>
+      <c r="K161" s="27" t="n"/>
+      <c r="L161" s="23" t="n"/>
       <c r="M161" s="13" t="n"/>
-      <c r="N161" s="16" t="n"/>
-      <c r="O161" s="12" t="n"/>
+      <c r="N161" s="27" t="n"/>
+      <c r="O161" s="23" t="n"/>
       <c r="P161" s="13" t="n"/>
-      <c r="Q161" s="16" t="n"/>
-      <c r="R161" s="12" t="n"/>
+      <c r="Q161" s="27" t="n"/>
+      <c r="R161" s="23" t="n"/>
       <c r="S161" s="13" t="n"/>
-      <c r="T161" s="16" t="n"/>
-      <c r="U161" s="12" t="n"/>
+      <c r="T161" s="27" t="n"/>
+      <c r="U161" s="23" t="n"/>
       <c r="V161" s="13" t="n"/>
     </row>
     <row r="162">
@@ -5692,26 +5703,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B162" s="16" t="n"/>
-      <c r="C162" s="12" t="n"/>
+      <c r="B162" s="27" t="n"/>
+      <c r="C162" s="23" t="n"/>
       <c r="D162" s="13" t="n"/>
-      <c r="E162" s="16" t="n"/>
-      <c r="F162" s="12" t="n"/>
+      <c r="E162" s="27" t="n"/>
+      <c r="F162" s="23" t="n"/>
       <c r="G162" s="13" t="n"/>
-      <c r="H162" s="16" t="n"/>
-      <c r="I162" s="12" t="n"/>
+      <c r="H162" s="27" t="n"/>
+      <c r="I162" s="23" t="n"/>
       <c r="J162" s="13" t="n"/>
-      <c r="K162" s="16" t="n"/>
-      <c r="L162" s="12" t="n"/>
+      <c r="K162" s="27" t="n"/>
+      <c r="L162" s="23" t="n"/>
       <c r="M162" s="13" t="n"/>
-      <c r="N162" s="16" t="n"/>
-      <c r="O162" s="12" t="n"/>
+      <c r="N162" s="27" t="n"/>
+      <c r="O162" s="23" t="n"/>
       <c r="P162" s="13" t="n"/>
-      <c r="Q162" s="16" t="n"/>
-      <c r="R162" s="12" t="n"/>
+      <c r="Q162" s="27" t="n"/>
+      <c r="R162" s="23" t="n"/>
       <c r="S162" s="13" t="n"/>
-      <c r="T162" s="16" t="n"/>
-      <c r="U162" s="12" t="n"/>
+      <c r="T162" s="27" t="n"/>
+      <c r="U162" s="23" t="n"/>
       <c r="V162" s="13" t="n"/>
     </row>
     <row r="163">
@@ -5720,26 +5731,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B163" s="16" t="n"/>
-      <c r="C163" s="12" t="n"/>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="23" t="n"/>
       <c r="D163" s="13" t="n"/>
-      <c r="E163" s="16" t="n"/>
-      <c r="F163" s="12" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="23" t="n"/>
       <c r="G163" s="13" t="n"/>
-      <c r="H163" s="16" t="n"/>
-      <c r="I163" s="12" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="23" t="n"/>
       <c r="J163" s="13" t="n"/>
-      <c r="K163" s="16" t="n"/>
-      <c r="L163" s="12" t="n"/>
+      <c r="K163" s="27" t="n"/>
+      <c r="L163" s="23" t="n"/>
       <c r="M163" s="13" t="n"/>
-      <c r="N163" s="16" t="n"/>
-      <c r="O163" s="12" t="n"/>
+      <c r="N163" s="27" t="n"/>
+      <c r="O163" s="23" t="n"/>
       <c r="P163" s="13" t="n"/>
-      <c r="Q163" s="16" t="n"/>
-      <c r="R163" s="12" t="n"/>
+      <c r="Q163" s="27" t="n"/>
+      <c r="R163" s="23" t="n"/>
       <c r="S163" s="13" t="n"/>
-      <c r="T163" s="16" t="n"/>
-      <c r="U163" s="12" t="n"/>
+      <c r="T163" s="27" t="n"/>
+      <c r="U163" s="23" t="n"/>
       <c r="V163" s="13" t="n"/>
     </row>
     <row r="164">
@@ -5748,26 +5759,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B164" s="16" t="n"/>
-      <c r="C164" s="12" t="n"/>
+      <c r="B164" s="27" t="n"/>
+      <c r="C164" s="23" t="n"/>
       <c r="D164" s="13" t="n"/>
-      <c r="E164" s="16" t="n"/>
-      <c r="F164" s="12" t="n"/>
+      <c r="E164" s="27" t="n"/>
+      <c r="F164" s="23" t="n"/>
       <c r="G164" s="13" t="n"/>
-      <c r="H164" s="16" t="n"/>
-      <c r="I164" s="12" t="n"/>
+      <c r="H164" s="27" t="n"/>
+      <c r="I164" s="23" t="n"/>
       <c r="J164" s="13" t="n"/>
-      <c r="K164" s="16" t="n"/>
-      <c r="L164" s="12" t="n"/>
+      <c r="K164" s="27" t="n"/>
+      <c r="L164" s="23" t="n"/>
       <c r="M164" s="13" t="n"/>
-      <c r="N164" s="16" t="n"/>
-      <c r="O164" s="12" t="n"/>
+      <c r="N164" s="27" t="n"/>
+      <c r="O164" s="23" t="n"/>
       <c r="P164" s="13" t="n"/>
-      <c r="Q164" s="16" t="n"/>
-      <c r="R164" s="12" t="n"/>
+      <c r="Q164" s="27" t="n"/>
+      <c r="R164" s="23" t="n"/>
       <c r="S164" s="13" t="n"/>
-      <c r="T164" s="16" t="n"/>
-      <c r="U164" s="12" t="n"/>
+      <c r="T164" s="27" t="n"/>
+      <c r="U164" s="23" t="n"/>
       <c r="V164" s="13" t="n"/>
     </row>
     <row r="165">
@@ -5776,50 +5787,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B165" s="16" t="n"/>
-      <c r="C165" s="25" t="inlineStr">
+      <c r="B165" s="27" t="n"/>
+      <c r="C165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="D165" s="13" t="n"/>
-      <c r="E165" s="16" t="n"/>
-      <c r="F165" s="25" t="inlineStr">
+      <c r="E165" s="27" t="n"/>
+      <c r="F165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="G165" s="13" t="n"/>
-      <c r="H165" s="16" t="n"/>
-      <c r="I165" s="25" t="inlineStr">
+      <c r="H165" s="27" t="n"/>
+      <c r="I165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="J165" s="13" t="n"/>
-      <c r="K165" s="16" t="n"/>
-      <c r="L165" s="25" t="inlineStr">
+      <c r="K165" s="27" t="n"/>
+      <c r="L165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="M165" s="13" t="n"/>
-      <c r="N165" s="16" t="n"/>
-      <c r="O165" s="25" t="inlineStr">
+      <c r="N165" s="27" t="n"/>
+      <c r="O165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="P165" s="13" t="n"/>
-      <c r="Q165" s="16" t="n"/>
-      <c r="R165" s="25" t="inlineStr">
+      <c r="Q165" s="27" t="n"/>
+      <c r="R165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="S165" s="13" t="n"/>
-      <c r="T165" s="16" t="n"/>
-      <c r="U165" s="25" t="inlineStr">
+      <c r="T165" s="27" t="n"/>
+      <c r="U165" s="30" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
@@ -5832,26 +5843,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B166" s="16" t="n"/>
-      <c r="C166" s="23" t="n"/>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="28" t="n"/>
       <c r="D166" s="13" t="n"/>
-      <c r="E166" s="16" t="n"/>
-      <c r="F166" s="23" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="28" t="n"/>
       <c r="G166" s="13" t="n"/>
-      <c r="H166" s="16" t="n"/>
-      <c r="I166" s="23" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="28" t="n"/>
       <c r="J166" s="13" t="n"/>
-      <c r="K166" s="16" t="n"/>
-      <c r="L166" s="23" t="n"/>
+      <c r="K166" s="27" t="n"/>
+      <c r="L166" s="28" t="n"/>
       <c r="M166" s="13" t="n"/>
-      <c r="N166" s="16" t="n"/>
-      <c r="O166" s="23" t="n"/>
+      <c r="N166" s="27" t="n"/>
+      <c r="O166" s="28" t="n"/>
       <c r="P166" s="13" t="n"/>
-      <c r="Q166" s="16" t="n"/>
-      <c r="R166" s="23" t="n"/>
+      <c r="Q166" s="27" t="n"/>
+      <c r="R166" s="28" t="n"/>
       <c r="S166" s="13" t="n"/>
-      <c r="T166" s="16" t="n"/>
-      <c r="U166" s="23" t="n"/>
+      <c r="T166" s="27" t="n"/>
+      <c r="U166" s="28" t="n"/>
       <c r="V166" s="13" t="n"/>
     </row>
     <row r="167">
@@ -5860,26 +5871,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B167" s="16" t="n"/>
-      <c r="C167" s="23" t="n"/>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="28" t="n"/>
       <c r="D167" s="13" t="n"/>
-      <c r="E167" s="16" t="n"/>
-      <c r="F167" s="23" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="28" t="n"/>
       <c r="G167" s="13" t="n"/>
-      <c r="H167" s="16" t="n"/>
-      <c r="I167" s="23" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="28" t="n"/>
       <c r="J167" s="13" t="n"/>
-      <c r="K167" s="16" t="n"/>
-      <c r="L167" s="23" t="n"/>
+      <c r="K167" s="27" t="n"/>
+      <c r="L167" s="28" t="n"/>
       <c r="M167" s="13" t="n"/>
-      <c r="N167" s="16" t="n"/>
-      <c r="O167" s="23" t="n"/>
+      <c r="N167" s="27" t="n"/>
+      <c r="O167" s="28" t="n"/>
       <c r="P167" s="13" t="n"/>
-      <c r="Q167" s="16" t="n"/>
-      <c r="R167" s="23" t="n"/>
+      <c r="Q167" s="27" t="n"/>
+      <c r="R167" s="28" t="n"/>
       <c r="S167" s="13" t="n"/>
-      <c r="T167" s="16" t="n"/>
-      <c r="U167" s="23" t="n"/>
+      <c r="T167" s="27" t="n"/>
+      <c r="U167" s="28" t="n"/>
       <c r="V167" s="13" t="n"/>
     </row>
     <row r="168">
@@ -5888,26 +5899,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B168" s="16" t="n"/>
-      <c r="C168" s="23" t="n"/>
+      <c r="B168" s="27" t="n"/>
+      <c r="C168" s="28" t="n"/>
       <c r="D168" s="13" t="n"/>
-      <c r="E168" s="16" t="n"/>
-      <c r="F168" s="23" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="28" t="n"/>
       <c r="G168" s="13" t="n"/>
-      <c r="H168" s="16" t="n"/>
-      <c r="I168" s="23" t="n"/>
+      <c r="H168" s="27" t="n"/>
+      <c r="I168" s="28" t="n"/>
       <c r="J168" s="13" t="n"/>
-      <c r="K168" s="16" t="n"/>
-      <c r="L168" s="23" t="n"/>
+      <c r="K168" s="27" t="n"/>
+      <c r="L168" s="28" t="n"/>
       <c r="M168" s="13" t="n"/>
-      <c r="N168" s="16" t="n"/>
-      <c r="O168" s="23" t="n"/>
+      <c r="N168" s="27" t="n"/>
+      <c r="O168" s="28" t="n"/>
       <c r="P168" s="13" t="n"/>
-      <c r="Q168" s="16" t="n"/>
-      <c r="R168" s="23" t="n"/>
+      <c r="Q168" s="27" t="n"/>
+      <c r="R168" s="28" t="n"/>
       <c r="S168" s="13" t="n"/>
-      <c r="T168" s="16" t="n"/>
-      <c r="U168" s="23" t="n"/>
+      <c r="T168" s="27" t="n"/>
+      <c r="U168" s="28" t="n"/>
       <c r="V168" s="13" t="n"/>
     </row>
     <row r="169">
@@ -5916,26 +5927,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B169" s="16" t="n"/>
-      <c r="C169" s="24" t="n"/>
+      <c r="B169" s="27" t="n"/>
+      <c r="C169" s="29" t="n"/>
       <c r="D169" s="13" t="n"/>
-      <c r="E169" s="16" t="n"/>
-      <c r="F169" s="24" t="n"/>
+      <c r="E169" s="27" t="n"/>
+      <c r="F169" s="29" t="n"/>
       <c r="G169" s="13" t="n"/>
-      <c r="H169" s="16" t="n"/>
-      <c r="I169" s="24" t="n"/>
+      <c r="H169" s="27" t="n"/>
+      <c r="I169" s="29" t="n"/>
       <c r="J169" s="13" t="n"/>
-      <c r="K169" s="16" t="n"/>
-      <c r="L169" s="24" t="n"/>
+      <c r="K169" s="27" t="n"/>
+      <c r="L169" s="29" t="n"/>
       <c r="M169" s="13" t="n"/>
-      <c r="N169" s="16" t="n"/>
-      <c r="O169" s="24" t="n"/>
+      <c r="N169" s="27" t="n"/>
+      <c r="O169" s="29" t="n"/>
       <c r="P169" s="13" t="n"/>
-      <c r="Q169" s="16" t="n"/>
-      <c r="R169" s="24" t="n"/>
+      <c r="Q169" s="27" t="n"/>
+      <c r="R169" s="29" t="n"/>
       <c r="S169" s="13" t="n"/>
-      <c r="T169" s="16" t="n"/>
-      <c r="U169" s="24" t="n"/>
+      <c r="T169" s="27" t="n"/>
+      <c r="U169" s="29" t="n"/>
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
@@ -5944,55 +5955,55 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B170" s="18" t="n"/>
-      <c r="C170" s="19" t="n"/>
+      <c r="B170" s="31" t="n"/>
+      <c r="C170" s="24" t="n"/>
       <c r="D170" s="20" t="n"/>
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="19" t="n"/>
+      <c r="E170" s="31" t="n"/>
+      <c r="F170" s="24" t="n"/>
       <c r="G170" s="20" t="n"/>
-      <c r="H170" s="18" t="n"/>
-      <c r="I170" s="19" t="n"/>
+      <c r="H170" s="31" t="n"/>
+      <c r="I170" s="24" t="n"/>
       <c r="J170" s="20" t="n"/>
-      <c r="K170" s="18" t="n"/>
-      <c r="L170" s="19" t="n"/>
+      <c r="K170" s="31" t="n"/>
+      <c r="L170" s="24" t="n"/>
       <c r="M170" s="20" t="n"/>
-      <c r="N170" s="18" t="n"/>
-      <c r="O170" s="19" t="n"/>
+      <c r="N170" s="31" t="n"/>
+      <c r="O170" s="24" t="n"/>
       <c r="P170" s="20" t="n"/>
-      <c r="Q170" s="18" t="n"/>
-      <c r="R170" s="19" t="n"/>
+      <c r="Q170" s="31" t="n"/>
+      <c r="R170" s="24" t="n"/>
       <c r="S170" s="20" t="n"/>
-      <c r="T170" s="18" t="n"/>
-      <c r="U170" s="19" t="n"/>
+      <c r="T170" s="31" t="n"/>
+      <c r="U170" s="24" t="n"/>
       <c r="V170" s="20" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="26" t="inlineStr">
+      <c r="A171" s="32" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="B171" s="27" t="n"/>
-      <c r="C171" s="28" t="n"/>
-      <c r="D171" s="29" t="n"/>
-      <c r="E171" s="27" t="n"/>
-      <c r="F171" s="28" t="n"/>
-      <c r="G171" s="29" t="n"/>
-      <c r="H171" s="27" t="n"/>
-      <c r="I171" s="28" t="n"/>
-      <c r="J171" s="29" t="n"/>
-      <c r="K171" s="27" t="n"/>
-      <c r="L171" s="28" t="n"/>
-      <c r="M171" s="29" t="n"/>
-      <c r="N171" s="27" t="n"/>
-      <c r="O171" s="28" t="n"/>
-      <c r="P171" s="29" t="n"/>
-      <c r="Q171" s="27" t="n"/>
-      <c r="R171" s="28" t="n"/>
-      <c r="S171" s="29" t="n"/>
-      <c r="T171" s="27" t="n"/>
-      <c r="U171" s="28" t="n"/>
-      <c r="V171" s="29" t="n"/>
+      <c r="B171" s="33" t="n"/>
+      <c r="C171" s="34" t="n"/>
+      <c r="D171" s="35" t="n"/>
+      <c r="E171" s="33" t="n"/>
+      <c r="F171" s="34" t="n"/>
+      <c r="G171" s="35" t="n"/>
+      <c r="H171" s="33" t="n"/>
+      <c r="I171" s="34" t="n"/>
+      <c r="J171" s="35" t="n"/>
+      <c r="K171" s="33" t="n"/>
+      <c r="L171" s="34" t="n"/>
+      <c r="M171" s="35" t="n"/>
+      <c r="N171" s="33" t="n"/>
+      <c r="O171" s="34" t="n"/>
+      <c r="P171" s="35" t="n"/>
+      <c r="Q171" s="33" t="n"/>
+      <c r="R171" s="34" t="n"/>
+      <c r="S171" s="35" t="n"/>
+      <c r="T171" s="33" t="n"/>
+      <c r="U171" s="34" t="n"/>
+      <c r="V171" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="76">

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -2714,22 +2714,22 @@
       <c r="B59" s="16" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="11" t="n"/>
+      <c r="E59" s="14" t="n"/>
       <c r="F59" s="12" t="n"/>
       <c r="G59" s="13" t="n"/>
-      <c r="H59" s="11" t="n"/>
+      <c r="H59" s="14" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="13" t="n"/>
       <c r="K59" s="16" t="n"/>
       <c r="L59" s="12" t="n"/>
       <c r="M59" s="13" t="n"/>
-      <c r="N59" s="11" t="n"/>
+      <c r="N59" s="14" t="n"/>
       <c r="O59" s="12" t="n"/>
       <c r="P59" s="13" t="n"/>
-      <c r="Q59" s="11" t="n"/>
+      <c r="Q59" s="14" t="n"/>
       <c r="R59" s="12" t="n"/>
       <c r="S59" s="13" t="n"/>
-      <c r="T59" s="11" t="n"/>
+      <c r="T59" s="14" t="n"/>
       <c r="U59" s="12" t="n"/>
       <c r="V59" s="13" t="n"/>
     </row>
@@ -2742,22 +2742,22 @@
       <c r="B60" s="16" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="11" t="n"/>
+      <c r="E60" s="16" t="n"/>
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="11" t="n"/>
+      <c r="H60" s="16" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="16" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="N60" s="11" t="n"/>
+      <c r="N60" s="16" t="n"/>
       <c r="O60" s="12" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="11" t="n"/>
+      <c r="Q60" s="16" t="n"/>
       <c r="R60" s="12" t="n"/>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="11" t="n"/>
+      <c r="T60" s="16" t="n"/>
       <c r="U60" s="12" t="n"/>
       <c r="V60" s="13" t="n"/>
     </row>
@@ -2770,22 +2770,22 @@
       <c r="B61" s="16" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
-      <c r="E61" s="11" t="n"/>
+      <c r="E61" s="16" t="n"/>
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="11" t="n"/>
+      <c r="H61" s="16" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
       <c r="K61" s="16" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
-      <c r="N61" s="11" t="n"/>
+      <c r="N61" s="16" t="n"/>
       <c r="O61" s="12" t="n"/>
       <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="11" t="n"/>
+      <c r="Q61" s="16" t="n"/>
       <c r="R61" s="12" t="n"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="11" t="n"/>
+      <c r="T61" s="16" t="n"/>
       <c r="U61" s="12" t="n"/>
       <c r="V61" s="13" t="n"/>
     </row>
@@ -2798,22 +2798,22 @@
       <c r="B62" s="18" t="n"/>
       <c r="C62" s="19" t="n"/>
       <c r="D62" s="20" t="n"/>
-      <c r="E62" s="14" t="n"/>
+      <c r="E62" s="18" t="n"/>
       <c r="F62" s="19" t="n"/>
       <c r="G62" s="20" t="n"/>
-      <c r="H62" s="14" t="n"/>
+      <c r="H62" s="18" t="n"/>
       <c r="I62" s="19" t="n"/>
       <c r="J62" s="20" t="n"/>
       <c r="K62" s="18" t="n"/>
       <c r="L62" s="19" t="n"/>
       <c r="M62" s="20" t="n"/>
-      <c r="N62" s="14" t="n"/>
+      <c r="N62" s="18" t="n"/>
       <c r="O62" s="19" t="n"/>
       <c r="P62" s="20" t="n"/>
-      <c r="Q62" s="14" t="n"/>
+      <c r="Q62" s="18" t="n"/>
       <c r="R62" s="19" t="n"/>
       <c r="S62" s="20" t="n"/>
-      <c r="T62" s="14" t="n"/>
+      <c r="T62" s="18" t="n"/>
       <c r="U62" s="19" t="n"/>
       <c r="V62" s="20" t="n"/>
     </row>
@@ -6007,16 +6007,18 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="Q57:Q62"/>
+    <mergeCell ref="H57:H59"/>
     <mergeCell ref="Q9:Q11"/>
     <mergeCell ref="K63:K73"/>
     <mergeCell ref="I111:I115"/>
+    <mergeCell ref="N57:N59"/>
     <mergeCell ref="C123:C127"/>
     <mergeCell ref="T6:T8"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="U165:U169"/>
     <mergeCell ref="F165:F169"/>
+    <mergeCell ref="E57:E59"/>
     <mergeCell ref="I123:I127"/>
     <mergeCell ref="O123:O127"/>
     <mergeCell ref="E54:E56"/>
@@ -6031,19 +6033,20 @@
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="N9:N11"/>
     <mergeCell ref="F111:F115"/>
-    <mergeCell ref="T57:T62"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="K6:K8"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="T3:T5"/>
+    <mergeCell ref="Q57:Q59"/>
+    <mergeCell ref="F123:F127"/>
     <mergeCell ref="U123:U127"/>
-    <mergeCell ref="F123:F127"/>
+    <mergeCell ref="L123:L127"/>
     <mergeCell ref="H87:H91"/>
-    <mergeCell ref="L123:L127"/>
     <mergeCell ref="F117:F121"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="N51:N53"/>
     <mergeCell ref="C165:C169"/>
+    <mergeCell ref="T57:T59"/>
     <mergeCell ref="O165:O169"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="R117:R121"/>
@@ -6055,14 +6058,11 @@
     <mergeCell ref="T75:T85"/>
     <mergeCell ref="R123:R127"/>
     <mergeCell ref="K54:K56"/>
-    <mergeCell ref="E57:E62"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="L165:L169"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="O117:O121"/>
-    <mergeCell ref="H57:H62"/>
-    <mergeCell ref="N57:N62"/>
     <mergeCell ref="B63:B73"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="H1:J1"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -433,16 +433,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2823,28 +2823,16 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：入浴掃除</t>
-        </is>
-      </c>
+      <c r="B63" s="21" t="n"/>
       <c r="C63" s="22" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：買い物代行</t>
-        </is>
-      </c>
+      <c r="E63" s="21" t="n"/>
       <c r="F63" s="22" t="n"/>
       <c r="G63" s="9" t="n"/>
       <c r="H63" s="21" t="n"/>
       <c r="I63" s="22" t="n"/>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：入浴掃除</t>
-        </is>
-      </c>
+      <c r="K63" s="21" t="n"/>
       <c r="L63" s="22" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="21" t="n"/>
@@ -2863,16 +2851,16 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n"/>
+      <c r="B64" s="16" t="n"/>
       <c r="C64" s="23" t="n"/>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="11" t="n"/>
+      <c r="E64" s="16" t="n"/>
       <c r="F64" s="23" t="n"/>
       <c r="G64" s="13" t="n"/>
       <c r="H64" s="16" t="n"/>
       <c r="I64" s="23" t="n"/>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="11" t="n"/>
+      <c r="K64" s="16" t="n"/>
       <c r="L64" s="23" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="16" t="n"/>
@@ -2891,16 +2879,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B65" s="11" t="n"/>
+      <c r="B65" s="16" t="n"/>
       <c r="C65" s="23" t="n"/>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="11" t="n"/>
+      <c r="E65" s="16" t="n"/>
       <c r="F65" s="23" t="n"/>
       <c r="G65" s="13" t="n"/>
       <c r="H65" s="16" t="n"/>
       <c r="I65" s="23" t="n"/>
       <c r="J65" s="13" t="n"/>
-      <c r="K65" s="11" t="n"/>
+      <c r="K65" s="16" t="n"/>
       <c r="L65" s="23" t="n"/>
       <c r="M65" s="13" t="n"/>
       <c r="N65" s="16" t="n"/>
@@ -2919,16 +2907,16 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n"/>
+      <c r="B66" s="16" t="n"/>
       <c r="C66" s="23" t="n"/>
       <c r="D66" s="13" t="n"/>
-      <c r="E66" s="11" t="n"/>
+      <c r="E66" s="16" t="n"/>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="13" t="n"/>
       <c r="H66" s="16" t="n"/>
       <c r="I66" s="23" t="n"/>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="11" t="n"/>
+      <c r="K66" s="16" t="n"/>
       <c r="L66" s="23" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="16" t="n"/>
@@ -2947,16 +2935,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B67" s="11" t="n"/>
+      <c r="B67" s="16" t="n"/>
       <c r="C67" s="23" t="n"/>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="14" t="n"/>
+      <c r="E67" s="16" t="n"/>
       <c r="F67" s="23" t="n"/>
       <c r="G67" s="13" t="n"/>
       <c r="H67" s="16" t="n"/>
       <c r="I67" s="23" t="n"/>
       <c r="J67" s="13" t="n"/>
-      <c r="K67" s="11" t="n"/>
+      <c r="K67" s="16" t="n"/>
       <c r="L67" s="23" t="n"/>
       <c r="M67" s="13" t="n"/>
       <c r="N67" s="16" t="n"/>
@@ -2975,7 +2963,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B68" s="11" t="n"/>
+      <c r="B68" s="16" t="n"/>
       <c r="C68" s="23" t="n"/>
       <c r="D68" s="13" t="n"/>
       <c r="E68" s="16" t="n"/>
@@ -2984,7 +2972,7 @@
       <c r="H68" s="16" t="n"/>
       <c r="I68" s="23" t="n"/>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="11" t="n"/>
+      <c r="K68" s="16" t="n"/>
       <c r="L68" s="23" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="16" t="n"/>
@@ -3003,7 +2991,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n"/>
+      <c r="B69" s="16" t="n"/>
       <c r="C69" s="23" t="n"/>
       <c r="D69" s="13" t="n"/>
       <c r="E69" s="16" t="n"/>
@@ -3012,7 +3000,7 @@
       <c r="H69" s="16" t="n"/>
       <c r="I69" s="23" t="n"/>
       <c r="J69" s="13" t="n"/>
-      <c r="K69" s="11" t="n"/>
+      <c r="K69" s="16" t="n"/>
       <c r="L69" s="23" t="n"/>
       <c r="M69" s="13" t="n"/>
       <c r="N69" s="16" t="n"/>
@@ -3031,7 +3019,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B70" s="11" t="n"/>
+      <c r="B70" s="16" t="n"/>
       <c r="C70" s="23" t="n"/>
       <c r="D70" s="13" t="n"/>
       <c r="E70" s="16" t="n"/>
@@ -3040,7 +3028,7 @@
       <c r="H70" s="16" t="n"/>
       <c r="I70" s="23" t="n"/>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="11" t="n"/>
+      <c r="K70" s="16" t="n"/>
       <c r="L70" s="23" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="16" t="n"/>
@@ -3059,7 +3047,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B71" s="11" t="n"/>
+      <c r="B71" s="16" t="n"/>
       <c r="C71" s="23" t="n"/>
       <c r="D71" s="13" t="n"/>
       <c r="E71" s="16" t="n"/>
@@ -3068,7 +3056,7 @@
       <c r="H71" s="16" t="n"/>
       <c r="I71" s="23" t="n"/>
       <c r="J71" s="13" t="n"/>
-      <c r="K71" s="11" t="n"/>
+      <c r="K71" s="16" t="n"/>
       <c r="L71" s="23" t="n"/>
       <c r="M71" s="13" t="n"/>
       <c r="N71" s="16" t="n"/>
@@ -3087,7 +3075,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n"/>
+      <c r="B72" s="16" t="n"/>
       <c r="C72" s="23" t="n"/>
       <c r="D72" s="13" t="n"/>
       <c r="E72" s="16" t="n"/>
@@ -3096,7 +3084,7 @@
       <c r="H72" s="16" t="n"/>
       <c r="I72" s="23" t="n"/>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="11" t="n"/>
+      <c r="K72" s="16" t="n"/>
       <c r="L72" s="23" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="16" t="n"/>
@@ -3115,7 +3103,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n"/>
+      <c r="B73" s="16" t="n"/>
       <c r="C73" s="23" t="n"/>
       <c r="D73" s="13" t="n"/>
       <c r="E73" s="16" t="n"/>
@@ -3124,7 +3112,7 @@
       <c r="H73" s="16" t="n"/>
       <c r="I73" s="23" t="n"/>
       <c r="J73" s="13" t="n"/>
-      <c r="K73" s="14" t="n"/>
+      <c r="K73" s="16" t="n"/>
       <c r="L73" s="23" t="n"/>
       <c r="M73" s="13" t="n"/>
       <c r="N73" s="16" t="n"/>
@@ -3171,16 +3159,28 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="B75" s="21" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="C75" s="22" t="n"/>
       <c r="D75" s="9" t="n"/>
-      <c r="E75" s="21" t="n"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：買い物代行</t>
+        </is>
+      </c>
       <c r="F75" s="22" t="n"/>
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="21" t="n"/>
       <c r="I75" s="22" t="n"/>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="21" t="n"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：入浴掃除</t>
+        </is>
+      </c>
       <c r="L75" s="22" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="21" t="n"/>
@@ -3203,16 +3203,16 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B76" s="16" t="n"/>
+      <c r="B76" s="11" t="n"/>
       <c r="C76" s="23" t="n"/>
       <c r="D76" s="13" t="n"/>
-      <c r="E76" s="16" t="n"/>
+      <c r="E76" s="11" t="n"/>
       <c r="F76" s="23" t="n"/>
       <c r="G76" s="13" t="n"/>
       <c r="H76" s="16" t="n"/>
       <c r="I76" s="23" t="n"/>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="16" t="n"/>
+      <c r="K76" s="11" t="n"/>
       <c r="L76" s="23" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="16" t="n"/>
@@ -3231,16 +3231,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n"/>
+      <c r="B77" s="11" t="n"/>
       <c r="C77" s="23" t="n"/>
       <c r="D77" s="13" t="n"/>
-      <c r="E77" s="16" t="n"/>
+      <c r="E77" s="11" t="n"/>
       <c r="F77" s="23" t="n"/>
       <c r="G77" s="13" t="n"/>
       <c r="H77" s="16" t="n"/>
       <c r="I77" s="23" t="n"/>
       <c r="J77" s="13" t="n"/>
-      <c r="K77" s="16" t="n"/>
+      <c r="K77" s="11" t="n"/>
       <c r="L77" s="23" t="n"/>
       <c r="M77" s="13" t="n"/>
       <c r="N77" s="16" t="n"/>
@@ -3259,16 +3259,16 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B78" s="16" t="n"/>
+      <c r="B78" s="11" t="n"/>
       <c r="C78" s="23" t="n"/>
       <c r="D78" s="13" t="n"/>
-      <c r="E78" s="16" t="n"/>
+      <c r="E78" s="11" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="13" t="n"/>
       <c r="H78" s="16" t="n"/>
       <c r="I78" s="23" t="n"/>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="16" t="n"/>
+      <c r="K78" s="11" t="n"/>
       <c r="L78" s="23" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="16" t="n"/>
@@ -3287,16 +3287,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B79" s="16" t="n"/>
+      <c r="B79" s="11" t="n"/>
       <c r="C79" s="23" t="n"/>
       <c r="D79" s="13" t="n"/>
-      <c r="E79" s="16" t="n"/>
+      <c r="E79" s="14" t="n"/>
       <c r="F79" s="23" t="n"/>
       <c r="G79" s="13" t="n"/>
       <c r="H79" s="16" t="n"/>
       <c r="I79" s="23" t="n"/>
       <c r="J79" s="13" t="n"/>
-      <c r="K79" s="16" t="n"/>
+      <c r="K79" s="11" t="n"/>
       <c r="L79" s="23" t="n"/>
       <c r="M79" s="13" t="n"/>
       <c r="N79" s="16" t="n"/>
@@ -3315,7 +3315,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B80" s="16" t="n"/>
+      <c r="B80" s="11" t="n"/>
       <c r="C80" s="23" t="n"/>
       <c r="D80" s="13" t="n"/>
       <c r="E80" s="16" t="n"/>
@@ -3324,7 +3324,7 @@
       <c r="H80" s="16" t="n"/>
       <c r="I80" s="23" t="n"/>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="16" t="n"/>
+      <c r="K80" s="11" t="n"/>
       <c r="L80" s="23" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="16" t="n"/>
@@ -3343,7 +3343,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B81" s="16" t="n"/>
+      <c r="B81" s="11" t="n"/>
       <c r="C81" s="23" t="n"/>
       <c r="D81" s="13" t="n"/>
       <c r="E81" s="16" t="n"/>
@@ -3352,12 +3352,12 @@
       <c r="H81" s="16" t="n"/>
       <c r="I81" s="23" t="n"/>
       <c r="J81" s="13" t="n"/>
-      <c r="K81" s="15" t="inlineStr">
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：掃除</t>
         </is>
       </c>
-      <c r="L81" s="23" t="n"/>
       <c r="M81" s="13" t="n"/>
       <c r="N81" s="16" t="n"/>
       <c r="O81" s="23" t="n"/>
@@ -3375,7 +3375,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B82" s="16" t="n"/>
+      <c r="B82" s="11" t="n"/>
       <c r="C82" s="23" t="n"/>
       <c r="D82" s="13" t="n"/>
       <c r="E82" s="16" t="n"/>
@@ -3385,7 +3385,7 @@
       <c r="I82" s="23" t="n"/>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="11" t="n"/>
-      <c r="L82" s="23" t="n"/>
+      <c r="L82" s="26" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="16" t="n"/>
       <c r="O82" s="23" t="n"/>
@@ -3403,7 +3403,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B83" s="16" t="n"/>
+      <c r="B83" s="11" t="n"/>
       <c r="C83" s="23" t="n"/>
       <c r="D83" s="13" t="n"/>
       <c r="E83" s="16" t="n"/>
@@ -3413,7 +3413,7 @@
       <c r="I83" s="23" t="n"/>
       <c r="J83" s="13" t="n"/>
       <c r="K83" s="11" t="n"/>
-      <c r="L83" s="23" t="n"/>
+      <c r="L83" s="26" t="n"/>
       <c r="M83" s="13" t="n"/>
       <c r="N83" s="16" t="n"/>
       <c r="O83" s="23" t="n"/>
@@ -3431,7 +3431,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B84" s="16" t="n"/>
+      <c r="B84" s="11" t="n"/>
       <c r="C84" s="23" t="n"/>
       <c r="D84" s="13" t="n"/>
       <c r="E84" s="16" t="n"/>
@@ -3441,7 +3441,7 @@
       <c r="I84" s="23" t="n"/>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="11" t="n"/>
-      <c r="L84" s="23" t="n"/>
+      <c r="L84" s="26" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="16" t="n"/>
       <c r="O84" s="23" t="n"/>
@@ -3459,7 +3459,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B85" s="16" t="n"/>
+      <c r="B85" s="14" t="n"/>
       <c r="C85" s="23" t="n"/>
       <c r="D85" s="13" t="n"/>
       <c r="E85" s="16" t="n"/>
@@ -3468,8 +3468,8 @@
       <c r="H85" s="16" t="n"/>
       <c r="I85" s="23" t="n"/>
       <c r="J85" s="13" t="n"/>
-      <c r="K85" s="11" t="n"/>
-      <c r="L85" s="23" t="n"/>
+      <c r="K85" s="14" t="n"/>
+      <c r="L85" s="26" t="n"/>
       <c r="M85" s="13" t="n"/>
       <c r="N85" s="16" t="n"/>
       <c r="O85" s="23" t="n"/>
@@ -3496,8 +3496,8 @@
       <c r="H86" s="18" t="n"/>
       <c r="I86" s="24" t="n"/>
       <c r="J86" s="20" t="n"/>
-      <c r="K86" s="11" t="n"/>
-      <c r="L86" s="24" t="n"/>
+      <c r="K86" s="18" t="n"/>
+      <c r="L86" s="26" t="n"/>
       <c r="M86" s="20" t="n"/>
       <c r="N86" s="18" t="n"/>
       <c r="O86" s="24" t="n"/>
@@ -3528,8 +3528,8 @@
       </c>
       <c r="I87" s="22" t="n"/>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="11" t="n"/>
-      <c r="L87" s="22" t="n"/>
+      <c r="K87" s="21" t="n"/>
+      <c r="L87" s="26" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="21" t="n"/>
       <c r="O87" s="22" t="n"/>
@@ -3556,8 +3556,8 @@
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="23" t="n"/>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="11" t="n"/>
-      <c r="L88" s="23" t="n"/>
+      <c r="K88" s="16" t="n"/>
+      <c r="L88" s="26" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="16" t="n"/>
       <c r="O88" s="23" t="n"/>
@@ -3584,8 +3584,8 @@
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="23" t="n"/>
       <c r="J89" s="13" t="n"/>
-      <c r="K89" s="11" t="n"/>
-      <c r="L89" s="23" t="n"/>
+      <c r="K89" s="16" t="n"/>
+      <c r="L89" s="26" t="n"/>
       <c r="M89" s="13" t="n"/>
       <c r="N89" s="16" t="n"/>
       <c r="O89" s="23" t="n"/>
@@ -3612,8 +3612,8 @@
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="23" t="n"/>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="11" t="n"/>
-      <c r="L90" s="23" t="n"/>
+      <c r="K90" s="16" t="n"/>
+      <c r="L90" s="26" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="16" t="n"/>
       <c r="O90" s="23" t="n"/>
@@ -3640,8 +3640,8 @@
       <c r="H91" s="14" t="n"/>
       <c r="I91" s="23" t="n"/>
       <c r="J91" s="13" t="n"/>
-      <c r="K91" s="14" t="n"/>
-      <c r="L91" s="23" t="n"/>
+      <c r="K91" s="16" t="n"/>
+      <c r="L91" s="27" t="n"/>
       <c r="M91" s="13" t="n"/>
       <c r="N91" s="16" t="n"/>
       <c r="O91" s="23" t="n"/>
@@ -4191,50 +4191,50 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="26" t="inlineStr">
+      <c r="B111" s="28" t="n"/>
+      <c r="C111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
-      <c r="E111" s="25" t="n"/>
-      <c r="F111" s="26" t="inlineStr">
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="G111" s="9" t="n"/>
-      <c r="H111" s="25" t="n"/>
-      <c r="I111" s="26" t="inlineStr">
+      <c r="H111" s="28" t="n"/>
+      <c r="I111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="J111" s="9" t="n"/>
-      <c r="K111" s="25" t="n"/>
-      <c r="L111" s="26" t="inlineStr">
+      <c r="K111" s="28" t="n"/>
+      <c r="L111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="M111" s="9" t="n"/>
-      <c r="N111" s="25" t="n"/>
-      <c r="O111" s="26" t="inlineStr">
+      <c r="N111" s="28" t="n"/>
+      <c r="O111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="25" t="n"/>
-      <c r="R111" s="26" t="inlineStr">
+      <c r="Q111" s="28" t="n"/>
+      <c r="R111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="S111" s="9" t="n"/>
-      <c r="T111" s="25" t="n"/>
-      <c r="U111" s="26" t="inlineStr">
+      <c r="T111" s="28" t="n"/>
+      <c r="U111" s="29" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
@@ -4247,26 +4247,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B112" s="27" t="n"/>
-      <c r="C112" s="28" t="n"/>
+      <c r="B112" s="30" t="n"/>
+      <c r="C112" s="26" t="n"/>
       <c r="D112" s="13" t="n"/>
-      <c r="E112" s="27" t="n"/>
-      <c r="F112" s="28" t="n"/>
+      <c r="E112" s="30" t="n"/>
+      <c r="F112" s="26" t="n"/>
       <c r="G112" s="13" t="n"/>
-      <c r="H112" s="27" t="n"/>
-      <c r="I112" s="28" t="n"/>
+      <c r="H112" s="30" t="n"/>
+      <c r="I112" s="26" t="n"/>
       <c r="J112" s="13" t="n"/>
-      <c r="K112" s="27" t="n"/>
-      <c r="L112" s="28" t="n"/>
+      <c r="K112" s="30" t="n"/>
+      <c r="L112" s="26" t="n"/>
       <c r="M112" s="13" t="n"/>
-      <c r="N112" s="27" t="n"/>
-      <c r="O112" s="28" t="n"/>
+      <c r="N112" s="30" t="n"/>
+      <c r="O112" s="26" t="n"/>
       <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="27" t="n"/>
-      <c r="R112" s="28" t="n"/>
+      <c r="Q112" s="30" t="n"/>
+      <c r="R112" s="26" t="n"/>
       <c r="S112" s="13" t="n"/>
-      <c r="T112" s="27" t="n"/>
-      <c r="U112" s="28" t="n"/>
+      <c r="T112" s="30" t="n"/>
+      <c r="U112" s="26" t="n"/>
       <c r="V112" s="13" t="n"/>
     </row>
     <row r="113">
@@ -4275,26 +4275,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B113" s="27" t="n"/>
-      <c r="C113" s="28" t="n"/>
+      <c r="B113" s="30" t="n"/>
+      <c r="C113" s="26" t="n"/>
       <c r="D113" s="13" t="n"/>
-      <c r="E113" s="27" t="n"/>
-      <c r="F113" s="28" t="n"/>
+      <c r="E113" s="30" t="n"/>
+      <c r="F113" s="26" t="n"/>
       <c r="G113" s="13" t="n"/>
-      <c r="H113" s="27" t="n"/>
-      <c r="I113" s="28" t="n"/>
+      <c r="H113" s="30" t="n"/>
+      <c r="I113" s="26" t="n"/>
       <c r="J113" s="13" t="n"/>
-      <c r="K113" s="27" t="n"/>
-      <c r="L113" s="28" t="n"/>
+      <c r="K113" s="30" t="n"/>
+      <c r="L113" s="26" t="n"/>
       <c r="M113" s="13" t="n"/>
-      <c r="N113" s="27" t="n"/>
-      <c r="O113" s="28" t="n"/>
+      <c r="N113" s="30" t="n"/>
+      <c r="O113" s="26" t="n"/>
       <c r="P113" s="13" t="n"/>
-      <c r="Q113" s="27" t="n"/>
-      <c r="R113" s="28" t="n"/>
+      <c r="Q113" s="30" t="n"/>
+      <c r="R113" s="26" t="n"/>
       <c r="S113" s="13" t="n"/>
-      <c r="T113" s="27" t="n"/>
-      <c r="U113" s="28" t="n"/>
+      <c r="T113" s="30" t="n"/>
+      <c r="U113" s="26" t="n"/>
       <c r="V113" s="13" t="n"/>
     </row>
     <row r="114">
@@ -4303,26 +4303,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B114" s="27" t="n"/>
-      <c r="C114" s="28" t="n"/>
+      <c r="B114" s="30" t="n"/>
+      <c r="C114" s="26" t="n"/>
       <c r="D114" s="13" t="n"/>
-      <c r="E114" s="27" t="n"/>
-      <c r="F114" s="28" t="n"/>
+      <c r="E114" s="30" t="n"/>
+      <c r="F114" s="26" t="n"/>
       <c r="G114" s="13" t="n"/>
-      <c r="H114" s="27" t="n"/>
-      <c r="I114" s="28" t="n"/>
+      <c r="H114" s="30" t="n"/>
+      <c r="I114" s="26" t="n"/>
       <c r="J114" s="13" t="n"/>
-      <c r="K114" s="27" t="n"/>
-      <c r="L114" s="28" t="n"/>
+      <c r="K114" s="30" t="n"/>
+      <c r="L114" s="26" t="n"/>
       <c r="M114" s="13" t="n"/>
-      <c r="N114" s="27" t="n"/>
-      <c r="O114" s="28" t="n"/>
+      <c r="N114" s="30" t="n"/>
+      <c r="O114" s="26" t="n"/>
       <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="27" t="n"/>
-      <c r="R114" s="28" t="n"/>
+      <c r="Q114" s="30" t="n"/>
+      <c r="R114" s="26" t="n"/>
       <c r="S114" s="13" t="n"/>
-      <c r="T114" s="27" t="n"/>
-      <c r="U114" s="28" t="n"/>
+      <c r="T114" s="30" t="n"/>
+      <c r="U114" s="26" t="n"/>
       <c r="V114" s="13" t="n"/>
     </row>
     <row r="115">
@@ -4331,26 +4331,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B115" s="27" t="n"/>
-      <c r="C115" s="29" t="n"/>
+      <c r="B115" s="30" t="n"/>
+      <c r="C115" s="27" t="n"/>
       <c r="D115" s="13" t="n"/>
-      <c r="E115" s="27" t="n"/>
-      <c r="F115" s="29" t="n"/>
+      <c r="E115" s="30" t="n"/>
+      <c r="F115" s="27" t="n"/>
       <c r="G115" s="13" t="n"/>
-      <c r="H115" s="27" t="n"/>
-      <c r="I115" s="29" t="n"/>
+      <c r="H115" s="30" t="n"/>
+      <c r="I115" s="27" t="n"/>
       <c r="J115" s="13" t="n"/>
-      <c r="K115" s="27" t="n"/>
-      <c r="L115" s="29" t="n"/>
+      <c r="K115" s="30" t="n"/>
+      <c r="L115" s="27" t="n"/>
       <c r="M115" s="13" t="n"/>
-      <c r="N115" s="27" t="n"/>
-      <c r="O115" s="29" t="n"/>
+      <c r="N115" s="30" t="n"/>
+      <c r="O115" s="27" t="n"/>
       <c r="P115" s="13" t="n"/>
-      <c r="Q115" s="27" t="n"/>
-      <c r="R115" s="29" t="n"/>
+      <c r="Q115" s="30" t="n"/>
+      <c r="R115" s="27" t="n"/>
       <c r="S115" s="13" t="n"/>
-      <c r="T115" s="27" t="n"/>
-      <c r="U115" s="29" t="n"/>
+      <c r="T115" s="30" t="n"/>
+      <c r="U115" s="27" t="n"/>
       <c r="V115" s="13" t="n"/>
     </row>
     <row r="116">
@@ -4359,25 +4359,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B116" s="27" t="n"/>
+      <c r="B116" s="30" t="n"/>
       <c r="C116" s="23" t="n"/>
       <c r="D116" s="13" t="n"/>
-      <c r="E116" s="27" t="n"/>
+      <c r="E116" s="30" t="n"/>
       <c r="F116" s="23" t="n"/>
       <c r="G116" s="13" t="n"/>
-      <c r="H116" s="27" t="n"/>
+      <c r="H116" s="30" t="n"/>
       <c r="I116" s="23" t="n"/>
       <c r="J116" s="13" t="n"/>
-      <c r="K116" s="27" t="n"/>
+      <c r="K116" s="30" t="n"/>
       <c r="L116" s="23" t="n"/>
       <c r="M116" s="13" t="n"/>
-      <c r="N116" s="27" t="n"/>
+      <c r="N116" s="30" t="n"/>
       <c r="O116" s="23" t="n"/>
       <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="27" t="n"/>
+      <c r="Q116" s="30" t="n"/>
       <c r="R116" s="23" t="n"/>
       <c r="S116" s="13" t="n"/>
-      <c r="T116" s="27" t="n"/>
+      <c r="T116" s="30" t="n"/>
       <c r="U116" s="23" t="n"/>
       <c r="V116" s="13" t="n"/>
     </row>
@@ -4387,50 +4387,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B117" s="27" t="n"/>
-      <c r="C117" s="30" t="inlineStr">
+      <c r="B117" s="30" t="n"/>
+      <c r="C117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="D117" s="13" t="n"/>
-      <c r="E117" s="27" t="n"/>
-      <c r="F117" s="30" t="inlineStr">
+      <c r="E117" s="30" t="n"/>
+      <c r="F117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="G117" s="13" t="n"/>
-      <c r="H117" s="27" t="n"/>
-      <c r="I117" s="30" t="inlineStr">
+      <c r="H117" s="30" t="n"/>
+      <c r="I117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="J117" s="13" t="n"/>
-      <c r="K117" s="27" t="n"/>
-      <c r="L117" s="30" t="inlineStr">
+      <c r="K117" s="30" t="n"/>
+      <c r="L117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="M117" s="13" t="n"/>
-      <c r="N117" s="27" t="n"/>
-      <c r="O117" s="30" t="inlineStr">
+      <c r="N117" s="30" t="n"/>
+      <c r="O117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="P117" s="13" t="n"/>
-      <c r="Q117" s="27" t="n"/>
-      <c r="R117" s="30" t="inlineStr">
+      <c r="Q117" s="30" t="n"/>
+      <c r="R117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="S117" s="13" t="n"/>
-      <c r="T117" s="27" t="n"/>
-      <c r="U117" s="30" t="inlineStr">
+      <c r="T117" s="30" t="n"/>
+      <c r="U117" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
@@ -4443,26 +4443,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B118" s="27" t="n"/>
-      <c r="C118" s="28" t="n"/>
+      <c r="B118" s="30" t="n"/>
+      <c r="C118" s="26" t="n"/>
       <c r="D118" s="13" t="n"/>
-      <c r="E118" s="27" t="n"/>
-      <c r="F118" s="28" t="n"/>
+      <c r="E118" s="30" t="n"/>
+      <c r="F118" s="26" t="n"/>
       <c r="G118" s="13" t="n"/>
-      <c r="H118" s="27" t="n"/>
-      <c r="I118" s="28" t="n"/>
+      <c r="H118" s="30" t="n"/>
+      <c r="I118" s="26" t="n"/>
       <c r="J118" s="13" t="n"/>
-      <c r="K118" s="27" t="n"/>
-      <c r="L118" s="28" t="n"/>
+      <c r="K118" s="30" t="n"/>
+      <c r="L118" s="26" t="n"/>
       <c r="M118" s="13" t="n"/>
-      <c r="N118" s="27" t="n"/>
-      <c r="O118" s="28" t="n"/>
+      <c r="N118" s="30" t="n"/>
+      <c r="O118" s="26" t="n"/>
       <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="27" t="n"/>
-      <c r="R118" s="28" t="n"/>
+      <c r="Q118" s="30" t="n"/>
+      <c r="R118" s="26" t="n"/>
       <c r="S118" s="13" t="n"/>
-      <c r="T118" s="27" t="n"/>
-      <c r="U118" s="28" t="n"/>
+      <c r="T118" s="30" t="n"/>
+      <c r="U118" s="26" t="n"/>
       <c r="V118" s="13" t="n"/>
     </row>
     <row r="119">
@@ -4471,26 +4471,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B119" s="27" t="n"/>
-      <c r="C119" s="28" t="n"/>
+      <c r="B119" s="30" t="n"/>
+      <c r="C119" s="26" t="n"/>
       <c r="D119" s="13" t="n"/>
-      <c r="E119" s="27" t="n"/>
-      <c r="F119" s="28" t="n"/>
+      <c r="E119" s="30" t="n"/>
+      <c r="F119" s="26" t="n"/>
       <c r="G119" s="13" t="n"/>
-      <c r="H119" s="27" t="n"/>
-      <c r="I119" s="28" t="n"/>
+      <c r="H119" s="30" t="n"/>
+      <c r="I119" s="26" t="n"/>
       <c r="J119" s="13" t="n"/>
-      <c r="K119" s="27" t="n"/>
-      <c r="L119" s="28" t="n"/>
+      <c r="K119" s="30" t="n"/>
+      <c r="L119" s="26" t="n"/>
       <c r="M119" s="13" t="n"/>
-      <c r="N119" s="27" t="n"/>
-      <c r="O119" s="28" t="n"/>
+      <c r="N119" s="30" t="n"/>
+      <c r="O119" s="26" t="n"/>
       <c r="P119" s="13" t="n"/>
-      <c r="Q119" s="27" t="n"/>
-      <c r="R119" s="28" t="n"/>
+      <c r="Q119" s="30" t="n"/>
+      <c r="R119" s="26" t="n"/>
       <c r="S119" s="13" t="n"/>
-      <c r="T119" s="27" t="n"/>
-      <c r="U119" s="28" t="n"/>
+      <c r="T119" s="30" t="n"/>
+      <c r="U119" s="26" t="n"/>
       <c r="V119" s="13" t="n"/>
     </row>
     <row r="120">
@@ -4499,26 +4499,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B120" s="27" t="n"/>
-      <c r="C120" s="28" t="n"/>
+      <c r="B120" s="30" t="n"/>
+      <c r="C120" s="26" t="n"/>
       <c r="D120" s="13" t="n"/>
-      <c r="E120" s="27" t="n"/>
-      <c r="F120" s="28" t="n"/>
+      <c r="E120" s="30" t="n"/>
+      <c r="F120" s="26" t="n"/>
       <c r="G120" s="13" t="n"/>
-      <c r="H120" s="27" t="n"/>
-      <c r="I120" s="28" t="n"/>
+      <c r="H120" s="30" t="n"/>
+      <c r="I120" s="26" t="n"/>
       <c r="J120" s="13" t="n"/>
-      <c r="K120" s="27" t="n"/>
-      <c r="L120" s="28" t="n"/>
+      <c r="K120" s="30" t="n"/>
+      <c r="L120" s="26" t="n"/>
       <c r="M120" s="13" t="n"/>
-      <c r="N120" s="27" t="n"/>
-      <c r="O120" s="28" t="n"/>
+      <c r="N120" s="30" t="n"/>
+      <c r="O120" s="26" t="n"/>
       <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="27" t="n"/>
-      <c r="R120" s="28" t="n"/>
+      <c r="Q120" s="30" t="n"/>
+      <c r="R120" s="26" t="n"/>
       <c r="S120" s="13" t="n"/>
-      <c r="T120" s="27" t="n"/>
-      <c r="U120" s="28" t="n"/>
+      <c r="T120" s="30" t="n"/>
+      <c r="U120" s="26" t="n"/>
       <c r="V120" s="13" t="n"/>
     </row>
     <row r="121">
@@ -4527,26 +4527,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B121" s="27" t="n"/>
-      <c r="C121" s="29" t="n"/>
+      <c r="B121" s="30" t="n"/>
+      <c r="C121" s="27" t="n"/>
       <c r="D121" s="13" t="n"/>
-      <c r="E121" s="27" t="n"/>
-      <c r="F121" s="29" t="n"/>
+      <c r="E121" s="30" t="n"/>
+      <c r="F121" s="27" t="n"/>
       <c r="G121" s="13" t="n"/>
-      <c r="H121" s="27" t="n"/>
-      <c r="I121" s="29" t="n"/>
+      <c r="H121" s="30" t="n"/>
+      <c r="I121" s="27" t="n"/>
       <c r="J121" s="13" t="n"/>
-      <c r="K121" s="27" t="n"/>
-      <c r="L121" s="29" t="n"/>
+      <c r="K121" s="30" t="n"/>
+      <c r="L121" s="27" t="n"/>
       <c r="M121" s="13" t="n"/>
-      <c r="N121" s="27" t="n"/>
-      <c r="O121" s="29" t="n"/>
+      <c r="N121" s="30" t="n"/>
+      <c r="O121" s="27" t="n"/>
       <c r="P121" s="13" t="n"/>
-      <c r="Q121" s="27" t="n"/>
-      <c r="R121" s="29" t="n"/>
+      <c r="Q121" s="30" t="n"/>
+      <c r="R121" s="27" t="n"/>
       <c r="S121" s="13" t="n"/>
-      <c r="T121" s="27" t="n"/>
-      <c r="U121" s="29" t="n"/>
+      <c r="T121" s="30" t="n"/>
+      <c r="U121" s="27" t="n"/>
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
@@ -4583,50 +4583,50 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B123" s="25" t="n"/>
-      <c r="C123" s="26" t="inlineStr">
+      <c r="B123" s="28" t="n"/>
+      <c r="C123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
-      <c r="E123" s="25" t="n"/>
-      <c r="F123" s="26" t="inlineStr">
+      <c r="E123" s="28" t="n"/>
+      <c r="F123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="G123" s="9" t="n"/>
-      <c r="H123" s="25" t="n"/>
-      <c r="I123" s="26" t="inlineStr">
+      <c r="H123" s="28" t="n"/>
+      <c r="I123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="J123" s="9" t="n"/>
-      <c r="K123" s="25" t="n"/>
-      <c r="L123" s="26" t="inlineStr">
+      <c r="K123" s="28" t="n"/>
+      <c r="L123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="M123" s="9" t="n"/>
-      <c r="N123" s="25" t="n"/>
-      <c r="O123" s="26" t="inlineStr">
+      <c r="N123" s="28" t="n"/>
+      <c r="O123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="25" t="n"/>
-      <c r="R123" s="26" t="inlineStr">
+      <c r="Q123" s="28" t="n"/>
+      <c r="R123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="S123" s="9" t="n"/>
-      <c r="T123" s="25" t="n"/>
-      <c r="U123" s="26" t="inlineStr">
+      <c r="T123" s="28" t="n"/>
+      <c r="U123" s="29" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
@@ -4639,26 +4639,26 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B124" s="27" t="n"/>
-      <c r="C124" s="28" t="n"/>
+      <c r="B124" s="30" t="n"/>
+      <c r="C124" s="26" t="n"/>
       <c r="D124" s="13" t="n"/>
-      <c r="E124" s="27" t="n"/>
-      <c r="F124" s="28" t="n"/>
+      <c r="E124" s="30" t="n"/>
+      <c r="F124" s="26" t="n"/>
       <c r="G124" s="13" t="n"/>
-      <c r="H124" s="27" t="n"/>
-      <c r="I124" s="28" t="n"/>
+      <c r="H124" s="30" t="n"/>
+      <c r="I124" s="26" t="n"/>
       <c r="J124" s="13" t="n"/>
-      <c r="K124" s="27" t="n"/>
-      <c r="L124" s="28" t="n"/>
+      <c r="K124" s="30" t="n"/>
+      <c r="L124" s="26" t="n"/>
       <c r="M124" s="13" t="n"/>
-      <c r="N124" s="27" t="n"/>
-      <c r="O124" s="28" t="n"/>
+      <c r="N124" s="30" t="n"/>
+      <c r="O124" s="26" t="n"/>
       <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="27" t="n"/>
-      <c r="R124" s="28" t="n"/>
+      <c r="Q124" s="30" t="n"/>
+      <c r="R124" s="26" t="n"/>
       <c r="S124" s="13" t="n"/>
-      <c r="T124" s="27" t="n"/>
-      <c r="U124" s="28" t="n"/>
+      <c r="T124" s="30" t="n"/>
+      <c r="U124" s="26" t="n"/>
       <c r="V124" s="13" t="n"/>
     </row>
     <row r="125">
@@ -4667,26 +4667,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B125" s="27" t="n"/>
-      <c r="C125" s="28" t="n"/>
+      <c r="B125" s="30" t="n"/>
+      <c r="C125" s="26" t="n"/>
       <c r="D125" s="13" t="n"/>
-      <c r="E125" s="27" t="n"/>
-      <c r="F125" s="28" t="n"/>
+      <c r="E125" s="30" t="n"/>
+      <c r="F125" s="26" t="n"/>
       <c r="G125" s="13" t="n"/>
-      <c r="H125" s="27" t="n"/>
-      <c r="I125" s="28" t="n"/>
+      <c r="H125" s="30" t="n"/>
+      <c r="I125" s="26" t="n"/>
       <c r="J125" s="13" t="n"/>
-      <c r="K125" s="27" t="n"/>
-      <c r="L125" s="28" t="n"/>
+      <c r="K125" s="30" t="n"/>
+      <c r="L125" s="26" t="n"/>
       <c r="M125" s="13" t="n"/>
-      <c r="N125" s="27" t="n"/>
-      <c r="O125" s="28" t="n"/>
+      <c r="N125" s="30" t="n"/>
+      <c r="O125" s="26" t="n"/>
       <c r="P125" s="13" t="n"/>
-      <c r="Q125" s="27" t="n"/>
-      <c r="R125" s="28" t="n"/>
+      <c r="Q125" s="30" t="n"/>
+      <c r="R125" s="26" t="n"/>
       <c r="S125" s="13" t="n"/>
-      <c r="T125" s="27" t="n"/>
-      <c r="U125" s="28" t="n"/>
+      <c r="T125" s="30" t="n"/>
+      <c r="U125" s="26" t="n"/>
       <c r="V125" s="13" t="n"/>
     </row>
     <row r="126">
@@ -4695,26 +4695,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B126" s="27" t="n"/>
-      <c r="C126" s="28" t="n"/>
+      <c r="B126" s="30" t="n"/>
+      <c r="C126" s="26" t="n"/>
       <c r="D126" s="13" t="n"/>
-      <c r="E126" s="27" t="n"/>
-      <c r="F126" s="28" t="n"/>
+      <c r="E126" s="30" t="n"/>
+      <c r="F126" s="26" t="n"/>
       <c r="G126" s="13" t="n"/>
-      <c r="H126" s="27" t="n"/>
-      <c r="I126" s="28" t="n"/>
+      <c r="H126" s="30" t="n"/>
+      <c r="I126" s="26" t="n"/>
       <c r="J126" s="13" t="n"/>
-      <c r="K126" s="27" t="n"/>
-      <c r="L126" s="28" t="n"/>
+      <c r="K126" s="30" t="n"/>
+      <c r="L126" s="26" t="n"/>
       <c r="M126" s="13" t="n"/>
-      <c r="N126" s="27" t="n"/>
-      <c r="O126" s="28" t="n"/>
+      <c r="N126" s="30" t="n"/>
+      <c r="O126" s="26" t="n"/>
       <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="27" t="n"/>
-      <c r="R126" s="28" t="n"/>
+      <c r="Q126" s="30" t="n"/>
+      <c r="R126" s="26" t="n"/>
       <c r="S126" s="13" t="n"/>
-      <c r="T126" s="27" t="n"/>
-      <c r="U126" s="28" t="n"/>
+      <c r="T126" s="30" t="n"/>
+      <c r="U126" s="26" t="n"/>
       <c r="V126" s="13" t="n"/>
     </row>
     <row r="127">
@@ -4723,26 +4723,26 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B127" s="27" t="n"/>
-      <c r="C127" s="29" t="n"/>
+      <c r="B127" s="30" t="n"/>
+      <c r="C127" s="27" t="n"/>
       <c r="D127" s="13" t="n"/>
-      <c r="E127" s="27" t="n"/>
-      <c r="F127" s="29" t="n"/>
+      <c r="E127" s="30" t="n"/>
+      <c r="F127" s="27" t="n"/>
       <c r="G127" s="13" t="n"/>
-      <c r="H127" s="27" t="n"/>
-      <c r="I127" s="29" t="n"/>
+      <c r="H127" s="30" t="n"/>
+      <c r="I127" s="27" t="n"/>
       <c r="J127" s="13" t="n"/>
-      <c r="K127" s="27" t="n"/>
-      <c r="L127" s="29" t="n"/>
+      <c r="K127" s="30" t="n"/>
+      <c r="L127" s="27" t="n"/>
       <c r="M127" s="13" t="n"/>
-      <c r="N127" s="27" t="n"/>
-      <c r="O127" s="29" t="n"/>
+      <c r="N127" s="30" t="n"/>
+      <c r="O127" s="27" t="n"/>
       <c r="P127" s="13" t="n"/>
-      <c r="Q127" s="27" t="n"/>
-      <c r="R127" s="29" t="n"/>
+      <c r="Q127" s="30" t="n"/>
+      <c r="R127" s="27" t="n"/>
       <c r="S127" s="13" t="n"/>
-      <c r="T127" s="27" t="n"/>
-      <c r="U127" s="29" t="n"/>
+      <c r="T127" s="30" t="n"/>
+      <c r="U127" s="27" t="n"/>
       <c r="V127" s="13" t="n"/>
     </row>
     <row r="128">
@@ -4751,25 +4751,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B128" s="27" t="n"/>
+      <c r="B128" s="30" t="n"/>
       <c r="C128" s="23" t="n"/>
       <c r="D128" s="13" t="n"/>
-      <c r="E128" s="27" t="n"/>
+      <c r="E128" s="30" t="n"/>
       <c r="F128" s="23" t="n"/>
       <c r="G128" s="13" t="n"/>
-      <c r="H128" s="27" t="n"/>
+      <c r="H128" s="30" t="n"/>
       <c r="I128" s="23" t="n"/>
       <c r="J128" s="13" t="n"/>
-      <c r="K128" s="27" t="n"/>
+      <c r="K128" s="30" t="n"/>
       <c r="L128" s="23" t="n"/>
       <c r="M128" s="13" t="n"/>
-      <c r="N128" s="27" t="n"/>
+      <c r="N128" s="30" t="n"/>
       <c r="O128" s="23" t="n"/>
       <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="27" t="n"/>
+      <c r="Q128" s="30" t="n"/>
       <c r="R128" s="23" t="n"/>
       <c r="S128" s="13" t="n"/>
-      <c r="T128" s="27" t="n"/>
+      <c r="T128" s="30" t="n"/>
       <c r="U128" s="23" t="n"/>
       <c r="V128" s="13" t="n"/>
     </row>
@@ -4779,25 +4779,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B129" s="27" t="n"/>
+      <c r="B129" s="30" t="n"/>
       <c r="C129" s="23" t="n"/>
       <c r="D129" s="13" t="n"/>
-      <c r="E129" s="27" t="n"/>
+      <c r="E129" s="30" t="n"/>
       <c r="F129" s="23" t="n"/>
       <c r="G129" s="13" t="n"/>
-      <c r="H129" s="27" t="n"/>
+      <c r="H129" s="30" t="n"/>
       <c r="I129" s="23" t="n"/>
       <c r="J129" s="13" t="n"/>
-      <c r="K129" s="27" t="n"/>
+      <c r="K129" s="30" t="n"/>
       <c r="L129" s="23" t="n"/>
       <c r="M129" s="13" t="n"/>
-      <c r="N129" s="27" t="n"/>
+      <c r="N129" s="30" t="n"/>
       <c r="O129" s="23" t="n"/>
       <c r="P129" s="13" t="n"/>
-      <c r="Q129" s="27" t="n"/>
+      <c r="Q129" s="30" t="n"/>
       <c r="R129" s="23" t="n"/>
       <c r="S129" s="13" t="n"/>
-      <c r="T129" s="27" t="n"/>
+      <c r="T129" s="30" t="n"/>
       <c r="U129" s="23" t="n"/>
       <c r="V129" s="13" t="n"/>
     </row>
@@ -4807,25 +4807,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B130" s="27" t="n"/>
+      <c r="B130" s="30" t="n"/>
       <c r="C130" s="23" t="n"/>
       <c r="D130" s="13" t="n"/>
-      <c r="E130" s="27" t="n"/>
+      <c r="E130" s="30" t="n"/>
       <c r="F130" s="23" t="n"/>
       <c r="G130" s="13" t="n"/>
-      <c r="H130" s="27" t="n"/>
+      <c r="H130" s="30" t="n"/>
       <c r="I130" s="23" t="n"/>
       <c r="J130" s="13" t="n"/>
-      <c r="K130" s="27" t="n"/>
+      <c r="K130" s="30" t="n"/>
       <c r="L130" s="23" t="n"/>
       <c r="M130" s="13" t="n"/>
-      <c r="N130" s="27" t="n"/>
+      <c r="N130" s="30" t="n"/>
       <c r="O130" s="23" t="n"/>
       <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="27" t="n"/>
+      <c r="Q130" s="30" t="n"/>
       <c r="R130" s="23" t="n"/>
       <c r="S130" s="13" t="n"/>
-      <c r="T130" s="27" t="n"/>
+      <c r="T130" s="30" t="n"/>
       <c r="U130" s="23" t="n"/>
       <c r="V130" s="13" t="n"/>
     </row>
@@ -4835,25 +4835,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B131" s="27" t="n"/>
+      <c r="B131" s="30" t="n"/>
       <c r="C131" s="23" t="n"/>
       <c r="D131" s="13" t="n"/>
-      <c r="E131" s="27" t="n"/>
+      <c r="E131" s="30" t="n"/>
       <c r="F131" s="23" t="n"/>
       <c r="G131" s="13" t="n"/>
-      <c r="H131" s="27" t="n"/>
+      <c r="H131" s="30" t="n"/>
       <c r="I131" s="23" t="n"/>
       <c r="J131" s="13" t="n"/>
-      <c r="K131" s="27" t="n"/>
+      <c r="K131" s="30" t="n"/>
       <c r="L131" s="23" t="n"/>
       <c r="M131" s="13" t="n"/>
-      <c r="N131" s="27" t="n"/>
+      <c r="N131" s="30" t="n"/>
       <c r="O131" s="23" t="n"/>
       <c r="P131" s="13" t="n"/>
-      <c r="Q131" s="27" t="n"/>
+      <c r="Q131" s="30" t="n"/>
       <c r="R131" s="23" t="n"/>
       <c r="S131" s="13" t="n"/>
-      <c r="T131" s="27" t="n"/>
+      <c r="T131" s="30" t="n"/>
       <c r="U131" s="23" t="n"/>
       <c r="V131" s="13" t="n"/>
     </row>
@@ -4863,25 +4863,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B132" s="27" t="n"/>
+      <c r="B132" s="30" t="n"/>
       <c r="C132" s="23" t="n"/>
       <c r="D132" s="13" t="n"/>
-      <c r="E132" s="27" t="n"/>
+      <c r="E132" s="30" t="n"/>
       <c r="F132" s="23" t="n"/>
       <c r="G132" s="13" t="n"/>
-      <c r="H132" s="27" t="n"/>
+      <c r="H132" s="30" t="n"/>
       <c r="I132" s="23" t="n"/>
       <c r="J132" s="13" t="n"/>
-      <c r="K132" s="27" t="n"/>
+      <c r="K132" s="30" t="n"/>
       <c r="L132" s="23" t="n"/>
       <c r="M132" s="13" t="n"/>
-      <c r="N132" s="27" t="n"/>
+      <c r="N132" s="30" t="n"/>
       <c r="O132" s="23" t="n"/>
       <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="27" t="n"/>
+      <c r="Q132" s="30" t="n"/>
       <c r="R132" s="23" t="n"/>
       <c r="S132" s="13" t="n"/>
-      <c r="T132" s="27" t="n"/>
+      <c r="T132" s="30" t="n"/>
       <c r="U132" s="23" t="n"/>
       <c r="V132" s="13" t="n"/>
     </row>
@@ -4891,25 +4891,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B133" s="27" t="n"/>
+      <c r="B133" s="30" t="n"/>
       <c r="C133" s="23" t="n"/>
       <c r="D133" s="13" t="n"/>
-      <c r="E133" s="27" t="n"/>
+      <c r="E133" s="30" t="n"/>
       <c r="F133" s="23" t="n"/>
       <c r="G133" s="13" t="n"/>
-      <c r="H133" s="27" t="n"/>
+      <c r="H133" s="30" t="n"/>
       <c r="I133" s="23" t="n"/>
       <c r="J133" s="13" t="n"/>
-      <c r="K133" s="27" t="n"/>
+      <c r="K133" s="30" t="n"/>
       <c r="L133" s="23" t="n"/>
       <c r="M133" s="13" t="n"/>
-      <c r="N133" s="27" t="n"/>
+      <c r="N133" s="30" t="n"/>
       <c r="O133" s="23" t="n"/>
       <c r="P133" s="13" t="n"/>
-      <c r="Q133" s="27" t="n"/>
+      <c r="Q133" s="30" t="n"/>
       <c r="R133" s="23" t="n"/>
       <c r="S133" s="13" t="n"/>
-      <c r="T133" s="27" t="n"/>
+      <c r="T133" s="30" t="n"/>
       <c r="U133" s="23" t="n"/>
       <c r="V133" s="13" t="n"/>
     </row>
@@ -4947,25 +4947,25 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B135" s="25" t="n"/>
+      <c r="B135" s="28" t="n"/>
       <c r="C135" s="22" t="n"/>
       <c r="D135" s="9" t="n"/>
-      <c r="E135" s="25" t="n"/>
+      <c r="E135" s="28" t="n"/>
       <c r="F135" s="22" t="n"/>
       <c r="G135" s="9" t="n"/>
-      <c r="H135" s="25" t="n"/>
+      <c r="H135" s="28" t="n"/>
       <c r="I135" s="22" t="n"/>
       <c r="J135" s="9" t="n"/>
-      <c r="K135" s="25" t="n"/>
+      <c r="K135" s="28" t="n"/>
       <c r="L135" s="22" t="n"/>
       <c r="M135" s="9" t="n"/>
-      <c r="N135" s="25" t="n"/>
+      <c r="N135" s="28" t="n"/>
       <c r="O135" s="22" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="25" t="n"/>
+      <c r="Q135" s="28" t="n"/>
       <c r="R135" s="22" t="n"/>
       <c r="S135" s="9" t="n"/>
-      <c r="T135" s="25" t="n"/>
+      <c r="T135" s="28" t="n"/>
       <c r="U135" s="22" t="n"/>
       <c r="V135" s="9" t="n"/>
     </row>
@@ -4975,25 +4975,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B136" s="27" t="n"/>
+      <c r="B136" s="30" t="n"/>
       <c r="C136" s="23" t="n"/>
       <c r="D136" s="13" t="n"/>
-      <c r="E136" s="27" t="n"/>
+      <c r="E136" s="30" t="n"/>
       <c r="F136" s="23" t="n"/>
       <c r="G136" s="13" t="n"/>
-      <c r="H136" s="27" t="n"/>
+      <c r="H136" s="30" t="n"/>
       <c r="I136" s="23" t="n"/>
       <c r="J136" s="13" t="n"/>
-      <c r="K136" s="27" t="n"/>
+      <c r="K136" s="30" t="n"/>
       <c r="L136" s="23" t="n"/>
       <c r="M136" s="13" t="n"/>
-      <c r="N136" s="27" t="n"/>
+      <c r="N136" s="30" t="n"/>
       <c r="O136" s="23" t="n"/>
       <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="27" t="n"/>
+      <c r="Q136" s="30" t="n"/>
       <c r="R136" s="23" t="n"/>
       <c r="S136" s="13" t="n"/>
-      <c r="T136" s="27" t="n"/>
+      <c r="T136" s="30" t="n"/>
       <c r="U136" s="23" t="n"/>
       <c r="V136" s="13" t="n"/>
     </row>
@@ -5003,25 +5003,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B137" s="27" t="n"/>
+      <c r="B137" s="30" t="n"/>
       <c r="C137" s="23" t="n"/>
       <c r="D137" s="13" t="n"/>
-      <c r="E137" s="27" t="n"/>
+      <c r="E137" s="30" t="n"/>
       <c r="F137" s="23" t="n"/>
       <c r="G137" s="13" t="n"/>
-      <c r="H137" s="27" t="n"/>
+      <c r="H137" s="30" t="n"/>
       <c r="I137" s="23" t="n"/>
       <c r="J137" s="13" t="n"/>
-      <c r="K137" s="27" t="n"/>
+      <c r="K137" s="30" t="n"/>
       <c r="L137" s="23" t="n"/>
       <c r="M137" s="13" t="n"/>
-      <c r="N137" s="27" t="n"/>
+      <c r="N137" s="30" t="n"/>
       <c r="O137" s="23" t="n"/>
       <c r="P137" s="13" t="n"/>
-      <c r="Q137" s="27" t="n"/>
+      <c r="Q137" s="30" t="n"/>
       <c r="R137" s="23" t="n"/>
       <c r="S137" s="13" t="n"/>
-      <c r="T137" s="27" t="n"/>
+      <c r="T137" s="30" t="n"/>
       <c r="U137" s="23" t="n"/>
       <c r="V137" s="13" t="n"/>
     </row>
@@ -5031,25 +5031,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B138" s="27" t="n"/>
+      <c r="B138" s="30" t="n"/>
       <c r="C138" s="23" t="n"/>
       <c r="D138" s="13" t="n"/>
-      <c r="E138" s="27" t="n"/>
+      <c r="E138" s="30" t="n"/>
       <c r="F138" s="23" t="n"/>
       <c r="G138" s="13" t="n"/>
-      <c r="H138" s="27" t="n"/>
+      <c r="H138" s="30" t="n"/>
       <c r="I138" s="23" t="n"/>
       <c r="J138" s="13" t="n"/>
-      <c r="K138" s="27" t="n"/>
+      <c r="K138" s="30" t="n"/>
       <c r="L138" s="23" t="n"/>
       <c r="M138" s="13" t="n"/>
-      <c r="N138" s="27" t="n"/>
+      <c r="N138" s="30" t="n"/>
       <c r="O138" s="23" t="n"/>
       <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="27" t="n"/>
+      <c r="Q138" s="30" t="n"/>
       <c r="R138" s="23" t="n"/>
       <c r="S138" s="13" t="n"/>
-      <c r="T138" s="27" t="n"/>
+      <c r="T138" s="30" t="n"/>
       <c r="U138" s="23" t="n"/>
       <c r="V138" s="13" t="n"/>
     </row>
@@ -5059,25 +5059,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B139" s="27" t="n"/>
+      <c r="B139" s="30" t="n"/>
       <c r="C139" s="23" t="n"/>
       <c r="D139" s="13" t="n"/>
-      <c r="E139" s="27" t="n"/>
+      <c r="E139" s="30" t="n"/>
       <c r="F139" s="23" t="n"/>
       <c r="G139" s="13" t="n"/>
-      <c r="H139" s="27" t="n"/>
+      <c r="H139" s="30" t="n"/>
       <c r="I139" s="23" t="n"/>
       <c r="J139" s="13" t="n"/>
-      <c r="K139" s="27" t="n"/>
+      <c r="K139" s="30" t="n"/>
       <c r="L139" s="23" t="n"/>
       <c r="M139" s="13" t="n"/>
-      <c r="N139" s="27" t="n"/>
+      <c r="N139" s="30" t="n"/>
       <c r="O139" s="23" t="n"/>
       <c r="P139" s="13" t="n"/>
-      <c r="Q139" s="27" t="n"/>
+      <c r="Q139" s="30" t="n"/>
       <c r="R139" s="23" t="n"/>
       <c r="S139" s="13" t="n"/>
-      <c r="T139" s="27" t="n"/>
+      <c r="T139" s="30" t="n"/>
       <c r="U139" s="23" t="n"/>
       <c r="V139" s="13" t="n"/>
     </row>
@@ -5087,25 +5087,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B140" s="27" t="n"/>
+      <c r="B140" s="30" t="n"/>
       <c r="C140" s="23" t="n"/>
       <c r="D140" s="13" t="n"/>
-      <c r="E140" s="27" t="n"/>
+      <c r="E140" s="30" t="n"/>
       <c r="F140" s="23" t="n"/>
       <c r="G140" s="13" t="n"/>
-      <c r="H140" s="27" t="n"/>
+      <c r="H140" s="30" t="n"/>
       <c r="I140" s="23" t="n"/>
       <c r="J140" s="13" t="n"/>
-      <c r="K140" s="27" t="n"/>
+      <c r="K140" s="30" t="n"/>
       <c r="L140" s="23" t="n"/>
       <c r="M140" s="13" t="n"/>
-      <c r="N140" s="27" t="n"/>
+      <c r="N140" s="30" t="n"/>
       <c r="O140" s="23" t="n"/>
       <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="27" t="n"/>
+      <c r="Q140" s="30" t="n"/>
       <c r="R140" s="23" t="n"/>
       <c r="S140" s="13" t="n"/>
-      <c r="T140" s="27" t="n"/>
+      <c r="T140" s="30" t="n"/>
       <c r="U140" s="23" t="n"/>
       <c r="V140" s="13" t="n"/>
     </row>
@@ -5115,25 +5115,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B141" s="27" t="n"/>
+      <c r="B141" s="30" t="n"/>
       <c r="C141" s="23" t="n"/>
       <c r="D141" s="13" t="n"/>
-      <c r="E141" s="27" t="n"/>
+      <c r="E141" s="30" t="n"/>
       <c r="F141" s="23" t="n"/>
       <c r="G141" s="13" t="n"/>
-      <c r="H141" s="27" t="n"/>
+      <c r="H141" s="30" t="n"/>
       <c r="I141" s="23" t="n"/>
       <c r="J141" s="13" t="n"/>
-      <c r="K141" s="27" t="n"/>
+      <c r="K141" s="30" t="n"/>
       <c r="L141" s="23" t="n"/>
       <c r="M141" s="13" t="n"/>
-      <c r="N141" s="27" t="n"/>
+      <c r="N141" s="30" t="n"/>
       <c r="O141" s="23" t="n"/>
       <c r="P141" s="13" t="n"/>
-      <c r="Q141" s="27" t="n"/>
+      <c r="Q141" s="30" t="n"/>
       <c r="R141" s="23" t="n"/>
       <c r="S141" s="13" t="n"/>
-      <c r="T141" s="27" t="n"/>
+      <c r="T141" s="30" t="n"/>
       <c r="U141" s="23" t="n"/>
       <c r="V141" s="13" t="n"/>
     </row>
@@ -5143,25 +5143,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B142" s="27" t="n"/>
+      <c r="B142" s="30" t="n"/>
       <c r="C142" s="23" t="n"/>
       <c r="D142" s="13" t="n"/>
-      <c r="E142" s="27" t="n"/>
+      <c r="E142" s="30" t="n"/>
       <c r="F142" s="23" t="n"/>
       <c r="G142" s="13" t="n"/>
-      <c r="H142" s="27" t="n"/>
+      <c r="H142" s="30" t="n"/>
       <c r="I142" s="23" t="n"/>
       <c r="J142" s="13" t="n"/>
-      <c r="K142" s="27" t="n"/>
+      <c r="K142" s="30" t="n"/>
       <c r="L142" s="23" t="n"/>
       <c r="M142" s="13" t="n"/>
-      <c r="N142" s="27" t="n"/>
+      <c r="N142" s="30" t="n"/>
       <c r="O142" s="23" t="n"/>
       <c r="P142" s="13" t="n"/>
-      <c r="Q142" s="27" t="n"/>
+      <c r="Q142" s="30" t="n"/>
       <c r="R142" s="23" t="n"/>
       <c r="S142" s="13" t="n"/>
-      <c r="T142" s="27" t="n"/>
+      <c r="T142" s="30" t="n"/>
       <c r="U142" s="23" t="n"/>
       <c r="V142" s="13" t="n"/>
     </row>
@@ -5171,25 +5171,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B143" s="27" t="n"/>
+      <c r="B143" s="30" t="n"/>
       <c r="C143" s="23" t="n"/>
       <c r="D143" s="13" t="n"/>
-      <c r="E143" s="27" t="n"/>
+      <c r="E143" s="30" t="n"/>
       <c r="F143" s="23" t="n"/>
       <c r="G143" s="13" t="n"/>
-      <c r="H143" s="27" t="n"/>
+      <c r="H143" s="30" t="n"/>
       <c r="I143" s="23" t="n"/>
       <c r="J143" s="13" t="n"/>
-      <c r="K143" s="27" t="n"/>
+      <c r="K143" s="30" t="n"/>
       <c r="L143" s="23" t="n"/>
       <c r="M143" s="13" t="n"/>
-      <c r="N143" s="27" t="n"/>
+      <c r="N143" s="30" t="n"/>
       <c r="O143" s="23" t="n"/>
       <c r="P143" s="13" t="n"/>
-      <c r="Q143" s="27" t="n"/>
+      <c r="Q143" s="30" t="n"/>
       <c r="R143" s="23" t="n"/>
       <c r="S143" s="13" t="n"/>
-      <c r="T143" s="27" t="n"/>
+      <c r="T143" s="30" t="n"/>
       <c r="U143" s="23" t="n"/>
       <c r="V143" s="13" t="n"/>
     </row>
@@ -5199,25 +5199,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B144" s="27" t="n"/>
+      <c r="B144" s="30" t="n"/>
       <c r="C144" s="23" t="n"/>
       <c r="D144" s="13" t="n"/>
-      <c r="E144" s="27" t="n"/>
+      <c r="E144" s="30" t="n"/>
       <c r="F144" s="23" t="n"/>
       <c r="G144" s="13" t="n"/>
-      <c r="H144" s="27" t="n"/>
+      <c r="H144" s="30" t="n"/>
       <c r="I144" s="23" t="n"/>
       <c r="J144" s="13" t="n"/>
-      <c r="K144" s="27" t="n"/>
+      <c r="K144" s="30" t="n"/>
       <c r="L144" s="23" t="n"/>
       <c r="M144" s="13" t="n"/>
-      <c r="N144" s="27" t="n"/>
+      <c r="N144" s="30" t="n"/>
       <c r="O144" s="23" t="n"/>
       <c r="P144" s="13" t="n"/>
-      <c r="Q144" s="27" t="n"/>
+      <c r="Q144" s="30" t="n"/>
       <c r="R144" s="23" t="n"/>
       <c r="S144" s="13" t="n"/>
-      <c r="T144" s="27" t="n"/>
+      <c r="T144" s="30" t="n"/>
       <c r="U144" s="23" t="n"/>
       <c r="V144" s="13" t="n"/>
     </row>
@@ -5227,25 +5227,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B145" s="27" t="n"/>
+      <c r="B145" s="30" t="n"/>
       <c r="C145" s="23" t="n"/>
       <c r="D145" s="13" t="n"/>
-      <c r="E145" s="27" t="n"/>
+      <c r="E145" s="30" t="n"/>
       <c r="F145" s="23" t="n"/>
       <c r="G145" s="13" t="n"/>
-      <c r="H145" s="27" t="n"/>
+      <c r="H145" s="30" t="n"/>
       <c r="I145" s="23" t="n"/>
       <c r="J145" s="13" t="n"/>
-      <c r="K145" s="27" t="n"/>
+      <c r="K145" s="30" t="n"/>
       <c r="L145" s="23" t="n"/>
       <c r="M145" s="13" t="n"/>
-      <c r="N145" s="27" t="n"/>
+      <c r="N145" s="30" t="n"/>
       <c r="O145" s="23" t="n"/>
       <c r="P145" s="13" t="n"/>
-      <c r="Q145" s="27" t="n"/>
+      <c r="Q145" s="30" t="n"/>
       <c r="R145" s="23" t="n"/>
       <c r="S145" s="13" t="n"/>
-      <c r="T145" s="27" t="n"/>
+      <c r="T145" s="30" t="n"/>
       <c r="U145" s="23" t="n"/>
       <c r="V145" s="13" t="n"/>
     </row>
@@ -5283,25 +5283,25 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B147" s="25" t="n"/>
+      <c r="B147" s="28" t="n"/>
       <c r="C147" s="22" t="n"/>
       <c r="D147" s="9" t="n"/>
-      <c r="E147" s="25" t="n"/>
+      <c r="E147" s="28" t="n"/>
       <c r="F147" s="22" t="n"/>
       <c r="G147" s="9" t="n"/>
-      <c r="H147" s="25" t="n"/>
+      <c r="H147" s="28" t="n"/>
       <c r="I147" s="22" t="n"/>
       <c r="J147" s="9" t="n"/>
-      <c r="K147" s="25" t="n"/>
+      <c r="K147" s="28" t="n"/>
       <c r="L147" s="22" t="n"/>
       <c r="M147" s="9" t="n"/>
-      <c r="N147" s="25" t="n"/>
+      <c r="N147" s="28" t="n"/>
       <c r="O147" s="22" t="n"/>
       <c r="P147" s="9" t="n"/>
-      <c r="Q147" s="25" t="n"/>
+      <c r="Q147" s="28" t="n"/>
       <c r="R147" s="22" t="n"/>
       <c r="S147" s="9" t="n"/>
-      <c r="T147" s="25" t="n"/>
+      <c r="T147" s="28" t="n"/>
       <c r="U147" s="22" t="n"/>
       <c r="V147" s="9" t="n"/>
     </row>
@@ -5311,25 +5311,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B148" s="27" t="n"/>
+      <c r="B148" s="30" t="n"/>
       <c r="C148" s="23" t="n"/>
       <c r="D148" s="13" t="n"/>
-      <c r="E148" s="27" t="n"/>
+      <c r="E148" s="30" t="n"/>
       <c r="F148" s="23" t="n"/>
       <c r="G148" s="13" t="n"/>
-      <c r="H148" s="27" t="n"/>
+      <c r="H148" s="30" t="n"/>
       <c r="I148" s="23" t="n"/>
       <c r="J148" s="13" t="n"/>
-      <c r="K148" s="27" t="n"/>
+      <c r="K148" s="30" t="n"/>
       <c r="L148" s="23" t="n"/>
       <c r="M148" s="13" t="n"/>
-      <c r="N148" s="27" t="n"/>
+      <c r="N148" s="30" t="n"/>
       <c r="O148" s="23" t="n"/>
       <c r="P148" s="13" t="n"/>
-      <c r="Q148" s="27" t="n"/>
+      <c r="Q148" s="30" t="n"/>
       <c r="R148" s="23" t="n"/>
       <c r="S148" s="13" t="n"/>
-      <c r="T148" s="27" t="n"/>
+      <c r="T148" s="30" t="n"/>
       <c r="U148" s="23" t="n"/>
       <c r="V148" s="13" t="n"/>
     </row>
@@ -5339,25 +5339,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B149" s="27" t="n"/>
+      <c r="B149" s="30" t="n"/>
       <c r="C149" s="23" t="n"/>
       <c r="D149" s="13" t="n"/>
-      <c r="E149" s="27" t="n"/>
+      <c r="E149" s="30" t="n"/>
       <c r="F149" s="23" t="n"/>
       <c r="G149" s="13" t="n"/>
-      <c r="H149" s="27" t="n"/>
+      <c r="H149" s="30" t="n"/>
       <c r="I149" s="23" t="n"/>
       <c r="J149" s="13" t="n"/>
-      <c r="K149" s="27" t="n"/>
+      <c r="K149" s="30" t="n"/>
       <c r="L149" s="23" t="n"/>
       <c r="M149" s="13" t="n"/>
-      <c r="N149" s="27" t="n"/>
+      <c r="N149" s="30" t="n"/>
       <c r="O149" s="23" t="n"/>
       <c r="P149" s="13" t="n"/>
-      <c r="Q149" s="27" t="n"/>
+      <c r="Q149" s="30" t="n"/>
       <c r="R149" s="23" t="n"/>
       <c r="S149" s="13" t="n"/>
-      <c r="T149" s="27" t="n"/>
+      <c r="T149" s="30" t="n"/>
       <c r="U149" s="23" t="n"/>
       <c r="V149" s="13" t="n"/>
     </row>
@@ -5367,25 +5367,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B150" s="27" t="n"/>
+      <c r="B150" s="30" t="n"/>
       <c r="C150" s="23" t="n"/>
       <c r="D150" s="13" t="n"/>
-      <c r="E150" s="27" t="n"/>
+      <c r="E150" s="30" t="n"/>
       <c r="F150" s="23" t="n"/>
       <c r="G150" s="13" t="n"/>
-      <c r="H150" s="27" t="n"/>
+      <c r="H150" s="30" t="n"/>
       <c r="I150" s="23" t="n"/>
       <c r="J150" s="13" t="n"/>
-      <c r="K150" s="27" t="n"/>
+      <c r="K150" s="30" t="n"/>
       <c r="L150" s="23" t="n"/>
       <c r="M150" s="13" t="n"/>
-      <c r="N150" s="27" t="n"/>
+      <c r="N150" s="30" t="n"/>
       <c r="O150" s="23" t="n"/>
       <c r="P150" s="13" t="n"/>
-      <c r="Q150" s="27" t="n"/>
+      <c r="Q150" s="30" t="n"/>
       <c r="R150" s="23" t="n"/>
       <c r="S150" s="13" t="n"/>
-      <c r="T150" s="27" t="n"/>
+      <c r="T150" s="30" t="n"/>
       <c r="U150" s="23" t="n"/>
       <c r="V150" s="13" t="n"/>
     </row>
@@ -5395,25 +5395,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B151" s="27" t="n"/>
+      <c r="B151" s="30" t="n"/>
       <c r="C151" s="23" t="n"/>
       <c r="D151" s="13" t="n"/>
-      <c r="E151" s="27" t="n"/>
+      <c r="E151" s="30" t="n"/>
       <c r="F151" s="23" t="n"/>
       <c r="G151" s="13" t="n"/>
-      <c r="H151" s="27" t="n"/>
+      <c r="H151" s="30" t="n"/>
       <c r="I151" s="23" t="n"/>
       <c r="J151" s="13" t="n"/>
-      <c r="K151" s="27" t="n"/>
+      <c r="K151" s="30" t="n"/>
       <c r="L151" s="23" t="n"/>
       <c r="M151" s="13" t="n"/>
-      <c r="N151" s="27" t="n"/>
+      <c r="N151" s="30" t="n"/>
       <c r="O151" s="23" t="n"/>
       <c r="P151" s="13" t="n"/>
-      <c r="Q151" s="27" t="n"/>
+      <c r="Q151" s="30" t="n"/>
       <c r="R151" s="23" t="n"/>
       <c r="S151" s="13" t="n"/>
-      <c r="T151" s="27" t="n"/>
+      <c r="T151" s="30" t="n"/>
       <c r="U151" s="23" t="n"/>
       <c r="V151" s="13" t="n"/>
     </row>
@@ -5423,25 +5423,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B152" s="27" t="n"/>
+      <c r="B152" s="30" t="n"/>
       <c r="C152" s="23" t="n"/>
       <c r="D152" s="13" t="n"/>
-      <c r="E152" s="27" t="n"/>
+      <c r="E152" s="30" t="n"/>
       <c r="F152" s="23" t="n"/>
       <c r="G152" s="13" t="n"/>
-      <c r="H152" s="27" t="n"/>
+      <c r="H152" s="30" t="n"/>
       <c r="I152" s="23" t="n"/>
       <c r="J152" s="13" t="n"/>
-      <c r="K152" s="27" t="n"/>
+      <c r="K152" s="30" t="n"/>
       <c r="L152" s="23" t="n"/>
       <c r="M152" s="13" t="n"/>
-      <c r="N152" s="27" t="n"/>
+      <c r="N152" s="30" t="n"/>
       <c r="O152" s="23" t="n"/>
       <c r="P152" s="13" t="n"/>
-      <c r="Q152" s="27" t="n"/>
+      <c r="Q152" s="30" t="n"/>
       <c r="R152" s="23" t="n"/>
       <c r="S152" s="13" t="n"/>
-      <c r="T152" s="27" t="n"/>
+      <c r="T152" s="30" t="n"/>
       <c r="U152" s="23" t="n"/>
       <c r="V152" s="13" t="n"/>
     </row>
@@ -5451,25 +5451,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B153" s="27" t="n"/>
+      <c r="B153" s="30" t="n"/>
       <c r="C153" s="23" t="n"/>
       <c r="D153" s="13" t="n"/>
-      <c r="E153" s="27" t="n"/>
+      <c r="E153" s="30" t="n"/>
       <c r="F153" s="23" t="n"/>
       <c r="G153" s="13" t="n"/>
-      <c r="H153" s="27" t="n"/>
+      <c r="H153" s="30" t="n"/>
       <c r="I153" s="23" t="n"/>
       <c r="J153" s="13" t="n"/>
-      <c r="K153" s="27" t="n"/>
+      <c r="K153" s="30" t="n"/>
       <c r="L153" s="23" t="n"/>
       <c r="M153" s="13" t="n"/>
-      <c r="N153" s="27" t="n"/>
+      <c r="N153" s="30" t="n"/>
       <c r="O153" s="23" t="n"/>
       <c r="P153" s="13" t="n"/>
-      <c r="Q153" s="27" t="n"/>
+      <c r="Q153" s="30" t="n"/>
       <c r="R153" s="23" t="n"/>
       <c r="S153" s="13" t="n"/>
-      <c r="T153" s="27" t="n"/>
+      <c r="T153" s="30" t="n"/>
       <c r="U153" s="23" t="n"/>
       <c r="V153" s="13" t="n"/>
     </row>
@@ -5479,25 +5479,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B154" s="27" t="n"/>
+      <c r="B154" s="30" t="n"/>
       <c r="C154" s="23" t="n"/>
       <c r="D154" s="13" t="n"/>
-      <c r="E154" s="27" t="n"/>
+      <c r="E154" s="30" t="n"/>
       <c r="F154" s="23" t="n"/>
       <c r="G154" s="13" t="n"/>
-      <c r="H154" s="27" t="n"/>
+      <c r="H154" s="30" t="n"/>
       <c r="I154" s="23" t="n"/>
       <c r="J154" s="13" t="n"/>
-      <c r="K154" s="27" t="n"/>
+      <c r="K154" s="30" t="n"/>
       <c r="L154" s="23" t="n"/>
       <c r="M154" s="13" t="n"/>
-      <c r="N154" s="27" t="n"/>
+      <c r="N154" s="30" t="n"/>
       <c r="O154" s="23" t="n"/>
       <c r="P154" s="13" t="n"/>
-      <c r="Q154" s="27" t="n"/>
+      <c r="Q154" s="30" t="n"/>
       <c r="R154" s="23" t="n"/>
       <c r="S154" s="13" t="n"/>
-      <c r="T154" s="27" t="n"/>
+      <c r="T154" s="30" t="n"/>
       <c r="U154" s="23" t="n"/>
       <c r="V154" s="13" t="n"/>
     </row>
@@ -5507,25 +5507,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B155" s="27" t="n"/>
+      <c r="B155" s="30" t="n"/>
       <c r="C155" s="23" t="n"/>
       <c r="D155" s="13" t="n"/>
-      <c r="E155" s="27" t="n"/>
+      <c r="E155" s="30" t="n"/>
       <c r="F155" s="23" t="n"/>
       <c r="G155" s="13" t="n"/>
-      <c r="H155" s="27" t="n"/>
+      <c r="H155" s="30" t="n"/>
       <c r="I155" s="23" t="n"/>
       <c r="J155" s="13" t="n"/>
-      <c r="K155" s="27" t="n"/>
+      <c r="K155" s="30" t="n"/>
       <c r="L155" s="23" t="n"/>
       <c r="M155" s="13" t="n"/>
-      <c r="N155" s="27" t="n"/>
+      <c r="N155" s="30" t="n"/>
       <c r="O155" s="23" t="n"/>
       <c r="P155" s="13" t="n"/>
-      <c r="Q155" s="27" t="n"/>
+      <c r="Q155" s="30" t="n"/>
       <c r="R155" s="23" t="n"/>
       <c r="S155" s="13" t="n"/>
-      <c r="T155" s="27" t="n"/>
+      <c r="T155" s="30" t="n"/>
       <c r="U155" s="23" t="n"/>
       <c r="V155" s="13" t="n"/>
     </row>
@@ -5535,25 +5535,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B156" s="27" t="n"/>
+      <c r="B156" s="30" t="n"/>
       <c r="C156" s="23" t="n"/>
       <c r="D156" s="13" t="n"/>
-      <c r="E156" s="27" t="n"/>
+      <c r="E156" s="30" t="n"/>
       <c r="F156" s="23" t="n"/>
       <c r="G156" s="13" t="n"/>
-      <c r="H156" s="27" t="n"/>
+      <c r="H156" s="30" t="n"/>
       <c r="I156" s="23" t="n"/>
       <c r="J156" s="13" t="n"/>
-      <c r="K156" s="27" t="n"/>
+      <c r="K156" s="30" t="n"/>
       <c r="L156" s="23" t="n"/>
       <c r="M156" s="13" t="n"/>
-      <c r="N156" s="27" t="n"/>
+      <c r="N156" s="30" t="n"/>
       <c r="O156" s="23" t="n"/>
       <c r="P156" s="13" t="n"/>
-      <c r="Q156" s="27" t="n"/>
+      <c r="Q156" s="30" t="n"/>
       <c r="R156" s="23" t="n"/>
       <c r="S156" s="13" t="n"/>
-      <c r="T156" s="27" t="n"/>
+      <c r="T156" s="30" t="n"/>
       <c r="U156" s="23" t="n"/>
       <c r="V156" s="13" t="n"/>
     </row>
@@ -5563,25 +5563,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B157" s="27" t="n"/>
+      <c r="B157" s="30" t="n"/>
       <c r="C157" s="23" t="n"/>
       <c r="D157" s="13" t="n"/>
-      <c r="E157" s="27" t="n"/>
+      <c r="E157" s="30" t="n"/>
       <c r="F157" s="23" t="n"/>
       <c r="G157" s="13" t="n"/>
-      <c r="H157" s="27" t="n"/>
+      <c r="H157" s="30" t="n"/>
       <c r="I157" s="23" t="n"/>
       <c r="J157" s="13" t="n"/>
-      <c r="K157" s="27" t="n"/>
+      <c r="K157" s="30" t="n"/>
       <c r="L157" s="23" t="n"/>
       <c r="M157" s="13" t="n"/>
-      <c r="N157" s="27" t="n"/>
+      <c r="N157" s="30" t="n"/>
       <c r="O157" s="23" t="n"/>
       <c r="P157" s="13" t="n"/>
-      <c r="Q157" s="27" t="n"/>
+      <c r="Q157" s="30" t="n"/>
       <c r="R157" s="23" t="n"/>
       <c r="S157" s="13" t="n"/>
-      <c r="T157" s="27" t="n"/>
+      <c r="T157" s="30" t="n"/>
       <c r="U157" s="23" t="n"/>
       <c r="V157" s="13" t="n"/>
     </row>
@@ -5619,25 +5619,25 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B159" s="25" t="n"/>
+      <c r="B159" s="28" t="n"/>
       <c r="C159" s="22" t="n"/>
       <c r="D159" s="9" t="n"/>
-      <c r="E159" s="25" t="n"/>
+      <c r="E159" s="28" t="n"/>
       <c r="F159" s="22" t="n"/>
       <c r="G159" s="9" t="n"/>
-      <c r="H159" s="25" t="n"/>
+      <c r="H159" s="28" t="n"/>
       <c r="I159" s="22" t="n"/>
       <c r="J159" s="9" t="n"/>
-      <c r="K159" s="25" t="n"/>
+      <c r="K159" s="28" t="n"/>
       <c r="L159" s="22" t="n"/>
       <c r="M159" s="9" t="n"/>
-      <c r="N159" s="25" t="n"/>
+      <c r="N159" s="28" t="n"/>
       <c r="O159" s="22" t="n"/>
       <c r="P159" s="9" t="n"/>
-      <c r="Q159" s="25" t="n"/>
+      <c r="Q159" s="28" t="n"/>
       <c r="R159" s="22" t="n"/>
       <c r="S159" s="9" t="n"/>
-      <c r="T159" s="25" t="n"/>
+      <c r="T159" s="28" t="n"/>
       <c r="U159" s="22" t="n"/>
       <c r="V159" s="9" t="n"/>
     </row>
@@ -5647,25 +5647,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B160" s="27" t="n"/>
+      <c r="B160" s="30" t="n"/>
       <c r="C160" s="23" t="n"/>
       <c r="D160" s="13" t="n"/>
-      <c r="E160" s="27" t="n"/>
+      <c r="E160" s="30" t="n"/>
       <c r="F160" s="23" t="n"/>
       <c r="G160" s="13" t="n"/>
-      <c r="H160" s="27" t="n"/>
+      <c r="H160" s="30" t="n"/>
       <c r="I160" s="23" t="n"/>
       <c r="J160" s="13" t="n"/>
-      <c r="K160" s="27" t="n"/>
+      <c r="K160" s="30" t="n"/>
       <c r="L160" s="23" t="n"/>
       <c r="M160" s="13" t="n"/>
-      <c r="N160" s="27" t="n"/>
+      <c r="N160" s="30" t="n"/>
       <c r="O160" s="23" t="n"/>
       <c r="P160" s="13" t="n"/>
-      <c r="Q160" s="27" t="n"/>
+      <c r="Q160" s="30" t="n"/>
       <c r="R160" s="23" t="n"/>
       <c r="S160" s="13" t="n"/>
-      <c r="T160" s="27" t="n"/>
+      <c r="T160" s="30" t="n"/>
       <c r="U160" s="23" t="n"/>
       <c r="V160" s="13" t="n"/>
     </row>
@@ -5675,25 +5675,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B161" s="27" t="n"/>
+      <c r="B161" s="30" t="n"/>
       <c r="C161" s="23" t="n"/>
       <c r="D161" s="13" t="n"/>
-      <c r="E161" s="27" t="n"/>
+      <c r="E161" s="30" t="n"/>
       <c r="F161" s="23" t="n"/>
       <c r="G161" s="13" t="n"/>
-      <c r="H161" s="27" t="n"/>
+      <c r="H161" s="30" t="n"/>
       <c r="I161" s="23" t="n"/>
       <c r="J161" s="13" t="n"/>
-      <c r="K161" s="27" t="n"/>
+      <c r="K161" s="30" t="n"/>
       <c r="L161" s="23" t="n"/>
       <c r="M161" s="13" t="n"/>
-      <c r="N161" s="27" t="n"/>
+      <c r="N161" s="30" t="n"/>
       <c r="O161" s="23" t="n"/>
       <c r="P161" s="13" t="n"/>
-      <c r="Q161" s="27" t="n"/>
+      <c r="Q161" s="30" t="n"/>
       <c r="R161" s="23" t="n"/>
       <c r="S161" s="13" t="n"/>
-      <c r="T161" s="27" t="n"/>
+      <c r="T161" s="30" t="n"/>
       <c r="U161" s="23" t="n"/>
       <c r="V161" s="13" t="n"/>
     </row>
@@ -5703,25 +5703,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B162" s="27" t="n"/>
+      <c r="B162" s="30" t="n"/>
       <c r="C162" s="23" t="n"/>
       <c r="D162" s="13" t="n"/>
-      <c r="E162" s="27" t="n"/>
+      <c r="E162" s="30" t="n"/>
       <c r="F162" s="23" t="n"/>
       <c r="G162" s="13" t="n"/>
-      <c r="H162" s="27" t="n"/>
+      <c r="H162" s="30" t="n"/>
       <c r="I162" s="23" t="n"/>
       <c r="J162" s="13" t="n"/>
-      <c r="K162" s="27" t="n"/>
+      <c r="K162" s="30" t="n"/>
       <c r="L162" s="23" t="n"/>
       <c r="M162" s="13" t="n"/>
-      <c r="N162" s="27" t="n"/>
+      <c r="N162" s="30" t="n"/>
       <c r="O162" s="23" t="n"/>
       <c r="P162" s="13" t="n"/>
-      <c r="Q162" s="27" t="n"/>
+      <c r="Q162" s="30" t="n"/>
       <c r="R162" s="23" t="n"/>
       <c r="S162" s="13" t="n"/>
-      <c r="T162" s="27" t="n"/>
+      <c r="T162" s="30" t="n"/>
       <c r="U162" s="23" t="n"/>
       <c r="V162" s="13" t="n"/>
     </row>
@@ -5731,25 +5731,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B163" s="27" t="n"/>
+      <c r="B163" s="30" t="n"/>
       <c r="C163" s="23" t="n"/>
       <c r="D163" s="13" t="n"/>
-      <c r="E163" s="27" t="n"/>
+      <c r="E163" s="30" t="n"/>
       <c r="F163" s="23" t="n"/>
       <c r="G163" s="13" t="n"/>
-      <c r="H163" s="27" t="n"/>
+      <c r="H163" s="30" t="n"/>
       <c r="I163" s="23" t="n"/>
       <c r="J163" s="13" t="n"/>
-      <c r="K163" s="27" t="n"/>
+      <c r="K163" s="30" t="n"/>
       <c r="L163" s="23" t="n"/>
       <c r="M163" s="13" t="n"/>
-      <c r="N163" s="27" t="n"/>
+      <c r="N163" s="30" t="n"/>
       <c r="O163" s="23" t="n"/>
       <c r="P163" s="13" t="n"/>
-      <c r="Q163" s="27" t="n"/>
+      <c r="Q163" s="30" t="n"/>
       <c r="R163" s="23" t="n"/>
       <c r="S163" s="13" t="n"/>
-      <c r="T163" s="27" t="n"/>
+      <c r="T163" s="30" t="n"/>
       <c r="U163" s="23" t="n"/>
       <c r="V163" s="13" t="n"/>
     </row>
@@ -5759,25 +5759,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B164" s="27" t="n"/>
+      <c r="B164" s="30" t="n"/>
       <c r="C164" s="23" t="n"/>
       <c r="D164" s="13" t="n"/>
-      <c r="E164" s="27" t="n"/>
+      <c r="E164" s="30" t="n"/>
       <c r="F164" s="23" t="n"/>
       <c r="G164" s="13" t="n"/>
-      <c r="H164" s="27" t="n"/>
+      <c r="H164" s="30" t="n"/>
       <c r="I164" s="23" t="n"/>
       <c r="J164" s="13" t="n"/>
-      <c r="K164" s="27" t="n"/>
+      <c r="K164" s="30" t="n"/>
       <c r="L164" s="23" t="n"/>
       <c r="M164" s="13" t="n"/>
-      <c r="N164" s="27" t="n"/>
+      <c r="N164" s="30" t="n"/>
       <c r="O164" s="23" t="n"/>
       <c r="P164" s="13" t="n"/>
-      <c r="Q164" s="27" t="n"/>
+      <c r="Q164" s="30" t="n"/>
       <c r="R164" s="23" t="n"/>
       <c r="S164" s="13" t="n"/>
-      <c r="T164" s="27" t="n"/>
+      <c r="T164" s="30" t="n"/>
       <c r="U164" s="23" t="n"/>
       <c r="V164" s="13" t="n"/>
     </row>
@@ -5787,50 +5787,50 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B165" s="27" t="n"/>
-      <c r="C165" s="30" t="inlineStr">
+      <c r="B165" s="30" t="n"/>
+      <c r="C165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="D165" s="13" t="n"/>
-      <c r="E165" s="27" t="n"/>
-      <c r="F165" s="30" t="inlineStr">
+      <c r="E165" s="30" t="n"/>
+      <c r="F165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="G165" s="13" t="n"/>
-      <c r="H165" s="27" t="n"/>
-      <c r="I165" s="30" t="inlineStr">
+      <c r="H165" s="30" t="n"/>
+      <c r="I165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="J165" s="13" t="n"/>
-      <c r="K165" s="27" t="n"/>
-      <c r="L165" s="30" t="inlineStr">
+      <c r="K165" s="30" t="n"/>
+      <c r="L165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="M165" s="13" t="n"/>
-      <c r="N165" s="27" t="n"/>
-      <c r="O165" s="30" t="inlineStr">
+      <c r="N165" s="30" t="n"/>
+      <c r="O165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="P165" s="13" t="n"/>
-      <c r="Q165" s="27" t="n"/>
-      <c r="R165" s="30" t="inlineStr">
+      <c r="Q165" s="30" t="n"/>
+      <c r="R165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="S165" s="13" t="n"/>
-      <c r="T165" s="27" t="n"/>
-      <c r="U165" s="30" t="inlineStr">
+      <c r="T165" s="30" t="n"/>
+      <c r="U165" s="25" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
@@ -5843,26 +5843,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B166" s="27" t="n"/>
-      <c r="C166" s="28" t="n"/>
+      <c r="B166" s="30" t="n"/>
+      <c r="C166" s="26" t="n"/>
       <c r="D166" s="13" t="n"/>
-      <c r="E166" s="27" t="n"/>
-      <c r="F166" s="28" t="n"/>
+      <c r="E166" s="30" t="n"/>
+      <c r="F166" s="26" t="n"/>
       <c r="G166" s="13" t="n"/>
-      <c r="H166" s="27" t="n"/>
-      <c r="I166" s="28" t="n"/>
+      <c r="H166" s="30" t="n"/>
+      <c r="I166" s="26" t="n"/>
       <c r="J166" s="13" t="n"/>
-      <c r="K166" s="27" t="n"/>
-      <c r="L166" s="28" t="n"/>
+      <c r="K166" s="30" t="n"/>
+      <c r="L166" s="26" t="n"/>
       <c r="M166" s="13" t="n"/>
-      <c r="N166" s="27" t="n"/>
-      <c r="O166" s="28" t="n"/>
+      <c r="N166" s="30" t="n"/>
+      <c r="O166" s="26" t="n"/>
       <c r="P166" s="13" t="n"/>
-      <c r="Q166" s="27" t="n"/>
-      <c r="R166" s="28" t="n"/>
+      <c r="Q166" s="30" t="n"/>
+      <c r="R166" s="26" t="n"/>
       <c r="S166" s="13" t="n"/>
-      <c r="T166" s="27" t="n"/>
-      <c r="U166" s="28" t="n"/>
+      <c r="T166" s="30" t="n"/>
+      <c r="U166" s="26" t="n"/>
       <c r="V166" s="13" t="n"/>
     </row>
     <row r="167">
@@ -5871,26 +5871,26 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B167" s="27" t="n"/>
-      <c r="C167" s="28" t="n"/>
+      <c r="B167" s="30" t="n"/>
+      <c r="C167" s="26" t="n"/>
       <c r="D167" s="13" t="n"/>
-      <c r="E167" s="27" t="n"/>
-      <c r="F167" s="28" t="n"/>
+      <c r="E167" s="30" t="n"/>
+      <c r="F167" s="26" t="n"/>
       <c r="G167" s="13" t="n"/>
-      <c r="H167" s="27" t="n"/>
-      <c r="I167" s="28" t="n"/>
+      <c r="H167" s="30" t="n"/>
+      <c r="I167" s="26" t="n"/>
       <c r="J167" s="13" t="n"/>
-      <c r="K167" s="27" t="n"/>
-      <c r="L167" s="28" t="n"/>
+      <c r="K167" s="30" t="n"/>
+      <c r="L167" s="26" t="n"/>
       <c r="M167" s="13" t="n"/>
-      <c r="N167" s="27" t="n"/>
-      <c r="O167" s="28" t="n"/>
+      <c r="N167" s="30" t="n"/>
+      <c r="O167" s="26" t="n"/>
       <c r="P167" s="13" t="n"/>
-      <c r="Q167" s="27" t="n"/>
-      <c r="R167" s="28" t="n"/>
+      <c r="Q167" s="30" t="n"/>
+      <c r="R167" s="26" t="n"/>
       <c r="S167" s="13" t="n"/>
-      <c r="T167" s="27" t="n"/>
-      <c r="U167" s="28" t="n"/>
+      <c r="T167" s="30" t="n"/>
+      <c r="U167" s="26" t="n"/>
       <c r="V167" s="13" t="n"/>
     </row>
     <row r="168">
@@ -5899,26 +5899,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B168" s="27" t="n"/>
-      <c r="C168" s="28" t="n"/>
+      <c r="B168" s="30" t="n"/>
+      <c r="C168" s="26" t="n"/>
       <c r="D168" s="13" t="n"/>
-      <c r="E168" s="27" t="n"/>
-      <c r="F168" s="28" t="n"/>
+      <c r="E168" s="30" t="n"/>
+      <c r="F168" s="26" t="n"/>
       <c r="G168" s="13" t="n"/>
-      <c r="H168" s="27" t="n"/>
-      <c r="I168" s="28" t="n"/>
+      <c r="H168" s="30" t="n"/>
+      <c r="I168" s="26" t="n"/>
       <c r="J168" s="13" t="n"/>
-      <c r="K168" s="27" t="n"/>
-      <c r="L168" s="28" t="n"/>
+      <c r="K168" s="30" t="n"/>
+      <c r="L168" s="26" t="n"/>
       <c r="M168" s="13" t="n"/>
-      <c r="N168" s="27" t="n"/>
-      <c r="O168" s="28" t="n"/>
+      <c r="N168" s="30" t="n"/>
+      <c r="O168" s="26" t="n"/>
       <c r="P168" s="13" t="n"/>
-      <c r="Q168" s="27" t="n"/>
-      <c r="R168" s="28" t="n"/>
+      <c r="Q168" s="30" t="n"/>
+      <c r="R168" s="26" t="n"/>
       <c r="S168" s="13" t="n"/>
-      <c r="T168" s="27" t="n"/>
-      <c r="U168" s="28" t="n"/>
+      <c r="T168" s="30" t="n"/>
+      <c r="U168" s="26" t="n"/>
       <c r="V168" s="13" t="n"/>
     </row>
     <row r="169">
@@ -5927,26 +5927,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B169" s="27" t="n"/>
-      <c r="C169" s="29" t="n"/>
+      <c r="B169" s="30" t="n"/>
+      <c r="C169" s="27" t="n"/>
       <c r="D169" s="13" t="n"/>
-      <c r="E169" s="27" t="n"/>
-      <c r="F169" s="29" t="n"/>
+      <c r="E169" s="30" t="n"/>
+      <c r="F169" s="27" t="n"/>
       <c r="G169" s="13" t="n"/>
-      <c r="H169" s="27" t="n"/>
-      <c r="I169" s="29" t="n"/>
+      <c r="H169" s="30" t="n"/>
+      <c r="I169" s="27" t="n"/>
       <c r="J169" s="13" t="n"/>
-      <c r="K169" s="27" t="n"/>
-      <c r="L169" s="29" t="n"/>
+      <c r="K169" s="30" t="n"/>
+      <c r="L169" s="27" t="n"/>
       <c r="M169" s="13" t="n"/>
-      <c r="N169" s="27" t="n"/>
-      <c r="O169" s="29" t="n"/>
+      <c r="N169" s="30" t="n"/>
+      <c r="O169" s="27" t="n"/>
       <c r="P169" s="13" t="n"/>
-      <c r="Q169" s="27" t="n"/>
-      <c r="R169" s="29" t="n"/>
+      <c r="Q169" s="30" t="n"/>
+      <c r="R169" s="27" t="n"/>
       <c r="S169" s="13" t="n"/>
-      <c r="T169" s="27" t="n"/>
-      <c r="U169" s="29" t="n"/>
+      <c r="T169" s="30" t="n"/>
+      <c r="U169" s="27" t="n"/>
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
@@ -6009,11 +6009,11 @@
   <mergeCells count="76">
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="K63:K73"/>
+    <mergeCell ref="N57:N59"/>
     <mergeCell ref="I111:I115"/>
-    <mergeCell ref="N57:N59"/>
     <mergeCell ref="C123:C127"/>
     <mergeCell ref="T6:T8"/>
+    <mergeCell ref="K75:K85"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="U165:U169"/>
@@ -6029,7 +6029,6 @@
     <mergeCell ref="N6:N8"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="K81:K91"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="N9:N11"/>
     <mergeCell ref="F111:F115"/>
@@ -6052,8 +6051,10 @@
     <mergeCell ref="R117:R121"/>
     <mergeCell ref="L111:L115"/>
     <mergeCell ref="R111:R115"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="L81:L91"/>
+    <mergeCell ref="C111:C115"/>
     <mergeCell ref="K9:K11"/>
-    <mergeCell ref="C111:C115"/>
     <mergeCell ref="O111:O115"/>
     <mergeCell ref="T75:T85"/>
     <mergeCell ref="R123:R127"/>
@@ -6063,12 +6064,11 @@
     <mergeCell ref="L165:L169"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="O117:O121"/>
-    <mergeCell ref="B63:B73"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="E63:E67"/>
+    <mergeCell ref="Q54:Q56"/>
     <mergeCell ref="U111:U115"/>
-    <mergeCell ref="Q54:Q56"/>
+    <mergeCell ref="B75:B85"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="T9:T11"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -3469,7 +3469,7 @@
       <c r="I85" s="23" t="n"/>
       <c r="J85" s="13" t="n"/>
       <c r="K85" s="14" t="n"/>
-      <c r="L85" s="26" t="n"/>
+      <c r="L85" s="27" t="n"/>
       <c r="M85" s="13" t="n"/>
       <c r="N85" s="16" t="n"/>
       <c r="O85" s="23" t="n"/>
@@ -3497,7 +3497,7 @@
       <c r="I86" s="24" t="n"/>
       <c r="J86" s="20" t="n"/>
       <c r="K86" s="18" t="n"/>
-      <c r="L86" s="26" t="n"/>
+      <c r="L86" s="24" t="n"/>
       <c r="M86" s="20" t="n"/>
       <c r="N86" s="18" t="n"/>
       <c r="O86" s="24" t="n"/>
@@ -3529,7 +3529,7 @@
       <c r="I87" s="22" t="n"/>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="21" t="n"/>
-      <c r="L87" s="26" t="n"/>
+      <c r="L87" s="22" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="21" t="n"/>
       <c r="O87" s="22" t="n"/>
@@ -3557,7 +3557,7 @@
       <c r="I88" s="23" t="n"/>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="16" t="n"/>
-      <c r="L88" s="26" t="n"/>
+      <c r="L88" s="23" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="16" t="n"/>
       <c r="O88" s="23" t="n"/>
@@ -3585,7 +3585,7 @@
       <c r="I89" s="23" t="n"/>
       <c r="J89" s="13" t="n"/>
       <c r="K89" s="16" t="n"/>
-      <c r="L89" s="26" t="n"/>
+      <c r="L89" s="23" t="n"/>
       <c r="M89" s="13" t="n"/>
       <c r="N89" s="16" t="n"/>
       <c r="O89" s="23" t="n"/>
@@ -3613,7 +3613,7 @@
       <c r="I90" s="23" t="n"/>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="16" t="n"/>
-      <c r="L90" s="26" t="n"/>
+      <c r="L90" s="23" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="16" t="n"/>
       <c r="O90" s="23" t="n"/>
@@ -3641,7 +3641,7 @@
       <c r="I91" s="23" t="n"/>
       <c r="J91" s="13" t="n"/>
       <c r="K91" s="16" t="n"/>
-      <c r="L91" s="27" t="n"/>
+      <c r="L91" s="23" t="n"/>
       <c r="M91" s="13" t="n"/>
       <c r="N91" s="16" t="n"/>
       <c r="O91" s="23" t="n"/>
@@ -6039,6 +6039,7 @@
     <mergeCell ref="Q57:Q59"/>
     <mergeCell ref="F123:F127"/>
     <mergeCell ref="U123:U127"/>
+    <mergeCell ref="L81:L85"/>
     <mergeCell ref="L123:L127"/>
     <mergeCell ref="H87:H91"/>
     <mergeCell ref="F117:F121"/>
@@ -6052,9 +6053,8 @@
     <mergeCell ref="L111:L115"/>
     <mergeCell ref="R111:R115"/>
     <mergeCell ref="E75:E79"/>
-    <mergeCell ref="L81:L91"/>
+    <mergeCell ref="K9:K11"/>
     <mergeCell ref="C111:C115"/>
-    <mergeCell ref="K9:K11"/>
     <mergeCell ref="O111:O115"/>
     <mergeCell ref="T75:T85"/>
     <mergeCell ref="R123:R127"/>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -422,14 +422,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1343,25 +1343,53 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="C12" s="12" t="n"/>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="16" t="n"/>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="16" t="n"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="13" t="n"/>
-      <c r="N12" s="16" t="n"/>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="16" t="n"/>
+      <c r="Q12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="R12" s="12" t="n"/>
       <c r="S12" s="13" t="n"/>
-      <c r="T12" s="16" t="n"/>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="n"/>
       <c r="V12" s="13" t="n"/>
     </row>
@@ -1371,55 +1399,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="11" t="n"/>
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="16" t="n"/>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="16" t="n"/>
+      <c r="H13" s="11" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="13" t="n"/>
-      <c r="K13" s="16" t="n"/>
+      <c r="K13" s="11" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="13" t="n"/>
-      <c r="N13" s="16" t="n"/>
+      <c r="N13" s="11" t="n"/>
       <c r="O13" s="12" t="n"/>
       <c r="P13" s="13" t="n"/>
-      <c r="Q13" s="16" t="n"/>
+      <c r="Q13" s="11" t="n"/>
       <c r="R13" s="12" t="n"/>
       <c r="S13" s="13" t="n"/>
-      <c r="T13" s="16" t="n"/>
+      <c r="T13" s="11" t="n"/>
       <c r="U13" s="12" t="n"/>
       <c r="V13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="18" t="n"/>
-      <c r="O14" s="19" t="n"/>
-      <c r="P14" s="20" t="n"/>
-      <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="19" t="n"/>
-      <c r="S14" s="20" t="n"/>
-      <c r="T14" s="18" t="n"/>
-      <c r="U14" s="19" t="n"/>
-      <c r="V14" s="20" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="17" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="17" t="n"/>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="14" t="n"/>
+      <c r="U14" s="17" t="n"/>
+      <c r="V14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1427,25 +1455,25 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n"/>
+      <c r="B15" s="19" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="E15" s="19" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="21" t="n"/>
+      <c r="H15" s="19" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="21" t="n"/>
+      <c r="K15" s="19" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="9" t="n"/>
-      <c r="N15" s="21" t="n"/>
+      <c r="N15" s="19" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="21" t="n"/>
+      <c r="Q15" s="19" t="n"/>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="9" t="n"/>
-      <c r="T15" s="21" t="n"/>
+      <c r="T15" s="19" t="n"/>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="9" t="n"/>
     </row>
@@ -1455,25 +1483,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="20" t="n"/>
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="16" t="n"/>
+      <c r="E16" s="20" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="16" t="n"/>
+      <c r="H16" s="20" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="16" t="n"/>
+      <c r="K16" s="20" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="n"/>
-      <c r="N16" s="16" t="n"/>
+      <c r="N16" s="20" t="n"/>
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="16" t="n"/>
+      <c r="Q16" s="20" t="n"/>
       <c r="R16" s="12" t="n"/>
       <c r="S16" s="13" t="n"/>
-      <c r="T16" s="16" t="n"/>
+      <c r="T16" s="20" t="n"/>
       <c r="U16" s="12" t="n"/>
       <c r="V16" s="13" t="n"/>
     </row>
@@ -1483,25 +1511,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="20" t="n"/>
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="16" t="n"/>
+      <c r="E17" s="20" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="16" t="n"/>
+      <c r="H17" s="20" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="13" t="n"/>
-      <c r="K17" s="16" t="n"/>
+      <c r="K17" s="20" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="n"/>
-      <c r="N17" s="16" t="n"/>
+      <c r="N17" s="20" t="n"/>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="16" t="n"/>
+      <c r="Q17" s="20" t="n"/>
       <c r="R17" s="12" t="n"/>
       <c r="S17" s="13" t="n"/>
-      <c r="T17" s="16" t="n"/>
+      <c r="T17" s="20" t="n"/>
       <c r="U17" s="12" t="n"/>
       <c r="V17" s="13" t="n"/>
     </row>
@@ -1511,25 +1539,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="20" t="n"/>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="16" t="n"/>
+      <c r="E18" s="20" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="16" t="n"/>
+      <c r="H18" s="20" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="16" t="n"/>
+      <c r="K18" s="20" t="n"/>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="n"/>
-      <c r="N18" s="16" t="n"/>
+      <c r="N18" s="20" t="n"/>
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="16" t="n"/>
+      <c r="Q18" s="20" t="n"/>
       <c r="R18" s="12" t="n"/>
       <c r="S18" s="13" t="n"/>
-      <c r="T18" s="16" t="n"/>
+      <c r="T18" s="20" t="n"/>
       <c r="U18" s="12" t="n"/>
       <c r="V18" s="13" t="n"/>
     </row>
@@ -1539,25 +1567,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="20" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="16" t="n"/>
+      <c r="E19" s="20" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="13" t="n"/>
-      <c r="H19" s="16" t="n"/>
+      <c r="H19" s="20" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="13" t="n"/>
-      <c r="K19" s="16" t="n"/>
+      <c r="K19" s="20" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="n"/>
-      <c r="N19" s="16" t="n"/>
+      <c r="N19" s="20" t="n"/>
       <c r="O19" s="12" t="n"/>
       <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="16" t="n"/>
+      <c r="Q19" s="20" t="n"/>
       <c r="R19" s="12" t="n"/>
       <c r="S19" s="13" t="n"/>
-      <c r="T19" s="16" t="n"/>
+      <c r="T19" s="20" t="n"/>
       <c r="U19" s="12" t="n"/>
       <c r="V19" s="13" t="n"/>
     </row>
@@ -1567,25 +1595,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
+      <c r="B20" s="20" t="n"/>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="16" t="n"/>
+      <c r="E20" s="20" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="16" t="n"/>
+      <c r="H20" s="20" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="16" t="n"/>
+      <c r="K20" s="20" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="n"/>
-      <c r="N20" s="16" t="n"/>
+      <c r="N20" s="20" t="n"/>
       <c r="O20" s="12" t="n"/>
       <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="16" t="n"/>
+      <c r="Q20" s="20" t="n"/>
       <c r="R20" s="12" t="n"/>
       <c r="S20" s="13" t="n"/>
-      <c r="T20" s="16" t="n"/>
+      <c r="T20" s="20" t="n"/>
       <c r="U20" s="12" t="n"/>
       <c r="V20" s="13" t="n"/>
     </row>
@@ -1595,25 +1623,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="20" t="n"/>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="20" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="13" t="n"/>
-      <c r="H21" s="16" t="n"/>
+      <c r="H21" s="20" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="13" t="n"/>
-      <c r="K21" s="16" t="n"/>
+      <c r="K21" s="20" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="n"/>
-      <c r="N21" s="16" t="n"/>
+      <c r="N21" s="20" t="n"/>
       <c r="O21" s="12" t="n"/>
       <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="16" t="n"/>
+      <c r="Q21" s="20" t="n"/>
       <c r="R21" s="12" t="n"/>
       <c r="S21" s="13" t="n"/>
-      <c r="T21" s="16" t="n"/>
+      <c r="T21" s="20" t="n"/>
       <c r="U21" s="12" t="n"/>
       <c r="V21" s="13" t="n"/>
     </row>
@@ -1623,25 +1651,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="20" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="16" t="n"/>
+      <c r="E22" s="20" t="n"/>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="13" t="n"/>
-      <c r="H22" s="16" t="n"/>
+      <c r="H22" s="20" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="16" t="n"/>
+      <c r="K22" s="20" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="n"/>
-      <c r="N22" s="16" t="n"/>
+      <c r="N22" s="20" t="n"/>
       <c r="O22" s="12" t="n"/>
       <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="16" t="n"/>
+      <c r="Q22" s="20" t="n"/>
       <c r="R22" s="12" t="n"/>
       <c r="S22" s="13" t="n"/>
-      <c r="T22" s="16" t="n"/>
+      <c r="T22" s="20" t="n"/>
       <c r="U22" s="12" t="n"/>
       <c r="V22" s="13" t="n"/>
     </row>
@@ -1651,25 +1679,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
+      <c r="B23" s="20" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="16" t="n"/>
+      <c r="E23" s="20" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="13" t="n"/>
-      <c r="H23" s="16" t="n"/>
+      <c r="H23" s="20" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="13" t="n"/>
-      <c r="K23" s="16" t="n"/>
+      <c r="K23" s="20" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="n"/>
-      <c r="N23" s="16" t="n"/>
+      <c r="N23" s="20" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="16" t="n"/>
+      <c r="Q23" s="20" t="n"/>
       <c r="R23" s="12" t="n"/>
       <c r="S23" s="13" t="n"/>
-      <c r="T23" s="16" t="n"/>
+      <c r="T23" s="20" t="n"/>
       <c r="U23" s="12" t="n"/>
       <c r="V23" s="13" t="n"/>
     </row>
@@ -1679,25 +1707,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="20" t="n"/>
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="16" t="n"/>
+      <c r="E24" s="20" t="n"/>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="13" t="n"/>
-      <c r="H24" s="16" t="n"/>
+      <c r="H24" s="20" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="16" t="n"/>
+      <c r="K24" s="20" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="n"/>
-      <c r="N24" s="16" t="n"/>
+      <c r="N24" s="20" t="n"/>
       <c r="O24" s="12" t="n"/>
       <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="16" t="n"/>
+      <c r="Q24" s="20" t="n"/>
       <c r="R24" s="12" t="n"/>
       <c r="S24" s="13" t="n"/>
-      <c r="T24" s="16" t="n"/>
+      <c r="T24" s="20" t="n"/>
       <c r="U24" s="12" t="n"/>
       <c r="V24" s="13" t="n"/>
     </row>
@@ -1707,55 +1735,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="20" t="n"/>
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="16" t="n"/>
+      <c r="E25" s="20" t="n"/>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="13" t="n"/>
-      <c r="H25" s="16" t="n"/>
+      <c r="H25" s="20" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="13" t="n"/>
-      <c r="K25" s="16" t="n"/>
+      <c r="K25" s="20" t="n"/>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="n"/>
-      <c r="N25" s="16" t="n"/>
+      <c r="N25" s="20" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="13" t="n"/>
-      <c r="Q25" s="16" t="n"/>
+      <c r="Q25" s="20" t="n"/>
       <c r="R25" s="12" t="n"/>
       <c r="S25" s="13" t="n"/>
-      <c r="T25" s="16" t="n"/>
+      <c r="T25" s="20" t="n"/>
       <c r="U25" s="12" t="n"/>
       <c r="V25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="I26" s="19" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="20" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="O26" s="19" t="n"/>
-      <c r="P26" s="20" t="n"/>
-      <c r="Q26" s="18" t="n"/>
-      <c r="R26" s="19" t="n"/>
-      <c r="S26" s="20" t="n"/>
-      <c r="T26" s="18" t="n"/>
-      <c r="U26" s="19" t="n"/>
-      <c r="V26" s="20" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="17" t="n"/>
+      <c r="P26" s="18" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="17" t="n"/>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="17" t="n"/>
+      <c r="V26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1763,25 +1791,25 @@
           <t>9:00</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n"/>
+      <c r="B27" s="19" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="21" t="n"/>
+      <c r="E27" s="19" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="21" t="n"/>
+      <c r="H27" s="19" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="21" t="n"/>
+      <c r="K27" s="19" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="9" t="n"/>
-      <c r="N27" s="21" t="n"/>
+      <c r="N27" s="19" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="21" t="n"/>
+      <c r="Q27" s="19" t="n"/>
       <c r="R27" s="8" t="n"/>
       <c r="S27" s="9" t="n"/>
-      <c r="T27" s="21" t="n"/>
+      <c r="T27" s="19" t="n"/>
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="9" t="n"/>
     </row>
@@ -1791,25 +1819,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
+      <c r="B28" s="20" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="16" t="n"/>
+      <c r="E28" s="20" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="13" t="n"/>
-      <c r="H28" s="16" t="n"/>
+      <c r="H28" s="20" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="16" t="n"/>
+      <c r="K28" s="20" t="n"/>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="13" t="n"/>
-      <c r="N28" s="16" t="n"/>
+      <c r="N28" s="20" t="n"/>
       <c r="O28" s="12" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="16" t="n"/>
+      <c r="Q28" s="20" t="n"/>
       <c r="R28" s="12" t="n"/>
       <c r="S28" s="13" t="n"/>
-      <c r="T28" s="16" t="n"/>
+      <c r="T28" s="20" t="n"/>
       <c r="U28" s="12" t="n"/>
       <c r="V28" s="13" t="n"/>
     </row>
@@ -1819,25 +1847,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="20" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="16" t="n"/>
+      <c r="E29" s="20" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="13" t="n"/>
-      <c r="H29" s="16" t="n"/>
+      <c r="H29" s="20" t="n"/>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="13" t="n"/>
-      <c r="K29" s="16" t="n"/>
+      <c r="K29" s="20" t="n"/>
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="13" t="n"/>
-      <c r="N29" s="16" t="n"/>
+      <c r="N29" s="20" t="n"/>
       <c r="O29" s="12" t="n"/>
       <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="16" t="n"/>
+      <c r="Q29" s="20" t="n"/>
       <c r="R29" s="12" t="n"/>
       <c r="S29" s="13" t="n"/>
-      <c r="T29" s="16" t="n"/>
+      <c r="T29" s="20" t="n"/>
       <c r="U29" s="12" t="n"/>
       <c r="V29" s="13" t="n"/>
     </row>
@@ -1847,25 +1875,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
+      <c r="B30" s="20" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="16" t="n"/>
+      <c r="E30" s="20" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="13" t="n"/>
-      <c r="H30" s="16" t="n"/>
+      <c r="H30" s="20" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="16" t="n"/>
+      <c r="K30" s="20" t="n"/>
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="13" t="n"/>
-      <c r="N30" s="16" t="n"/>
+      <c r="N30" s="20" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="16" t="n"/>
+      <c r="Q30" s="20" t="n"/>
       <c r="R30" s="12" t="n"/>
       <c r="S30" s="13" t="n"/>
-      <c r="T30" s="16" t="n"/>
+      <c r="T30" s="20" t="n"/>
       <c r="U30" s="12" t="n"/>
       <c r="V30" s="13" t="n"/>
     </row>
@@ -1875,25 +1903,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="20" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="16" t="n"/>
+      <c r="E31" s="20" t="n"/>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="13" t="n"/>
-      <c r="H31" s="16" t="n"/>
+      <c r="H31" s="20" t="n"/>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="13" t="n"/>
-      <c r="K31" s="16" t="n"/>
+      <c r="K31" s="20" t="n"/>
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="13" t="n"/>
-      <c r="N31" s="16" t="n"/>
+      <c r="N31" s="20" t="n"/>
       <c r="O31" s="12" t="n"/>
       <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="16" t="n"/>
+      <c r="Q31" s="20" t="n"/>
       <c r="R31" s="12" t="n"/>
       <c r="S31" s="13" t="n"/>
-      <c r="T31" s="16" t="n"/>
+      <c r="T31" s="20" t="n"/>
       <c r="U31" s="12" t="n"/>
       <c r="V31" s="13" t="n"/>
     </row>
@@ -1903,25 +1931,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="20" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="16" t="n"/>
+      <c r="E32" s="20" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="13" t="n"/>
-      <c r="H32" s="16" t="n"/>
+      <c r="H32" s="20" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="16" t="n"/>
+      <c r="K32" s="20" t="n"/>
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="13" t="n"/>
-      <c r="N32" s="16" t="n"/>
+      <c r="N32" s="20" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="16" t="n"/>
+      <c r="Q32" s="20" t="n"/>
       <c r="R32" s="12" t="n"/>
       <c r="S32" s="13" t="n"/>
-      <c r="T32" s="16" t="n"/>
+      <c r="T32" s="20" t="n"/>
       <c r="U32" s="12" t="n"/>
       <c r="V32" s="13" t="n"/>
     </row>
@@ -1931,25 +1959,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="20" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="16" t="n"/>
+      <c r="E33" s="20" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="13" t="n"/>
-      <c r="H33" s="16" t="n"/>
+      <c r="H33" s="20" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="13" t="n"/>
-      <c r="K33" s="16" t="n"/>
+      <c r="K33" s="20" t="n"/>
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="13" t="n"/>
-      <c r="N33" s="16" t="n"/>
+      <c r="N33" s="20" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="16" t="n"/>
+      <c r="Q33" s="20" t="n"/>
       <c r="R33" s="12" t="n"/>
       <c r="S33" s="13" t="n"/>
-      <c r="T33" s="16" t="n"/>
+      <c r="T33" s="20" t="n"/>
       <c r="U33" s="12" t="n"/>
       <c r="V33" s="13" t="n"/>
     </row>
@@ -1959,25 +1987,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
+      <c r="B34" s="20" t="n"/>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="16" t="n"/>
+      <c r="E34" s="20" t="n"/>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="13" t="n"/>
-      <c r="H34" s="16" t="n"/>
+      <c r="H34" s="20" t="n"/>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="16" t="n"/>
+      <c r="K34" s="20" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="13" t="n"/>
-      <c r="N34" s="16" t="n"/>
+      <c r="N34" s="20" t="n"/>
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="16" t="n"/>
+      <c r="Q34" s="20" t="n"/>
       <c r="R34" s="12" t="n"/>
       <c r="S34" s="13" t="n"/>
-      <c r="T34" s="16" t="n"/>
+      <c r="T34" s="20" t="n"/>
       <c r="U34" s="12" t="n"/>
       <c r="V34" s="13" t="n"/>
     </row>
@@ -1987,25 +2015,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="20" t="n"/>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="16" t="n"/>
+      <c r="E35" s="20" t="n"/>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="13" t="n"/>
-      <c r="H35" s="16" t="n"/>
+      <c r="H35" s="20" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="13" t="n"/>
-      <c r="K35" s="16" t="n"/>
+      <c r="K35" s="20" t="n"/>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="13" t="n"/>
-      <c r="N35" s="16" t="n"/>
+      <c r="N35" s="20" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="13" t="n"/>
-      <c r="Q35" s="16" t="n"/>
+      <c r="Q35" s="20" t="n"/>
       <c r="R35" s="12" t="n"/>
       <c r="S35" s="13" t="n"/>
-      <c r="T35" s="16" t="n"/>
+      <c r="T35" s="20" t="n"/>
       <c r="U35" s="12" t="n"/>
       <c r="V35" s="13" t="n"/>
     </row>
@@ -2015,25 +2043,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="20" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="16" t="n"/>
+      <c r="E36" s="20" t="n"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="13" t="n"/>
-      <c r="H36" s="16" t="n"/>
+      <c r="H36" s="20" t="n"/>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="16" t="n"/>
+      <c r="K36" s="20" t="n"/>
       <c r="L36" s="12" t="n"/>
       <c r="M36" s="13" t="n"/>
-      <c r="N36" s="16" t="n"/>
+      <c r="N36" s="20" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="16" t="n"/>
+      <c r="Q36" s="20" t="n"/>
       <c r="R36" s="12" t="n"/>
       <c r="S36" s="13" t="n"/>
-      <c r="T36" s="16" t="n"/>
+      <c r="T36" s="20" t="n"/>
       <c r="U36" s="12" t="n"/>
       <c r="V36" s="13" t="n"/>
     </row>
@@ -2043,55 +2071,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="20" t="n"/>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="16" t="n"/>
+      <c r="E37" s="20" t="n"/>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="13" t="n"/>
-      <c r="H37" s="16" t="n"/>
+      <c r="H37" s="20" t="n"/>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="13" t="n"/>
-      <c r="K37" s="16" t="n"/>
+      <c r="K37" s="20" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="13" t="n"/>
-      <c r="N37" s="16" t="n"/>
+      <c r="N37" s="20" t="n"/>
       <c r="O37" s="12" t="n"/>
       <c r="P37" s="13" t="n"/>
-      <c r="Q37" s="16" t="n"/>
+      <c r="Q37" s="20" t="n"/>
       <c r="R37" s="12" t="n"/>
       <c r="S37" s="13" t="n"/>
-      <c r="T37" s="16" t="n"/>
+      <c r="T37" s="20" t="n"/>
       <c r="U37" s="12" t="n"/>
       <c r="V37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="20" t="n"/>
-      <c r="H38" s="18" t="n"/>
-      <c r="I38" s="19" t="n"/>
-      <c r="J38" s="20" t="n"/>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="19" t="n"/>
-      <c r="M38" s="20" t="n"/>
-      <c r="N38" s="18" t="n"/>
-      <c r="O38" s="19" t="n"/>
-      <c r="P38" s="20" t="n"/>
-      <c r="Q38" s="18" t="n"/>
-      <c r="R38" s="19" t="n"/>
-      <c r="S38" s="20" t="n"/>
-      <c r="T38" s="18" t="n"/>
-      <c r="U38" s="19" t="n"/>
-      <c r="V38" s="20" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="21" t="n"/>
+      <c r="L38" s="17" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="21" t="n"/>
+      <c r="O38" s="17" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="21" t="n"/>
+      <c r="R38" s="17" t="n"/>
+      <c r="S38" s="18" t="n"/>
+      <c r="T38" s="21" t="n"/>
+      <c r="U38" s="17" t="n"/>
+      <c r="V38" s="18" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2099,25 +2127,25 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n"/>
+      <c r="B39" s="19" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="21" t="n"/>
+      <c r="E39" s="19" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="21" t="n"/>
+      <c r="H39" s="19" t="n"/>
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="21" t="n"/>
+      <c r="K39" s="19" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="9" t="n"/>
-      <c r="N39" s="21" t="n"/>
+      <c r="N39" s="19" t="n"/>
       <c r="O39" s="8" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="21" t="n"/>
+      <c r="Q39" s="19" t="n"/>
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="9" t="n"/>
-      <c r="T39" s="21" t="n"/>
+      <c r="T39" s="19" t="n"/>
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="9" t="n"/>
     </row>
@@ -2127,25 +2155,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="20" t="n"/>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="16" t="n"/>
+      <c r="E40" s="20" t="n"/>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="13" t="n"/>
-      <c r="H40" s="16" t="n"/>
+      <c r="H40" s="20" t="n"/>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="16" t="n"/>
+      <c r="K40" s="20" t="n"/>
       <c r="L40" s="12" t="n"/>
       <c r="M40" s="13" t="n"/>
-      <c r="N40" s="16" t="n"/>
+      <c r="N40" s="20" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="16" t="n"/>
+      <c r="Q40" s="20" t="n"/>
       <c r="R40" s="12" t="n"/>
       <c r="S40" s="13" t="n"/>
-      <c r="T40" s="16" t="n"/>
+      <c r="T40" s="20" t="n"/>
       <c r="U40" s="12" t="n"/>
       <c r="V40" s="13" t="n"/>
     </row>
@@ -2155,25 +2183,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
+      <c r="B41" s="20" t="n"/>
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="16" t="n"/>
+      <c r="E41" s="20" t="n"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="13" t="n"/>
-      <c r="H41" s="16" t="n"/>
+      <c r="H41" s="20" t="n"/>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="13" t="n"/>
-      <c r="K41" s="16" t="n"/>
+      <c r="K41" s="20" t="n"/>
       <c r="L41" s="12" t="n"/>
       <c r="M41" s="13" t="n"/>
-      <c r="N41" s="16" t="n"/>
+      <c r="N41" s="20" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="13" t="n"/>
-      <c r="Q41" s="16" t="n"/>
+      <c r="Q41" s="20" t="n"/>
       <c r="R41" s="12" t="n"/>
       <c r="S41" s="13" t="n"/>
-      <c r="T41" s="16" t="n"/>
+      <c r="T41" s="20" t="n"/>
       <c r="U41" s="12" t="n"/>
       <c r="V41" s="13" t="n"/>
     </row>
@@ -2183,25 +2211,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
+      <c r="B42" s="20" t="n"/>
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="16" t="n"/>
+      <c r="E42" s="20" t="n"/>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="13" t="n"/>
-      <c r="H42" s="16" t="n"/>
+      <c r="H42" s="20" t="n"/>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="16" t="n"/>
+      <c r="K42" s="20" t="n"/>
       <c r="L42" s="12" t="n"/>
       <c r="M42" s="13" t="n"/>
-      <c r="N42" s="16" t="n"/>
+      <c r="N42" s="20" t="n"/>
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="16" t="n"/>
+      <c r="Q42" s="20" t="n"/>
       <c r="R42" s="12" t="n"/>
       <c r="S42" s="13" t="n"/>
-      <c r="T42" s="16" t="n"/>
+      <c r="T42" s="20" t="n"/>
       <c r="U42" s="12" t="n"/>
       <c r="V42" s="13" t="n"/>
     </row>
@@ -2211,25 +2239,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
+      <c r="B43" s="20" t="n"/>
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="16" t="n"/>
+      <c r="E43" s="20" t="n"/>
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="13" t="n"/>
-      <c r="H43" s="16" t="n"/>
+      <c r="H43" s="20" t="n"/>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="13" t="n"/>
-      <c r="K43" s="16" t="n"/>
+      <c r="K43" s="20" t="n"/>
       <c r="L43" s="12" t="n"/>
       <c r="M43" s="13" t="n"/>
-      <c r="N43" s="16" t="n"/>
+      <c r="N43" s="20" t="n"/>
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="13" t="n"/>
-      <c r="Q43" s="16" t="n"/>
+      <c r="Q43" s="20" t="n"/>
       <c r="R43" s="12" t="n"/>
       <c r="S43" s="13" t="n"/>
-      <c r="T43" s="16" t="n"/>
+      <c r="T43" s="20" t="n"/>
       <c r="U43" s="12" t="n"/>
       <c r="V43" s="13" t="n"/>
     </row>
@@ -2239,25 +2267,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
+      <c r="B44" s="20" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="16" t="n"/>
+      <c r="E44" s="20" t="n"/>
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="13" t="n"/>
-      <c r="H44" s="16" t="n"/>
+      <c r="H44" s="20" t="n"/>
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="16" t="n"/>
+      <c r="K44" s="20" t="n"/>
       <c r="L44" s="12" t="n"/>
       <c r="M44" s="13" t="n"/>
-      <c r="N44" s="16" t="n"/>
+      <c r="N44" s="20" t="n"/>
       <c r="O44" s="12" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="16" t="n"/>
+      <c r="Q44" s="20" t="n"/>
       <c r="R44" s="12" t="n"/>
       <c r="S44" s="13" t="n"/>
-      <c r="T44" s="16" t="n"/>
+      <c r="T44" s="20" t="n"/>
       <c r="U44" s="12" t="n"/>
       <c r="V44" s="13" t="n"/>
     </row>
@@ -2267,25 +2295,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
+      <c r="B45" s="20" t="n"/>
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="16" t="n"/>
+      <c r="E45" s="20" t="n"/>
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="13" t="n"/>
-      <c r="H45" s="16" t="n"/>
+      <c r="H45" s="20" t="n"/>
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="13" t="n"/>
-      <c r="K45" s="16" t="n"/>
+      <c r="K45" s="20" t="n"/>
       <c r="L45" s="12" t="n"/>
       <c r="M45" s="13" t="n"/>
-      <c r="N45" s="16" t="n"/>
+      <c r="N45" s="20" t="n"/>
       <c r="O45" s="12" t="n"/>
       <c r="P45" s="13" t="n"/>
-      <c r="Q45" s="16" t="n"/>
+      <c r="Q45" s="20" t="n"/>
       <c r="R45" s="12" t="n"/>
       <c r="S45" s="13" t="n"/>
-      <c r="T45" s="16" t="n"/>
+      <c r="T45" s="20" t="n"/>
       <c r="U45" s="12" t="n"/>
       <c r="V45" s="13" t="n"/>
     </row>
@@ -2295,25 +2323,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="20" t="n"/>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="16" t="n"/>
+      <c r="E46" s="20" t="n"/>
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="13" t="n"/>
-      <c r="H46" s="16" t="n"/>
+      <c r="H46" s="20" t="n"/>
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="16" t="n"/>
+      <c r="K46" s="20" t="n"/>
       <c r="L46" s="12" t="n"/>
       <c r="M46" s="13" t="n"/>
-      <c r="N46" s="16" t="n"/>
+      <c r="N46" s="20" t="n"/>
       <c r="O46" s="12" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="16" t="n"/>
+      <c r="Q46" s="20" t="n"/>
       <c r="R46" s="12" t="n"/>
       <c r="S46" s="13" t="n"/>
-      <c r="T46" s="16" t="n"/>
+      <c r="T46" s="20" t="n"/>
       <c r="U46" s="12" t="n"/>
       <c r="V46" s="13" t="n"/>
     </row>
@@ -2323,25 +2351,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
+      <c r="B47" s="20" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="16" t="n"/>
+      <c r="E47" s="20" t="n"/>
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="13" t="n"/>
-      <c r="H47" s="16" t="n"/>
+      <c r="H47" s="20" t="n"/>
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="13" t="n"/>
-      <c r="K47" s="16" t="n"/>
+      <c r="K47" s="20" t="n"/>
       <c r="L47" s="12" t="n"/>
       <c r="M47" s="13" t="n"/>
-      <c r="N47" s="16" t="n"/>
+      <c r="N47" s="20" t="n"/>
       <c r="O47" s="12" t="n"/>
       <c r="P47" s="13" t="n"/>
-      <c r="Q47" s="16" t="n"/>
+      <c r="Q47" s="20" t="n"/>
       <c r="R47" s="12" t="n"/>
       <c r="S47" s="13" t="n"/>
-      <c r="T47" s="16" t="n"/>
+      <c r="T47" s="20" t="n"/>
       <c r="U47" s="12" t="n"/>
       <c r="V47" s="13" t="n"/>
     </row>
@@ -2351,25 +2379,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
+      <c r="B48" s="20" t="n"/>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="16" t="n"/>
+      <c r="E48" s="20" t="n"/>
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="13" t="n"/>
-      <c r="H48" s="16" t="n"/>
+      <c r="H48" s="20" t="n"/>
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="16" t="n"/>
+      <c r="K48" s="20" t="n"/>
       <c r="L48" s="12" t="n"/>
       <c r="M48" s="13" t="n"/>
-      <c r="N48" s="16" t="n"/>
+      <c r="N48" s="20" t="n"/>
       <c r="O48" s="12" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="16" t="n"/>
+      <c r="Q48" s="20" t="n"/>
       <c r="R48" s="12" t="n"/>
       <c r="S48" s="13" t="n"/>
-      <c r="T48" s="16" t="n"/>
+      <c r="T48" s="20" t="n"/>
       <c r="U48" s="12" t="n"/>
       <c r="V48" s="13" t="n"/>
     </row>
@@ -2379,55 +2407,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="20" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="16" t="n"/>
+      <c r="E49" s="20" t="n"/>
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="13" t="n"/>
-      <c r="H49" s="16" t="n"/>
+      <c r="H49" s="20" t="n"/>
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="13" t="n"/>
-      <c r="K49" s="16" t="n"/>
+      <c r="K49" s="20" t="n"/>
       <c r="L49" s="12" t="n"/>
       <c r="M49" s="13" t="n"/>
-      <c r="N49" s="16" t="n"/>
+      <c r="N49" s="20" t="n"/>
       <c r="O49" s="12" t="n"/>
       <c r="P49" s="13" t="n"/>
-      <c r="Q49" s="16" t="n"/>
+      <c r="Q49" s="20" t="n"/>
       <c r="R49" s="12" t="n"/>
       <c r="S49" s="13" t="n"/>
-      <c r="T49" s="16" t="n"/>
+      <c r="T49" s="20" t="n"/>
       <c r="U49" s="12" t="n"/>
       <c r="V49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="19" t="n"/>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="18" t="n"/>
-      <c r="I50" s="19" t="n"/>
-      <c r="J50" s="20" t="n"/>
-      <c r="K50" s="18" t="n"/>
-      <c r="L50" s="19" t="n"/>
-      <c r="M50" s="20" t="n"/>
-      <c r="N50" s="18" t="n"/>
-      <c r="O50" s="19" t="n"/>
-      <c r="P50" s="20" t="n"/>
-      <c r="Q50" s="18" t="n"/>
-      <c r="R50" s="19" t="n"/>
-      <c r="S50" s="20" t="n"/>
-      <c r="T50" s="18" t="n"/>
-      <c r="U50" s="19" t="n"/>
-      <c r="V50" s="20" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="21" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="21" t="n"/>
+      <c r="L50" s="17" t="n"/>
+      <c r="M50" s="18" t="n"/>
+      <c r="N50" s="21" t="n"/>
+      <c r="O50" s="17" t="n"/>
+      <c r="P50" s="18" t="n"/>
+      <c r="Q50" s="21" t="n"/>
+      <c r="R50" s="17" t="n"/>
+      <c r="S50" s="18" t="n"/>
+      <c r="T50" s="21" t="n"/>
+      <c r="U50" s="17" t="n"/>
+      <c r="V50" s="18" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2435,10 +2463,10 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n"/>
+      <c r="B51" s="19" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="21" t="n"/>
+      <c r="E51" s="19" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="9" t="n"/>
       <c r="H51" s="7" t="inlineStr">
@@ -2448,7 +2476,7 @@
       </c>
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="21" t="n"/>
+      <c r="K51" s="19" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="7" t="inlineStr">
@@ -2479,16 +2507,16 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
+      <c r="B52" s="20" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="13" t="n"/>
-      <c r="E52" s="16" t="n"/>
+      <c r="E52" s="20" t="n"/>
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="13" t="n"/>
       <c r="H52" s="11" t="n"/>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="16" t="n"/>
+      <c r="K52" s="20" t="n"/>
       <c r="L52" s="12" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="11" t="n"/>
@@ -2507,16 +2535,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n"/>
+      <c r="B53" s="20" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="16" t="n"/>
+      <c r="E53" s="20" t="n"/>
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="13" t="n"/>
       <c r="H53" s="14" t="n"/>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="13" t="n"/>
-      <c r="K53" s="16" t="n"/>
+      <c r="K53" s="20" t="n"/>
       <c r="L53" s="12" t="n"/>
       <c r="M53" s="13" t="n"/>
       <c r="N53" s="14" t="n"/>
@@ -2549,7 +2577,7 @@
       </c>
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="13" t="n"/>
-      <c r="H54" s="16" t="n"/>
+      <c r="H54" s="20" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="15" t="inlineStr">
@@ -2559,7 +2587,7 @@
       </c>
       <c r="L54" s="12" t="n"/>
       <c r="M54" s="13" t="n"/>
-      <c r="N54" s="16" t="n"/>
+      <c r="N54" s="20" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="15" t="inlineStr">
@@ -2569,7 +2597,7 @@
       </c>
       <c r="R54" s="12" t="n"/>
       <c r="S54" s="13" t="n"/>
-      <c r="T54" s="16" t="n"/>
+      <c r="T54" s="20" t="n"/>
       <c r="U54" s="12" t="n"/>
       <c r="V54" s="13" t="n"/>
     </row>
@@ -2585,19 +2613,19 @@
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="13" t="n"/>
-      <c r="H55" s="16" t="n"/>
+      <c r="H55" s="20" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13" t="n"/>
       <c r="K55" s="11" t="n"/>
       <c r="L55" s="12" t="n"/>
       <c r="M55" s="13" t="n"/>
-      <c r="N55" s="16" t="n"/>
+      <c r="N55" s="20" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="13" t="n"/>
       <c r="Q55" s="11" t="n"/>
       <c r="R55" s="12" t="n"/>
       <c r="S55" s="13" t="n"/>
-      <c r="T55" s="16" t="n"/>
+      <c r="T55" s="20" t="n"/>
       <c r="U55" s="12" t="n"/>
       <c r="V55" s="13" t="n"/>
     </row>
@@ -2613,19 +2641,19 @@
       <c r="E56" s="14" t="n"/>
       <c r="F56" s="12" t="n"/>
       <c r="G56" s="13" t="n"/>
-      <c r="H56" s="16" t="n"/>
+      <c r="H56" s="20" t="n"/>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="12" t="n"/>
       <c r="M56" s="13" t="n"/>
-      <c r="N56" s="16" t="n"/>
+      <c r="N56" s="20" t="n"/>
       <c r="O56" s="12" t="n"/>
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="14" t="n"/>
       <c r="R56" s="12" t="n"/>
       <c r="S56" s="13" t="n"/>
-      <c r="T56" s="16" t="n"/>
+      <c r="T56" s="20" t="n"/>
       <c r="U56" s="12" t="n"/>
       <c r="V56" s="13" t="n"/>
     </row>
@@ -2635,7 +2663,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n"/>
+      <c r="B57" s="20" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="13" t="n"/>
       <c r="E57" s="15" t="inlineStr">
@@ -2652,7 +2680,11 @@
       </c>
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="13" t="n"/>
-      <c r="K57" s="16" t="n"/>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>鈴木信子：掃除</t>
+        </is>
+      </c>
       <c r="L57" s="12" t="n"/>
       <c r="M57" s="13" t="n"/>
       <c r="N57" s="15" t="inlineStr">
@@ -2683,7 +2715,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n"/>
+      <c r="B58" s="20" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="13" t="n"/>
       <c r="E58" s="11" t="n"/>
@@ -2692,7 +2724,7 @@
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="16" t="n"/>
+      <c r="K58" s="11" t="n"/>
       <c r="L58" s="12" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="11" t="n"/>
@@ -2711,7 +2743,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n"/>
+      <c r="B59" s="20" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
       <c r="E59" s="14" t="n"/>
@@ -2720,7 +2752,7 @@
       <c r="H59" s="14" t="n"/>
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="13" t="n"/>
-      <c r="K59" s="16" t="n"/>
+      <c r="K59" s="11" t="n"/>
       <c r="L59" s="12" t="n"/>
       <c r="M59" s="13" t="n"/>
       <c r="N59" s="14" t="n"/>
@@ -2739,25 +2771,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B60" s="16" t="n"/>
+      <c r="B60" s="20" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="16" t="n"/>
+      <c r="E60" s="20" t="n"/>
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="16" t="n"/>
+      <c r="H60" s="20" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="16" t="n"/>
+      <c r="K60" s="11" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="N60" s="16" t="n"/>
+      <c r="N60" s="20" t="n"/>
       <c r="O60" s="12" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="16" t="n"/>
+      <c r="Q60" s="20" t="n"/>
       <c r="R60" s="12" t="n"/>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="16" t="n"/>
+      <c r="T60" s="20" t="n"/>
       <c r="U60" s="12" t="n"/>
       <c r="V60" s="13" t="n"/>
     </row>
@@ -2767,55 +2799,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B61" s="16" t="n"/>
+      <c r="B61" s="20" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
-      <c r="E61" s="16" t="n"/>
+      <c r="E61" s="20" t="n"/>
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="16" t="n"/>
+      <c r="H61" s="20" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
-      <c r="K61" s="16" t="n"/>
+      <c r="K61" s="14" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
-      <c r="N61" s="16" t="n"/>
+      <c r="N61" s="20" t="n"/>
       <c r="O61" s="12" t="n"/>
       <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="16" t="n"/>
+      <c r="Q61" s="20" t="n"/>
       <c r="R61" s="12" t="n"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="16" t="n"/>
+      <c r="T61" s="20" t="n"/>
       <c r="U61" s="12" t="n"/>
       <c r="V61" s="13" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="20" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="20" t="n"/>
-      <c r="H62" s="18" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="20" t="n"/>
-      <c r="K62" s="18" t="n"/>
-      <c r="L62" s="19" t="n"/>
-      <c r="M62" s="20" t="n"/>
-      <c r="N62" s="18" t="n"/>
-      <c r="O62" s="19" t="n"/>
-      <c r="P62" s="20" t="n"/>
-      <c r="Q62" s="18" t="n"/>
-      <c r="R62" s="19" t="n"/>
-      <c r="S62" s="20" t="n"/>
-      <c r="T62" s="18" t="n"/>
-      <c r="U62" s="19" t="n"/>
-      <c r="V62" s="20" t="n"/>
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="21" t="n"/>
+      <c r="F62" s="17" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="17" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="21" t="n"/>
+      <c r="L62" s="17" t="n"/>
+      <c r="M62" s="18" t="n"/>
+      <c r="N62" s="21" t="n"/>
+      <c r="O62" s="17" t="n"/>
+      <c r="P62" s="18" t="n"/>
+      <c r="Q62" s="21" t="n"/>
+      <c r="R62" s="17" t="n"/>
+      <c r="S62" s="18" t="n"/>
+      <c r="T62" s="21" t="n"/>
+      <c r="U62" s="17" t="n"/>
+      <c r="V62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -2823,25 +2855,25 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B63" s="21" t="n"/>
+      <c r="B63" s="19" t="n"/>
       <c r="C63" s="22" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="21" t="n"/>
+      <c r="E63" s="19" t="n"/>
       <c r="F63" s="22" t="n"/>
       <c r="G63" s="9" t="n"/>
-      <c r="H63" s="21" t="n"/>
+      <c r="H63" s="19" t="n"/>
       <c r="I63" s="22" t="n"/>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="21" t="n"/>
+      <c r="K63" s="19" t="n"/>
       <c r="L63" s="22" t="n"/>
       <c r="M63" s="9" t="n"/>
-      <c r="N63" s="21" t="n"/>
+      <c r="N63" s="19" t="n"/>
       <c r="O63" s="22" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="21" t="n"/>
+      <c r="Q63" s="19" t="n"/>
       <c r="R63" s="22" t="n"/>
       <c r="S63" s="9" t="n"/>
-      <c r="T63" s="21" t="n"/>
+      <c r="T63" s="19" t="n"/>
       <c r="U63" s="22" t="n"/>
       <c r="V63" s="9" t="n"/>
     </row>
@@ -2851,25 +2883,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B64" s="16" t="n"/>
+      <c r="B64" s="20" t="n"/>
       <c r="C64" s="23" t="n"/>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="16" t="n"/>
+      <c r="E64" s="20" t="n"/>
       <c r="F64" s="23" t="n"/>
       <c r="G64" s="13" t="n"/>
-      <c r="H64" s="16" t="n"/>
+      <c r="H64" s="20" t="n"/>
       <c r="I64" s="23" t="n"/>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="16" t="n"/>
+      <c r="K64" s="20" t="n"/>
       <c r="L64" s="23" t="n"/>
       <c r="M64" s="13" t="n"/>
-      <c r="N64" s="16" t="n"/>
+      <c r="N64" s="20" t="n"/>
       <c r="O64" s="23" t="n"/>
       <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="16" t="n"/>
+      <c r="Q64" s="20" t="n"/>
       <c r="R64" s="23" t="n"/>
       <c r="S64" s="13" t="n"/>
-      <c r="T64" s="16" t="n"/>
+      <c r="T64" s="20" t="n"/>
       <c r="U64" s="23" t="n"/>
       <c r="V64" s="13" t="n"/>
     </row>
@@ -2879,25 +2911,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n"/>
+      <c r="B65" s="20" t="n"/>
       <c r="C65" s="23" t="n"/>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="16" t="n"/>
+      <c r="E65" s="20" t="n"/>
       <c r="F65" s="23" t="n"/>
       <c r="G65" s="13" t="n"/>
-      <c r="H65" s="16" t="n"/>
+      <c r="H65" s="20" t="n"/>
       <c r="I65" s="23" t="n"/>
       <c r="J65" s="13" t="n"/>
-      <c r="K65" s="16" t="n"/>
+      <c r="K65" s="20" t="n"/>
       <c r="L65" s="23" t="n"/>
       <c r="M65" s="13" t="n"/>
-      <c r="N65" s="16" t="n"/>
+      <c r="N65" s="20" t="n"/>
       <c r="O65" s="23" t="n"/>
       <c r="P65" s="13" t="n"/>
-      <c r="Q65" s="16" t="n"/>
+      <c r="Q65" s="20" t="n"/>
       <c r="R65" s="23" t="n"/>
       <c r="S65" s="13" t="n"/>
-      <c r="T65" s="16" t="n"/>
+      <c r="T65" s="20" t="n"/>
       <c r="U65" s="23" t="n"/>
       <c r="V65" s="13" t="n"/>
     </row>
@@ -2907,25 +2939,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B66" s="16" t="n"/>
+      <c r="B66" s="20" t="n"/>
       <c r="C66" s="23" t="n"/>
       <c r="D66" s="13" t="n"/>
-      <c r="E66" s="16" t="n"/>
+      <c r="E66" s="20" t="n"/>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="13" t="n"/>
-      <c r="H66" s="16" t="n"/>
+      <c r="H66" s="20" t="n"/>
       <c r="I66" s="23" t="n"/>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="16" t="n"/>
+      <c r="K66" s="20" t="n"/>
       <c r="L66" s="23" t="n"/>
       <c r="M66" s="13" t="n"/>
-      <c r="N66" s="16" t="n"/>
+      <c r="N66" s="20" t="n"/>
       <c r="O66" s="23" t="n"/>
       <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="16" t="n"/>
+      <c r="Q66" s="20" t="n"/>
       <c r="R66" s="23" t="n"/>
       <c r="S66" s="13" t="n"/>
-      <c r="T66" s="16" t="n"/>
+      <c r="T66" s="20" t="n"/>
       <c r="U66" s="23" t="n"/>
       <c r="V66" s="13" t="n"/>
     </row>
@@ -2935,25 +2967,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B67" s="16" t="n"/>
+      <c r="B67" s="20" t="n"/>
       <c r="C67" s="23" t="n"/>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="16" t="n"/>
+      <c r="E67" s="20" t="n"/>
       <c r="F67" s="23" t="n"/>
       <c r="G67" s="13" t="n"/>
-      <c r="H67" s="16" t="n"/>
+      <c r="H67" s="20" t="n"/>
       <c r="I67" s="23" t="n"/>
       <c r="J67" s="13" t="n"/>
-      <c r="K67" s="16" t="n"/>
+      <c r="K67" s="20" t="n"/>
       <c r="L67" s="23" t="n"/>
       <c r="M67" s="13" t="n"/>
-      <c r="N67" s="16" t="n"/>
+      <c r="N67" s="20" t="n"/>
       <c r="O67" s="23" t="n"/>
       <c r="P67" s="13" t="n"/>
-      <c r="Q67" s="16" t="n"/>
+      <c r="Q67" s="20" t="n"/>
       <c r="R67" s="23" t="n"/>
       <c r="S67" s="13" t="n"/>
-      <c r="T67" s="16" t="n"/>
+      <c r="T67" s="20" t="n"/>
       <c r="U67" s="23" t="n"/>
       <c r="V67" s="13" t="n"/>
     </row>
@@ -2963,25 +2995,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n"/>
+      <c r="B68" s="20" t="n"/>
       <c r="C68" s="23" t="n"/>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="16" t="n"/>
+      <c r="E68" s="20" t="n"/>
       <c r="F68" s="23" t="n"/>
       <c r="G68" s="13" t="n"/>
-      <c r="H68" s="16" t="n"/>
+      <c r="H68" s="20" t="n"/>
       <c r="I68" s="23" t="n"/>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="16" t="n"/>
+      <c r="K68" s="20" t="n"/>
       <c r="L68" s="23" t="n"/>
       <c r="M68" s="13" t="n"/>
-      <c r="N68" s="16" t="n"/>
+      <c r="N68" s="20" t="n"/>
       <c r="O68" s="23" t="n"/>
       <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="16" t="n"/>
+      <c r="Q68" s="20" t="n"/>
       <c r="R68" s="23" t="n"/>
       <c r="S68" s="13" t="n"/>
-      <c r="T68" s="16" t="n"/>
+      <c r="T68" s="20" t="n"/>
       <c r="U68" s="23" t="n"/>
       <c r="V68" s="13" t="n"/>
     </row>
@@ -2991,25 +3023,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n"/>
+      <c r="B69" s="20" t="n"/>
       <c r="C69" s="23" t="n"/>
       <c r="D69" s="13" t="n"/>
-      <c r="E69" s="16" t="n"/>
+      <c r="E69" s="20" t="n"/>
       <c r="F69" s="23" t="n"/>
       <c r="G69" s="13" t="n"/>
-      <c r="H69" s="16" t="n"/>
+      <c r="H69" s="20" t="n"/>
       <c r="I69" s="23" t="n"/>
       <c r="J69" s="13" t="n"/>
-      <c r="K69" s="16" t="n"/>
+      <c r="K69" s="20" t="n"/>
       <c r="L69" s="23" t="n"/>
       <c r="M69" s="13" t="n"/>
-      <c r="N69" s="16" t="n"/>
+      <c r="N69" s="20" t="n"/>
       <c r="O69" s="23" t="n"/>
       <c r="P69" s="13" t="n"/>
-      <c r="Q69" s="16" t="n"/>
+      <c r="Q69" s="20" t="n"/>
       <c r="R69" s="23" t="n"/>
       <c r="S69" s="13" t="n"/>
-      <c r="T69" s="16" t="n"/>
+      <c r="T69" s="20" t="n"/>
       <c r="U69" s="23" t="n"/>
       <c r="V69" s="13" t="n"/>
     </row>
@@ -3019,25 +3051,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B70" s="16" t="n"/>
+      <c r="B70" s="20" t="n"/>
       <c r="C70" s="23" t="n"/>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="16" t="n"/>
+      <c r="E70" s="20" t="n"/>
       <c r="F70" s="23" t="n"/>
       <c r="G70" s="13" t="n"/>
-      <c r="H70" s="16" t="n"/>
+      <c r="H70" s="20" t="n"/>
       <c r="I70" s="23" t="n"/>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="16" t="n"/>
+      <c r="K70" s="20" t="n"/>
       <c r="L70" s="23" t="n"/>
       <c r="M70" s="13" t="n"/>
-      <c r="N70" s="16" t="n"/>
+      <c r="N70" s="20" t="n"/>
       <c r="O70" s="23" t="n"/>
       <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="16" t="n"/>
+      <c r="Q70" s="20" t="n"/>
       <c r="R70" s="23" t="n"/>
       <c r="S70" s="13" t="n"/>
-      <c r="T70" s="16" t="n"/>
+      <c r="T70" s="20" t="n"/>
       <c r="U70" s="23" t="n"/>
       <c r="V70" s="13" t="n"/>
     </row>
@@ -3047,25 +3079,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B71" s="16" t="n"/>
+      <c r="B71" s="20" t="n"/>
       <c r="C71" s="23" t="n"/>
       <c r="D71" s="13" t="n"/>
-      <c r="E71" s="16" t="n"/>
+      <c r="E71" s="20" t="n"/>
       <c r="F71" s="23" t="n"/>
       <c r="G71" s="13" t="n"/>
-      <c r="H71" s="16" t="n"/>
+      <c r="H71" s="20" t="n"/>
       <c r="I71" s="23" t="n"/>
       <c r="J71" s="13" t="n"/>
-      <c r="K71" s="16" t="n"/>
+      <c r="K71" s="20" t="n"/>
       <c r="L71" s="23" t="n"/>
       <c r="M71" s="13" t="n"/>
-      <c r="N71" s="16" t="n"/>
+      <c r="N71" s="20" t="n"/>
       <c r="O71" s="23" t="n"/>
       <c r="P71" s="13" t="n"/>
-      <c r="Q71" s="16" t="n"/>
+      <c r="Q71" s="20" t="n"/>
       <c r="R71" s="23" t="n"/>
       <c r="S71" s="13" t="n"/>
-      <c r="T71" s="16" t="n"/>
+      <c r="T71" s="20" t="n"/>
       <c r="U71" s="23" t="n"/>
       <c r="V71" s="13" t="n"/>
     </row>
@@ -3075,25 +3107,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B72" s="16" t="n"/>
+      <c r="B72" s="20" t="n"/>
       <c r="C72" s="23" t="n"/>
       <c r="D72" s="13" t="n"/>
-      <c r="E72" s="16" t="n"/>
+      <c r="E72" s="20" t="n"/>
       <c r="F72" s="23" t="n"/>
       <c r="G72" s="13" t="n"/>
-      <c r="H72" s="16" t="n"/>
+      <c r="H72" s="20" t="n"/>
       <c r="I72" s="23" t="n"/>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="16" t="n"/>
+      <c r="K72" s="20" t="n"/>
       <c r="L72" s="23" t="n"/>
       <c r="M72" s="13" t="n"/>
-      <c r="N72" s="16" t="n"/>
+      <c r="N72" s="20" t="n"/>
       <c r="O72" s="23" t="n"/>
       <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="16" t="n"/>
+      <c r="Q72" s="20" t="n"/>
       <c r="R72" s="23" t="n"/>
       <c r="S72" s="13" t="n"/>
-      <c r="T72" s="16" t="n"/>
+      <c r="T72" s="20" t="n"/>
       <c r="U72" s="23" t="n"/>
       <c r="V72" s="13" t="n"/>
     </row>
@@ -3103,55 +3135,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B73" s="16" t="n"/>
+      <c r="B73" s="20" t="n"/>
       <c r="C73" s="23" t="n"/>
       <c r="D73" s="13" t="n"/>
-      <c r="E73" s="16" t="n"/>
+      <c r="E73" s="20" t="n"/>
       <c r="F73" s="23" t="n"/>
       <c r="G73" s="13" t="n"/>
-      <c r="H73" s="16" t="n"/>
+      <c r="H73" s="20" t="n"/>
       <c r="I73" s="23" t="n"/>
       <c r="J73" s="13" t="n"/>
-      <c r="K73" s="16" t="n"/>
+      <c r="K73" s="20" t="n"/>
       <c r="L73" s="23" t="n"/>
       <c r="M73" s="13" t="n"/>
-      <c r="N73" s="16" t="n"/>
+      <c r="N73" s="20" t="n"/>
       <c r="O73" s="23" t="n"/>
       <c r="P73" s="13" t="n"/>
-      <c r="Q73" s="16" t="n"/>
+      <c r="Q73" s="20" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="13" t="n"/>
-      <c r="T73" s="16" t="n"/>
+      <c r="T73" s="20" t="n"/>
       <c r="U73" s="23" t="n"/>
       <c r="V73" s="13" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B74" s="18" t="n"/>
+      <c r="B74" s="21" t="n"/>
       <c r="C74" s="24" t="n"/>
-      <c r="D74" s="20" t="n"/>
-      <c r="E74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="21" t="n"/>
       <c r="F74" s="24" t="n"/>
-      <c r="G74" s="20" t="n"/>
-      <c r="H74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="21" t="n"/>
       <c r="I74" s="24" t="n"/>
-      <c r="J74" s="20" t="n"/>
-      <c r="K74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="21" t="n"/>
       <c r="L74" s="24" t="n"/>
-      <c r="M74" s="20" t="n"/>
-      <c r="N74" s="18" t="n"/>
+      <c r="M74" s="18" t="n"/>
+      <c r="N74" s="21" t="n"/>
       <c r="O74" s="24" t="n"/>
-      <c r="P74" s="20" t="n"/>
-      <c r="Q74" s="18" t="n"/>
+      <c r="P74" s="18" t="n"/>
+      <c r="Q74" s="21" t="n"/>
       <c r="R74" s="24" t="n"/>
-      <c r="S74" s="20" t="n"/>
-      <c r="T74" s="18" t="n"/>
+      <c r="S74" s="18" t="n"/>
+      <c r="T74" s="21" t="n"/>
       <c r="U74" s="24" t="n"/>
-      <c r="V74" s="20" t="n"/>
+      <c r="V74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -3173,7 +3205,7 @@
       </c>
       <c r="F75" s="22" t="n"/>
       <c r="G75" s="9" t="n"/>
-      <c r="H75" s="21" t="n"/>
+      <c r="H75" s="19" t="n"/>
       <c r="I75" s="22" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="7" t="inlineStr">
@@ -3183,10 +3215,10 @@
       </c>
       <c r="L75" s="22" t="n"/>
       <c r="M75" s="9" t="n"/>
-      <c r="N75" s="21" t="n"/>
+      <c r="N75" s="19" t="n"/>
       <c r="O75" s="22" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="21" t="n"/>
+      <c r="Q75" s="19" t="n"/>
       <c r="R75" s="22" t="n"/>
       <c r="S75" s="9" t="n"/>
       <c r="T75" s="7" t="inlineStr">
@@ -3209,16 +3241,16 @@
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="23" t="n"/>
       <c r="G76" s="13" t="n"/>
-      <c r="H76" s="16" t="n"/>
+      <c r="H76" s="20" t="n"/>
       <c r="I76" s="23" t="n"/>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="11" t="n"/>
       <c r="L76" s="23" t="n"/>
       <c r="M76" s="13" t="n"/>
-      <c r="N76" s="16" t="n"/>
+      <c r="N76" s="20" t="n"/>
       <c r="O76" s="23" t="n"/>
       <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="16" t="n"/>
+      <c r="Q76" s="20" t="n"/>
       <c r="R76" s="23" t="n"/>
       <c r="S76" s="13" t="n"/>
       <c r="T76" s="11" t="n"/>
@@ -3237,16 +3269,16 @@
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="23" t="n"/>
       <c r="G77" s="13" t="n"/>
-      <c r="H77" s="16" t="n"/>
+      <c r="H77" s="20" t="n"/>
       <c r="I77" s="23" t="n"/>
       <c r="J77" s="13" t="n"/>
       <c r="K77" s="11" t="n"/>
       <c r="L77" s="23" t="n"/>
       <c r="M77" s="13" t="n"/>
-      <c r="N77" s="16" t="n"/>
+      <c r="N77" s="20" t="n"/>
       <c r="O77" s="23" t="n"/>
       <c r="P77" s="13" t="n"/>
-      <c r="Q77" s="16" t="n"/>
+      <c r="Q77" s="20" t="n"/>
       <c r="R77" s="23" t="n"/>
       <c r="S77" s="13" t="n"/>
       <c r="T77" s="11" t="n"/>
@@ -3265,16 +3297,16 @@
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="13" t="n"/>
-      <c r="H78" s="16" t="n"/>
+      <c r="H78" s="20" t="n"/>
       <c r="I78" s="23" t="n"/>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="11" t="n"/>
       <c r="L78" s="23" t="n"/>
       <c r="M78" s="13" t="n"/>
-      <c r="N78" s="16" t="n"/>
+      <c r="N78" s="20" t="n"/>
       <c r="O78" s="23" t="n"/>
       <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="16" t="n"/>
+      <c r="Q78" s="20" t="n"/>
       <c r="R78" s="23" t="n"/>
       <c r="S78" s="13" t="n"/>
       <c r="T78" s="11" t="n"/>
@@ -3293,16 +3325,16 @@
       <c r="E79" s="14" t="n"/>
       <c r="F79" s="23" t="n"/>
       <c r="G79" s="13" t="n"/>
-      <c r="H79" s="16" t="n"/>
+      <c r="H79" s="20" t="n"/>
       <c r="I79" s="23" t="n"/>
       <c r="J79" s="13" t="n"/>
       <c r="K79" s="11" t="n"/>
       <c r="L79" s="23" t="n"/>
       <c r="M79" s="13" t="n"/>
-      <c r="N79" s="16" t="n"/>
+      <c r="N79" s="20" t="n"/>
       <c r="O79" s="23" t="n"/>
       <c r="P79" s="13" t="n"/>
-      <c r="Q79" s="16" t="n"/>
+      <c r="Q79" s="20" t="n"/>
       <c r="R79" s="23" t="n"/>
       <c r="S79" s="13" t="n"/>
       <c r="T79" s="11" t="n"/>
@@ -3318,19 +3350,19 @@
       <c r="B80" s="11" t="n"/>
       <c r="C80" s="23" t="n"/>
       <c r="D80" s="13" t="n"/>
-      <c r="E80" s="16" t="n"/>
+      <c r="E80" s="20" t="n"/>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="13" t="n"/>
-      <c r="H80" s="16" t="n"/>
+      <c r="H80" s="20" t="n"/>
       <c r="I80" s="23" t="n"/>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="11" t="n"/>
       <c r="L80" s="23" t="n"/>
       <c r="M80" s="13" t="n"/>
-      <c r="N80" s="16" t="n"/>
+      <c r="N80" s="20" t="n"/>
       <c r="O80" s="23" t="n"/>
       <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="16" t="n"/>
+      <c r="Q80" s="20" t="n"/>
       <c r="R80" s="23" t="n"/>
       <c r="S80" s="13" t="n"/>
       <c r="T80" s="11" t="n"/>
@@ -3346,10 +3378,10 @@
       <c r="B81" s="11" t="n"/>
       <c r="C81" s="23" t="n"/>
       <c r="D81" s="13" t="n"/>
-      <c r="E81" s="16" t="n"/>
+      <c r="E81" s="20" t="n"/>
       <c r="F81" s="23" t="n"/>
       <c r="G81" s="13" t="n"/>
-      <c r="H81" s="16" t="n"/>
+      <c r="H81" s="20" t="n"/>
       <c r="I81" s="23" t="n"/>
       <c r="J81" s="13" t="n"/>
       <c r="K81" s="11" t="n"/>
@@ -3359,10 +3391,10 @@
         </is>
       </c>
       <c r="M81" s="13" t="n"/>
-      <c r="N81" s="16" t="n"/>
+      <c r="N81" s="20" t="n"/>
       <c r="O81" s="23" t="n"/>
       <c r="P81" s="13" t="n"/>
-      <c r="Q81" s="16" t="n"/>
+      <c r="Q81" s="20" t="n"/>
       <c r="R81" s="23" t="n"/>
       <c r="S81" s="13" t="n"/>
       <c r="T81" s="11" t="n"/>
@@ -3378,19 +3410,19 @@
       <c r="B82" s="11" t="n"/>
       <c r="C82" s="23" t="n"/>
       <c r="D82" s="13" t="n"/>
-      <c r="E82" s="16" t="n"/>
+      <c r="E82" s="20" t="n"/>
       <c r="F82" s="23" t="n"/>
       <c r="G82" s="13" t="n"/>
-      <c r="H82" s="16" t="n"/>
+      <c r="H82" s="20" t="n"/>
       <c r="I82" s="23" t="n"/>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="11" t="n"/>
       <c r="L82" s="26" t="n"/>
       <c r="M82" s="13" t="n"/>
-      <c r="N82" s="16" t="n"/>
+      <c r="N82" s="20" t="n"/>
       <c r="O82" s="23" t="n"/>
       <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="16" t="n"/>
+      <c r="Q82" s="20" t="n"/>
       <c r="R82" s="23" t="n"/>
       <c r="S82" s="13" t="n"/>
       <c r="T82" s="11" t="n"/>
@@ -3406,19 +3438,19 @@
       <c r="B83" s="11" t="n"/>
       <c r="C83" s="23" t="n"/>
       <c r="D83" s="13" t="n"/>
-      <c r="E83" s="16" t="n"/>
+      <c r="E83" s="20" t="n"/>
       <c r="F83" s="23" t="n"/>
       <c r="G83" s="13" t="n"/>
-      <c r="H83" s="16" t="n"/>
+      <c r="H83" s="20" t="n"/>
       <c r="I83" s="23" t="n"/>
       <c r="J83" s="13" t="n"/>
       <c r="K83" s="11" t="n"/>
       <c r="L83" s="26" t="n"/>
       <c r="M83" s="13" t="n"/>
-      <c r="N83" s="16" t="n"/>
+      <c r="N83" s="20" t="n"/>
       <c r="O83" s="23" t="n"/>
       <c r="P83" s="13" t="n"/>
-      <c r="Q83" s="16" t="n"/>
+      <c r="Q83" s="20" t="n"/>
       <c r="R83" s="23" t="n"/>
       <c r="S83" s="13" t="n"/>
       <c r="T83" s="11" t="n"/>
@@ -3434,19 +3466,19 @@
       <c r="B84" s="11" t="n"/>
       <c r="C84" s="23" t="n"/>
       <c r="D84" s="13" t="n"/>
-      <c r="E84" s="16" t="n"/>
+      <c r="E84" s="20" t="n"/>
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="13" t="n"/>
-      <c r="H84" s="16" t="n"/>
+      <c r="H84" s="20" t="n"/>
       <c r="I84" s="23" t="n"/>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="11" t="n"/>
       <c r="L84" s="26" t="n"/>
       <c r="M84" s="13" t="n"/>
-      <c r="N84" s="16" t="n"/>
+      <c r="N84" s="20" t="n"/>
       <c r="O84" s="23" t="n"/>
       <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="16" t="n"/>
+      <c r="Q84" s="20" t="n"/>
       <c r="R84" s="23" t="n"/>
       <c r="S84" s="13" t="n"/>
       <c r="T84" s="11" t="n"/>
@@ -3462,19 +3494,19 @@
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="23" t="n"/>
       <c r="D85" s="13" t="n"/>
-      <c r="E85" s="16" t="n"/>
+      <c r="E85" s="20" t="n"/>
       <c r="F85" s="23" t="n"/>
       <c r="G85" s="13" t="n"/>
-      <c r="H85" s="16" t="n"/>
+      <c r="H85" s="20" t="n"/>
       <c r="I85" s="23" t="n"/>
       <c r="J85" s="13" t="n"/>
       <c r="K85" s="14" t="n"/>
       <c r="L85" s="27" t="n"/>
       <c r="M85" s="13" t="n"/>
-      <c r="N85" s="16" t="n"/>
+      <c r="N85" s="20" t="n"/>
       <c r="O85" s="23" t="n"/>
       <c r="P85" s="13" t="n"/>
-      <c r="Q85" s="16" t="n"/>
+      <c r="Q85" s="20" t="n"/>
       <c r="R85" s="23" t="n"/>
       <c r="S85" s="13" t="n"/>
       <c r="T85" s="14" t="n"/>
@@ -3482,32 +3514,32 @@
       <c r="V85" s="13" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B86" s="18" t="n"/>
+      <c r="B86" s="21" t="n"/>
       <c r="C86" s="24" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="21" t="n"/>
       <c r="F86" s="24" t="n"/>
-      <c r="G86" s="20" t="n"/>
-      <c r="H86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="21" t="n"/>
       <c r="I86" s="24" t="n"/>
-      <c r="J86" s="20" t="n"/>
-      <c r="K86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="21" t="n"/>
       <c r="L86" s="24" t="n"/>
-      <c r="M86" s="20" t="n"/>
-      <c r="N86" s="18" t="n"/>
+      <c r="M86" s="18" t="n"/>
+      <c r="N86" s="21" t="n"/>
       <c r="O86" s="24" t="n"/>
-      <c r="P86" s="20" t="n"/>
-      <c r="Q86" s="18" t="n"/>
+      <c r="P86" s="18" t="n"/>
+      <c r="Q86" s="21" t="n"/>
       <c r="R86" s="24" t="n"/>
-      <c r="S86" s="20" t="n"/>
-      <c r="T86" s="18" t="n"/>
+      <c r="S86" s="18" t="n"/>
+      <c r="T86" s="21" t="n"/>
       <c r="U86" s="24" t="n"/>
-      <c r="V86" s="20" t="n"/>
+      <c r="V86" s="18" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -3515,10 +3547,10 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B87" s="21" t="n"/>
+      <c r="B87" s="19" t="n"/>
       <c r="C87" s="22" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="21" t="n"/>
+      <c r="E87" s="19" t="n"/>
       <c r="F87" s="22" t="n"/>
       <c r="G87" s="9" t="n"/>
       <c r="H87" s="7" t="inlineStr">
@@ -3528,16 +3560,16 @@
       </c>
       <c r="I87" s="22" t="n"/>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="21" t="n"/>
+      <c r="K87" s="19" t="n"/>
       <c r="L87" s="22" t="n"/>
       <c r="M87" s="9" t="n"/>
-      <c r="N87" s="21" t="n"/>
+      <c r="N87" s="19" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="21" t="n"/>
+      <c r="Q87" s="19" t="n"/>
       <c r="R87" s="22" t="n"/>
       <c r="S87" s="9" t="n"/>
-      <c r="T87" s="21" t="n"/>
+      <c r="T87" s="19" t="n"/>
       <c r="U87" s="22" t="n"/>
       <c r="V87" s="9" t="n"/>
     </row>
@@ -3547,25 +3579,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B88" s="16" t="n"/>
+      <c r="B88" s="20" t="n"/>
       <c r="C88" s="23" t="n"/>
       <c r="D88" s="13" t="n"/>
-      <c r="E88" s="16" t="n"/>
+      <c r="E88" s="20" t="n"/>
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="13" t="n"/>
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="23" t="n"/>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="16" t="n"/>
+      <c r="K88" s="20" t="n"/>
       <c r="L88" s="23" t="n"/>
       <c r="M88" s="13" t="n"/>
-      <c r="N88" s="16" t="n"/>
+      <c r="N88" s="20" t="n"/>
       <c r="O88" s="23" t="n"/>
       <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="16" t="n"/>
+      <c r="Q88" s="20" t="n"/>
       <c r="R88" s="23" t="n"/>
       <c r="S88" s="13" t="n"/>
-      <c r="T88" s="16" t="n"/>
+      <c r="T88" s="20" t="n"/>
       <c r="U88" s="23" t="n"/>
       <c r="V88" s="13" t="n"/>
     </row>
@@ -3575,25 +3607,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B89" s="16" t="n"/>
+      <c r="B89" s="20" t="n"/>
       <c r="C89" s="23" t="n"/>
       <c r="D89" s="13" t="n"/>
-      <c r="E89" s="16" t="n"/>
+      <c r="E89" s="20" t="n"/>
       <c r="F89" s="23" t="n"/>
       <c r="G89" s="13" t="n"/>
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="23" t="n"/>
       <c r="J89" s="13" t="n"/>
-      <c r="K89" s="16" t="n"/>
+      <c r="K89" s="20" t="n"/>
       <c r="L89" s="23" t="n"/>
       <c r="M89" s="13" t="n"/>
-      <c r="N89" s="16" t="n"/>
+      <c r="N89" s="20" t="n"/>
       <c r="O89" s="23" t="n"/>
       <c r="P89" s="13" t="n"/>
-      <c r="Q89" s="16" t="n"/>
+      <c r="Q89" s="20" t="n"/>
       <c r="R89" s="23" t="n"/>
       <c r="S89" s="13" t="n"/>
-      <c r="T89" s="16" t="n"/>
+      <c r="T89" s="20" t="n"/>
       <c r="U89" s="23" t="n"/>
       <c r="V89" s="13" t="n"/>
     </row>
@@ -3603,25 +3635,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B90" s="16" t="n"/>
+      <c r="B90" s="20" t="n"/>
       <c r="C90" s="23" t="n"/>
       <c r="D90" s="13" t="n"/>
-      <c r="E90" s="16" t="n"/>
+      <c r="E90" s="20" t="n"/>
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="13" t="n"/>
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="23" t="n"/>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="16" t="n"/>
+      <c r="K90" s="20" t="n"/>
       <c r="L90" s="23" t="n"/>
       <c r="M90" s="13" t="n"/>
-      <c r="N90" s="16" t="n"/>
+      <c r="N90" s="20" t="n"/>
       <c r="O90" s="23" t="n"/>
       <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="16" t="n"/>
+      <c r="Q90" s="20" t="n"/>
       <c r="R90" s="23" t="n"/>
       <c r="S90" s="13" t="n"/>
-      <c r="T90" s="16" t="n"/>
+      <c r="T90" s="20" t="n"/>
       <c r="U90" s="23" t="n"/>
       <c r="V90" s="13" t="n"/>
     </row>
@@ -3631,25 +3663,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B91" s="16" t="n"/>
+      <c r="B91" s="20" t="n"/>
       <c r="C91" s="23" t="n"/>
       <c r="D91" s="13" t="n"/>
-      <c r="E91" s="16" t="n"/>
+      <c r="E91" s="20" t="n"/>
       <c r="F91" s="23" t="n"/>
       <c r="G91" s="13" t="n"/>
       <c r="H91" s="14" t="n"/>
       <c r="I91" s="23" t="n"/>
       <c r="J91" s="13" t="n"/>
-      <c r="K91" s="16" t="n"/>
+      <c r="K91" s="20" t="n"/>
       <c r="L91" s="23" t="n"/>
       <c r="M91" s="13" t="n"/>
-      <c r="N91" s="16" t="n"/>
+      <c r="N91" s="20" t="n"/>
       <c r="O91" s="23" t="n"/>
       <c r="P91" s="13" t="n"/>
-      <c r="Q91" s="16" t="n"/>
+      <c r="Q91" s="20" t="n"/>
       <c r="R91" s="23" t="n"/>
       <c r="S91" s="13" t="n"/>
-      <c r="T91" s="16" t="n"/>
+      <c r="T91" s="20" t="n"/>
       <c r="U91" s="23" t="n"/>
       <c r="V91" s="13" t="n"/>
     </row>
@@ -3659,25 +3691,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B92" s="16" t="n"/>
+      <c r="B92" s="20" t="n"/>
       <c r="C92" s="23" t="n"/>
       <c r="D92" s="13" t="n"/>
-      <c r="E92" s="16" t="n"/>
+      <c r="E92" s="20" t="n"/>
       <c r="F92" s="23" t="n"/>
       <c r="G92" s="13" t="n"/>
-      <c r="H92" s="16" t="n"/>
+      <c r="H92" s="20" t="n"/>
       <c r="I92" s="23" t="n"/>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="16" t="n"/>
+      <c r="K92" s="20" t="n"/>
       <c r="L92" s="23" t="n"/>
       <c r="M92" s="13" t="n"/>
-      <c r="N92" s="16" t="n"/>
+      <c r="N92" s="20" t="n"/>
       <c r="O92" s="23" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="16" t="n"/>
+      <c r="Q92" s="20" t="n"/>
       <c r="R92" s="23" t="n"/>
       <c r="S92" s="13" t="n"/>
-      <c r="T92" s="16" t="n"/>
+      <c r="T92" s="20" t="n"/>
       <c r="U92" s="23" t="n"/>
       <c r="V92" s="13" t="n"/>
     </row>
@@ -3687,25 +3719,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B93" s="16" t="n"/>
+      <c r="B93" s="20" t="n"/>
       <c r="C93" s="23" t="n"/>
       <c r="D93" s="13" t="n"/>
-      <c r="E93" s="16" t="n"/>
+      <c r="E93" s="20" t="n"/>
       <c r="F93" s="23" t="n"/>
       <c r="G93" s="13" t="n"/>
-      <c r="H93" s="16" t="n"/>
+      <c r="H93" s="20" t="n"/>
       <c r="I93" s="23" t="n"/>
       <c r="J93" s="13" t="n"/>
-      <c r="K93" s="16" t="n"/>
+      <c r="K93" s="20" t="n"/>
       <c r="L93" s="23" t="n"/>
       <c r="M93" s="13" t="n"/>
-      <c r="N93" s="16" t="n"/>
+      <c r="N93" s="20" t="n"/>
       <c r="O93" s="23" t="n"/>
       <c r="P93" s="13" t="n"/>
-      <c r="Q93" s="16" t="n"/>
+      <c r="Q93" s="20" t="n"/>
       <c r="R93" s="23" t="n"/>
       <c r="S93" s="13" t="n"/>
-      <c r="T93" s="16" t="n"/>
+      <c r="T93" s="20" t="n"/>
       <c r="U93" s="23" t="n"/>
       <c r="V93" s="13" t="n"/>
     </row>
@@ -3715,25 +3747,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B94" s="16" t="n"/>
+      <c r="B94" s="20" t="n"/>
       <c r="C94" s="23" t="n"/>
       <c r="D94" s="13" t="n"/>
-      <c r="E94" s="16" t="n"/>
+      <c r="E94" s="20" t="n"/>
       <c r="F94" s="23" t="n"/>
       <c r="G94" s="13" t="n"/>
-      <c r="H94" s="16" t="n"/>
+      <c r="H94" s="20" t="n"/>
       <c r="I94" s="23" t="n"/>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="16" t="n"/>
+      <c r="K94" s="20" t="n"/>
       <c r="L94" s="23" t="n"/>
       <c r="M94" s="13" t="n"/>
-      <c r="N94" s="16" t="n"/>
+      <c r="N94" s="20" t="n"/>
       <c r="O94" s="23" t="n"/>
       <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="16" t="n"/>
+      <c r="Q94" s="20" t="n"/>
       <c r="R94" s="23" t="n"/>
       <c r="S94" s="13" t="n"/>
-      <c r="T94" s="16" t="n"/>
+      <c r="T94" s="20" t="n"/>
       <c r="U94" s="23" t="n"/>
       <c r="V94" s="13" t="n"/>
     </row>
@@ -3743,25 +3775,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B95" s="16" t="n"/>
+      <c r="B95" s="20" t="n"/>
       <c r="C95" s="23" t="n"/>
       <c r="D95" s="13" t="n"/>
-      <c r="E95" s="16" t="n"/>
+      <c r="E95" s="20" t="n"/>
       <c r="F95" s="23" t="n"/>
       <c r="G95" s="13" t="n"/>
-      <c r="H95" s="16" t="n"/>
+      <c r="H95" s="20" t="n"/>
       <c r="I95" s="23" t="n"/>
       <c r="J95" s="13" t="n"/>
-      <c r="K95" s="16" t="n"/>
+      <c r="K95" s="20" t="n"/>
       <c r="L95" s="23" t="n"/>
       <c r="M95" s="13" t="n"/>
-      <c r="N95" s="16" t="n"/>
+      <c r="N95" s="20" t="n"/>
       <c r="O95" s="23" t="n"/>
       <c r="P95" s="13" t="n"/>
-      <c r="Q95" s="16" t="n"/>
+      <c r="Q95" s="20" t="n"/>
       <c r="R95" s="23" t="n"/>
       <c r="S95" s="13" t="n"/>
-      <c r="T95" s="16" t="n"/>
+      <c r="T95" s="20" t="n"/>
       <c r="U95" s="23" t="n"/>
       <c r="V95" s="13" t="n"/>
     </row>
@@ -3771,25 +3803,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B96" s="16" t="n"/>
+      <c r="B96" s="20" t="n"/>
       <c r="C96" s="23" t="n"/>
       <c r="D96" s="13" t="n"/>
-      <c r="E96" s="16" t="n"/>
+      <c r="E96" s="20" t="n"/>
       <c r="F96" s="23" t="n"/>
       <c r="G96" s="13" t="n"/>
-      <c r="H96" s="16" t="n"/>
+      <c r="H96" s="20" t="n"/>
       <c r="I96" s="23" t="n"/>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="16" t="n"/>
+      <c r="K96" s="20" t="n"/>
       <c r="L96" s="23" t="n"/>
       <c r="M96" s="13" t="n"/>
-      <c r="N96" s="16" t="n"/>
+      <c r="N96" s="20" t="n"/>
       <c r="O96" s="23" t="n"/>
       <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="16" t="n"/>
+      <c r="Q96" s="20" t="n"/>
       <c r="R96" s="23" t="n"/>
       <c r="S96" s="13" t="n"/>
-      <c r="T96" s="16" t="n"/>
+      <c r="T96" s="20" t="n"/>
       <c r="U96" s="23" t="n"/>
       <c r="V96" s="13" t="n"/>
     </row>
@@ -3799,55 +3831,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B97" s="16" t="n"/>
+      <c r="B97" s="20" t="n"/>
       <c r="C97" s="23" t="n"/>
       <c r="D97" s="13" t="n"/>
-      <c r="E97" s="16" t="n"/>
+      <c r="E97" s="20" t="n"/>
       <c r="F97" s="23" t="n"/>
       <c r="G97" s="13" t="n"/>
-      <c r="H97" s="16" t="n"/>
+      <c r="H97" s="20" t="n"/>
       <c r="I97" s="23" t="n"/>
       <c r="J97" s="13" t="n"/>
-      <c r="K97" s="16" t="n"/>
+      <c r="K97" s="20" t="n"/>
       <c r="L97" s="23" t="n"/>
       <c r="M97" s="13" t="n"/>
-      <c r="N97" s="16" t="n"/>
+      <c r="N97" s="20" t="n"/>
       <c r="O97" s="23" t="n"/>
       <c r="P97" s="13" t="n"/>
-      <c r="Q97" s="16" t="n"/>
+      <c r="Q97" s="20" t="n"/>
       <c r="R97" s="23" t="n"/>
       <c r="S97" s="13" t="n"/>
-      <c r="T97" s="16" t="n"/>
+      <c r="T97" s="20" t="n"/>
       <c r="U97" s="23" t="n"/>
       <c r="V97" s="13" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="17" t="inlineStr">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B98" s="18" t="n"/>
+      <c r="B98" s="21" t="n"/>
       <c r="C98" s="24" t="n"/>
-      <c r="D98" s="20" t="n"/>
-      <c r="E98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="21" t="n"/>
       <c r="F98" s="24" t="n"/>
-      <c r="G98" s="20" t="n"/>
-      <c r="H98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="21" t="n"/>
       <c r="I98" s="24" t="n"/>
-      <c r="J98" s="20" t="n"/>
-      <c r="K98" s="18" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="21" t="n"/>
       <c r="L98" s="24" t="n"/>
-      <c r="M98" s="20" t="n"/>
-      <c r="N98" s="18" t="n"/>
+      <c r="M98" s="18" t="n"/>
+      <c r="N98" s="21" t="n"/>
       <c r="O98" s="24" t="n"/>
-      <c r="P98" s="20" t="n"/>
-      <c r="Q98" s="18" t="n"/>
+      <c r="P98" s="18" t="n"/>
+      <c r="Q98" s="21" t="n"/>
       <c r="R98" s="24" t="n"/>
-      <c r="S98" s="20" t="n"/>
-      <c r="T98" s="18" t="n"/>
+      <c r="S98" s="18" t="n"/>
+      <c r="T98" s="21" t="n"/>
       <c r="U98" s="24" t="n"/>
-      <c r="V98" s="20" t="n"/>
+      <c r="V98" s="18" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -3855,25 +3887,25 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B99" s="21" t="n"/>
+      <c r="B99" s="19" t="n"/>
       <c r="C99" s="22" t="n"/>
       <c r="D99" s="9" t="n"/>
-      <c r="E99" s="21" t="n"/>
+      <c r="E99" s="19" t="n"/>
       <c r="F99" s="22" t="n"/>
       <c r="G99" s="9" t="n"/>
-      <c r="H99" s="21" t="n"/>
+      <c r="H99" s="19" t="n"/>
       <c r="I99" s="22" t="n"/>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="21" t="n"/>
+      <c r="K99" s="19" t="n"/>
       <c r="L99" s="22" t="n"/>
       <c r="M99" s="9" t="n"/>
-      <c r="N99" s="21" t="n"/>
+      <c r="N99" s="19" t="n"/>
       <c r="O99" s="22" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="21" t="n"/>
+      <c r="Q99" s="19" t="n"/>
       <c r="R99" s="22" t="n"/>
       <c r="S99" s="9" t="n"/>
-      <c r="T99" s="21" t="n"/>
+      <c r="T99" s="19" t="n"/>
       <c r="U99" s="22" t="n"/>
       <c r="V99" s="9" t="n"/>
     </row>
@@ -3883,25 +3915,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B100" s="16" t="n"/>
+      <c r="B100" s="20" t="n"/>
       <c r="C100" s="23" t="n"/>
       <c r="D100" s="13" t="n"/>
-      <c r="E100" s="16" t="n"/>
+      <c r="E100" s="20" t="n"/>
       <c r="F100" s="23" t="n"/>
       <c r="G100" s="13" t="n"/>
-      <c r="H100" s="16" t="n"/>
+      <c r="H100" s="20" t="n"/>
       <c r="I100" s="23" t="n"/>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="16" t="n"/>
+      <c r="K100" s="20" t="n"/>
       <c r="L100" s="23" t="n"/>
       <c r="M100" s="13" t="n"/>
-      <c r="N100" s="16" t="n"/>
+      <c r="N100" s="20" t="n"/>
       <c r="O100" s="23" t="n"/>
       <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="16" t="n"/>
+      <c r="Q100" s="20" t="n"/>
       <c r="R100" s="23" t="n"/>
       <c r="S100" s="13" t="n"/>
-      <c r="T100" s="16" t="n"/>
+      <c r="T100" s="20" t="n"/>
       <c r="U100" s="23" t="n"/>
       <c r="V100" s="13" t="n"/>
     </row>
@@ -3911,25 +3943,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B101" s="16" t="n"/>
+      <c r="B101" s="20" t="n"/>
       <c r="C101" s="23" t="n"/>
       <c r="D101" s="13" t="n"/>
-      <c r="E101" s="16" t="n"/>
+      <c r="E101" s="20" t="n"/>
       <c r="F101" s="23" t="n"/>
       <c r="G101" s="13" t="n"/>
-      <c r="H101" s="16" t="n"/>
+      <c r="H101" s="20" t="n"/>
       <c r="I101" s="23" t="n"/>
       <c r="J101" s="13" t="n"/>
-      <c r="K101" s="16" t="n"/>
+      <c r="K101" s="20" t="n"/>
       <c r="L101" s="23" t="n"/>
       <c r="M101" s="13" t="n"/>
-      <c r="N101" s="16" t="n"/>
+      <c r="N101" s="20" t="n"/>
       <c r="O101" s="23" t="n"/>
       <c r="P101" s="13" t="n"/>
-      <c r="Q101" s="16" t="n"/>
+      <c r="Q101" s="20" t="n"/>
       <c r="R101" s="23" t="n"/>
       <c r="S101" s="13" t="n"/>
-      <c r="T101" s="16" t="n"/>
+      <c r="T101" s="20" t="n"/>
       <c r="U101" s="23" t="n"/>
       <c r="V101" s="13" t="n"/>
     </row>
@@ -3939,25 +3971,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B102" s="16" t="n"/>
+      <c r="B102" s="20" t="n"/>
       <c r="C102" s="23" t="n"/>
       <c r="D102" s="13" t="n"/>
-      <c r="E102" s="16" t="n"/>
+      <c r="E102" s="20" t="n"/>
       <c r="F102" s="23" t="n"/>
       <c r="G102" s="13" t="n"/>
-      <c r="H102" s="16" t="n"/>
+      <c r="H102" s="20" t="n"/>
       <c r="I102" s="23" t="n"/>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="16" t="n"/>
+      <c r="K102" s="20" t="n"/>
       <c r="L102" s="23" t="n"/>
       <c r="M102" s="13" t="n"/>
-      <c r="N102" s="16" t="n"/>
+      <c r="N102" s="20" t="n"/>
       <c r="O102" s="23" t="n"/>
       <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="16" t="n"/>
+      <c r="Q102" s="20" t="n"/>
       <c r="R102" s="23" t="n"/>
       <c r="S102" s="13" t="n"/>
-      <c r="T102" s="16" t="n"/>
+      <c r="T102" s="20" t="n"/>
       <c r="U102" s="23" t="n"/>
       <c r="V102" s="13" t="n"/>
     </row>
@@ -3967,25 +3999,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B103" s="16" t="n"/>
+      <c r="B103" s="20" t="n"/>
       <c r="C103" s="23" t="n"/>
       <c r="D103" s="13" t="n"/>
-      <c r="E103" s="16" t="n"/>
+      <c r="E103" s="20" t="n"/>
       <c r="F103" s="23" t="n"/>
       <c r="G103" s="13" t="n"/>
-      <c r="H103" s="16" t="n"/>
+      <c r="H103" s="20" t="n"/>
       <c r="I103" s="23" t="n"/>
       <c r="J103" s="13" t="n"/>
-      <c r="K103" s="16" t="n"/>
+      <c r="K103" s="20" t="n"/>
       <c r="L103" s="23" t="n"/>
       <c r="M103" s="13" t="n"/>
-      <c r="N103" s="16" t="n"/>
+      <c r="N103" s="20" t="n"/>
       <c r="O103" s="23" t="n"/>
       <c r="P103" s="13" t="n"/>
-      <c r="Q103" s="16" t="n"/>
+      <c r="Q103" s="20" t="n"/>
       <c r="R103" s="23" t="n"/>
       <c r="S103" s="13" t="n"/>
-      <c r="T103" s="16" t="n"/>
+      <c r="T103" s="20" t="n"/>
       <c r="U103" s="23" t="n"/>
       <c r="V103" s="13" t="n"/>
     </row>
@@ -3995,25 +4027,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B104" s="16" t="n"/>
+      <c r="B104" s="20" t="n"/>
       <c r="C104" s="23" t="n"/>
       <c r="D104" s="13" t="n"/>
-      <c r="E104" s="16" t="n"/>
+      <c r="E104" s="20" t="n"/>
       <c r="F104" s="23" t="n"/>
       <c r="G104" s="13" t="n"/>
-      <c r="H104" s="16" t="n"/>
+      <c r="H104" s="20" t="n"/>
       <c r="I104" s="23" t="n"/>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="16" t="n"/>
+      <c r="K104" s="20" t="n"/>
       <c r="L104" s="23" t="n"/>
       <c r="M104" s="13" t="n"/>
-      <c r="N104" s="16" t="n"/>
+      <c r="N104" s="20" t="n"/>
       <c r="O104" s="23" t="n"/>
       <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="16" t="n"/>
+      <c r="Q104" s="20" t="n"/>
       <c r="R104" s="23" t="n"/>
       <c r="S104" s="13" t="n"/>
-      <c r="T104" s="16" t="n"/>
+      <c r="T104" s="20" t="n"/>
       <c r="U104" s="23" t="n"/>
       <c r="V104" s="13" t="n"/>
     </row>
@@ -4023,25 +4055,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B105" s="16" t="n"/>
+      <c r="B105" s="20" t="n"/>
       <c r="C105" s="23" t="n"/>
       <c r="D105" s="13" t="n"/>
-      <c r="E105" s="16" t="n"/>
+      <c r="E105" s="20" t="n"/>
       <c r="F105" s="23" t="n"/>
       <c r="G105" s="13" t="n"/>
-      <c r="H105" s="16" t="n"/>
+      <c r="H105" s="20" t="n"/>
       <c r="I105" s="23" t="n"/>
       <c r="J105" s="13" t="n"/>
-      <c r="K105" s="16" t="n"/>
+      <c r="K105" s="20" t="n"/>
       <c r="L105" s="23" t="n"/>
       <c r="M105" s="13" t="n"/>
-      <c r="N105" s="16" t="n"/>
+      <c r="N105" s="20" t="n"/>
       <c r="O105" s="23" t="n"/>
       <c r="P105" s="13" t="n"/>
-      <c r="Q105" s="16" t="n"/>
+      <c r="Q105" s="20" t="n"/>
       <c r="R105" s="23" t="n"/>
       <c r="S105" s="13" t="n"/>
-      <c r="T105" s="16" t="n"/>
+      <c r="T105" s="20" t="n"/>
       <c r="U105" s="23" t="n"/>
       <c r="V105" s="13" t="n"/>
     </row>
@@ -4051,25 +4083,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B106" s="16" t="n"/>
+      <c r="B106" s="20" t="n"/>
       <c r="C106" s="23" t="n"/>
       <c r="D106" s="13" t="n"/>
-      <c r="E106" s="16" t="n"/>
+      <c r="E106" s="20" t="n"/>
       <c r="F106" s="23" t="n"/>
       <c r="G106" s="13" t="n"/>
-      <c r="H106" s="16" t="n"/>
+      <c r="H106" s="20" t="n"/>
       <c r="I106" s="23" t="n"/>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="16" t="n"/>
+      <c r="K106" s="20" t="n"/>
       <c r="L106" s="23" t="n"/>
       <c r="M106" s="13" t="n"/>
-      <c r="N106" s="16" t="n"/>
+      <c r="N106" s="20" t="n"/>
       <c r="O106" s="23" t="n"/>
       <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="16" t="n"/>
+      <c r="Q106" s="20" t="n"/>
       <c r="R106" s="23" t="n"/>
       <c r="S106" s="13" t="n"/>
-      <c r="T106" s="16" t="n"/>
+      <c r="T106" s="20" t="n"/>
       <c r="U106" s="23" t="n"/>
       <c r="V106" s="13" t="n"/>
     </row>
@@ -4079,25 +4111,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B107" s="16" t="n"/>
+      <c r="B107" s="20" t="n"/>
       <c r="C107" s="23" t="n"/>
       <c r="D107" s="13" t="n"/>
-      <c r="E107" s="16" t="n"/>
+      <c r="E107" s="20" t="n"/>
       <c r="F107" s="23" t="n"/>
       <c r="G107" s="13" t="n"/>
-      <c r="H107" s="16" t="n"/>
+      <c r="H107" s="20" t="n"/>
       <c r="I107" s="23" t="n"/>
       <c r="J107" s="13" t="n"/>
-      <c r="K107" s="16" t="n"/>
+      <c r="K107" s="20" t="n"/>
       <c r="L107" s="23" t="n"/>
       <c r="M107" s="13" t="n"/>
-      <c r="N107" s="16" t="n"/>
+      <c r="N107" s="20" t="n"/>
       <c r="O107" s="23" t="n"/>
       <c r="P107" s="13" t="n"/>
-      <c r="Q107" s="16" t="n"/>
+      <c r="Q107" s="20" t="n"/>
       <c r="R107" s="23" t="n"/>
       <c r="S107" s="13" t="n"/>
-      <c r="T107" s="16" t="n"/>
+      <c r="T107" s="20" t="n"/>
       <c r="U107" s="23" t="n"/>
       <c r="V107" s="13" t="n"/>
     </row>
@@ -4107,25 +4139,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B108" s="16" t="n"/>
+      <c r="B108" s="20" t="n"/>
       <c r="C108" s="23" t="n"/>
       <c r="D108" s="13" t="n"/>
-      <c r="E108" s="16" t="n"/>
+      <c r="E108" s="20" t="n"/>
       <c r="F108" s="23" t="n"/>
       <c r="G108" s="13" t="n"/>
-      <c r="H108" s="16" t="n"/>
+      <c r="H108" s="20" t="n"/>
       <c r="I108" s="23" t="n"/>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="16" t="n"/>
+      <c r="K108" s="20" t="n"/>
       <c r="L108" s="23" t="n"/>
       <c r="M108" s="13" t="n"/>
-      <c r="N108" s="16" t="n"/>
+      <c r="N108" s="20" t="n"/>
       <c r="O108" s="23" t="n"/>
       <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="16" t="n"/>
+      <c r="Q108" s="20" t="n"/>
       <c r="R108" s="23" t="n"/>
       <c r="S108" s="13" t="n"/>
-      <c r="T108" s="16" t="n"/>
+      <c r="T108" s="20" t="n"/>
       <c r="U108" s="23" t="n"/>
       <c r="V108" s="13" t="n"/>
     </row>
@@ -4135,55 +4167,55 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B109" s="16" t="n"/>
+      <c r="B109" s="20" t="n"/>
       <c r="C109" s="23" t="n"/>
       <c r="D109" s="13" t="n"/>
-      <c r="E109" s="16" t="n"/>
+      <c r="E109" s="20" t="n"/>
       <c r="F109" s="23" t="n"/>
       <c r="G109" s="13" t="n"/>
-      <c r="H109" s="16" t="n"/>
+      <c r="H109" s="20" t="n"/>
       <c r="I109" s="23" t="n"/>
       <c r="J109" s="13" t="n"/>
-      <c r="K109" s="16" t="n"/>
+      <c r="K109" s="20" t="n"/>
       <c r="L109" s="23" t="n"/>
       <c r="M109" s="13" t="n"/>
-      <c r="N109" s="16" t="n"/>
+      <c r="N109" s="20" t="n"/>
       <c r="O109" s="23" t="n"/>
       <c r="P109" s="13" t="n"/>
-      <c r="Q109" s="16" t="n"/>
+      <c r="Q109" s="20" t="n"/>
       <c r="R109" s="23" t="n"/>
       <c r="S109" s="13" t="n"/>
-      <c r="T109" s="16" t="n"/>
+      <c r="T109" s="20" t="n"/>
       <c r="U109" s="23" t="n"/>
       <c r="V109" s="13" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="17" t="inlineStr">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B110" s="18" t="n"/>
+      <c r="B110" s="21" t="n"/>
       <c r="C110" s="24" t="n"/>
-      <c r="D110" s="20" t="n"/>
-      <c r="E110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="21" t="n"/>
       <c r="F110" s="24" t="n"/>
-      <c r="G110" s="20" t="n"/>
-      <c r="H110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="21" t="n"/>
       <c r="I110" s="24" t="n"/>
-      <c r="J110" s="20" t="n"/>
-      <c r="K110" s="18" t="n"/>
+      <c r="J110" s="18" t="n"/>
+      <c r="K110" s="21" t="n"/>
       <c r="L110" s="24" t="n"/>
-      <c r="M110" s="20" t="n"/>
-      <c r="N110" s="18" t="n"/>
+      <c r="M110" s="18" t="n"/>
+      <c r="N110" s="21" t="n"/>
       <c r="O110" s="24" t="n"/>
-      <c r="P110" s="20" t="n"/>
-      <c r="Q110" s="18" t="n"/>
+      <c r="P110" s="18" t="n"/>
+      <c r="Q110" s="21" t="n"/>
       <c r="R110" s="24" t="n"/>
-      <c r="S110" s="20" t="n"/>
-      <c r="T110" s="18" t="n"/>
+      <c r="S110" s="18" t="n"/>
+      <c r="T110" s="21" t="n"/>
       <c r="U110" s="24" t="n"/>
-      <c r="V110" s="20" t="n"/>
+      <c r="V110" s="18" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -4550,32 +4582,32 @@
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
       <c r="B122" s="31" t="n"/>
       <c r="C122" s="24" t="n"/>
-      <c r="D122" s="20" t="n"/>
+      <c r="D122" s="18" t="n"/>
       <c r="E122" s="31" t="n"/>
       <c r="F122" s="24" t="n"/>
-      <c r="G122" s="20" t="n"/>
+      <c r="G122" s="18" t="n"/>
       <c r="H122" s="31" t="n"/>
       <c r="I122" s="24" t="n"/>
-      <c r="J122" s="20" t="n"/>
+      <c r="J122" s="18" t="n"/>
       <c r="K122" s="31" t="n"/>
       <c r="L122" s="24" t="n"/>
-      <c r="M122" s="20" t="n"/>
+      <c r="M122" s="18" t="n"/>
       <c r="N122" s="31" t="n"/>
       <c r="O122" s="24" t="n"/>
-      <c r="P122" s="20" t="n"/>
+      <c r="P122" s="18" t="n"/>
       <c r="Q122" s="31" t="n"/>
       <c r="R122" s="24" t="n"/>
-      <c r="S122" s="20" t="n"/>
+      <c r="S122" s="18" t="n"/>
       <c r="T122" s="31" t="n"/>
       <c r="U122" s="24" t="n"/>
-      <c r="V122" s="20" t="n"/>
+      <c r="V122" s="18" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -4780,25 +4812,53 @@
         </is>
       </c>
       <c r="B129" s="30" t="n"/>
-      <c r="C129" s="23" t="n"/>
+      <c r="C129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="D129" s="13" t="n"/>
       <c r="E129" s="30" t="n"/>
-      <c r="F129" s="23" t="n"/>
+      <c r="F129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="G129" s="13" t="n"/>
       <c r="H129" s="30" t="n"/>
-      <c r="I129" s="23" t="n"/>
+      <c r="I129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="J129" s="13" t="n"/>
       <c r="K129" s="30" t="n"/>
-      <c r="L129" s="23" t="n"/>
+      <c r="L129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="M129" s="13" t="n"/>
       <c r="N129" s="30" t="n"/>
-      <c r="O129" s="23" t="n"/>
+      <c r="O129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="P129" s="13" t="n"/>
       <c r="Q129" s="30" t="n"/>
-      <c r="R129" s="23" t="n"/>
+      <c r="R129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="S129" s="13" t="n"/>
       <c r="T129" s="30" t="n"/>
-      <c r="U129" s="23" t="n"/>
+      <c r="U129" s="25" t="inlineStr">
+        <is>
+          <t>鈴木信子：排泄介助</t>
+        </is>
+      </c>
       <c r="V129" s="13" t="n"/>
     </row>
     <row r="130">
@@ -4808,25 +4868,25 @@
         </is>
       </c>
       <c r="B130" s="30" t="n"/>
-      <c r="C130" s="23" t="n"/>
+      <c r="C130" s="26" t="n"/>
       <c r="D130" s="13" t="n"/>
       <c r="E130" s="30" t="n"/>
-      <c r="F130" s="23" t="n"/>
+      <c r="F130" s="26" t="n"/>
       <c r="G130" s="13" t="n"/>
       <c r="H130" s="30" t="n"/>
-      <c r="I130" s="23" t="n"/>
+      <c r="I130" s="26" t="n"/>
       <c r="J130" s="13" t="n"/>
       <c r="K130" s="30" t="n"/>
-      <c r="L130" s="23" t="n"/>
+      <c r="L130" s="26" t="n"/>
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="30" t="n"/>
-      <c r="O130" s="23" t="n"/>
+      <c r="O130" s="26" t="n"/>
       <c r="P130" s="13" t="n"/>
       <c r="Q130" s="30" t="n"/>
-      <c r="R130" s="23" t="n"/>
+      <c r="R130" s="26" t="n"/>
       <c r="S130" s="13" t="n"/>
       <c r="T130" s="30" t="n"/>
-      <c r="U130" s="23" t="n"/>
+      <c r="U130" s="26" t="n"/>
       <c r="V130" s="13" t="n"/>
     </row>
     <row r="131">
@@ -4836,25 +4896,25 @@
         </is>
       </c>
       <c r="B131" s="30" t="n"/>
-      <c r="C131" s="23" t="n"/>
+      <c r="C131" s="27" t="n"/>
       <c r="D131" s="13" t="n"/>
       <c r="E131" s="30" t="n"/>
-      <c r="F131" s="23" t="n"/>
+      <c r="F131" s="27" t="n"/>
       <c r="G131" s="13" t="n"/>
       <c r="H131" s="30" t="n"/>
-      <c r="I131" s="23" t="n"/>
+      <c r="I131" s="27" t="n"/>
       <c r="J131" s="13" t="n"/>
       <c r="K131" s="30" t="n"/>
-      <c r="L131" s="23" t="n"/>
+      <c r="L131" s="27" t="n"/>
       <c r="M131" s="13" t="n"/>
       <c r="N131" s="30" t="n"/>
-      <c r="O131" s="23" t="n"/>
+      <c r="O131" s="27" t="n"/>
       <c r="P131" s="13" t="n"/>
       <c r="Q131" s="30" t="n"/>
-      <c r="R131" s="23" t="n"/>
+      <c r="R131" s="27" t="n"/>
       <c r="S131" s="13" t="n"/>
       <c r="T131" s="30" t="n"/>
-      <c r="U131" s="23" t="n"/>
+      <c r="U131" s="27" t="n"/>
       <c r="V131" s="13" t="n"/>
     </row>
     <row r="132">
@@ -4914,32 +4974,32 @@
       <c r="V133" s="13" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="17" t="inlineStr">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
       <c r="B134" s="31" t="n"/>
       <c r="C134" s="24" t="n"/>
-      <c r="D134" s="20" t="n"/>
+      <c r="D134" s="18" t="n"/>
       <c r="E134" s="31" t="n"/>
       <c r="F134" s="24" t="n"/>
-      <c r="G134" s="20" t="n"/>
+      <c r="G134" s="18" t="n"/>
       <c r="H134" s="31" t="n"/>
       <c r="I134" s="24" t="n"/>
-      <c r="J134" s="20" t="n"/>
+      <c r="J134" s="18" t="n"/>
       <c r="K134" s="31" t="n"/>
       <c r="L134" s="24" t="n"/>
-      <c r="M134" s="20" t="n"/>
+      <c r="M134" s="18" t="n"/>
       <c r="N134" s="31" t="n"/>
       <c r="O134" s="24" t="n"/>
-      <c r="P134" s="20" t="n"/>
+      <c r="P134" s="18" t="n"/>
       <c r="Q134" s="31" t="n"/>
       <c r="R134" s="24" t="n"/>
-      <c r="S134" s="20" t="n"/>
+      <c r="S134" s="18" t="n"/>
       <c r="T134" s="31" t="n"/>
       <c r="U134" s="24" t="n"/>
-      <c r="V134" s="20" t="n"/>
+      <c r="V134" s="18" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -5250,32 +5310,32 @@
       <c r="V145" s="13" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="17" t="inlineStr">
+      <c r="A146" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
       <c r="B146" s="31" t="n"/>
       <c r="C146" s="24" t="n"/>
-      <c r="D146" s="20" t="n"/>
+      <c r="D146" s="18" t="n"/>
       <c r="E146" s="31" t="n"/>
       <c r="F146" s="24" t="n"/>
-      <c r="G146" s="20" t="n"/>
+      <c r="G146" s="18" t="n"/>
       <c r="H146" s="31" t="n"/>
       <c r="I146" s="24" t="n"/>
-      <c r="J146" s="20" t="n"/>
+      <c r="J146" s="18" t="n"/>
       <c r="K146" s="31" t="n"/>
       <c r="L146" s="24" t="n"/>
-      <c r="M146" s="20" t="n"/>
+      <c r="M146" s="18" t="n"/>
       <c r="N146" s="31" t="n"/>
       <c r="O146" s="24" t="n"/>
-      <c r="P146" s="20" t="n"/>
+      <c r="P146" s="18" t="n"/>
       <c r="Q146" s="31" t="n"/>
       <c r="R146" s="24" t="n"/>
-      <c r="S146" s="20" t="n"/>
+      <c r="S146" s="18" t="n"/>
       <c r="T146" s="31" t="n"/>
       <c r="U146" s="24" t="n"/>
-      <c r="V146" s="20" t="n"/>
+      <c r="V146" s="18" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -5586,32 +5646,32 @@
       <c r="V157" s="13" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="17" t="inlineStr">
+      <c r="A158" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
       <c r="B158" s="31" t="n"/>
       <c r="C158" s="24" t="n"/>
-      <c r="D158" s="20" t="n"/>
+      <c r="D158" s="18" t="n"/>
       <c r="E158" s="31" t="n"/>
       <c r="F158" s="24" t="n"/>
-      <c r="G158" s="20" t="n"/>
+      <c r="G158" s="18" t="n"/>
       <c r="H158" s="31" t="n"/>
       <c r="I158" s="24" t="n"/>
-      <c r="J158" s="20" t="n"/>
+      <c r="J158" s="18" t="n"/>
       <c r="K158" s="31" t="n"/>
       <c r="L158" s="24" t="n"/>
-      <c r="M158" s="20" t="n"/>
+      <c r="M158" s="18" t="n"/>
       <c r="N158" s="31" t="n"/>
       <c r="O158" s="24" t="n"/>
-      <c r="P158" s="20" t="n"/>
+      <c r="P158" s="18" t="n"/>
       <c r="Q158" s="31" t="n"/>
       <c r="R158" s="24" t="n"/>
-      <c r="S158" s="20" t="n"/>
+      <c r="S158" s="18" t="n"/>
       <c r="T158" s="31" t="n"/>
       <c r="U158" s="24" t="n"/>
-      <c r="V158" s="20" t="n"/>
+      <c r="V158" s="18" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -5950,32 +6010,32 @@
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="17" t="inlineStr">
+      <c r="A170" s="16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
       <c r="B170" s="31" t="n"/>
       <c r="C170" s="24" t="n"/>
-      <c r="D170" s="20" t="n"/>
+      <c r="D170" s="18" t="n"/>
       <c r="E170" s="31" t="n"/>
       <c r="F170" s="24" t="n"/>
-      <c r="G170" s="20" t="n"/>
+      <c r="G170" s="18" t="n"/>
       <c r="H170" s="31" t="n"/>
       <c r="I170" s="24" t="n"/>
-      <c r="J170" s="20" t="n"/>
+      <c r="J170" s="18" t="n"/>
       <c r="K170" s="31" t="n"/>
       <c r="L170" s="24" t="n"/>
-      <c r="M170" s="20" t="n"/>
+      <c r="M170" s="18" t="n"/>
       <c r="N170" s="31" t="n"/>
       <c r="O170" s="24" t="n"/>
-      <c r="P170" s="20" t="n"/>
+      <c r="P170" s="18" t="n"/>
       <c r="Q170" s="31" t="n"/>
       <c r="R170" s="24" t="n"/>
-      <c r="S170" s="20" t="n"/>
+      <c r="S170" s="18" t="n"/>
       <c r="T170" s="31" t="n"/>
       <c r="U170" s="24" t="n"/>
-      <c r="V170" s="20" t="n"/>
+      <c r="V170" s="18" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="32" t="inlineStr">
@@ -6006,83 +6066,98 @@
       <c r="V171" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="91">
+    <mergeCell ref="N57:N59"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="O129:O131"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="U117:U121"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="U129:U131"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="K57:K61"/>
+    <mergeCell ref="Q57:Q59"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="R117:R121"/>
+    <mergeCell ref="R111:R115"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="I129:I131"/>
+    <mergeCell ref="L165:L169"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F129:F131"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="T12:T14"/>
+    <mergeCell ref="T51:T53"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="L129:L131"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="N57:N59"/>
-    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="U165:U169"/>
+    <mergeCell ref="I117:I121"/>
+    <mergeCell ref="H87:H91"/>
+    <mergeCell ref="F123:F127"/>
+    <mergeCell ref="L81:L85"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="O111:O115"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="Q51:Q53"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="L117:L121"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="I123:I127"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="O165:O169"/>
+    <mergeCell ref="E75:E79"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="C111:C115"/>
+    <mergeCell ref="T75:T85"/>
+    <mergeCell ref="R123:R127"/>
+    <mergeCell ref="K54:K56"/>
+    <mergeCell ref="Q12:Q14"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="Q54:Q56"/>
+    <mergeCell ref="U111:U115"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="K1:M1"/>
     <mergeCell ref="C123:C127"/>
-    <mergeCell ref="T6:T8"/>
     <mergeCell ref="K75:K85"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="U165:U169"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="O123:O127"/>
     <mergeCell ref="F165:F169"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="I123:I127"/>
-    <mergeCell ref="O123:O127"/>
     <mergeCell ref="E54:E56"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="U117:U121"/>
     <mergeCell ref="R165:R169"/>
-    <mergeCell ref="N6:N8"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="N9:N11"/>
     <mergeCell ref="F111:F115"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="T3:T5"/>
-    <mergeCell ref="Q57:Q59"/>
-    <mergeCell ref="F123:F127"/>
     <mergeCell ref="U123:U127"/>
-    <mergeCell ref="L81:L85"/>
-    <mergeCell ref="L123:L127"/>
-    <mergeCell ref="H87:H91"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="N51:N53"/>
     <mergeCell ref="C165:C169"/>
     <mergeCell ref="T57:T59"/>
-    <mergeCell ref="O165:O169"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="R117:R121"/>
     <mergeCell ref="L111:L115"/>
-    <mergeCell ref="R111:R115"/>
-    <mergeCell ref="E75:E79"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="C111:C115"/>
-    <mergeCell ref="O111:O115"/>
-    <mergeCell ref="T75:T85"/>
-    <mergeCell ref="R123:R127"/>
-    <mergeCell ref="K54:K56"/>
     <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="L165:L169"/>
-    <mergeCell ref="K1:M1"/>
     <mergeCell ref="O117:O121"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="Q54:Q56"/>
-    <mergeCell ref="U111:U115"/>
     <mergeCell ref="B75:B85"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="Q51:Q53"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="H51:H53"/>
     <mergeCell ref="I165:I169"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="L117:L121"/>
-    <mergeCell ref="T51:T53"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="R129:R131"/>
+    <mergeCell ref="C129:C131"/>
+    <mergeCell ref="L123:L127"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/シフト早見表_7時-21時.xlsx
+++ b/シフト早見表_7時-21時.xlsx
@@ -427,21 +427,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1455,25 +1455,53 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="19" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="19" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="19" t="n"/>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="9" t="n"/>
-      <c r="N15" s="19" t="n"/>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="19" t="n"/>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="9" t="n"/>
-      <c r="T15" s="19" t="n"/>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="9" t="n"/>
     </row>
@@ -1483,25 +1511,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
+      <c r="B16" s="11" t="n"/>
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="20" t="n"/>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="20" t="n"/>
+      <c r="H16" s="11" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="20" t="n"/>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="13" t="n"/>
-      <c r="N16" s="20" t="n"/>
+      <c r="N16" s="11" t="n"/>
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="20" t="n"/>
+      <c r="Q16" s="11" t="n"/>
       <c r="R16" s="12" t="n"/>
       <c r="S16" s="13" t="n"/>
-      <c r="T16" s="20" t="n"/>
+      <c r="T16" s="11" t="n"/>
       <c r="U16" s="12" t="n"/>
       <c r="V16" s="13" t="n"/>
     </row>
@@ -1511,25 +1539,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
+      <c r="B17" s="14" t="n"/>
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="20" t="n"/>
+      <c r="E17" s="14" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="20" t="n"/>
+      <c r="H17" s="14" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="13" t="n"/>
-      <c r="K17" s="20" t="n"/>
+      <c r="K17" s="14" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="13" t="n"/>
-      <c r="N17" s="20" t="n"/>
+      <c r="N17" s="14" t="n"/>
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="20" t="n"/>
+      <c r="Q17" s="14" t="n"/>
       <c r="R17" s="12" t="n"/>
       <c r="S17" s="13" t="n"/>
-      <c r="T17" s="20" t="n"/>
+      <c r="T17" s="14" t="n"/>
       <c r="U17" s="12" t="n"/>
       <c r="V17" s="13" t="n"/>
     </row>
@@ -1539,25 +1567,53 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="20" t="n"/>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="20" t="n"/>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="20" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="13" t="n"/>
-      <c r="N18" s="20" t="n"/>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="20" t="n"/>
+      <c r="Q18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="R18" s="12" t="n"/>
       <c r="S18" s="13" t="n"/>
-      <c r="T18" s="20" t="n"/>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="n"/>
       <c r="V18" s="13" t="n"/>
     </row>
@@ -1567,25 +1623,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n"/>
+      <c r="B19" s="11" t="n"/>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="20" t="n"/>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="13" t="n"/>
-      <c r="H19" s="20" t="n"/>
+      <c r="H19" s="11" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="13" t="n"/>
-      <c r="K19" s="20" t="n"/>
+      <c r="K19" s="11" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="13" t="n"/>
-      <c r="N19" s="20" t="n"/>
+      <c r="N19" s="11" t="n"/>
       <c r="O19" s="12" t="n"/>
       <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="20" t="n"/>
+      <c r="Q19" s="11" t="n"/>
       <c r="R19" s="12" t="n"/>
       <c r="S19" s="13" t="n"/>
-      <c r="T19" s="20" t="n"/>
+      <c r="T19" s="11" t="n"/>
       <c r="U19" s="12" t="n"/>
       <c r="V19" s="13" t="n"/>
     </row>
@@ -1595,25 +1651,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
+      <c r="B20" s="14" t="n"/>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="20" t="n"/>
+      <c r="E20" s="14" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="20" t="n"/>
+      <c r="H20" s="14" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="20" t="n"/>
+      <c r="K20" s="14" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="13" t="n"/>
-      <c r="N20" s="20" t="n"/>
+      <c r="N20" s="14" t="n"/>
       <c r="O20" s="12" t="n"/>
       <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="20" t="n"/>
+      <c r="Q20" s="14" t="n"/>
       <c r="R20" s="12" t="n"/>
       <c r="S20" s="13" t="n"/>
-      <c r="T20" s="20" t="n"/>
+      <c r="T20" s="14" t="n"/>
       <c r="U20" s="12" t="n"/>
       <c r="V20" s="13" t="n"/>
     </row>
@@ -1623,25 +1679,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
+      <c r="B21" s="19" t="n"/>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="20" t="n"/>
+      <c r="E21" s="19" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="13" t="n"/>
-      <c r="H21" s="20" t="n"/>
+      <c r="H21" s="19" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="13" t="n"/>
-      <c r="K21" s="20" t="n"/>
+      <c r="K21" s="19" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="13" t="n"/>
-      <c r="N21" s="20" t="n"/>
+      <c r="N21" s="19" t="n"/>
       <c r="O21" s="12" t="n"/>
       <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="20" t="n"/>
+      <c r="Q21" s="19" t="n"/>
       <c r="R21" s="12" t="n"/>
       <c r="S21" s="13" t="n"/>
-      <c r="T21" s="20" t="n"/>
+      <c r="T21" s="19" t="n"/>
       <c r="U21" s="12" t="n"/>
       <c r="V21" s="13" t="n"/>
     </row>
@@ -1651,25 +1707,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
+      <c r="B22" s="19" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="20" t="n"/>
+      <c r="E22" s="19" t="n"/>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="13" t="n"/>
-      <c r="H22" s="20" t="n"/>
+      <c r="H22" s="19" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="20" t="n"/>
+      <c r="K22" s="19" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="13" t="n"/>
-      <c r="N22" s="20" t="n"/>
+      <c r="N22" s="19" t="n"/>
       <c r="O22" s="12" t="n"/>
       <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="20" t="n"/>
+      <c r="Q22" s="19" t="n"/>
       <c r="R22" s="12" t="n"/>
       <c r="S22" s="13" t="n"/>
-      <c r="T22" s="20" t="n"/>
+      <c r="T22" s="19" t="n"/>
       <c r="U22" s="12" t="n"/>
       <c r="V22" s="13" t="n"/>
     </row>
@@ -1679,25 +1735,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n"/>
+      <c r="B23" s="19" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="20" t="n"/>
+      <c r="E23" s="19" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="13" t="n"/>
-      <c r="H23" s="20" t="n"/>
+      <c r="H23" s="19" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="13" t="n"/>
-      <c r="K23" s="20" t="n"/>
+      <c r="K23" s="19" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="13" t="n"/>
-      <c r="N23" s="20" t="n"/>
+      <c r="N23" s="19" t="n"/>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="20" t="n"/>
+      <c r="Q23" s="19" t="n"/>
       <c r="R23" s="12" t="n"/>
       <c r="S23" s="13" t="n"/>
-      <c r="T23" s="20" t="n"/>
+      <c r="T23" s="19" t="n"/>
       <c r="U23" s="12" t="n"/>
       <c r="V23" s="13" t="n"/>
     </row>
@@ -1707,25 +1763,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
+      <c r="B24" s="19" t="n"/>
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="20" t="n"/>
+      <c r="E24" s="19" t="n"/>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="13" t="n"/>
-      <c r="H24" s="20" t="n"/>
+      <c r="H24" s="19" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="20" t="n"/>
+      <c r="K24" s="19" t="n"/>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="13" t="n"/>
-      <c r="N24" s="20" t="n"/>
+      <c r="N24" s="19" t="n"/>
       <c r="O24" s="12" t="n"/>
       <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="20" t="n"/>
+      <c r="Q24" s="19" t="n"/>
       <c r="R24" s="12" t="n"/>
       <c r="S24" s="13" t="n"/>
-      <c r="T24" s="20" t="n"/>
+      <c r="T24" s="19" t="n"/>
       <c r="U24" s="12" t="n"/>
       <c r="V24" s="13" t="n"/>
     </row>
@@ -1735,25 +1791,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
+      <c r="B25" s="19" t="n"/>
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="20" t="n"/>
+      <c r="E25" s="19" t="n"/>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="13" t="n"/>
-      <c r="H25" s="20" t="n"/>
+      <c r="H25" s="19" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="13" t="n"/>
-      <c r="K25" s="20" t="n"/>
+      <c r="K25" s="19" t="n"/>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="13" t="n"/>
-      <c r="N25" s="20" t="n"/>
+      <c r="N25" s="19" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="13" t="n"/>
-      <c r="Q25" s="20" t="n"/>
+      <c r="Q25" s="19" t="n"/>
       <c r="R25" s="12" t="n"/>
       <c r="S25" s="13" t="n"/>
-      <c r="T25" s="20" t="n"/>
+      <c r="T25" s="19" t="n"/>
       <c r="U25" s="12" t="n"/>
       <c r="V25" s="13" t="n"/>
     </row>
@@ -1763,25 +1819,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n"/>
+      <c r="B26" s="20" t="n"/>
       <c r="C26" s="17" t="n"/>
       <c r="D26" s="18" t="n"/>
-      <c r="E26" s="21" t="n"/>
+      <c r="E26" s="20" t="n"/>
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="18" t="n"/>
-      <c r="H26" s="21" t="n"/>
+      <c r="H26" s="20" t="n"/>
       <c r="I26" s="17" t="n"/>
       <c r="J26" s="18" t="n"/>
-      <c r="K26" s="21" t="n"/>
+      <c r="K26" s="20" t="n"/>
       <c r="L26" s="17" t="n"/>
       <c r="M26" s="18" t="n"/>
-      <c r="N26" s="21" t="n"/>
+      <c r="N26" s="20" t="n"/>
       <c r="O26" s="17" t="n"/>
       <c r="P26" s="18" t="n"/>
-      <c r="Q26" s="21" t="n"/>
+      <c r="Q26" s="20" t="n"/>
       <c r="R26" s="17" t="n"/>
       <c r="S26" s="18" t="n"/>
-      <c r="T26" s="21" t="n"/>
+      <c r="T26" s="20" t="n"/>
       <c r="U26" s="17" t="n"/>
       <c r="V26" s="18" t="n"/>
     </row>
@@ -1791,25 +1847,25 @@
           <t>9:00</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n"/>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="19" t="n"/>
+      <c r="E27" s="21" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="19" t="n"/>
+      <c r="H27" s="21" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="19" t="n"/>
+      <c r="K27" s="21" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="9" t="n"/>
-      <c r="N27" s="19" t="n"/>
+      <c r="N27" s="21" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="19" t="n"/>
+      <c r="Q27" s="21" t="n"/>
       <c r="R27" s="8" t="n"/>
       <c r="S27" s="9" t="n"/>
-      <c r="T27" s="19" t="n"/>
+      <c r="T27" s="21" t="n"/>
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="9" t="n"/>
     </row>
@@ -1819,25 +1875,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
+      <c r="B28" s="19" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="20" t="n"/>
+      <c r="E28" s="19" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="13" t="n"/>
-      <c r="H28" s="20" t="n"/>
+      <c r="H28" s="19" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="20" t="n"/>
+      <c r="K28" s="19" t="n"/>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="13" t="n"/>
-      <c r="N28" s="20" t="n"/>
+      <c r="N28" s="19" t="n"/>
       <c r="O28" s="12" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="20" t="n"/>
+      <c r="Q28" s="19" t="n"/>
       <c r="R28" s="12" t="n"/>
       <c r="S28" s="13" t="n"/>
-      <c r="T28" s="20" t="n"/>
+      <c r="T28" s="19" t="n"/>
       <c r="U28" s="12" t="n"/>
       <c r="V28" s="13" t="n"/>
     </row>
@@ -1847,25 +1903,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n"/>
+      <c r="B29" s="19" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="20" t="n"/>
+      <c r="E29" s="19" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="13" t="n"/>
-      <c r="H29" s="20" t="n"/>
+      <c r="H29" s="19" t="n"/>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="13" t="n"/>
-      <c r="K29" s="20" t="n"/>
+      <c r="K29" s="19" t="n"/>
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="13" t="n"/>
-      <c r="N29" s="20" t="n"/>
+      <c r="N29" s="19" t="n"/>
       <c r="O29" s="12" t="n"/>
       <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="20" t="n"/>
+      <c r="Q29" s="19" t="n"/>
       <c r="R29" s="12" t="n"/>
       <c r="S29" s="13" t="n"/>
-      <c r="T29" s="20" t="n"/>
+      <c r="T29" s="19" t="n"/>
       <c r="U29" s="12" t="n"/>
       <c r="V29" s="13" t="n"/>
     </row>
@@ -1875,25 +1931,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
+      <c r="B30" s="19" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="20" t="n"/>
+      <c r="E30" s="19" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="13" t="n"/>
-      <c r="H30" s="20" t="n"/>
+      <c r="H30" s="19" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="20" t="n"/>
+      <c r="K30" s="19" t="n"/>
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="13" t="n"/>
-      <c r="N30" s="20" t="n"/>
+      <c r="N30" s="19" t="n"/>
       <c r="O30" s="12" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="20" t="n"/>
+      <c r="Q30" s="19" t="n"/>
       <c r="R30" s="12" t="n"/>
       <c r="S30" s="13" t="n"/>
-      <c r="T30" s="20" t="n"/>
+      <c r="T30" s="19" t="n"/>
       <c r="U30" s="12" t="n"/>
       <c r="V30" s="13" t="n"/>
     </row>
@@ -1903,25 +1959,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n"/>
+      <c r="B31" s="19" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="20" t="n"/>
+      <c r="E31" s="19" t="n"/>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="13" t="n"/>
-      <c r="H31" s="20" t="n"/>
+      <c r="H31" s="19" t="n"/>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="13" t="n"/>
-      <c r="K31" s="20" t="n"/>
+      <c r="K31" s="19" t="n"/>
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="13" t="n"/>
-      <c r="N31" s="20" t="n"/>
+      <c r="N31" s="19" t="n"/>
       <c r="O31" s="12" t="n"/>
       <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="20" t="n"/>
+      <c r="Q31" s="19" t="n"/>
       <c r="R31" s="12" t="n"/>
       <c r="S31" s="13" t="n"/>
-      <c r="T31" s="20" t="n"/>
+      <c r="T31" s="19" t="n"/>
       <c r="U31" s="12" t="n"/>
       <c r="V31" s="13" t="n"/>
     </row>
@@ -1931,25 +1987,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n"/>
+      <c r="B32" s="19" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="20" t="n"/>
+      <c r="E32" s="19" t="n"/>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="13" t="n"/>
-      <c r="H32" s="20" t="n"/>
+      <c r="H32" s="19" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="20" t="n"/>
+      <c r="K32" s="19" t="n"/>
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="13" t="n"/>
-      <c r="N32" s="20" t="n"/>
+      <c r="N32" s="19" t="n"/>
       <c r="O32" s="12" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="20" t="n"/>
+      <c r="Q32" s="19" t="n"/>
       <c r="R32" s="12" t="n"/>
       <c r="S32" s="13" t="n"/>
-      <c r="T32" s="20" t="n"/>
+      <c r="T32" s="19" t="n"/>
       <c r="U32" s="12" t="n"/>
       <c r="V32" s="13" t="n"/>
     </row>
@@ -1959,25 +2015,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n"/>
+      <c r="B33" s="19" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="20" t="n"/>
+      <c r="E33" s="19" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="13" t="n"/>
-      <c r="H33" s="20" t="n"/>
+      <c r="H33" s="19" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="13" t="n"/>
-      <c r="K33" s="20" t="n"/>
+      <c r="K33" s="19" t="n"/>
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="13" t="n"/>
-      <c r="N33" s="20" t="n"/>
+      <c r="N33" s="19" t="n"/>
       <c r="O33" s="12" t="n"/>
       <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="20" t="n"/>
+      <c r="Q33" s="19" t="n"/>
       <c r="R33" s="12" t="n"/>
       <c r="S33" s="13" t="n"/>
-      <c r="T33" s="20" t="n"/>
+      <c r="T33" s="19" t="n"/>
       <c r="U33" s="12" t="n"/>
       <c r="V33" s="13" t="n"/>
     </row>
@@ -1987,25 +2043,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n"/>
+      <c r="B34" s="19" t="n"/>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="20" t="n"/>
+      <c r="E34" s="19" t="n"/>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="13" t="n"/>
-      <c r="H34" s="20" t="n"/>
+      <c r="H34" s="19" t="n"/>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="20" t="n"/>
+      <c r="K34" s="19" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="13" t="n"/>
-      <c r="N34" s="20" t="n"/>
+      <c r="N34" s="19" t="n"/>
       <c r="O34" s="12" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="20" t="n"/>
+      <c r="Q34" s="19" t="n"/>
       <c r="R34" s="12" t="n"/>
       <c r="S34" s="13" t="n"/>
-      <c r="T34" s="20" t="n"/>
+      <c r="T34" s="19" t="n"/>
       <c r="U34" s="12" t="n"/>
       <c r="V34" s="13" t="n"/>
     </row>
@@ -2015,25 +2071,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n"/>
+      <c r="B35" s="19" t="n"/>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="20" t="n"/>
+      <c r="E35" s="19" t="n"/>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="13" t="n"/>
-      <c r="H35" s="20" t="n"/>
+      <c r="H35" s="19" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="13" t="n"/>
-      <c r="K35" s="20" t="n"/>
+      <c r="K35" s="19" t="n"/>
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="13" t="n"/>
-      <c r="N35" s="20" t="n"/>
+      <c r="N35" s="19" t="n"/>
       <c r="O35" s="12" t="n"/>
       <c r="P35" s="13" t="n"/>
-      <c r="Q35" s="20" t="n"/>
+      <c r="Q35" s="19" t="n"/>
       <c r="R35" s="12" t="n"/>
       <c r="S35" s="13" t="n"/>
-      <c r="T35" s="20" t="n"/>
+      <c r="T35" s="19" t="n"/>
       <c r="U35" s="12" t="n"/>
       <c r="V35" s="13" t="n"/>
     </row>
@@ -2043,25 +2099,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n"/>
+      <c r="B36" s="19" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="20" t="n"/>
+      <c r="E36" s="19" t="n"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="13" t="n"/>
-      <c r="H36" s="20" t="n"/>
+      <c r="H36" s="19" t="n"/>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="20" t="n"/>
+      <c r="K36" s="19" t="n"/>
       <c r="L36" s="12" t="n"/>
       <c r="M36" s="13" t="n"/>
-      <c r="N36" s="20" t="n"/>
+      <c r="N36" s="19" t="n"/>
       <c r="O36" s="12" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="20" t="n"/>
+      <c r="Q36" s="19" t="n"/>
       <c r="R36" s="12" t="n"/>
       <c r="S36" s="13" t="n"/>
-      <c r="T36" s="20" t="n"/>
+      <c r="T36" s="19" t="n"/>
       <c r="U36" s="12" t="n"/>
       <c r="V36" s="13" t="n"/>
     </row>
@@ -2071,25 +2127,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n"/>
+      <c r="B37" s="19" t="n"/>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="20" t="n"/>
+      <c r="E37" s="19" t="n"/>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="13" t="n"/>
-      <c r="H37" s="20" t="n"/>
+      <c r="H37" s="19" t="n"/>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="13" t="n"/>
-      <c r="K37" s="20" t="n"/>
+      <c r="K37" s="19" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="13" t="n"/>
-      <c r="N37" s="20" t="n"/>
+      <c r="N37" s="19" t="n"/>
       <c r="O37" s="12" t="n"/>
       <c r="P37" s="13" t="n"/>
-      <c r="Q37" s="20" t="n"/>
+      <c r="Q37" s="19" t="n"/>
       <c r="R37" s="12" t="n"/>
       <c r="S37" s="13" t="n"/>
-      <c r="T37" s="20" t="n"/>
+      <c r="T37" s="19" t="n"/>
       <c r="U37" s="12" t="n"/>
       <c r="V37" s="13" t="n"/>
     </row>
@@ -2099,25 +2155,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
+      <c r="B38" s="20" t="n"/>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="18" t="n"/>
-      <c r="E38" s="21" t="n"/>
+      <c r="E38" s="20" t="n"/>
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="18" t="n"/>
-      <c r="H38" s="21" t="n"/>
+      <c r="H38" s="20" t="n"/>
       <c r="I38" s="17" t="n"/>
       <c r="J38" s="18" t="n"/>
-      <c r="K38" s="21" t="n"/>
+      <c r="K38" s="20" t="n"/>
       <c r="L38" s="17" t="n"/>
       <c r="M38" s="18" t="n"/>
-      <c r="N38" s="21" t="n"/>
+      <c r="N38" s="20" t="n"/>
       <c r="O38" s="17" t="n"/>
       <c r="P38" s="18" t="n"/>
-      <c r="Q38" s="21" t="n"/>
+      <c r="Q38" s="20" t="n"/>
       <c r="R38" s="17" t="n"/>
       <c r="S38" s="18" t="n"/>
-      <c r="T38" s="21" t="n"/>
+      <c r="T38" s="20" t="n"/>
       <c r="U38" s="17" t="n"/>
       <c r="V38" s="18" t="n"/>
     </row>
@@ -2127,25 +2183,25 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="19" t="n"/>
+      <c r="E39" s="21" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="19" t="n"/>
+      <c r="H39" s="21" t="n"/>
       <c r="I39" s="8" t="n"/>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="19" t="n"/>
+      <c r="K39" s="21" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="9" t="n"/>
-      <c r="N39" s="19" t="n"/>
+      <c r="N39" s="21" t="n"/>
       <c r="O39" s="8" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="19" t="n"/>
+      <c r="Q39" s="21" t="n"/>
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="9" t="n"/>
-      <c r="T39" s="19" t="n"/>
+      <c r="T39" s="21" t="n"/>
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="9" t="n"/>
     </row>
@@ -2155,25 +2211,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n"/>
+      <c r="B40" s="19" t="n"/>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="20" t="n"/>
+      <c r="E40" s="19" t="n"/>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="13" t="n"/>
-      <c r="H40" s="20" t="n"/>
+      <c r="H40" s="19" t="n"/>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="20" t="n"/>
+      <c r="K40" s="19" t="n"/>
       <c r="L40" s="12" t="n"/>
       <c r="M40" s="13" t="n"/>
-      <c r="N40" s="20" t="n"/>
+      <c r="N40" s="19" t="n"/>
       <c r="O40" s="12" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="20" t="n"/>
+      <c r="Q40" s="19" t="n"/>
       <c r="R40" s="12" t="n"/>
       <c r="S40" s="13" t="n"/>
-      <c r="T40" s="20" t="n"/>
+      <c r="T40" s="19" t="n"/>
       <c r="U40" s="12" t="n"/>
       <c r="V40" s="13" t="n"/>
     </row>
@@ -2183,25 +2239,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n"/>
+      <c r="B41" s="19" t="n"/>
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="20" t="n"/>
+      <c r="E41" s="19" t="n"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="13" t="n"/>
-      <c r="H41" s="20" t="n"/>
+      <c r="H41" s="19" t="n"/>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="13" t="n"/>
-      <c r="K41" s="20" t="n"/>
+      <c r="K41" s="19" t="n"/>
       <c r="L41" s="12" t="n"/>
       <c r="M41" s="13" t="n"/>
-      <c r="N41" s="20" t="n"/>
+      <c r="N41" s="19" t="n"/>
       <c r="O41" s="12" t="n"/>
       <c r="P41" s="13" t="n"/>
-      <c r="Q41" s="20" t="n"/>
+      <c r="Q41" s="19" t="n"/>
       <c r="R41" s="12" t="n"/>
       <c r="S41" s="13" t="n"/>
-      <c r="T41" s="20" t="n"/>
+      <c r="T41" s="19" t="n"/>
       <c r="U41" s="12" t="n"/>
       <c r="V41" s="13" t="n"/>
     </row>
@@ -2211,25 +2267,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n"/>
+      <c r="B42" s="19" t="n"/>
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="20" t="n"/>
+      <c r="E42" s="19" t="n"/>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="13" t="n"/>
-      <c r="H42" s="20" t="n"/>
+      <c r="H42" s="19" t="n"/>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="20" t="n"/>
+      <c r="K42" s="19" t="n"/>
       <c r="L42" s="12" t="n"/>
       <c r="M42" s="13" t="n"/>
-      <c r="N42" s="20" t="n"/>
+      <c r="N42" s="19" t="n"/>
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="20" t="n"/>
+      <c r="Q42" s="19" t="n"/>
       <c r="R42" s="12" t="n"/>
       <c r="S42" s="13" t="n"/>
-      <c r="T42" s="20" t="n"/>
+      <c r="T42" s="19" t="n"/>
       <c r="U42" s="12" t="n"/>
       <c r="V42" s="13" t="n"/>
     </row>
@@ -2239,25 +2295,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n"/>
+      <c r="B43" s="19" t="n"/>
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="20" t="n"/>
+      <c r="E43" s="19" t="n"/>
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="13" t="n"/>
-      <c r="H43" s="20" t="n"/>
+      <c r="H43" s="19" t="n"/>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="13" t="n"/>
-      <c r="K43" s="20" t="n"/>
+      <c r="K43" s="19" t="n"/>
       <c r="L43" s="12" t="n"/>
       <c r="M43" s="13" t="n"/>
-      <c r="N43" s="20" t="n"/>
+      <c r="N43" s="19" t="n"/>
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="13" t="n"/>
-      <c r="Q43" s="20" t="n"/>
+      <c r="Q43" s="19" t="n"/>
       <c r="R43" s="12" t="n"/>
       <c r="S43" s="13" t="n"/>
-      <c r="T43" s="20" t="n"/>
+      <c r="T43" s="19" t="n"/>
       <c r="U43" s="12" t="n"/>
       <c r="V43" s="13" t="n"/>
     </row>
@@ -2267,25 +2323,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n"/>
+      <c r="B44" s="19" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="20" t="n"/>
+      <c r="E44" s="19" t="n"/>
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="13" t="n"/>
-      <c r="H44" s="20" t="n"/>
+      <c r="H44" s="19" t="n"/>
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="20" t="n"/>
+      <c r="K44" s="19" t="n"/>
       <c r="L44" s="12" t="n"/>
       <c r="M44" s="13" t="n"/>
-      <c r="N44" s="20" t="n"/>
+      <c r="N44" s="19" t="n"/>
       <c r="O44" s="12" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="20" t="n"/>
+      <c r="Q44" s="19" t="n"/>
       <c r="R44" s="12" t="n"/>
       <c r="S44" s="13" t="n"/>
-      <c r="T44" s="20" t="n"/>
+      <c r="T44" s="19" t="n"/>
       <c r="U44" s="12" t="n"/>
       <c r="V44" s="13" t="n"/>
     </row>
@@ -2295,25 +2351,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n"/>
+      <c r="B45" s="19" t="n"/>
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="20" t="n"/>
+      <c r="E45" s="19" t="n"/>
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="13" t="n"/>
-      <c r="H45" s="20" t="n"/>
+      <c r="H45" s="19" t="n"/>
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="13" t="n"/>
-      <c r="K45" s="20" t="n"/>
+      <c r="K45" s="19" t="n"/>
       <c r="L45" s="12" t="n"/>
       <c r="M45" s="13" t="n"/>
-      <c r="N45" s="20" t="n"/>
+      <c r="N45" s="19" t="n"/>
       <c r="O45" s="12" t="n"/>
       <c r="P45" s="13" t="n"/>
-      <c r="Q45" s="20" t="n"/>
+      <c r="Q45" s="19" t="n"/>
       <c r="R45" s="12" t="n"/>
       <c r="S45" s="13" t="n"/>
-      <c r="T45" s="20" t="n"/>
+      <c r="T45" s="19" t="n"/>
       <c r="U45" s="12" t="n"/>
       <c r="V45" s="13" t="n"/>
     </row>
@@ -2323,25 +2379,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n"/>
+      <c r="B46" s="19" t="n"/>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="20" t="n"/>
+      <c r="E46" s="19" t="n"/>
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="13" t="n"/>
-      <c r="H46" s="20" t="n"/>
+      <c r="H46" s="19" t="n"/>
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="20" t="n"/>
+      <c r="K46" s="19" t="n"/>
       <c r="L46" s="12" t="n"/>
       <c r="M46" s="13" t="n"/>
-      <c r="N46" s="20" t="n"/>
+      <c r="N46" s="19" t="n"/>
       <c r="O46" s="12" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="20" t="n"/>
+      <c r="Q46" s="19" t="n"/>
       <c r="R46" s="12" t="n"/>
       <c r="S46" s="13" t="n"/>
-      <c r="T46" s="20" t="n"/>
+      <c r="T46" s="19" t="n"/>
       <c r="U46" s="12" t="n"/>
       <c r="V46" s="13" t="n"/>
     </row>
@@ -2351,25 +2407,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n"/>
+      <c r="B47" s="19" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="20" t="n"/>
+      <c r="E47" s="19" t="n"/>
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="13" t="n"/>
-      <c r="H47" s="20" t="n"/>
+      <c r="H47" s="19" t="n"/>
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="13" t="n"/>
-      <c r="K47" s="20" t="n"/>
+      <c r="K47" s="19" t="n"/>
       <c r="L47" s="12" t="n"/>
       <c r="M47" s="13" t="n"/>
-      <c r="N47" s="20" t="n"/>
+      <c r="N47" s="19" t="n"/>
       <c r="O47" s="12" t="n"/>
       <c r="P47" s="13" t="n"/>
-      <c r="Q47" s="20" t="n"/>
+      <c r="Q47" s="19" t="n"/>
       <c r="R47" s="12" t="n"/>
       <c r="S47" s="13" t="n"/>
-      <c r="T47" s="20" t="n"/>
+      <c r="T47" s="19" t="n"/>
       <c r="U47" s="12" t="n"/>
       <c r="V47" s="13" t="n"/>
     </row>
@@ -2379,25 +2435,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B48" s="20" t="n"/>
+      <c r="B48" s="19" t="n"/>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="20" t="n"/>
+      <c r="E48" s="19" t="n"/>
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="13" t="n"/>
-      <c r="H48" s="20" t="n"/>
+      <c r="H48" s="19" t="n"/>
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="20" t="n"/>
+      <c r="K48" s="19" t="n"/>
       <c r="L48" s="12" t="n"/>
       <c r="M48" s="13" t="n"/>
-      <c r="N48" s="20" t="n"/>
+      <c r="N48" s="19" t="n"/>
       <c r="O48" s="12" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="20" t="n"/>
+      <c r="Q48" s="19" t="n"/>
       <c r="R48" s="12" t="n"/>
       <c r="S48" s="13" t="n"/>
-      <c r="T48" s="20" t="n"/>
+      <c r="T48" s="19" t="n"/>
       <c r="U48" s="12" t="n"/>
       <c r="V48" s="13" t="n"/>
     </row>
@@ -2407,25 +2463,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n"/>
+      <c r="B49" s="19" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="20" t="n"/>
+      <c r="E49" s="19" t="n"/>
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="13" t="n"/>
-      <c r="H49" s="20" t="n"/>
+      <c r="H49" s="19" t="n"/>
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="13" t="n"/>
-      <c r="K49" s="20" t="n"/>
+      <c r="K49" s="19" t="n"/>
       <c r="L49" s="12" t="n"/>
       <c r="M49" s="13" t="n"/>
-      <c r="N49" s="20" t="n"/>
+      <c r="N49" s="19" t="n"/>
       <c r="O49" s="12" t="n"/>
       <c r="P49" s="13" t="n"/>
-      <c r="Q49" s="20" t="n"/>
+      <c r="Q49" s="19" t="n"/>
       <c r="R49" s="12" t="n"/>
       <c r="S49" s="13" t="n"/>
-      <c r="T49" s="20" t="n"/>
+      <c r="T49" s="19" t="n"/>
       <c r="U49" s="12" t="n"/>
       <c r="V49" s="13" t="n"/>
     </row>
@@ -2435,25 +2491,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
+      <c r="B50" s="20" t="n"/>
       <c r="C50" s="17" t="n"/>
       <c r="D50" s="18" t="n"/>
-      <c r="E50" s="21" t="n"/>
+      <c r="E50" s="20" t="n"/>
       <c r="F50" s="17" t="n"/>
       <c r="G50" s="18" t="n"/>
-      <c r="H50" s="21" t="n"/>
+      <c r="H50" s="20" t="n"/>
       <c r="I50" s="17" t="n"/>
       <c r="J50" s="18" t="n"/>
-      <c r="K50" s="21" t="n"/>
+      <c r="K50" s="20" t="n"/>
       <c r="L50" s="17" t="n"/>
       <c r="M50" s="18" t="n"/>
-      <c r="N50" s="21" t="n"/>
+      <c r="N50" s="20" t="n"/>
       <c r="O50" s="17" t="n"/>
       <c r="P50" s="18" t="n"/>
-      <c r="Q50" s="21" t="n"/>
+      <c r="Q50" s="20" t="n"/>
       <c r="R50" s="17" t="n"/>
       <c r="S50" s="18" t="n"/>
-      <c r="T50" s="21" t="n"/>
+      <c r="T50" s="20" t="n"/>
       <c r="U50" s="17" t="n"/>
       <c r="V50" s="18" t="n"/>
     </row>
@@ -2463,41 +2519,25 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n"/>
+      <c r="B51" s="21" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="19" t="n"/>
+      <c r="E51" s="21" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：食事排泄</t>
-        </is>
-      </c>
+      <c r="H51" s="21" t="n"/>
       <c r="I51" s="8" t="n"/>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="19" t="n"/>
+      <c r="K51" s="21" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="9" t="n"/>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：食事排泄</t>
-        </is>
-      </c>
+      <c r="N51" s="21" t="n"/>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：食事排泄</t>
-        </is>
-      </c>
+      <c r="Q51" s="21" t="n"/>
       <c r="R51" s="8" t="n"/>
       <c r="S51" s="9" t="n"/>
-      <c r="T51" s="7" t="inlineStr">
-        <is>
-          <t>林郁子：食事排泄</t>
-        </is>
-      </c>
+      <c r="T51" s="21" t="n"/>
       <c r="U51" s="8" t="n"/>
       <c r="V51" s="9" t="n"/>
     </row>
@@ -2507,25 +2547,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n"/>
+      <c r="B52" s="19" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="13" t="n"/>
-      <c r="E52" s="20" t="n"/>
+      <c r="E52" s="19" t="n"/>
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="13" t="n"/>
-      <c r="H52" s="11" t="n"/>
+      <c r="H52" s="19" t="n"/>
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="20" t="n"/>
+      <c r="K52" s="19" t="n"/>
       <c r="L52" s="12" t="n"/>
       <c r="M52" s="13" t="n"/>
-      <c r="N52" s="11" t="n"/>
+      <c r="N52" s="19" t="n"/>
       <c r="O52" s="12" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="11" t="n"/>
+      <c r="Q52" s="19" t="n"/>
       <c r="R52" s="12" t="n"/>
       <c r="S52" s="13" t="n"/>
-      <c r="T52" s="11" t="n"/>
+      <c r="T52" s="19" t="n"/>
       <c r="U52" s="12" t="n"/>
       <c r="V52" s="13" t="n"/>
     </row>
@@ -2535,25 +2575,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
+      <c r="B53" s="19" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="20" t="n"/>
+      <c r="E53" s="19" t="n"/>
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="13" t="n"/>
-      <c r="H53" s="14" t="n"/>
+      <c r="H53" s="19" t="n"/>
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="13" t="n"/>
-      <c r="K53" s="20" t="n"/>
+      <c r="K53" s="19" t="n"/>
       <c r="L53" s="12" t="n"/>
       <c r="M53" s="13" t="n"/>
-      <c r="N53" s="14" t="n"/>
+      <c r="N53" s="19" t="n"/>
       <c r="O53" s="12" t="n"/>
       <c r="P53" s="13" t="n"/>
-      <c r="Q53" s="14" t="n"/>
+      <c r="Q53" s="19" t="n"/>
       <c r="R53" s="12" t="n"/>
       <c r="S53" s="13" t="n"/>
-      <c r="T53" s="14" t="n"/>
+      <c r="T53" s="19" t="n"/>
       <c r="U53" s="12" t="n"/>
       <c r="V53" s="13" t="n"/>
     </row>
@@ -2577,7 +2617,7 @@
       </c>
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="13" t="n"/>
-      <c r="H54" s="20" t="n"/>
+      <c r="H54" s="19" t="n"/>
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="15" t="inlineStr">
@@ -2587,7 +2627,7 @@
       </c>
       <c r="L54" s="12" t="n"/>
       <c r="M54" s="13" t="n"/>
-      <c r="N54" s="20" t="n"/>
+      <c r="N54" s="19" t="n"/>
       <c r="O54" s="12" t="n"/>
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="15" t="inlineStr">
@@ -2597,7 +2637,7 @@
       </c>
       <c r="R54" s="12" t="n"/>
       <c r="S54" s="13" t="n"/>
-      <c r="T54" s="20" t="n"/>
+      <c r="T54" s="19" t="n"/>
       <c r="U54" s="12" t="n"/>
       <c r="V54" s="13" t="n"/>
     </row>
@@ -2613,19 +2653,19 @@
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="13" t="n"/>
-      <c r="H55" s="20" t="n"/>
+      <c r="H55" s="19" t="n"/>
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="13" t="n"/>
       <c r="K55" s="11" t="n"/>
       <c r="L55" s="12" t="n"/>
       <c r="M55" s="13" t="n"/>
-      <c r="N55" s="20" t="n"/>
+      <c r="N55" s="19" t="n"/>
       <c r="O55" s="12" t="n"/>
       <c r="P55" s="13" t="n"/>
       <c r="Q55" s="11" t="n"/>
       <c r="R55" s="12" t="n"/>
       <c r="S55" s="13" t="n"/>
-      <c r="T55" s="20" t="n"/>
+      <c r="T55" s="19" t="n"/>
       <c r="U55" s="12" t="n"/>
       <c r="V55" s="13" t="n"/>
     </row>
@@ -2641,19 +2681,19 @@
       <c r="E56" s="14" t="n"/>
       <c r="F56" s="12" t="n"/>
       <c r="G56" s="13" t="n"/>
-      <c r="H56" s="20" t="n"/>
+      <c r="H56" s="19" t="n"/>
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="12" t="n"/>
       <c r="M56" s="13" t="n"/>
-      <c r="N56" s="20" t="n"/>
+      <c r="N56" s="19" t="n"/>
       <c r="O56" s="12" t="n"/>
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="14" t="n"/>
       <c r="R56" s="12" t="n"/>
       <c r="S56" s="13" t="n"/>
-      <c r="T56" s="20" t="n"/>
+      <c r="T56" s="19" t="n"/>
       <c r="U56" s="12" t="n"/>
       <c r="V56" s="13" t="n"/>
     </row>
@@ -2663,7 +2703,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n"/>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>上村春子：掃除</t>
+        </is>
+      </c>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="13" t="n"/>
       <c r="E57" s="15" t="inlineStr">
@@ -2715,7 +2759,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n"/>
+      <c r="B58" s="11" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="13" t="n"/>
       <c r="E58" s="11" t="n"/>
@@ -2743,7 +2787,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
+      <c r="B59" s="11" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="13" t="n"/>
       <c r="E59" s="14" t="n"/>
@@ -2771,25 +2815,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B60" s="20" t="n"/>
+      <c r="B60" s="11" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="20" t="n"/>
+      <c r="E60" s="19" t="n"/>
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="20" t="n"/>
+      <c r="H60" s="19" t="n"/>
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="11" t="n"/>
       <c r="L60" s="12" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="N60" s="20" t="n"/>
+      <c r="N60" s="19" t="n"/>
       <c r="O60" s="12" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="20" t="n"/>
+      <c r="Q60" s="19" t="n"/>
       <c r="R60" s="12" t="n"/>
       <c r="S60" s="13" t="n"/>
-      <c r="T60" s="20" t="n"/>
+      <c r="T60" s="19" t="n"/>
       <c r="U60" s="12" t="n"/>
       <c r="V60" s="13" t="n"/>
     </row>
@@ -2799,25 +2843,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
+      <c r="B61" s="14" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="13" t="n"/>
-      <c r="E61" s="20" t="n"/>
+      <c r="E61" s="19" t="n"/>
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="20" t="n"/>
+      <c r="H61" s="19" t="n"/>
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="13" t="n"/>
       <c r="K61" s="14" t="n"/>
       <c r="L61" s="12" t="n"/>
       <c r="M61" s="13" t="n"/>
-      <c r="N61" s="20" t="n"/>
+      <c r="N61" s="19" t="n"/>
       <c r="O61" s="12" t="n"/>
       <c r="P61" s="13" t="n"/>
-      <c r="Q61" s="20" t="n"/>
+      <c r="Q61" s="19" t="n"/>
       <c r="R61" s="12" t="n"/>
       <c r="S61" s="13" t="n"/>
-      <c r="T61" s="20" t="n"/>
+      <c r="T61" s="19" t="n"/>
       <c r="U61" s="12" t="n"/>
       <c r="V61" s="13" t="n"/>
     </row>
@@ -2827,25 +2871,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B62" s="21" t="n"/>
+      <c r="B62" s="20" t="n"/>
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="18" t="n"/>
-      <c r="E62" s="21" t="n"/>
+      <c r="E62" s="20" t="n"/>
       <c r="F62" s="17" t="n"/>
       <c r="G62" s="18" t="n"/>
-      <c r="H62" s="21" t="n"/>
+      <c r="H62" s="20" t="n"/>
       <c r="I62" s="17" t="n"/>
       <c r="J62" s="18" t="n"/>
-      <c r="K62" s="21" t="n"/>
+      <c r="K62" s="20" t="n"/>
       <c r="L62" s="17" t="n"/>
       <c r="M62" s="18" t="n"/>
-      <c r="N62" s="21" t="n"/>
+      <c r="N62" s="20" t="n"/>
       <c r="O62" s="17" t="n"/>
       <c r="P62" s="18" t="n"/>
-      <c r="Q62" s="21" t="n"/>
+      <c r="Q62" s="20" t="n"/>
       <c r="R62" s="17" t="n"/>
       <c r="S62" s="18" t="n"/>
-      <c r="T62" s="21" t="n"/>
+      <c r="T62" s="20" t="n"/>
       <c r="U62" s="17" t="n"/>
       <c r="V62" s="18" t="n"/>
     </row>
@@ -2855,25 +2899,53 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="C63" s="22" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="19" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="F63" s="22" t="n"/>
       <c r="G63" s="9" t="n"/>
-      <c r="H63" s="19" t="n"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="I63" s="22" t="n"/>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="19" t="n"/>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="L63" s="22" t="n"/>
       <c r="M63" s="9" t="n"/>
-      <c r="N63" s="19" t="n"/>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="O63" s="22" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="19" t="n"/>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="R63" s="22" t="n"/>
       <c r="S63" s="9" t="n"/>
-      <c r="T63" s="19" t="n"/>
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="U63" s="22" t="n"/>
       <c r="V63" s="9" t="n"/>
     </row>
@@ -2883,25 +2955,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B64" s="20" t="n"/>
+      <c r="B64" s="11" t="n"/>
       <c r="C64" s="23" t="n"/>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="20" t="n"/>
+      <c r="E64" s="11" t="n"/>
       <c r="F64" s="23" t="n"/>
       <c r="G64" s="13" t="n"/>
-      <c r="H64" s="20" t="n"/>
+      <c r="H64" s="11" t="n"/>
       <c r="I64" s="23" t="n"/>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="20" t="n"/>
+      <c r="K64" s="11" t="n"/>
       <c r="L64" s="23" t="n"/>
       <c r="M64" s="13" t="n"/>
-      <c r="N64" s="20" t="n"/>
+      <c r="N64" s="11" t="n"/>
       <c r="O64" s="23" t="n"/>
       <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="20" t="n"/>
+      <c r="Q64" s="11" t="n"/>
       <c r="R64" s="23" t="n"/>
       <c r="S64" s="13" t="n"/>
-      <c r="T64" s="20" t="n"/>
+      <c r="T64" s="11" t="n"/>
       <c r="U64" s="23" t="n"/>
       <c r="V64" s="13" t="n"/>
     </row>
@@ -2911,25 +2983,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B65" s="20" t="n"/>
+      <c r="B65" s="14" t="n"/>
       <c r="C65" s="23" t="n"/>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="20" t="n"/>
+      <c r="E65" s="14" t="n"/>
       <c r="F65" s="23" t="n"/>
       <c r="G65" s="13" t="n"/>
-      <c r="H65" s="20" t="n"/>
+      <c r="H65" s="14" t="n"/>
       <c r="I65" s="23" t="n"/>
       <c r="J65" s="13" t="n"/>
-      <c r="K65" s="20" t="n"/>
+      <c r="K65" s="14" t="n"/>
       <c r="L65" s="23" t="n"/>
       <c r="M65" s="13" t="n"/>
-      <c r="N65" s="20" t="n"/>
+      <c r="N65" s="14" t="n"/>
       <c r="O65" s="23" t="n"/>
       <c r="P65" s="13" t="n"/>
-      <c r="Q65" s="20" t="n"/>
+      <c r="Q65" s="14" t="n"/>
       <c r="R65" s="23" t="n"/>
       <c r="S65" s="13" t="n"/>
-      <c r="T65" s="20" t="n"/>
+      <c r="T65" s="14" t="n"/>
       <c r="U65" s="23" t="n"/>
       <c r="V65" s="13" t="n"/>
     </row>
@@ -2939,25 +3011,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n"/>
+      <c r="B66" s="19" t="n"/>
       <c r="C66" s="23" t="n"/>
       <c r="D66" s="13" t="n"/>
-      <c r="E66" s="20" t="n"/>
+      <c r="E66" s="19" t="n"/>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="13" t="n"/>
-      <c r="H66" s="20" t="n"/>
+      <c r="H66" s="19" t="n"/>
       <c r="I66" s="23" t="n"/>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="20" t="n"/>
+      <c r="K66" s="19" t="n"/>
       <c r="L66" s="23" t="n"/>
       <c r="M66" s="13" t="n"/>
-      <c r="N66" s="20" t="n"/>
+      <c r="N66" s="19" t="n"/>
       <c r="O66" s="23" t="n"/>
       <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="20" t="n"/>
+      <c r="Q66" s="19" t="n"/>
       <c r="R66" s="23" t="n"/>
       <c r="S66" s="13" t="n"/>
-      <c r="T66" s="20" t="n"/>
+      <c r="T66" s="19" t="n"/>
       <c r="U66" s="23" t="n"/>
       <c r="V66" s="13" t="n"/>
     </row>
@@ -2967,25 +3039,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B67" s="20" t="n"/>
+      <c r="B67" s="19" t="n"/>
       <c r="C67" s="23" t="n"/>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="20" t="n"/>
+      <c r="E67" s="19" t="n"/>
       <c r="F67" s="23" t="n"/>
       <c r="G67" s="13" t="n"/>
-      <c r="H67" s="20" t="n"/>
+      <c r="H67" s="19" t="n"/>
       <c r="I67" s="23" t="n"/>
       <c r="J67" s="13" t="n"/>
-      <c r="K67" s="20" t="n"/>
+      <c r="K67" s="19" t="n"/>
       <c r="L67" s="23" t="n"/>
       <c r="M67" s="13" t="n"/>
-      <c r="N67" s="20" t="n"/>
+      <c r="N67" s="19" t="n"/>
       <c r="O67" s="23" t="n"/>
       <c r="P67" s="13" t="n"/>
-      <c r="Q67" s="20" t="n"/>
+      <c r="Q67" s="19" t="n"/>
       <c r="R67" s="23" t="n"/>
       <c r="S67" s="13" t="n"/>
-      <c r="T67" s="20" t="n"/>
+      <c r="T67" s="19" t="n"/>
       <c r="U67" s="23" t="n"/>
       <c r="V67" s="13" t="n"/>
     </row>
@@ -2995,25 +3067,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
+      <c r="B68" s="19" t="n"/>
       <c r="C68" s="23" t="n"/>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="20" t="n"/>
+      <c r="E68" s="19" t="n"/>
       <c r="F68" s="23" t="n"/>
       <c r="G68" s="13" t="n"/>
-      <c r="H68" s="20" t="n"/>
+      <c r="H68" s="19" t="n"/>
       <c r="I68" s="23" t="n"/>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="20" t="n"/>
+      <c r="K68" s="19" t="n"/>
       <c r="L68" s="23" t="n"/>
       <c r="M68" s="13" t="n"/>
-      <c r="N68" s="20" t="n"/>
+      <c r="N68" s="19" t="n"/>
       <c r="O68" s="23" t="n"/>
       <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="20" t="n"/>
+      <c r="Q68" s="19" t="n"/>
       <c r="R68" s="23" t="n"/>
       <c r="S68" s="13" t="n"/>
-      <c r="T68" s="20" t="n"/>
+      <c r="T68" s="19" t="n"/>
       <c r="U68" s="23" t="n"/>
       <c r="V68" s="13" t="n"/>
     </row>
@@ -3023,25 +3095,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B69" s="20" t="n"/>
+      <c r="B69" s="19" t="n"/>
       <c r="C69" s="23" t="n"/>
       <c r="D69" s="13" t="n"/>
-      <c r="E69" s="20" t="n"/>
+      <c r="E69" s="19" t="n"/>
       <c r="F69" s="23" t="n"/>
       <c r="G69" s="13" t="n"/>
-      <c r="H69" s="20" t="n"/>
+      <c r="H69" s="19" t="n"/>
       <c r="I69" s="23" t="n"/>
       <c r="J69" s="13" t="n"/>
-      <c r="K69" s="20" t="n"/>
+      <c r="K69" s="19" t="n"/>
       <c r="L69" s="23" t="n"/>
       <c r="M69" s="13" t="n"/>
-      <c r="N69" s="20" t="n"/>
+      <c r="N69" s="19" t="n"/>
       <c r="O69" s="23" t="n"/>
       <c r="P69" s="13" t="n"/>
-      <c r="Q69" s="20" t="n"/>
+      <c r="Q69" s="19" t="n"/>
       <c r="R69" s="23" t="n"/>
       <c r="S69" s="13" t="n"/>
-      <c r="T69" s="20" t="n"/>
+      <c r="T69" s="19" t="n"/>
       <c r="U69" s="23" t="n"/>
       <c r="V69" s="13" t="n"/>
     </row>
@@ -3051,25 +3123,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B70" s="20" t="n"/>
+      <c r="B70" s="19" t="n"/>
       <c r="C70" s="23" t="n"/>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="20" t="n"/>
+      <c r="E70" s="19" t="n"/>
       <c r="F70" s="23" t="n"/>
       <c r="G70" s="13" t="n"/>
-      <c r="H70" s="20" t="n"/>
+      <c r="H70" s="19" t="n"/>
       <c r="I70" s="23" t="n"/>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="20" t="n"/>
+      <c r="K70" s="19" t="n"/>
       <c r="L70" s="23" t="n"/>
       <c r="M70" s="13" t="n"/>
-      <c r="N70" s="20" t="n"/>
+      <c r="N70" s="19" t="n"/>
       <c r="O70" s="23" t="n"/>
       <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="20" t="n"/>
+      <c r="Q70" s="19" t="n"/>
       <c r="R70" s="23" t="n"/>
       <c r="S70" s="13" t="n"/>
-      <c r="T70" s="20" t="n"/>
+      <c r="T70" s="19" t="n"/>
       <c r="U70" s="23" t="n"/>
       <c r="V70" s="13" t="n"/>
     </row>
@@ -3079,25 +3151,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n"/>
+      <c r="B71" s="19" t="n"/>
       <c r="C71" s="23" t="n"/>
       <c r="D71" s="13" t="n"/>
-      <c r="E71" s="20" t="n"/>
+      <c r="E71" s="19" t="n"/>
       <c r="F71" s="23" t="n"/>
       <c r="G71" s="13" t="n"/>
-      <c r="H71" s="20" t="n"/>
+      <c r="H71" s="19" t="n"/>
       <c r="I71" s="23" t="n"/>
       <c r="J71" s="13" t="n"/>
-      <c r="K71" s="20" t="n"/>
+      <c r="K71" s="19" t="n"/>
       <c r="L71" s="23" t="n"/>
       <c r="M71" s="13" t="n"/>
-      <c r="N71" s="20" t="n"/>
+      <c r="N71" s="19" t="n"/>
       <c r="O71" s="23" t="n"/>
       <c r="P71" s="13" t="n"/>
-      <c r="Q71" s="20" t="n"/>
+      <c r="Q71" s="19" t="n"/>
       <c r="R71" s="23" t="n"/>
       <c r="S71" s="13" t="n"/>
-      <c r="T71" s="20" t="n"/>
+      <c r="T71" s="19" t="n"/>
       <c r="U71" s="23" t="n"/>
       <c r="V71" s="13" t="n"/>
     </row>
@@ -3107,25 +3179,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B72" s="20" t="n"/>
+      <c r="B72" s="19" t="n"/>
       <c r="C72" s="23" t="n"/>
       <c r="D72" s="13" t="n"/>
-      <c r="E72" s="20" t="n"/>
+      <c r="E72" s="19" t="n"/>
       <c r="F72" s="23" t="n"/>
       <c r="G72" s="13" t="n"/>
-      <c r="H72" s="20" t="n"/>
+      <c r="H72" s="19" t="n"/>
       <c r="I72" s="23" t="n"/>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="20" t="n"/>
+      <c r="K72" s="19" t="n"/>
       <c r="L72" s="23" t="n"/>
       <c r="M72" s="13" t="n"/>
-      <c r="N72" s="20" t="n"/>
+      <c r="N72" s="19" t="n"/>
       <c r="O72" s="23" t="n"/>
       <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="20" t="n"/>
+      <c r="Q72" s="19" t="n"/>
       <c r="R72" s="23" t="n"/>
       <c r="S72" s="13" t="n"/>
-      <c r="T72" s="20" t="n"/>
+      <c r="T72" s="19" t="n"/>
       <c r="U72" s="23" t="n"/>
       <c r="V72" s="13" t="n"/>
     </row>
@@ -3135,25 +3207,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n"/>
+      <c r="B73" s="19" t="n"/>
       <c r="C73" s="23" t="n"/>
       <c r="D73" s="13" t="n"/>
-      <c r="E73" s="20" t="n"/>
+      <c r="E73" s="19" t="n"/>
       <c r="F73" s="23" t="n"/>
       <c r="G73" s="13" t="n"/>
-      <c r="H73" s="20" t="n"/>
+      <c r="H73" s="19" t="n"/>
       <c r="I73" s="23" t="n"/>
       <c r="J73" s="13" t="n"/>
-      <c r="K73" s="20" t="n"/>
+      <c r="K73" s="19" t="n"/>
       <c r="L73" s="23" t="n"/>
       <c r="M73" s="13" t="n"/>
-      <c r="N73" s="20" t="n"/>
+      <c r="N73" s="19" t="n"/>
       <c r="O73" s="23" t="n"/>
       <c r="P73" s="13" t="n"/>
-      <c r="Q73" s="20" t="n"/>
+      <c r="Q73" s="19" t="n"/>
       <c r="R73" s="23" t="n"/>
       <c r="S73" s="13" t="n"/>
-      <c r="T73" s="20" t="n"/>
+      <c r="T73" s="19" t="n"/>
       <c r="U73" s="23" t="n"/>
       <c r="V73" s="13" t="n"/>
     </row>
@@ -3163,25 +3235,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B74" s="21" t="n"/>
+      <c r="B74" s="20" t="n"/>
       <c r="C74" s="24" t="n"/>
       <c r="D74" s="18" t="n"/>
-      <c r="E74" s="21" t="n"/>
+      <c r="E74" s="20" t="n"/>
       <c r="F74" s="24" t="n"/>
       <c r="G74" s="18" t="n"/>
-      <c r="H74" s="21" t="n"/>
+      <c r="H74" s="20" t="n"/>
       <c r="I74" s="24" t="n"/>
       <c r="J74" s="18" t="n"/>
-      <c r="K74" s="21" t="n"/>
+      <c r="K74" s="20" t="n"/>
       <c r="L74" s="24" t="n"/>
       <c r="M74" s="18" t="n"/>
-      <c r="N74" s="21" t="n"/>
+      <c r="N74" s="20" t="n"/>
       <c r="O74" s="24" t="n"/>
       <c r="P74" s="18" t="n"/>
-      <c r="Q74" s="21" t="n"/>
+      <c r="Q74" s="20" t="n"/>
       <c r="R74" s="24" t="n"/>
       <c r="S74" s="18" t="n"/>
-      <c r="T74" s="21" t="n"/>
+      <c r="T74" s="20" t="n"/>
       <c r="U74" s="24" t="n"/>
       <c r="V74" s="18" t="n"/>
     </row>
@@ -3205,7 +3277,11 @@
       </c>
       <c r="F75" s="22" t="n"/>
       <c r="G75" s="9" t="n"/>
-      <c r="H75" s="19" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="I75" s="22" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="7" t="inlineStr">
@@ -3215,18 +3291,30 @@
       </c>
       <c r="L75" s="22" t="n"/>
       <c r="M75" s="9" t="n"/>
-      <c r="N75" s="19" t="n"/>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="O75" s="22" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="19" t="n"/>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
       <c r="R75" s="22" t="n"/>
       <c r="S75" s="9" t="n"/>
       <c r="T75" s="7" t="inlineStr">
         <is>
+          <t>林郁子：食事排泄</t>
+        </is>
+      </c>
+      <c r="U75" s="25" t="inlineStr">
+        <is>
           <t>長谷部融子：外出</t>
         </is>
       </c>
-      <c r="U75" s="22" t="n"/>
       <c r="V75" s="9" t="n"/>
     </row>
     <row r="76">
@@ -3241,20 +3329,20 @@
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="23" t="n"/>
       <c r="G76" s="13" t="n"/>
-      <c r="H76" s="20" t="n"/>
+      <c r="H76" s="11" t="n"/>
       <c r="I76" s="23" t="n"/>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="11" t="n"/>
       <c r="L76" s="23" t="n"/>
       <c r="M76" s="13" t="n"/>
-      <c r="N76" s="20" t="n"/>
+      <c r="N76" s="11" t="n"/>
       <c r="O76" s="23" t="n"/>
       <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="20" t="n"/>
+      <c r="Q76" s="11" t="n"/>
       <c r="R76" s="23" t="n"/>
       <c r="S76" s="13" t="n"/>
       <c r="T76" s="11" t="n"/>
-      <c r="U76" s="23" t="n"/>
+      <c r="U76" s="26" t="n"/>
       <c r="V76" s="13" t="n"/>
     </row>
     <row r="77">
@@ -3269,20 +3357,20 @@
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="23" t="n"/>
       <c r="G77" s="13" t="n"/>
-      <c r="H77" s="20" t="n"/>
+      <c r="H77" s="14" t="n"/>
       <c r="I77" s="23" t="n"/>
       <c r="J77" s="13" t="n"/>
       <c r="K77" s="11" t="n"/>
       <c r="L77" s="23" t="n"/>
       <c r="M77" s="13" t="n"/>
-      <c r="N77" s="20" t="n"/>
+      <c r="N77" s="14" t="n"/>
       <c r="O77" s="23" t="n"/>
       <c r="P77" s="13" t="n"/>
-      <c r="Q77" s="20" t="n"/>
+      <c r="Q77" s="14" t="n"/>
       <c r="R77" s="23" t="n"/>
       <c r="S77" s="13" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="23" t="n"/>
+      <c r="T77" s="14" t="n"/>
+      <c r="U77" s="26" t="n"/>
       <c r="V77" s="13" t="n"/>
     </row>
     <row r="78">
@@ -3297,20 +3385,20 @@
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="13" t="n"/>
-      <c r="H78" s="20" t="n"/>
+      <c r="H78" s="19" t="n"/>
       <c r="I78" s="23" t="n"/>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="11" t="n"/>
       <c r="L78" s="23" t="n"/>
       <c r="M78" s="13" t="n"/>
-      <c r="N78" s="20" t="n"/>
+      <c r="N78" s="19" t="n"/>
       <c r="O78" s="23" t="n"/>
       <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="20" t="n"/>
+      <c r="Q78" s="19" t="n"/>
       <c r="R78" s="23" t="n"/>
       <c r="S78" s="13" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="23" t="n"/>
+      <c r="T78" s="19" t="n"/>
+      <c r="U78" s="26" t="n"/>
       <c r="V78" s="13" t="n"/>
     </row>
     <row r="79">
@@ -3325,20 +3413,20 @@
       <c r="E79" s="14" t="n"/>
       <c r="F79" s="23" t="n"/>
       <c r="G79" s="13" t="n"/>
-      <c r="H79" s="20" t="n"/>
+      <c r="H79" s="19" t="n"/>
       <c r="I79" s="23" t="n"/>
       <c r="J79" s="13" t="n"/>
       <c r="K79" s="11" t="n"/>
       <c r="L79" s="23" t="n"/>
       <c r="M79" s="13" t="n"/>
-      <c r="N79" s="20" t="n"/>
+      <c r="N79" s="19" t="n"/>
       <c r="O79" s="23" t="n"/>
       <c r="P79" s="13" t="n"/>
-      <c r="Q79" s="20" t="n"/>
+      <c r="Q79" s="19" t="n"/>
       <c r="R79" s="23" t="n"/>
       <c r="S79" s="13" t="n"/>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="23" t="n"/>
+      <c r="T79" s="19" t="n"/>
+      <c r="U79" s="26" t="n"/>
       <c r="V79" s="13" t="n"/>
     </row>
     <row r="80">
@@ -3350,23 +3438,23 @@
       <c r="B80" s="11" t="n"/>
       <c r="C80" s="23" t="n"/>
       <c r="D80" s="13" t="n"/>
-      <c r="E80" s="20" t="n"/>
+      <c r="E80" s="19" t="n"/>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="13" t="n"/>
-      <c r="H80" s="20" t="n"/>
+      <c r="H80" s="19" t="n"/>
       <c r="I80" s="23" t="n"/>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="11" t="n"/>
       <c r="L80" s="23" t="n"/>
       <c r="M80" s="13" t="n"/>
-      <c r="N80" s="20" t="n"/>
+      <c r="N80" s="19" t="n"/>
       <c r="O80" s="23" t="n"/>
       <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="20" t="n"/>
+      <c r="Q80" s="19" t="n"/>
       <c r="R80" s="23" t="n"/>
       <c r="S80" s="13" t="n"/>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="23" t="n"/>
+      <c r="T80" s="19" t="n"/>
+      <c r="U80" s="26" t="n"/>
       <c r="V80" s="13" t="n"/>
     </row>
     <row r="81">
@@ -3378,27 +3466,27 @@
       <c r="B81" s="11" t="n"/>
       <c r="C81" s="23" t="n"/>
       <c r="D81" s="13" t="n"/>
-      <c r="E81" s="20" t="n"/>
+      <c r="E81" s="19" t="n"/>
       <c r="F81" s="23" t="n"/>
       <c r="G81" s="13" t="n"/>
-      <c r="H81" s="20" t="n"/>
+      <c r="H81" s="19" t="n"/>
       <c r="I81" s="23" t="n"/>
       <c r="J81" s="13" t="n"/>
       <c r="K81" s="11" t="n"/>
-      <c r="L81" s="25" t="inlineStr">
+      <c r="L81" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：掃除</t>
         </is>
       </c>
       <c r="M81" s="13" t="n"/>
-      <c r="N81" s="20" t="n"/>
+      <c r="N81" s="19" t="n"/>
       <c r="O81" s="23" t="n"/>
       <c r="P81" s="13" t="n"/>
-      <c r="Q81" s="20" t="n"/>
+      <c r="Q81" s="19" t="n"/>
       <c r="R81" s="23" t="n"/>
       <c r="S81" s="13" t="n"/>
-      <c r="T81" s="11" t="n"/>
-      <c r="U81" s="23" t="n"/>
+      <c r="T81" s="19" t="n"/>
+      <c r="U81" s="26" t="n"/>
       <c r="V81" s="13" t="n"/>
     </row>
     <row r="82">
@@ -3410,23 +3498,23 @@
       <c r="B82" s="11" t="n"/>
       <c r="C82" s="23" t="n"/>
       <c r="D82" s="13" t="n"/>
-      <c r="E82" s="20" t="n"/>
+      <c r="E82" s="19" t="n"/>
       <c r="F82" s="23" t="n"/>
       <c r="G82" s="13" t="n"/>
-      <c r="H82" s="20" t="n"/>
+      <c r="H82" s="19" t="n"/>
       <c r="I82" s="23" t="n"/>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="11" t="n"/>
       <c r="L82" s="26" t="n"/>
       <c r="M82" s="13" t="n"/>
-      <c r="N82" s="20" t="n"/>
+      <c r="N82" s="19" t="n"/>
       <c r="O82" s="23" t="n"/>
       <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="20" t="n"/>
+      <c r="Q82" s="19" t="n"/>
       <c r="R82" s="23" t="n"/>
       <c r="S82" s="13" t="n"/>
-      <c r="T82" s="11" t="n"/>
-      <c r="U82" s="23" t="n"/>
+      <c r="T82" s="19" t="n"/>
+      <c r="U82" s="26" t="n"/>
       <c r="V82" s="13" t="n"/>
     </row>
     <row r="83">
@@ -3438,23 +3526,23 @@
       <c r="B83" s="11" t="n"/>
       <c r="C83" s="23" t="n"/>
       <c r="D83" s="13" t="n"/>
-      <c r="E83" s="20" t="n"/>
+      <c r="E83" s="19" t="n"/>
       <c r="F83" s="23" t="n"/>
       <c r="G83" s="13" t="n"/>
-      <c r="H83" s="20" t="n"/>
+      <c r="H83" s="19" t="n"/>
       <c r="I83" s="23" t="n"/>
       <c r="J83" s="13" t="n"/>
       <c r="K83" s="11" t="n"/>
       <c r="L83" s="26" t="n"/>
       <c r="M83" s="13" t="n"/>
-      <c r="N83" s="20" t="n"/>
+      <c r="N83" s="19" t="n"/>
       <c r="O83" s="23" t="n"/>
       <c r="P83" s="13" t="n"/>
-      <c r="Q83" s="20" t="n"/>
+      <c r="Q83" s="19" t="n"/>
       <c r="R83" s="23" t="n"/>
       <c r="S83" s="13" t="n"/>
-      <c r="T83" s="11" t="n"/>
-      <c r="U83" s="23" t="n"/>
+      <c r="T83" s="19" t="n"/>
+      <c r="U83" s="26" t="n"/>
       <c r="V83" s="13" t="n"/>
     </row>
     <row r="84">
@@ -3466,23 +3554,23 @@
       <c r="B84" s="11" t="n"/>
       <c r="C84" s="23" t="n"/>
       <c r="D84" s="13" t="n"/>
-      <c r="E84" s="20" t="n"/>
+      <c r="E84" s="19" t="n"/>
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="13" t="n"/>
-      <c r="H84" s="20" t="n"/>
+      <c r="H84" s="19" t="n"/>
       <c r="I84" s="23" t="n"/>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="11" t="n"/>
       <c r="L84" s="26" t="n"/>
       <c r="M84" s="13" t="n"/>
-      <c r="N84" s="20" t="n"/>
+      <c r="N84" s="19" t="n"/>
       <c r="O84" s="23" t="n"/>
       <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="20" t="n"/>
+      <c r="Q84" s="19" t="n"/>
       <c r="R84" s="23" t="n"/>
       <c r="S84" s="13" t="n"/>
-      <c r="T84" s="11" t="n"/>
-      <c r="U84" s="23" t="n"/>
+      <c r="T84" s="19" t="n"/>
+      <c r="U84" s="26" t="n"/>
       <c r="V84" s="13" t="n"/>
     </row>
     <row r="85">
@@ -3494,23 +3582,23 @@
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="23" t="n"/>
       <c r="D85" s="13" t="n"/>
-      <c r="E85" s="20" t="n"/>
+      <c r="E85" s="19" t="n"/>
       <c r="F85" s="23" t="n"/>
       <c r="G85" s="13" t="n"/>
-      <c r="H85" s="20" t="n"/>
+      <c r="H85" s="19" t="n"/>
       <c r="I85" s="23" t="n"/>
       <c r="J85" s="13" t="n"/>
       <c r="K85" s="14" t="n"/>
-      <c r="L85" s="27" t="n"/>
+      <c r="L85" s="28" t="n"/>
       <c r="M85" s="13" t="n"/>
-      <c r="N85" s="20" t="n"/>
+      <c r="N85" s="19" t="n"/>
       <c r="O85" s="23" t="n"/>
       <c r="P85" s="13" t="n"/>
-      <c r="Q85" s="20" t="n"/>
+      <c r="Q85" s="19" t="n"/>
       <c r="R85" s="23" t="n"/>
       <c r="S85" s="13" t="n"/>
-      <c r="T85" s="14" t="n"/>
-      <c r="U85" s="23" t="n"/>
+      <c r="T85" s="19" t="n"/>
+      <c r="U85" s="28" t="n"/>
       <c r="V85" s="13" t="n"/>
     </row>
     <row r="86">
@@ -3519,25 +3607,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B86" s="21" t="n"/>
+      <c r="B86" s="20" t="n"/>
       <c r="C86" s="24" t="n"/>
       <c r="D86" s="18" t="n"/>
-      <c r="E86" s="21" t="n"/>
+      <c r="E86" s="20" t="n"/>
       <c r="F86" s="24" t="n"/>
       <c r="G86" s="18" t="n"/>
-      <c r="H86" s="21" t="n"/>
+      <c r="H86" s="20" t="n"/>
       <c r="I86" s="24" t="n"/>
       <c r="J86" s="18" t="n"/>
-      <c r="K86" s="21" t="n"/>
+      <c r="K86" s="20" t="n"/>
       <c r="L86" s="24" t="n"/>
       <c r="M86" s="18" t="n"/>
-      <c r="N86" s="21" t="n"/>
+      <c r="N86" s="20" t="n"/>
       <c r="O86" s="24" t="n"/>
       <c r="P86" s="18" t="n"/>
-      <c r="Q86" s="21" t="n"/>
+      <c r="Q86" s="20" t="n"/>
       <c r="R86" s="24" t="n"/>
       <c r="S86" s="18" t="n"/>
-      <c r="T86" s="21" t="n"/>
+      <c r="T86" s="20" t="n"/>
       <c r="U86" s="24" t="n"/>
       <c r="V86" s="18" t="n"/>
     </row>
@@ -3547,10 +3635,10 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B87" s="19" t="n"/>
+      <c r="B87" s="21" t="n"/>
       <c r="C87" s="22" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="19" t="n"/>
+      <c r="E87" s="21" t="n"/>
       <c r="F87" s="22" t="n"/>
       <c r="G87" s="9" t="n"/>
       <c r="H87" s="7" t="inlineStr">
@@ -3560,16 +3648,16 @@
       </c>
       <c r="I87" s="22" t="n"/>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="19" t="n"/>
+      <c r="K87" s="21" t="n"/>
       <c r="L87" s="22" t="n"/>
       <c r="M87" s="9" t="n"/>
-      <c r="N87" s="19" t="n"/>
+      <c r="N87" s="21" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="19" t="n"/>
+      <c r="Q87" s="21" t="n"/>
       <c r="R87" s="22" t="n"/>
       <c r="S87" s="9" t="n"/>
-      <c r="T87" s="19" t="n"/>
+      <c r="T87" s="21" t="n"/>
       <c r="U87" s="22" t="n"/>
       <c r="V87" s="9" t="n"/>
     </row>
@@ -3579,25 +3667,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B88" s="20" t="n"/>
+      <c r="B88" s="19" t="n"/>
       <c r="C88" s="23" t="n"/>
       <c r="D88" s="13" t="n"/>
-      <c r="E88" s="20" t="n"/>
+      <c r="E88" s="19" t="n"/>
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="13" t="n"/>
       <c r="H88" s="11" t="n"/>
       <c r="I88" s="23" t="n"/>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="20" t="n"/>
+      <c r="K88" s="19" t="n"/>
       <c r="L88" s="23" t="n"/>
       <c r="M88" s="13" t="n"/>
-      <c r="N88" s="20" t="n"/>
+      <c r="N88" s="19" t="n"/>
       <c r="O88" s="23" t="n"/>
       <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="20" t="n"/>
+      <c r="Q88" s="19" t="n"/>
       <c r="R88" s="23" t="n"/>
       <c r="S88" s="13" t="n"/>
-      <c r="T88" s="20" t="n"/>
+      <c r="T88" s="19" t="n"/>
       <c r="U88" s="23" t="n"/>
       <c r="V88" s="13" t="n"/>
     </row>
@@ -3607,25 +3695,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B89" s="20" t="n"/>
+      <c r="B89" s="19" t="n"/>
       <c r="C89" s="23" t="n"/>
       <c r="D89" s="13" t="n"/>
-      <c r="E89" s="20" t="n"/>
+      <c r="E89" s="19" t="n"/>
       <c r="F89" s="23" t="n"/>
       <c r="G89" s="13" t="n"/>
       <c r="H89" s="11" t="n"/>
       <c r="I89" s="23" t="n"/>
       <c r="J89" s="13" t="n"/>
-      <c r="K89" s="20" t="n"/>
+      <c r="K89" s="19" t="n"/>
       <c r="L89" s="23" t="n"/>
       <c r="M89" s="13" t="n"/>
-      <c r="N89" s="20" t="n"/>
+      <c r="N89" s="19" t="n"/>
       <c r="O89" s="23" t="n"/>
       <c r="P89" s="13" t="n"/>
-      <c r="Q89" s="20" t="n"/>
+      <c r="Q89" s="19" t="n"/>
       <c r="R89" s="23" t="n"/>
       <c r="S89" s="13" t="n"/>
-      <c r="T89" s="20" t="n"/>
+      <c r="T89" s="19" t="n"/>
       <c r="U89" s="23" t="n"/>
       <c r="V89" s="13" t="n"/>
     </row>
@@ -3635,25 +3723,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n"/>
+      <c r="B90" s="19" t="n"/>
       <c r="C90" s="23" t="n"/>
       <c r="D90" s="13" t="n"/>
-      <c r="E90" s="20" t="n"/>
+      <c r="E90" s="19" t="n"/>
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="13" t="n"/>
       <c r="H90" s="11" t="n"/>
       <c r="I90" s="23" t="n"/>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="20" t="n"/>
+      <c r="K90" s="19" t="n"/>
       <c r="L90" s="23" t="n"/>
       <c r="M90" s="13" t="n"/>
-      <c r="N90" s="20" t="n"/>
+      <c r="N90" s="19" t="n"/>
       <c r="O90" s="23" t="n"/>
       <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="20" t="n"/>
+      <c r="Q90" s="19" t="n"/>
       <c r="R90" s="23" t="n"/>
       <c r="S90" s="13" t="n"/>
-      <c r="T90" s="20" t="n"/>
+      <c r="T90" s="19" t="n"/>
       <c r="U90" s="23" t="n"/>
       <c r="V90" s="13" t="n"/>
     </row>
@@ -3663,25 +3751,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B91" s="20" t="n"/>
+      <c r="B91" s="19" t="n"/>
       <c r="C91" s="23" t="n"/>
       <c r="D91" s="13" t="n"/>
-      <c r="E91" s="20" t="n"/>
+      <c r="E91" s="19" t="n"/>
       <c r="F91" s="23" t="n"/>
       <c r="G91" s="13" t="n"/>
       <c r="H91" s="14" t="n"/>
       <c r="I91" s="23" t="n"/>
       <c r="J91" s="13" t="n"/>
-      <c r="K91" s="20" t="n"/>
+      <c r="K91" s="19" t="n"/>
       <c r="L91" s="23" t="n"/>
       <c r="M91" s="13" t="n"/>
-      <c r="N91" s="20" t="n"/>
+      <c r="N91" s="19" t="n"/>
       <c r="O91" s="23" t="n"/>
       <c r="P91" s="13" t="n"/>
-      <c r="Q91" s="20" t="n"/>
+      <c r="Q91" s="19" t="n"/>
       <c r="R91" s="23" t="n"/>
       <c r="S91" s="13" t="n"/>
-      <c r="T91" s="20" t="n"/>
+      <c r="T91" s="19" t="n"/>
       <c r="U91" s="23" t="n"/>
       <c r="V91" s="13" t="n"/>
     </row>
@@ -3691,25 +3779,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B92" s="20" t="n"/>
+      <c r="B92" s="19" t="n"/>
       <c r="C92" s="23" t="n"/>
       <c r="D92" s="13" t="n"/>
-      <c r="E92" s="20" t="n"/>
+      <c r="E92" s="19" t="n"/>
       <c r="F92" s="23" t="n"/>
       <c r="G92" s="13" t="n"/>
-      <c r="H92" s="20" t="n"/>
+      <c r="H92" s="19" t="n"/>
       <c r="I92" s="23" t="n"/>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="20" t="n"/>
+      <c r="K92" s="19" t="n"/>
       <c r="L92" s="23" t="n"/>
       <c r="M92" s="13" t="n"/>
-      <c r="N92" s="20" t="n"/>
+      <c r="N92" s="19" t="n"/>
       <c r="O92" s="23" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="20" t="n"/>
+      <c r="Q92" s="19" t="n"/>
       <c r="R92" s="23" t="n"/>
       <c r="S92" s="13" t="n"/>
-      <c r="T92" s="20" t="n"/>
+      <c r="T92" s="19" t="n"/>
       <c r="U92" s="23" t="n"/>
       <c r="V92" s="13" t="n"/>
     </row>
@@ -3719,25 +3807,45 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B93" s="20" t="n"/>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：掃除</t>
+        </is>
+      </c>
       <c r="C93" s="23" t="n"/>
       <c r="D93" s="13" t="n"/>
-      <c r="E93" s="20" t="n"/>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：入浴介助</t>
+        </is>
+      </c>
       <c r="F93" s="23" t="n"/>
       <c r="G93" s="13" t="n"/>
-      <c r="H93" s="20" t="n"/>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：外出</t>
+        </is>
+      </c>
       <c r="I93" s="23" t="n"/>
       <c r="J93" s="13" t="n"/>
-      <c r="K93" s="20" t="n"/>
+      <c r="K93" s="19" t="n"/>
       <c r="L93" s="23" t="n"/>
       <c r="M93" s="13" t="n"/>
-      <c r="N93" s="20" t="n"/>
+      <c r="N93" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：掃除</t>
+        </is>
+      </c>
       <c r="O93" s="23" t="n"/>
       <c r="P93" s="13" t="n"/>
-      <c r="Q93" s="20" t="n"/>
+      <c r="Q93" s="15" t="inlineStr">
+        <is>
+          <t>河田晃晃：入浴介助</t>
+        </is>
+      </c>
       <c r="R93" s="23" t="n"/>
       <c r="S93" s="13" t="n"/>
-      <c r="T93" s="20" t="n"/>
+      <c r="T93" s="19" t="n"/>
       <c r="U93" s="23" t="n"/>
       <c r="V93" s="13" t="n"/>
     </row>
@@ -3747,25 +3855,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B94" s="20" t="n"/>
+      <c r="B94" s="11" t="n"/>
       <c r="C94" s="23" t="n"/>
       <c r="D94" s="13" t="n"/>
-      <c r="E94" s="20" t="n"/>
+      <c r="E94" s="11" t="n"/>
       <c r="F94" s="23" t="n"/>
       <c r="G94" s="13" t="n"/>
-      <c r="H94" s="20" t="n"/>
+      <c r="H94" s="11" t="n"/>
       <c r="I94" s="23" t="n"/>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="20" t="n"/>
+      <c r="K94" s="19" t="n"/>
       <c r="L94" s="23" t="n"/>
       <c r="M94" s="13" t="n"/>
-      <c r="N94" s="20" t="n"/>
+      <c r="N94" s="11" t="n"/>
       <c r="O94" s="23" t="n"/>
       <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="20" t="n"/>
+      <c r="Q94" s="11" t="n"/>
       <c r="R94" s="23" t="n"/>
       <c r="S94" s="13" t="n"/>
-      <c r="T94" s="20" t="n"/>
+      <c r="T94" s="19" t="n"/>
       <c r="U94" s="23" t="n"/>
       <c r="V94" s="13" t="n"/>
     </row>
@@ -3775,25 +3883,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B95" s="20" t="n"/>
+      <c r="B95" s="11" t="n"/>
       <c r="C95" s="23" t="n"/>
       <c r="D95" s="13" t="n"/>
-      <c r="E95" s="20" t="n"/>
+      <c r="E95" s="11" t="n"/>
       <c r="F95" s="23" t="n"/>
       <c r="G95" s="13" t="n"/>
-      <c r="H95" s="20" t="n"/>
+      <c r="H95" s="11" t="n"/>
       <c r="I95" s="23" t="n"/>
       <c r="J95" s="13" t="n"/>
-      <c r="K95" s="20" t="n"/>
+      <c r="K95" s="19" t="n"/>
       <c r="L95" s="23" t="n"/>
       <c r="M95" s="13" t="n"/>
-      <c r="N95" s="20" t="n"/>
+      <c r="N95" s="11" t="n"/>
       <c r="O95" s="23" t="n"/>
       <c r="P95" s="13" t="n"/>
-      <c r="Q95" s="20" t="n"/>
+      <c r="Q95" s="11" t="n"/>
       <c r="R95" s="23" t="n"/>
       <c r="S95" s="13" t="n"/>
-      <c r="T95" s="20" t="n"/>
+      <c r="T95" s="19" t="n"/>
       <c r="U95" s="23" t="n"/>
       <c r="V95" s="13" t="n"/>
     </row>
@@ -3803,25 +3911,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B96" s="20" t="n"/>
+      <c r="B96" s="11" t="n"/>
       <c r="C96" s="23" t="n"/>
       <c r="D96" s="13" t="n"/>
-      <c r="E96" s="20" t="n"/>
+      <c r="E96" s="11" t="n"/>
       <c r="F96" s="23" t="n"/>
       <c r="G96" s="13" t="n"/>
-      <c r="H96" s="20" t="n"/>
+      <c r="H96" s="11" t="n"/>
       <c r="I96" s="23" t="n"/>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="20" t="n"/>
+      <c r="K96" s="19" t="n"/>
       <c r="L96" s="23" t="n"/>
       <c r="M96" s="13" t="n"/>
-      <c r="N96" s="20" t="n"/>
+      <c r="N96" s="11" t="n"/>
       <c r="O96" s="23" t="n"/>
       <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="20" t="n"/>
+      <c r="Q96" s="11" t="n"/>
       <c r="R96" s="23" t="n"/>
       <c r="S96" s="13" t="n"/>
-      <c r="T96" s="20" t="n"/>
+      <c r="T96" s="19" t="n"/>
       <c r="U96" s="23" t="n"/>
       <c r="V96" s="13" t="n"/>
     </row>
@@ -3831,25 +3939,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B97" s="20" t="n"/>
+      <c r="B97" s="14" t="n"/>
       <c r="C97" s="23" t="n"/>
       <c r="D97" s="13" t="n"/>
-      <c r="E97" s="20" t="n"/>
+      <c r="E97" s="11" t="n"/>
       <c r="F97" s="23" t="n"/>
       <c r="G97" s="13" t="n"/>
-      <c r="H97" s="20" t="n"/>
+      <c r="H97" s="11" t="n"/>
       <c r="I97" s="23" t="n"/>
       <c r="J97" s="13" t="n"/>
-      <c r="K97" s="20" t="n"/>
+      <c r="K97" s="19" t="n"/>
       <c r="L97" s="23" t="n"/>
       <c r="M97" s="13" t="n"/>
-      <c r="N97" s="20" t="n"/>
+      <c r="N97" s="14" t="n"/>
       <c r="O97" s="23" t="n"/>
       <c r="P97" s="13" t="n"/>
-      <c r="Q97" s="20" t="n"/>
+      <c r="Q97" s="11" t="n"/>
       <c r="R97" s="23" t="n"/>
       <c r="S97" s="13" t="n"/>
-      <c r="T97" s="20" t="n"/>
+      <c r="T97" s="19" t="n"/>
       <c r="U97" s="23" t="n"/>
       <c r="V97" s="13" t="n"/>
     </row>
@@ -3859,25 +3967,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B98" s="21" t="n"/>
+      <c r="B98" s="20" t="n"/>
       <c r="C98" s="24" t="n"/>
       <c r="D98" s="18" t="n"/>
-      <c r="E98" s="21" t="n"/>
+      <c r="E98" s="11" t="n"/>
       <c r="F98" s="24" t="n"/>
       <c r="G98" s="18" t="n"/>
-      <c r="H98" s="21" t="n"/>
+      <c r="H98" s="11" t="n"/>
       <c r="I98" s="24" t="n"/>
       <c r="J98" s="18" t="n"/>
-      <c r="K98" s="21" t="n"/>
+      <c r="K98" s="20" t="n"/>
       <c r="L98" s="24" t="n"/>
       <c r="M98" s="18" t="n"/>
-      <c r="N98" s="21" t="n"/>
+      <c r="N98" s="20" t="n"/>
       <c r="O98" s="24" t="n"/>
       <c r="P98" s="18" t="n"/>
-      <c r="Q98" s="21" t="n"/>
+      <c r="Q98" s="11" t="n"/>
       <c r="R98" s="24" t="n"/>
       <c r="S98" s="18" t="n"/>
-      <c r="T98" s="21" t="n"/>
+      <c r="T98" s="20" t="n"/>
       <c r="U98" s="24" t="n"/>
       <c r="V98" s="18" t="n"/>
     </row>
@@ -3887,25 +3995,25 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
+      <c r="B99" s="21" t="n"/>
       <c r="C99" s="22" t="n"/>
       <c r="D99" s="9" t="n"/>
-      <c r="E99" s="19" t="n"/>
+      <c r="E99" s="11" t="n"/>
       <c r="F99" s="22" t="n"/>
       <c r="G99" s="9" t="n"/>
-      <c r="H99" s="19" t="n"/>
+      <c r="H99" s="11" t="n"/>
       <c r="I99" s="22" t="n"/>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="19" t="n"/>
+      <c r="K99" s="21" t="n"/>
       <c r="L99" s="22" t="n"/>
       <c r="M99" s="9" t="n"/>
-      <c r="N99" s="19" t="n"/>
+      <c r="N99" s="21" t="n"/>
       <c r="O99" s="22" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="19" t="n"/>
+      <c r="Q99" s="11" t="n"/>
       <c r="R99" s="22" t="n"/>
       <c r="S99" s="9" t="n"/>
-      <c r="T99" s="19" t="n"/>
+      <c r="T99" s="21" t="n"/>
       <c r="U99" s="22" t="n"/>
       <c r="V99" s="9" t="n"/>
     </row>
@@ -3915,25 +4023,25 @@
           <t>05</t>
         </is>
       </c>
-      <c r="B100" s="20" t="n"/>
+      <c r="B100" s="19" t="n"/>
       <c r="C100" s="23" t="n"/>
       <c r="D100" s="13" t="n"/>
-      <c r="E100" s="20" t="n"/>
+      <c r="E100" s="11" t="n"/>
       <c r="F100" s="23" t="n"/>
       <c r="G100" s="13" t="n"/>
-      <c r="H100" s="20" t="n"/>
+      <c r="H100" s="11" t="n"/>
       <c r="I100" s="23" t="n"/>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="20" t="n"/>
+      <c r="K100" s="19" t="n"/>
       <c r="L100" s="23" t="n"/>
       <c r="M100" s="13" t="n"/>
-      <c r="N100" s="20" t="n"/>
+      <c r="N100" s="19" t="n"/>
       <c r="O100" s="23" t="n"/>
       <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="20" t="n"/>
+      <c r="Q100" s="11" t="n"/>
       <c r="R100" s="23" t="n"/>
       <c r="S100" s="13" t="n"/>
-      <c r="T100" s="20" t="n"/>
+      <c r="T100" s="19" t="n"/>
       <c r="U100" s="23" t="n"/>
       <c r="V100" s="13" t="n"/>
     </row>
@@ -3943,25 +4051,25 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B101" s="20" t="n"/>
+      <c r="B101" s="19" t="n"/>
       <c r="C101" s="23" t="n"/>
       <c r="D101" s="13" t="n"/>
-      <c r="E101" s="20" t="n"/>
+      <c r="E101" s="11" t="n"/>
       <c r="F101" s="23" t="n"/>
       <c r="G101" s="13" t="n"/>
-      <c r="H101" s="20" t="n"/>
+      <c r="H101" s="11" t="n"/>
       <c r="I101" s="23" t="n"/>
       <c r="J101" s="13" t="n"/>
-      <c r="K101" s="20" t="n"/>
+      <c r="K101" s="19" t="n"/>
       <c r="L101" s="23" t="n"/>
       <c r="M101" s="13" t="n"/>
-      <c r="N101" s="20" t="n"/>
+      <c r="N101" s="19" t="n"/>
       <c r="O101" s="23" t="n"/>
       <c r="P101" s="13" t="n"/>
-      <c r="Q101" s="20" t="n"/>
+      <c r="Q101" s="11" t="n"/>
       <c r="R101" s="23" t="n"/>
       <c r="S101" s="13" t="n"/>
-      <c r="T101" s="20" t="n"/>
+      <c r="T101" s="19" t="n"/>
       <c r="U101" s="23" t="n"/>
       <c r="V101" s="13" t="n"/>
     </row>
@@ -3971,25 +4079,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B102" s="20" t="n"/>
+      <c r="B102" s="19" t="n"/>
       <c r="C102" s="23" t="n"/>
       <c r="D102" s="13" t="n"/>
-      <c r="E102" s="20" t="n"/>
+      <c r="E102" s="11" t="n"/>
       <c r="F102" s="23" t="n"/>
       <c r="G102" s="13" t="n"/>
-      <c r="H102" s="20" t="n"/>
+      <c r="H102" s="11" t="n"/>
       <c r="I102" s="23" t="n"/>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="20" t="n"/>
+      <c r="K102" s="19" t="n"/>
       <c r="L102" s="23" t="n"/>
       <c r="M102" s="13" t="n"/>
-      <c r="N102" s="20" t="n"/>
+      <c r="N102" s="19" t="n"/>
       <c r="O102" s="23" t="n"/>
       <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="20" t="n"/>
+      <c r="Q102" s="11" t="n"/>
       <c r="R102" s="23" t="n"/>
       <c r="S102" s="13" t="n"/>
-      <c r="T102" s="20" t="n"/>
+      <c r="T102" s="19" t="n"/>
       <c r="U102" s="23" t="n"/>
       <c r="V102" s="13" t="n"/>
     </row>
@@ -3999,25 +4107,25 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n"/>
+      <c r="B103" s="19" t="n"/>
       <c r="C103" s="23" t="n"/>
       <c r="D103" s="13" t="n"/>
-      <c r="E103" s="20" t="n"/>
+      <c r="E103" s="14" t="n"/>
       <c r="F103" s="23" t="n"/>
       <c r="G103" s="13" t="n"/>
-      <c r="H103" s="20" t="n"/>
+      <c r="H103" s="14" t="n"/>
       <c r="I103" s="23" t="n"/>
       <c r="J103" s="13" t="n"/>
-      <c r="K103" s="20" t="n"/>
+      <c r="K103" s="19" t="n"/>
       <c r="L103" s="23" t="n"/>
       <c r="M103" s="13" t="n"/>
-      <c r="N103" s="20" t="n"/>
+      <c r="N103" s="19" t="n"/>
       <c r="O103" s="23" t="n"/>
       <c r="P103" s="13" t="n"/>
-      <c r="Q103" s="20" t="n"/>
+      <c r="Q103" s="14" t="n"/>
       <c r="R103" s="23" t="n"/>
       <c r="S103" s="13" t="n"/>
-      <c r="T103" s="20" t="n"/>
+      <c r="T103" s="19" t="n"/>
       <c r="U103" s="23" t="n"/>
       <c r="V103" s="13" t="n"/>
     </row>
@@ -4027,25 +4135,25 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B104" s="20" t="n"/>
+      <c r="B104" s="19" t="n"/>
       <c r="C104" s="23" t="n"/>
       <c r="D104" s="13" t="n"/>
-      <c r="E104" s="20" t="n"/>
+      <c r="E104" s="19" t="n"/>
       <c r="F104" s="23" t="n"/>
       <c r="G104" s="13" t="n"/>
-      <c r="H104" s="20" t="n"/>
+      <c r="H104" s="19" t="n"/>
       <c r="I104" s="23" t="n"/>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="20" t="n"/>
+      <c r="K104" s="19" t="n"/>
       <c r="L104" s="23" t="n"/>
       <c r="M104" s="13" t="n"/>
-      <c r="N104" s="20" t="n"/>
+      <c r="N104" s="19" t="n"/>
       <c r="O104" s="23" t="n"/>
       <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="20" t="n"/>
+      <c r="Q104" s="19" t="n"/>
       <c r="R104" s="23" t="n"/>
       <c r="S104" s="13" t="n"/>
-      <c r="T104" s="20" t="n"/>
+      <c r="T104" s="19" t="n"/>
       <c r="U104" s="23" t="n"/>
       <c r="V104" s="13" t="n"/>
     </row>
@@ -4055,25 +4163,25 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B105" s="20" t="n"/>
+      <c r="B105" s="19" t="n"/>
       <c r="C105" s="23" t="n"/>
       <c r="D105" s="13" t="n"/>
-      <c r="E105" s="20" t="n"/>
+      <c r="E105" s="19" t="n"/>
       <c r="F105" s="23" t="n"/>
       <c r="G105" s="13" t="n"/>
-      <c r="H105" s="20" t="n"/>
+      <c r="H105" s="19" t="n"/>
       <c r="I105" s="23" t="n"/>
       <c r="J105" s="13" t="n"/>
-      <c r="K105" s="20" t="n"/>
+      <c r="K105" s="19" t="n"/>
       <c r="L105" s="23" t="n"/>
       <c r="M105" s="13" t="n"/>
-      <c r="N105" s="20" t="n"/>
+      <c r="N105" s="19" t="n"/>
       <c r="O105" s="23" t="n"/>
       <c r="P105" s="13" t="n"/>
-      <c r="Q105" s="20" t="n"/>
+      <c r="Q105" s="19" t="n"/>
       <c r="R105" s="23" t="n"/>
       <c r="S105" s="13" t="n"/>
-      <c r="T105" s="20" t="n"/>
+      <c r="T105" s="19" t="n"/>
       <c r="U105" s="23" t="n"/>
       <c r="V105" s="13" t="n"/>
     </row>
@@ -4083,25 +4191,25 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B106" s="20" t="n"/>
+      <c r="B106" s="19" t="n"/>
       <c r="C106" s="23" t="n"/>
       <c r="D106" s="13" t="n"/>
-      <c r="E106" s="20" t="n"/>
+      <c r="E106" s="19" t="n"/>
       <c r="F106" s="23" t="n"/>
       <c r="G106" s="13" t="n"/>
-      <c r="H106" s="20" t="n"/>
+      <c r="H106" s="19" t="n"/>
       <c r="I106" s="23" t="n"/>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="20" t="n"/>
+      <c r="K106" s="19" t="n"/>
       <c r="L106" s="23" t="n"/>
       <c r="M106" s="13" t="n"/>
-      <c r="N106" s="20" t="n"/>
+      <c r="N106" s="19" t="n"/>
       <c r="O106" s="23" t="n"/>
       <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="20" t="n"/>
+      <c r="Q106" s="19" t="n"/>
       <c r="R106" s="23" t="n"/>
       <c r="S106" s="13" t="n"/>
-      <c r="T106" s="20" t="n"/>
+      <c r="T106" s="19" t="n"/>
       <c r="U106" s="23" t="n"/>
       <c r="V106" s="13" t="n"/>
     </row>
@@ -4111,25 +4219,25 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B107" s="20" t="n"/>
+      <c r="B107" s="19" t="n"/>
       <c r="C107" s="23" t="n"/>
       <c r="D107" s="13" t="n"/>
-      <c r="E107" s="20" t="n"/>
+      <c r="E107" s="19" t="n"/>
       <c r="F107" s="23" t="n"/>
       <c r="G107" s="13" t="n"/>
-      <c r="H107" s="20" t="n"/>
+      <c r="H107" s="19" t="n"/>
       <c r="I107" s="23" t="n"/>
       <c r="J107" s="13" t="n"/>
-      <c r="K107" s="20" t="n"/>
+      <c r="K107" s="19" t="n"/>
       <c r="L107" s="23" t="n"/>
       <c r="M107" s="13" t="n"/>
-      <c r="N107" s="20" t="n"/>
+      <c r="N107" s="19" t="n"/>
       <c r="O107" s="23" t="n"/>
       <c r="P107" s="13" t="n"/>
-      <c r="Q107" s="20" t="n"/>
+      <c r="Q107" s="19" t="n"/>
       <c r="R107" s="23" t="n"/>
       <c r="S107" s="13" t="n"/>
-      <c r="T107" s="20" t="n"/>
+      <c r="T107" s="19" t="n"/>
       <c r="U107" s="23" t="n"/>
       <c r="V107" s="13" t="n"/>
     </row>
@@ -4139,25 +4247,25 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B108" s="20" t="n"/>
+      <c r="B108" s="19" t="n"/>
       <c r="C108" s="23" t="n"/>
       <c r="D108" s="13" t="n"/>
-      <c r="E108" s="20" t="n"/>
+      <c r="E108" s="19" t="n"/>
       <c r="F108" s="23" t="n"/>
       <c r="G108" s="13" t="n"/>
-      <c r="H108" s="20" t="n"/>
+      <c r="H108" s="19" t="n"/>
       <c r="I108" s="23" t="n"/>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="20" t="n"/>
+      <c r="K108" s="19" t="n"/>
       <c r="L108" s="23" t="n"/>
       <c r="M108" s="13" t="n"/>
-      <c r="N108" s="20" t="n"/>
+      <c r="N108" s="19" t="n"/>
       <c r="O108" s="23" t="n"/>
       <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="20" t="n"/>
+      <c r="Q108" s="19" t="n"/>
       <c r="R108" s="23" t="n"/>
       <c r="S108" s="13" t="n"/>
-      <c r="T108" s="20" t="n"/>
+      <c r="T108" s="19" t="n"/>
       <c r="U108" s="23" t="n"/>
       <c r="V108" s="13" t="n"/>
     </row>
@@ -4167,25 +4275,25 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B109" s="20" t="n"/>
+      <c r="B109" s="19" t="n"/>
       <c r="C109" s="23" t="n"/>
       <c r="D109" s="13" t="n"/>
-      <c r="E109" s="20" t="n"/>
+      <c r="E109" s="19" t="n"/>
       <c r="F109" s="23" t="n"/>
       <c r="G109" s="13" t="n"/>
-      <c r="H109" s="20" t="n"/>
+      <c r="H109" s="19" t="n"/>
       <c r="I109" s="23" t="n"/>
       <c r="J109" s="13" t="n"/>
-      <c r="K109" s="20" t="n"/>
+      <c r="K109" s="19" t="n"/>
       <c r="L109" s="23" t="n"/>
       <c r="M109" s="13" t="n"/>
-      <c r="N109" s="20" t="n"/>
+      <c r="N109" s="19" t="n"/>
       <c r="O109" s="23" t="n"/>
       <c r="P109" s="13" t="n"/>
-      <c r="Q109" s="20" t="n"/>
+      <c r="Q109" s="19" t="n"/>
       <c r="R109" s="23" t="n"/>
       <c r="S109" s="13" t="n"/>
-      <c r="T109" s="20" t="n"/>
+      <c r="T109" s="19" t="n"/>
       <c r="U109" s="23" t="n"/>
       <c r="V109" s="13" t="n"/>
     </row>
@@ -4195,25 +4303,25 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B110" s="21" t="n"/>
+      <c r="B110" s="20" t="n"/>
       <c r="C110" s="24" t="n"/>
       <c r="D110" s="18" t="n"/>
-      <c r="E110" s="21" t="n"/>
+      <c r="E110" s="20" t="n"/>
       <c r="F110" s="24" t="n"/>
       <c r="G110" s="18" t="n"/>
-      <c r="H110" s="21" t="n"/>
+      <c r="H110" s="20" t="n"/>
       <c r="I110" s="24" t="n"/>
       <c r="J110" s="18" t="n"/>
-      <c r="K110" s="21" t="n"/>
+      <c r="K110" s="20" t="n"/>
       <c r="L110" s="24" t="n"/>
       <c r="M110" s="18" t="n"/>
-      <c r="N110" s="21" t="n"/>
+      <c r="N110" s="20" t="n"/>
       <c r="O110" s="24" t="n"/>
       <c r="P110" s="18" t="n"/>
-      <c r="Q110" s="21" t="n"/>
+      <c r="Q110" s="20" t="n"/>
       <c r="R110" s="24" t="n"/>
       <c r="S110" s="18" t="n"/>
-      <c r="T110" s="21" t="n"/>
+      <c r="T110" s="20" t="n"/>
       <c r="U110" s="24" t="n"/>
       <c r="V110" s="18" t="n"/>
     </row>
@@ -4223,50 +4331,50 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B111" s="28" t="n"/>
-      <c r="C111" s="29" t="inlineStr">
+      <c r="B111" s="29" t="n"/>
+      <c r="C111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
-      <c r="E111" s="28" t="n"/>
-      <c r="F111" s="29" t="inlineStr">
+      <c r="E111" s="29" t="n"/>
+      <c r="F111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="G111" s="9" t="n"/>
-      <c r="H111" s="28" t="n"/>
-      <c r="I111" s="29" t="inlineStr">
+      <c r="H111" s="29" t="n"/>
+      <c r="I111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="J111" s="9" t="n"/>
-      <c r="K111" s="28" t="n"/>
-      <c r="L111" s="29" t="inlineStr">
+      <c r="K111" s="29" t="n"/>
+      <c r="L111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="M111" s="9" t="n"/>
-      <c r="N111" s="28" t="n"/>
-      <c r="O111" s="29" t="inlineStr">
+      <c r="N111" s="29" t="n"/>
+      <c r="O111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="29" t="inlineStr">
+      <c r="Q111" s="29" t="n"/>
+      <c r="R111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
       </c>
       <c r="S111" s="9" t="n"/>
-      <c r="T111" s="28" t="n"/>
-      <c r="U111" s="29" t="inlineStr">
+      <c r="T111" s="29" t="n"/>
+      <c r="U111" s="25" t="inlineStr">
         <is>
           <t>林郁子：食事排泄</t>
         </is>
@@ -4364,25 +4472,25 @@
         </is>
       </c>
       <c r="B115" s="30" t="n"/>
-      <c r="C115" s="27" t="n"/>
+      <c r="C115" s="28" t="n"/>
       <c r="D115" s="13" t="n"/>
       <c r="E115" s="30" t="n"/>
-      <c r="F115" s="27" t="n"/>
+      <c r="F115" s="28" t="n"/>
       <c r="G115" s="13" t="n"/>
       <c r="H115" s="30" t="n"/>
-      <c r="I115" s="27" t="n"/>
+      <c r="I115" s="28" t="n"/>
       <c r="J115" s="13" t="n"/>
       <c r="K115" s="30" t="n"/>
-      <c r="L115" s="27" t="n"/>
+      <c r="L115" s="28" t="n"/>
       <c r="M115" s="13" t="n"/>
       <c r="N115" s="30" t="n"/>
-      <c r="O115" s="27" t="n"/>
+      <c r="O115" s="28" t="n"/>
       <c r="P115" s="13" t="n"/>
       <c r="Q115" s="30" t="n"/>
-      <c r="R115" s="27" t="n"/>
+      <c r="R115" s="28" t="n"/>
       <c r="S115" s="13" t="n"/>
       <c r="T115" s="30" t="n"/>
-      <c r="U115" s="27" t="n"/>
+      <c r="U115" s="28" t="n"/>
       <c r="V115" s="13" t="n"/>
     </row>
     <row r="116">
@@ -4420,49 +4528,49 @@
         </is>
       </c>
       <c r="B117" s="30" t="n"/>
-      <c r="C117" s="25" t="inlineStr">
+      <c r="C117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="D117" s="13" t="n"/>
       <c r="E117" s="30" t="n"/>
-      <c r="F117" s="25" t="inlineStr">
+      <c r="F117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="G117" s="13" t="n"/>
       <c r="H117" s="30" t="n"/>
-      <c r="I117" s="25" t="inlineStr">
+      <c r="I117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="J117" s="13" t="n"/>
       <c r="K117" s="30" t="n"/>
-      <c r="L117" s="25" t="inlineStr">
+      <c r="L117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="M117" s="13" t="n"/>
       <c r="N117" s="30" t="n"/>
-      <c r="O117" s="25" t="inlineStr">
+      <c r="O117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="P117" s="13" t="n"/>
       <c r="Q117" s="30" t="n"/>
-      <c r="R117" s="25" t="inlineStr">
+      <c r="R117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
       </c>
       <c r="S117" s="13" t="n"/>
       <c r="T117" s="30" t="n"/>
-      <c r="U117" s="25" t="inlineStr">
+      <c r="U117" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：食事排泄</t>
         </is>
@@ -4560,25 +4668,25 @@
         </is>
       </c>
       <c r="B121" s="30" t="n"/>
-      <c r="C121" s="27" t="n"/>
+      <c r="C121" s="28" t="n"/>
       <c r="D121" s="13" t="n"/>
       <c r="E121" s="30" t="n"/>
-      <c r="F121" s="27" t="n"/>
+      <c r="F121" s="28" t="n"/>
       <c r="G121" s="13" t="n"/>
       <c r="H121" s="30" t="n"/>
-      <c r="I121" s="27" t="n"/>
+      <c r="I121" s="28" t="n"/>
       <c r="J121" s="13" t="n"/>
       <c r="K121" s="30" t="n"/>
-      <c r="L121" s="27" t="n"/>
+      <c r="L121" s="28" t="n"/>
       <c r="M121" s="13" t="n"/>
       <c r="N121" s="30" t="n"/>
-      <c r="O121" s="27" t="n"/>
+      <c r="O121" s="28" t="n"/>
       <c r="P121" s="13" t="n"/>
       <c r="Q121" s="30" t="n"/>
-      <c r="R121" s="27" t="n"/>
+      <c r="R121" s="28" t="n"/>
       <c r="S121" s="13" t="n"/>
       <c r="T121" s="30" t="n"/>
-      <c r="U121" s="27" t="n"/>
+      <c r="U121" s="28" t="n"/>
       <c r="V121" s="13" t="n"/>
     </row>
     <row r="122">
@@ -4615,50 +4723,50 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B123" s="28" t="n"/>
-      <c r="C123" s="29" t="inlineStr">
+      <c r="B123" s="29" t="n"/>
+      <c r="C123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
-      <c r="E123" s="28" t="n"/>
-      <c r="F123" s="29" t="inlineStr">
+      <c r="E123" s="29" t="n"/>
+      <c r="F123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="G123" s="9" t="n"/>
-      <c r="H123" s="28" t="n"/>
-      <c r="I123" s="29" t="inlineStr">
+      <c r="H123" s="29" t="n"/>
+      <c r="I123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="J123" s="9" t="n"/>
-      <c r="K123" s="28" t="n"/>
-      <c r="L123" s="29" t="inlineStr">
+      <c r="K123" s="29" t="n"/>
+      <c r="L123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="M123" s="9" t="n"/>
-      <c r="N123" s="28" t="n"/>
-      <c r="O123" s="29" t="inlineStr">
+      <c r="N123" s="29" t="n"/>
+      <c r="O123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="29" t="inlineStr">
+      <c r="Q123" s="29" t="n"/>
+      <c r="R123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
       </c>
       <c r="S123" s="9" t="n"/>
-      <c r="T123" s="28" t="n"/>
-      <c r="U123" s="29" t="inlineStr">
+      <c r="T123" s="29" t="n"/>
+      <c r="U123" s="25" t="inlineStr">
         <is>
           <t>藤本敏博：排泄介助</t>
         </is>
@@ -4756,25 +4864,25 @@
         </is>
       </c>
       <c r="B127" s="30" t="n"/>
-      <c r="C127" s="27" t="n"/>
+      <c r="C127" s="28" t="n"/>
       <c r="D127" s="13" t="n"/>
       <c r="E127" s="30" t="n"/>
-      <c r="F127" s="27" t="n"/>
+      <c r="F127" s="28" t="n"/>
       <c r="G127" s="13" t="n"/>
       <c r="H127" s="30" t="n"/>
-      <c r="I127" s="27" t="n"/>
+      <c r="I127" s="28" t="n"/>
       <c r="J127" s="13" t="n"/>
       <c r="K127" s="30" t="n"/>
-      <c r="L127" s="27" t="n"/>
+      <c r="L127" s="28" t="n"/>
       <c r="M127" s="13" t="n"/>
       <c r="N127" s="30" t="n"/>
-      <c r="O127" s="27" t="n"/>
+      <c r="O127" s="28" t="n"/>
       <c r="P127" s="13" t="n"/>
       <c r="Q127" s="30" t="n"/>
-      <c r="R127" s="27" t="n"/>
+      <c r="R127" s="28" t="n"/>
       <c r="S127" s="13" t="n"/>
       <c r="T127" s="30" t="n"/>
-      <c r="U127" s="27" t="n"/>
+      <c r="U127" s="28" t="n"/>
       <c r="V127" s="13" t="n"/>
     </row>
     <row r="128">
@@ -4812,49 +4920,49 @@
         </is>
       </c>
       <c r="B129" s="30" t="n"/>
-      <c r="C129" s="25" t="inlineStr">
+      <c r="C129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="D129" s="13" t="n"/>
       <c r="E129" s="30" t="n"/>
-      <c r="F129" s="25" t="inlineStr">
+      <c r="F129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="G129" s="13" t="n"/>
       <c r="H129" s="30" t="n"/>
-      <c r="I129" s="25" t="inlineStr">
+      <c r="I129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="J129" s="13" t="n"/>
       <c r="K129" s="30" t="n"/>
-      <c r="L129" s="25" t="inlineStr">
+      <c r="L129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="M129" s="13" t="n"/>
       <c r="N129" s="30" t="n"/>
-      <c r="O129" s="25" t="inlineStr">
+      <c r="O129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="P129" s="13" t="n"/>
       <c r="Q129" s="30" t="n"/>
-      <c r="R129" s="25" t="inlineStr">
+      <c r="R129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
       </c>
       <c r="S129" s="13" t="n"/>
       <c r="T129" s="30" t="n"/>
-      <c r="U129" s="25" t="inlineStr">
+      <c r="U129" s="27" t="inlineStr">
         <is>
           <t>鈴木信子：排泄介助</t>
         </is>
@@ -4896,25 +5004,25 @@
         </is>
       </c>
       <c r="B131" s="30" t="n"/>
-      <c r="C131" s="27" t="n"/>
+      <c r="C131" s="28" t="n"/>
       <c r="D131" s="13" t="n"/>
       <c r="E131" s="30" t="n"/>
-      <c r="F131" s="27" t="n"/>
+      <c r="F131" s="28" t="n"/>
       <c r="G131" s="13" t="n"/>
       <c r="H131" s="30" t="n"/>
-      <c r="I131" s="27" t="n"/>
+      <c r="I131" s="28" t="n"/>
       <c r="J131" s="13" t="n"/>
       <c r="K131" s="30" t="n"/>
-      <c r="L131" s="27" t="n"/>
+      <c r="L131" s="28" t="n"/>
       <c r="M131" s="13" t="n"/>
       <c r="N131" s="30" t="n"/>
-      <c r="O131" s="27" t="n"/>
+      <c r="O131" s="28" t="n"/>
       <c r="P131" s="13" t="n"/>
       <c r="Q131" s="30" t="n"/>
-      <c r="R131" s="27" t="n"/>
+      <c r="R131" s="28" t="n"/>
       <c r="S131" s="13" t="n"/>
       <c r="T131" s="30" t="n"/>
-      <c r="U131" s="27" t="n"/>
+      <c r="U131" s="28" t="n"/>
       <c r="V131" s="13" t="n"/>
     </row>
     <row r="132">
@@ -4924,25 +5032,53 @@
         </is>
       </c>
       <c r="B132" s="30" t="n"/>
-      <c r="C132" s="23" t="n"/>
+      <c r="C132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="D132" s="13" t="n"/>
       <c r="E132" s="30" t="n"/>
-      <c r="F132" s="23" t="n"/>
+      <c r="F132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="G132" s="13" t="n"/>
       <c r="H132" s="30" t="n"/>
-      <c r="I132" s="23" t="n"/>
+      <c r="I132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="J132" s="13" t="n"/>
       <c r="K132" s="30" t="n"/>
-      <c r="L132" s="23" t="n"/>
+      <c r="L132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="30" t="n"/>
-      <c r="O132" s="23" t="n"/>
+      <c r="O132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="P132" s="13" t="n"/>
       <c r="Q132" s="30" t="n"/>
-      <c r="R132" s="23" t="n"/>
+      <c r="R132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="S132" s="13" t="n"/>
       <c r="T132" s="30" t="n"/>
-      <c r="U132" s="23" t="n"/>
+      <c r="U132" s="27" t="inlineStr">
+        <is>
+          <t>河田晃晃：排泄介助</t>
+        </is>
+      </c>
       <c r="V132" s="13" t="n"/>
     </row>
     <row r="133">
@@ -4952,25 +5088,25 @@
         </is>
       </c>
       <c r="B133" s="30" t="n"/>
-      <c r="C133" s="23" t="n"/>
+      <c r="C133" s="26" t="n"/>
       <c r="D133" s="13" t="n"/>
       <c r="E133" s="30" t="n"/>
-      <c r="F133" s="23" t="n"/>
+      <c r="F133" s="26" t="n"/>
       <c r="G133" s="13" t="n"/>
       <c r="H133" s="30" t="n"/>
-      <c r="I133" s="23" t="n"/>
+      <c r="I133" s="26" t="n"/>
       <c r="J133" s="13" t="n"/>
       <c r="K133" s="30" t="n"/>
-      <c r="L133" s="23" t="n"/>
+      <c r="L133" s="26" t="n"/>
       <c r="M133" s="13" t="n"/>
       <c r="N133" s="30" t="n"/>
-      <c r="O133" s="23" t="n"/>
+      <c r="O133" s="26" t="n"/>
       <c r="P133" s="13" t="n"/>
       <c r="Q133" s="30" t="n"/>
-      <c r="R133" s="23" t="n"/>
+      <c r="R133" s="26" t="n"/>
       <c r="S133" s="13" t="n"/>
       <c r="T133" s="30" t="n"/>
-      <c r="U133" s="23" t="n"/>
+      <c r="U133" s="26" t="n"/>
       <c r="V133" s="13" t="n"/>
     </row>
     <row r="134">
@@ -4980,25 +5116,25 @@
         </is>
       </c>
       <c r="B134" s="31" t="n"/>
-      <c r="C134" s="24" t="n"/>
+      <c r="C134" s="28" t="n"/>
       <c r="D134" s="18" t="n"/>
       <c r="E134" s="31" t="n"/>
-      <c r="F134" s="24" t="n"/>
+      <c r="F134" s="28" t="n"/>
       <c r="G134" s="18" t="n"/>
       <c r="H134" s="31" t="n"/>
-      <c r="I134" s="24" t="n"/>
+      <c r="I134" s="28" t="n"/>
       <c r="J134" s="18" t="n"/>
       <c r="K134" s="31" t="n"/>
-      <c r="L134" s="24" t="n"/>
+      <c r="L134" s="28" t="n"/>
       <c r="M134" s="18" t="n"/>
       <c r="N134" s="31" t="n"/>
-      <c r="O134" s="24" t="n"/>
+      <c r="O134" s="28" t="n"/>
       <c r="P134" s="18" t="n"/>
       <c r="Q134" s="31" t="n"/>
-      <c r="R134" s="24" t="n"/>
+      <c r="R134" s="28" t="n"/>
       <c r="S134" s="18" t="n"/>
       <c r="T134" s="31" t="n"/>
-      <c r="U134" s="24" t="n"/>
+      <c r="U134" s="28" t="n"/>
       <c r="V134" s="18" t="n"/>
     </row>
     <row r="135">
@@ -5007,25 +5143,25 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B135" s="28" t="n"/>
+      <c r="B135" s="29" t="n"/>
       <c r="C135" s="22" t="n"/>
       <c r="D135" s="9" t="n"/>
-      <c r="E135" s="28" t="n"/>
+      <c r="E135" s="29" t="n"/>
       <c r="F135" s="22" t="n"/>
       <c r="G135" s="9" t="n"/>
-      <c r="H135" s="28" t="n"/>
+      <c r="H135" s="29" t="n"/>
       <c r="I135" s="22" t="n"/>
       <c r="J135" s="9" t="n"/>
-      <c r="K135" s="28" t="n"/>
+      <c r="K135" s="29" t="n"/>
       <c r="L135" s="22" t="n"/>
       <c r="M135" s="9" t="n"/>
-      <c r="N135" s="28" t="n"/>
+      <c r="N135" s="29" t="n"/>
       <c r="O135" s="22" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="28" t="n"/>
+      <c r="Q135" s="29" t="n"/>
       <c r="R135" s="22" t="n"/>
       <c r="S135" s="9" t="n"/>
-      <c r="T135" s="28" t="n"/>
+      <c r="T135" s="29" t="n"/>
       <c r="U135" s="22" t="n"/>
       <c r="V135" s="9" t="n"/>
     </row>
@@ -5343,25 +5479,25 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B147" s="28" t="n"/>
+      <c r="B147" s="29" t="n"/>
       <c r="C147" s="22" t="n"/>
       <c r="D147" s="9" t="n"/>
-      <c r="E147" s="28" t="n"/>
+      <c r="E147" s="29" t="n"/>
       <c r="F147" s="22" t="n"/>
       <c r="G147" s="9" t="n"/>
-      <c r="H147" s="28" t="n"/>
+      <c r="H147" s="29" t="n"/>
       <c r="I147" s="22" t="n"/>
       <c r="J147" s="9" t="n"/>
-      <c r="K147" s="28" t="n"/>
+      <c r="K147" s="29" t="n"/>
       <c r="L147" s="22" t="n"/>
       <c r="M147" s="9" t="n"/>
-      <c r="N147" s="28" t="n"/>
+      <c r="N147" s="29" t="n"/>
       <c r="O147" s="22" t="n"/>
       <c r="P147" s="9" t="n"/>
-      <c r="Q147" s="28" t="n"/>
+      <c r="Q147" s="29" t="n"/>
       <c r="R147" s="22" t="n"/>
       <c r="S147" s="9" t="n"/>
-      <c r="T147" s="28" t="n"/>
+      <c r="T147" s="29" t="n"/>
       <c r="U147" s="22" t="n"/>
       <c r="V147" s="9" t="n"/>
     </row>
@@ -5679,26 +5815,54 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B159" s="28" t="n"/>
-      <c r="C159" s="22" t="n"/>
+      <c r="B159" s="29" t="n"/>
+      <c r="C159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="D159" s="9" t="n"/>
-      <c r="E159" s="28" t="n"/>
-      <c r="F159" s="22" t="n"/>
+      <c r="E159" s="29" t="n"/>
+      <c r="F159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="G159" s="9" t="n"/>
-      <c r="H159" s="28" t="n"/>
-      <c r="I159" s="22" t="n"/>
+      <c r="H159" s="29" t="n"/>
+      <c r="I159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="J159" s="9" t="n"/>
-      <c r="K159" s="28" t="n"/>
-      <c r="L159" s="22" t="n"/>
+      <c r="K159" s="29" t="n"/>
+      <c r="L159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="M159" s="9" t="n"/>
-      <c r="N159" s="28" t="n"/>
-      <c r="O159" s="22" t="n"/>
+      <c r="N159" s="29" t="n"/>
+      <c r="O159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="P159" s="9" t="n"/>
-      <c r="Q159" s="28" t="n"/>
-      <c r="R159" s="22" t="n"/>
+      <c r="Q159" s="29" t="n"/>
+      <c r="R159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="S159" s="9" t="n"/>
-      <c r="T159" s="28" t="n"/>
-      <c r="U159" s="22" t="n"/>
+      <c r="T159" s="29" t="n"/>
+      <c r="U159" s="25" t="inlineStr">
+        <is>
+          <t>上村春子：排泄介助</t>
+        </is>
+      </c>
       <c r="V159" s="9" t="n"/>
     </row>
     <row r="160">
@@ -5708,25 +5872,25 @@
         </is>
       </c>
       <c r="B160" s="30" t="n"/>
-      <c r="C160" s="23" t="n"/>
+      <c r="C160" s="26" t="n"/>
       <c r="D160" s="13" t="n"/>
       <c r="E160" s="30" t="n"/>
-      <c r="F160" s="23" t="n"/>
+      <c r="F160" s="26" t="n"/>
       <c r="G160" s="13" t="n"/>
       <c r="H160" s="30" t="n"/>
-      <c r="I160" s="23" t="n"/>
+      <c r="I160" s="26" t="n"/>
       <c r="J160" s="13" t="n"/>
       <c r="K160" s="30" t="n"/>
-      <c r="L160" s="23" t="n"/>
+      <c r="L160" s="26" t="n"/>
       <c r="M160" s="13" t="n"/>
       <c r="N160" s="30" t="n"/>
-      <c r="O160" s="23" t="n"/>
+      <c r="O160" s="26" t="n"/>
       <c r="P160" s="13" t="n"/>
       <c r="Q160" s="30" t="n"/>
-      <c r="R160" s="23" t="n"/>
+      <c r="R160" s="26" t="n"/>
       <c r="S160" s="13" t="n"/>
       <c r="T160" s="30" t="n"/>
-      <c r="U160" s="23" t="n"/>
+      <c r="U160" s="26" t="n"/>
       <c r="V160" s="13" t="n"/>
     </row>
     <row r="161">
@@ -5736,25 +5900,25 @@
         </is>
       </c>
       <c r="B161" s="30" t="n"/>
-      <c r="C161" s="23" t="n"/>
+      <c r="C161" s="28" t="n"/>
       <c r="D161" s="13" t="n"/>
       <c r="E161" s="30" t="n"/>
-      <c r="F161" s="23" t="n"/>
+      <c r="F161" s="28" t="n"/>
       <c r="G161" s="13" t="n"/>
       <c r="H161" s="30" t="n"/>
-      <c r="I161" s="23" t="n"/>
+      <c r="I161" s="28" t="n"/>
       <c r="J161" s="13" t="n"/>
       <c r="K161" s="30" t="n"/>
-      <c r="L161" s="23" t="n"/>
+      <c r="L161" s="28" t="n"/>
       <c r="M161" s="13" t="n"/>
       <c r="N161" s="30" t="n"/>
-      <c r="O161" s="23" t="n"/>
+      <c r="O161" s="28" t="n"/>
       <c r="P161" s="13" t="n"/>
       <c r="Q161" s="30" t="n"/>
-      <c r="R161" s="23" t="n"/>
+      <c r="R161" s="28" t="n"/>
       <c r="S161" s="13" t="n"/>
       <c r="T161" s="30" t="n"/>
-      <c r="U161" s="23" t="n"/>
+      <c r="U161" s="28" t="n"/>
       <c r="V161" s="13" t="n"/>
     </row>
     <row r="162">
@@ -5848,49 +6012,49 @@
         </is>
       </c>
       <c r="B165" s="30" t="n"/>
-      <c r="C165" s="25" t="inlineStr">
+      <c r="C165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="D165" s="13" t="n"/>
       <c r="E165" s="30" t="n"/>
-      <c r="F165" s="25" t="inlineStr">
+      <c r="F165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="G165" s="13" t="n"/>
       <c r="H165" s="30" t="n"/>
-      <c r="I165" s="25" t="inlineStr">
+      <c r="I165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="J165" s="13" t="n"/>
       <c r="K165" s="30" t="n"/>
-      <c r="L165" s="25" t="inlineStr">
+      <c r="L165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="M165" s="13" t="n"/>
       <c r="N165" s="30" t="n"/>
-      <c r="O165" s="25" t="inlineStr">
+      <c r="O165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="P165" s="13" t="n"/>
       <c r="Q165" s="30" t="n"/>
-      <c r="R165" s="25" t="inlineStr">
+      <c r="R165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
       </c>
       <c r="S165" s="13" t="n"/>
       <c r="T165" s="30" t="n"/>
-      <c r="U165" s="25" t="inlineStr">
+      <c r="U165" s="27" t="inlineStr">
         <is>
           <t>長谷部融子：就寝介助</t>
         </is>
@@ -5988,25 +6152,25 @@
         </is>
       </c>
       <c r="B169" s="30" t="n"/>
-      <c r="C169" s="27" t="n"/>
+      <c r="C169" s="28" t="n"/>
       <c r="D169" s="13" t="n"/>
       <c r="E169" s="30" t="n"/>
-      <c r="F169" s="27" t="n"/>
+      <c r="F169" s="28" t="n"/>
       <c r="G169" s="13" t="n"/>
       <c r="H169" s="30" t="n"/>
-      <c r="I169" s="27" t="n"/>
+      <c r="I169" s="28" t="n"/>
       <c r="J169" s="13" t="n"/>
       <c r="K169" s="30" t="n"/>
-      <c r="L169" s="27" t="n"/>
+      <c r="L169" s="28" t="n"/>
       <c r="M169" s="13" t="n"/>
       <c r="N169" s="30" t="n"/>
-      <c r="O169" s="27" t="n"/>
+      <c r="O169" s="28" t="n"/>
       <c r="P169" s="13" t="n"/>
       <c r="Q169" s="30" t="n"/>
-      <c r="R169" s="27" t="n"/>
+      <c r="R169" s="28" t="n"/>
       <c r="S169" s="13" t="n"/>
       <c r="T169" s="30" t="n"/>
-      <c r="U169" s="27" t="n"/>
+      <c r="U169" s="28" t="n"/>
       <c r="V169" s="13" t="n"/>
     </row>
     <row r="170">
@@ -6066,16 +6230,18 @@
       <c r="V171" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="132">
     <mergeCell ref="N57:N59"/>
     <mergeCell ref="I111:I115"/>
     <mergeCell ref="O129:O131"/>
     <mergeCell ref="T6:T8"/>
     <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="Q15:Q17"/>
     <mergeCell ref="U117:U121"/>
     <mergeCell ref="N6:N8"/>
     <mergeCell ref="U129:U131"/>
     <mergeCell ref="N9:N11"/>
+    <mergeCell ref="U75:U85"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="K57:K61"/>
     <mergeCell ref="Q57:Q59"/>
@@ -6083,54 +6249,87 @@
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="R117:R121"/>
     <mergeCell ref="R111:R115"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="N75:N77"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="I129:I131"/>
     <mergeCell ref="L165:L169"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="F129:F131"/>
-    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="O132:O134"/>
     <mergeCell ref="T12:T14"/>
-    <mergeCell ref="T51:T53"/>
+    <mergeCell ref="L129:L131"/>
     <mergeCell ref="C117:C121"/>
-    <mergeCell ref="L129:L131"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="Q9:Q11"/>
     <mergeCell ref="U165:U169"/>
     <mergeCell ref="I117:I121"/>
+    <mergeCell ref="C159:C161"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="Q93:Q103"/>
+    <mergeCell ref="O159:O161"/>
     <mergeCell ref="H87:H91"/>
     <mergeCell ref="F123:F127"/>
     <mergeCell ref="L81:L85"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="F132:F134"/>
+    <mergeCell ref="K18:K20"/>
     <mergeCell ref="O111:O115"/>
+    <mergeCell ref="R132:R134"/>
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="K63:K65"/>
+    <mergeCell ref="B93:B97"/>
     <mergeCell ref="T9:T11"/>
     <mergeCell ref="N12:N14"/>
-    <mergeCell ref="Q51:Q53"/>
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="L117:L121"/>
+    <mergeCell ref="Q63:Q65"/>
+    <mergeCell ref="H93:H103"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="E9:E11"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="F159:F161"/>
+    <mergeCell ref="C132:C134"/>
+    <mergeCell ref="R159:R161"/>
+    <mergeCell ref="U159:U161"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="I123:I127"/>
+    <mergeCell ref="B15:B17"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="L159:L161"/>
+    <mergeCell ref="I132:I134"/>
     <mergeCell ref="K6:K8"/>
+    <mergeCell ref="U132:U134"/>
     <mergeCell ref="T1:V1"/>
-    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B63:B65"/>
     <mergeCell ref="O165:O169"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="Q75:Q77"/>
     <mergeCell ref="E75:E79"/>
     <mergeCell ref="K9:K11"/>
+    <mergeCell ref="T18:T20"/>
     <mergeCell ref="C111:C115"/>
-    <mergeCell ref="T75:T85"/>
+    <mergeCell ref="N63:N65"/>
     <mergeCell ref="R123:R127"/>
     <mergeCell ref="K54:K56"/>
     <mergeCell ref="Q12:Q14"/>
+    <mergeCell ref="H63:H65"/>
     <mergeCell ref="N3:N5"/>
+    <mergeCell ref="T63:T65"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="Q54:Q56"/>
     <mergeCell ref="U111:U115"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="I159:I161"/>
+    <mergeCell ref="E93:E103"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="N93:N97"/>
     <mergeCell ref="B6:B8"/>
+    <mergeCell ref="L132:L134"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="C123:C127"/>
     <mergeCell ref="K75:K85"/>
@@ -6141,18 +6340,24 @@
     <mergeCell ref="R165:R169"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="T75:T77"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="F111:F115"/>
     <mergeCell ref="H12:H14"/>
     <mergeCell ref="T3:T5"/>
     <mergeCell ref="U123:U127"/>
+    <mergeCell ref="N15:N17"/>
     <mergeCell ref="C165:C169"/>
     <mergeCell ref="T57:T59"/>
     <mergeCell ref="L111:L115"/>
+    <mergeCell ref="Q18:Q20"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="O117:O121"/>
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="B75:B85"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="B57:B61"/>
     <mergeCell ref="I165:I169"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="R129:R131"/>
